--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 34, 35, 148, 151, 1653, 1654, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1824, 1825, 1827, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2281, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 32, 33, 149, 150, 152, 1652, 1655, 1691, 1692, 1774, 1826, 1897, 1898, 2279, 2282, 2283, 2288, 2295)</t>
+    <t xml:space="preserve">c(17, 20, 23, 31, 32, 33, 34, 148, 149, 150, 152, 1652, 1653, 1654, 1692, 1693, 1750, 1751, 1754, 1755, 1772, 1773, 1774, 1825, 1826, 2054, 2058, 2177, 2179, 2227, 2229, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 35, 151, 1655, 1691, 1752, 1753, 1756, 1757, 1771, 1824, 1827, 1897, 1898, 1900, 2056, 2231, 2279, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 32, 34, 148, 149, 150, 152, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1754, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 1898, 1900, 2056, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 35, 151, 1653, 1751, 1752, 1753, 1755, 1825, 1827, 1897, 2054, 2058, 2177, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 33, 34, 148, 151, 152, 1652, 1653, 1654, 1692, 1693, 1750, 1751, 1752, 1753, 1756, 1774, 1824, 1825, 1826, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2227, 2231, 2279, 2283, 2288, 2290, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 35, 149, 150, 1655, 1691, 1754, 1755, 1757, 1771, 1772, 1773, 1827, 2179, 2229, 2281, 2282, 2289, 2293, 2295)</t>
+    <t xml:space="preserve">c(17, 18, 31, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1754, 1773, 1774, 1824, 1897, 2054, 2056, 2177, 2179, 2229, 2231, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 23, 32, 1653, 1692, 1753, 1755, 1756, 1757, 1771, 1772, 1825, 1826, 1827, 1898, 1900, 2058, 2227, 2279)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 31, 34, 35, 148, 149, 150, 151, 152, 1653, 1654, 1655, 1692, 1693, 1751, 1752, 1753, 1755, 1757, 1771, 1774, 1824, 1825, 1826, 1897, 1900, 2054, 2177, 2179, 2227, 2231, 2281, 2282, 2283, 2288, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 32, 33, 1652, 1691, 1750, 1754, 1756, 1772, 1773, 1827, 1898, 2056, 2058, 2229, 2279, 2289, 2290, 2294)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
@@ -107,937 +107,1165 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 43, 44, 224, 228, 275, 276, 278, 279, 1721, 1722, 1727, 1775, 1778, 1779, 1868, 1869, 1870, 2027, 2033, 2119, 2120, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 226, 277, 280, 1719, 1720, 1776, 1777, 2029, 2035, 2037, 2121, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 275, 276, 277, 278, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2033, 2037, 2119, 2120, 2121, 2124, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 222, 224, 226, 228, 279, 1722, 1868, 2027, 2029, 2035, 2126, 2224)</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 224, 226, 275, 276, 278, 279, 1719, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2033, 2035, 2119, 2124, 2125, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 222, 228, 277, 280, 1720, 1721, 2027, 2029, 2037, 2120, 2121, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 224, 228, 275, 278, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2027, 2033, 2037, 2119, 2121, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 226, 276, 277, 279, 1722, 1777, 2029, 2035, 2120, 2124, 2125, 2126)</t>
+    <t xml:space="preserve">c(44, 222, 226, 228, 275, 276, 278, 279, 280, 1720, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 2029, 2033, 2035, 2037, 2120, 2121, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 224, 277, 1719, 1721, 1722, 1870, 2027, 2119, 2124, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 222, 224, 226, 275, 278, 279, 280, 1719, 1720, 1727, 1775, 1776, 1779, 1868, 1869, 1870, 2029, 2035, 2037, 2120, 2124, 2125, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 228, 276, 277, 1721, 1722, 1777, 1778, 2027, 2033, 2119, 2121, 2127, 2224)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 210, 211, 213, 217, 218, 219, 220, 265, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 208, 209, 212, 214, 215, 216, 266, 267)</t>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 210, 211, 212, 213, 214, 216, 217, 218, 219, 265, 267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 208, 209, 215, 220, 266, 268, 2230)</t>
   </si>
   <si>
     <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 207, 208, 209, 211, 212, 215, 216, 218, 219, 220, 266, 267, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 206, 210, 213, 214, 217, 265, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 206, 209, 211, 212, 213, 214, 215, 216, 217, 218, 220, 265, 266, 267, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 205, 207, 208, 210, 219, 1899, 2230)</t>
+    <t xml:space="preserve">c(205, 206, 207, 208, 210, 211, 212, 213, 214, 216, 217, 219, 220, 265, 266, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 209, 215, 218, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 206, 208, 209, 210, 211, 212, 215, 216, 217, 218, 219, 220, 267, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 205, 207, 213, 214, 265, 266, 1899, 2230)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 141, 142, 143, 175, 176, 177, 178, 180, 182, 223, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 250, 273, 274, 282, 283, 286, 288, 289, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1763, 1766, 1838, 1839, 1840, 1865, 1867, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2034, 2036, 2128, 2130, 2131, 2137, 2138, 2139, 2194, 2222, 2257, 2300, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 140, 179, 181, 221, 225, 247, 249, 271, 272, 281, 284, 285, 287, 290, 291, 292, 1716, 1764, 1765, 1852, 1863, 1864, 1866, 1874, 1875, 2032, 2108, 2109, 2129, 2132, 2133, 2134, 2135, 2136, 2223, 2225, 2226, 2301, 2313)</t>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 130, 131, 132, 141, 142, 143, 177, 179, 180, 182, 227, 229, 230, 231, 233, 234, 235, 243, 245, 246, 247, 248, 250, 272, 273, 274, 282, 283, 284, 285, 286, 287, 289, 290, 291, 293, 294, 295, 296, 1718, 1760, 1762, 1763, 1764, 1765, 1766, 1840, 1852, 1863, 1864, 1865, 1866, 1874, 1875, 1935, 1990, 1991, 2028, 2036, 2108, 2129, 2130, 2133, 2134, 2135, 2136, 2138, 2139, 2222, 2223, 2225, 2300, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 140, 175, 176, 178, 181, 221, 223, 225, 236, 244, 249, 271, 281, 288, 292, 1716, 1717, 1761, 1838, 1839, 1867, 1876, 1992, 2026, 2030, 2032, 2034, 2109, 2128, 2131, 2132, 2137, 2194, 2226, 2257, 2302, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 
 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 70, 72, 73, 130, 131, 132, 141, 175, 178, 179, 180, 181, 182, 221, 223, 230, 231, 233, 235, 236, 243, 244, 246, 247, 248, 249, 272, 281, 282, 286, 287, 288, 291, 292, 293, 294, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1765, 1766, 1838, 1839, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2108, 2109, 2129, 2130, 2131, 2133, 2135, 2137, 2139, 2222, 2223, 2225, 2226, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 140, 142, 143, 176, 177, 225, 227, 229, 234, 245, 250, 271, 273, 274, 283, 284, 285, 289, 290, 295, 1717, 1764, 1840, 1852, 1863, 1864, 1865, 1935, 2030, 2128, 2132, 2134, 2136, 2138, 2194, 2257, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 70, 71, 72, 73, 132, 141, 142, 177, 178, 179, 180, 221, 223, 225, 229, 231, 234, 235, 236, 243, 244, 246, 247, 249, 271, 272, 274, 283, 284, 285, 286, 288, 289, 290, 291, 293, 294, 1716, 1717, 1718, 1761, 1762, 1763, 1764, 1766, 1838, 1840, 1852, 1863, 1864, 1867, 1874, 1875, 1876, 1935, 1990, 2026, 2030, 2032, 2034, 2036, 2108, 2109, 2129, 2130, 2131, 2133, 2136, 2137, 2138, 2139, 2194, 2222, 2226, 2300, 2301, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 130, 131, 140, 143, 175, 176, 181, 182, 227, 230, 233, 245, 248, 250, 273, 281, 282, 287, 292, 295, 296, 1760, 1765, 1839, 1865, 1866, 1991, 1992, 2028, 2128, 2132, 2134, 2135, 2223, 2225, 2257, 2302, 2303, 2313)</t>
+    <t xml:space="preserve">c(13, 14, 70, 71, 72, 73, 131, 132, 141, 142, 175, 177, 178, 179, 180, 182, 223, 231, 234, 235, 244, 245, 246, 247, 248, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 289, 291, 293, 295, 296, 1716, 1717, 1718, 1761, 1763, 1766, 1838, 1852, 1863, 1866, 1874, 1876, 1935, 1991, 1992, 2028, 2030, 2032, 2034, 2109, 2128, 2129, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2222, 2225, 2226, 2257, 2300, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 130, 140, 143, 176, 181, 221, 225, 227, 229, 230, 233, 236, 243, 249, 250, 288, 290, 292, 294, 1760, 1762, 1764, 1765, 1839, 1840, 1864, 1865, 1867, 1875, 1990, 2026, 2036, 2108, 2130, 2136, 2223, 2301, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 71, 73, 140, 141, 142, 143, 175, 176, 177, 178, 180, 181, 221, 223, 225, 227, 229, 231, 233, 234, 236, 243, 246, 249, 271, 272, 273, 274, 282, 283, 284, 287, 292, 294, 295, 1716, 1717, 1718, 1760, 1761, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1867, 1874, 1876, 1935, 1990, 1991, 2028, 2030, 2032, 2034, 2108, 2130, 2132, 2133, 2134, 2135, 2136, 2138, 2139, 2194, 2222, 2223, 2226, 2257, 2300, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 72, 130, 131, 132, 179, 182, 230, 235, 244, 245, 247, 248, 250, 281, 285, 286, 288, 289, 290, 291, 293, 296, 1762, 1763, 1865, 1866, 1875, 1992, 2026, 2036, 2109, 2128, 2129, 2131, 2137, 2225, 2301, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 148, 149, 151, 152, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1774, 1824, 1897, 1898, 2177, 2179, 2227, 2229, 2231, 2281, 2283, 2288, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 35, 150, 1652, 1655, 1757, 1772, 1773, 1825, 1826, 1827, 1900, 2054, 2056, 2058, 2279, 2282, 2289, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 33, 34, 35, 148, 149, 1652, 1653, 1691, 1692, 1750, 1751, 1752, 1754, 1757, 1771, 1772, 1773, 1824, 1825, 1826, 1827, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2231, 2281, 2288, 2289, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(31, 32, 150, 151, 152, 1654, 1655, 1693, 1753, 1755, 1756, 1774, 1897, 2054, 2179, 2279, 2282, 2283, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 148, 149, 151, 152, 1652, 1654, 1692, 1693, 1752, 1753, 1755, 1757, 1771, 1772, 1774, 1824, 1825, 1897, 1900, 2054, 2056, 2058, 2177, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 34, 35, 150, 1653, 1655, 1691, 1750, 1751, 1754, 1756, 1773, 1826, 1827, 1898, 2179, 2288, 2289, 2294, 2295)</t>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 34, 148, 149, 152, 1654, 1655, 1692, 1693, 1750, 1753, 1754, 1756, 1757, 1771, 1774, 1824, 1825, 1826, 1897, 1900, 2054, 2056, 2058, 2179, 2229, 2279, 2281, 2282, 2283, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 32, 33, 35, 150, 151, 1652, 1653, 1691, 1751, 1752, 1755, 1772, 1773, 1827, 1898, 2177, 2227, 2231, 2288)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 23, 31, 32, 33, 34, 35, 149, 151, 1652, 1653, 1655, 1691, 1752, 1754, 1755, 1756, 1757, 1773, 1774, 1824, 1825, 1827, 1897, 1898, 1900, 2054, 2058, 2177, 2227, 2231, 2281, 2282, 2283, 2288, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 148, 150, 152, 1654, 1692, 1693, 1750, 1751, 1753, 1771, 1772, 1826, 2056, 2179, 2229, 2279, 2289, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 148, 149, 150, 152, 1652, 1653, 1655, 1691, 1692, 1693, 1751, 1754, 1755, 1756, 1757, 1772, 1773, 1774, 1825, 1826, 1827, 1897, 1900, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2288, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 34, 35, 151, 1654, 1750, 1752, 1753, 1771, 1824, 1898, 2054, 2281, 2283, 2289, 2290, 2292, 2293, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 224, 226, 228, 275, 276, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1777, 1779, 1868, 1869, 1870, 2029, 2037, 2119, 2120, 2124, 2125, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 222, 277, 278, 279, 1722, 1778, 2027, 2033, 2035, 2121, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 228, 275, 276, 277, 279, 280, 1719, 1720, 1721, 1722, 1775, 1776, 1778, 1779, 1868, 1869, 2027, 2035, 2037, 2119, 2121, 2124, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 224, 226, 278, 1727, 1777, 1870, 2029, 2033, 2120, 2125, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 224, 228, 275, 279, 280, 1720, 1721, 1722, 1775, 1776, 1779, 1868, 1869, 1870, 2027, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 222, 226, 276, 277, 278, 1719, 1727, 1777, 1778, 2029, 2033, 2127)</t>
+    <t xml:space="preserve">c(41, 42, 43, 222, 226, 228, 275, 278, 279, 280, 1722, 1727, 1775, 1776, 1779, 1868, 1869, 2033, 2035, 2037, 2120, 2121, 2124, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 224, 276, 277, 1719, 1720, 1721, 1777, 1778, 1870, 2027, 2029, 2119, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 275, 276, 1719, 1721, 1722, 1727, 1776, 1777, 1779, 1868, 1869, 2029, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 277, 278, 279, 280, 1720, 1775, 1778, 1870, 2027, 2033, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 224, 226, 275, 276, 277, 279, 280, 1719, 1776, 1777, 1779, 1868, 1869, 2027, 2033, 2035, 2037, 2119, 2121, 2124, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 228, 278, 1720, 1721, 1722, 1727, 1775, 1778, 1870, 2029, 2120, 2125, 2224)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(202, 203, 204, 207, 208, 210, 211, 212, 213, 214, 215, 218, 220, 265, 266, 267, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 205, 206, 209, 216, 217, 219, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 207, 212, 213, 214, 215, 216, 217, 218, 220, 265, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 206, 208, 209, 210, 211, 219, 266, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 209, 210, 211, 212, 213, 216, 219, 220, 265, 266, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 206, 207, 208, 214, 215, 217, 218, 267)</t>
+    <t xml:space="preserve">c(201, 203, 204, 206, 208, 209, 210, 212, 214, 215, 216, 218, 220, 265, 266, 267, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 207, 211, 213, 217, 219, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 208, 209, 210, 211, 212, 214, 215, 216, 217, 218, 220, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 213, 219, 265, 266, 267, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 206, 207, 210, 211, 213, 214, 216, 217, 219, 265, 266, 267, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 208, 209, 212, 215, 218, 220, 1899, 2230)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 15, 71, 72, 130, 131, 132, 140, 141, 142, 143, 176, 178, 179, 180, 181, 223, 225, 227, 229, 230, 231, 233, 235, 236, 243, 245, 246, 250, 271, 272, 273, 281, 282, 283, 284, 285, 287, 289, 290, 292, 294, 295, 296, 1717, 1718, 1761, 1762, 1763, 1765, 1838, 1839, 1852, 1863, 1864, 1866, 1874, 1935, 1990, 1992, 2026, 2028, 2034, 2036, 2108, 2129, 2130, 2131, 2133, 2135, 2136, 2137, 2222, 2225, 2257, 2300, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 175, 177, 182, 221, 234, 244, 247, 248, 249, 274, 286, 288, 291, 293, 1716, 1760, 1764, 1766, 1840, 1865, 1867, 1875, 1876, 1991, 2030, 2032, 2109, 2128, 2132, 2134, 2138, 2139, 2194, 2223, 2226, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 71, 73, 130, 132, 140, 142, 143, 176, 179, 181, 221, 223, 225, 229, 230, 234, 236, 243, 244, 245, 246, 247, 249, 250, 271, 272, 273, 274, 281, 284, 285, 286, 287, 289, 291, 293, 294, 295, 1716, 1717, 1760, 1763, 1765, 1766, 1838, 1839, 1852, 1863, 1865, 1866, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2036, 2109, 2129, 2131, 2132, 2135, 2137, 2138, 2139, 2223, 2225, 2226, 2257, 2300, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 72, 131, 141, 175, 177, 178, 180, 182, 227, 231, 233, 235, 248, 282, 283, 288, 290, 292, 296, 1718, 1761, 1762, 1764, 1840, 1864, 1867, 2032, 2034, 2108, 2128, 2130, 2133, 2134, 2136, 2194, 2222, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 71, 73, 130, 131, 132, 143, 176, 179, 180, 181, 182, 221, 225, 227, 229, 231, 234, 235, 236, 244, 245, 246, 247, 248, 249, 250, 271, 273, 281, 283, 284, 285, 288, 289, 291, 293, 295, 296, 1716, 1717, 1761, 1762, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1867, 1874, 1875, 1876, 1990, 1992, 2032, 2034, 2036, 2109, 2129, 2131, 2136, 2137, 2138, 2194, 2222, 2225, 2226, 2257, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 140, 141, 142, 175, 177, 178, 223, 230, 233, 243, 272, 274, 282, 286, 287, 290, 292, 294, 1718, 1760, 1763, 1865, 1935, 1991, 2026, 2028, 2030, 2108, 2128, 2130, 2132, 2133, 2134, 2135, 2139, 2223, 2302, 2313)</t>
+    <t xml:space="preserve">c(13, 15, 71, 72, 73, 131, 132, 141, 142, 143, 175, 176, 177, 179, 181, 182, 223, 225, 227, 229, 230, 231, 234, 235, 236, 243, 244, 245, 248, 249, 250, 271, 274, 281, 282, 284, 286, 287, 288, 289, 290, 294, 296, 1717, 1718, 1762, 1764, 1765, 1766, 1838, 1863, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2222, 2223, 2225, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 70, 130, 140, 178, 180, 221, 233, 246, 247, 272, 273, 283, 285, 291, 292, 293, 295, 1716, 1760, 1761, 1763, 1839, 1840, 1852, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 2036, 2194, 2226, 2257, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 70, 71, 73, 131, 132, 140, 142, 143, 175, 177, 178, 179, 181, 182, 225, 227, 229, 230, 231, 235, 236, 243, 244, 245, 248, 250, 272, 273, 281, 282, 283, 285, 286, 288, 289, 290, 291, 293, 294, 295, 296, 1716, 1717, 1761, 1764, 1838, 1852, 1863, 1865, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2030, 2032, 2034, 2036, 2128, 2129, 2130, 2132, 2133, 2135, 2136, 2137, 2138, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 72, 130, 141, 176, 180, 221, 223, 233, 234, 246, 247, 249, 271, 274, 284, 287, 292, 1718, 1760, 1762, 1763, 1765, 1766, 1839, 1840, 1864, 1866, 1867, 1935, 2028, 2108, 2109, 2131, 2134, 2139, 2194, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 72, 73, 132, 140, 143, 177, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 234, 235, 236, 244, 245, 246, 247, 250, 274, 283, 284, 285, 287, 288, 291, 292, 293, 294, 295, 296, 1716, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1852, 1863, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2108, 2129, 2130, 2131, 2133, 2134, 2135, 2136, 2137, 2222, 2223, 2225, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 71, 130, 131, 141, 142, 175, 176, 178, 179, 233, 243, 248, 249, 271, 272, 273, 281, 282, 286, 289, 290, 1717, 1718, 1760, 1840, 1864, 1865, 1935, 2036, 2109, 2128, 2132, 2138, 2139, 2194, 2226, 2257, 2303, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 33, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1693, 1750, 1753, 1754, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1827, 1897, 1898, 1900, 2177, 2227, 2231, 2279, 2282, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 32, 34, 35, 1692, 1751, 1752, 1755, 1825, 1826, 2054, 2056, 2058, 2179, 2229, 2281, 2283, 2288, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1755, 1757, 1772, 1774, 1824, 1826, 1827, 1897, 1900, 2056, 2058, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 31, 32, 33, 34, 35, 148, 149, 1753, 1754, 1756, 1771, 1773, 1825, 1898, 2054, 2177, 2229, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 31, 32, 34, 35, 148, 150, 152, 1652, 1653, 1693, 1750, 1752, 1753, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1898, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2288, 2289, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 23, 33, 149, 151, 1654, 1655, 1691, 1692, 1751, 1754, 1755, 1826, 1827, 1897, 1900, 2282, 2283, 2294, 2295)</t>
+    <t xml:space="preserve">c(17, 18, 23, 33, 34, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1692, 1693, 1751, 1752, 1754, 1755, 1771, 1772, 1824, 1825, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 31, 32, 35, 1653, 1691, 1750, 1753, 1756, 1757, 1773, 1774, 1826, 1827, 1897, 2279, 2281, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 31, 32, 35, 148, 149, 152, 1652, 1653, 1655, 1691, 1692, 1693, 1751, 1754, 1755, 1756, 1771, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 1900, 2056, 2058, 2177, 2229, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 33, 34, 150, 151, 1654, 1750, 1752, 1753, 1757, 1772, 1827, 2054, 2179, 2227, 2231, 2283, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 33, 34, 35, 148, 149, 150, 152, 1652, 1654, 1691, 1692, 1693, 1753, 1756, 1757, 1771, 1773, 1824, 1825, 1826, 1897, 1898, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 31, 32, 151, 1653, 1655, 1750, 1751, 1752, 1754, 1755, 1772, 1774, 1827, 1900, 2054, 2056, 2281, 2290)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 275, 276, 277, 278, 280, 1721, 1722, 1727, 1775, 1776, 1778, 1868, 1869, 1870, 2027, 2033, 2035, 2037, 2124, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 224, 226, 228, 279, 1719, 1720, 1777, 1779, 2029, 2119, 2120, 2121, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 222, 224, 226, 275, 276, 277, 279, 280, 1719, 1721, 1722, 1727, 1779, 1868, 1869, 2027, 2029, 2033, 2035, 2037, 2119, 2121, 2124, 2125, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 228, 278, 1720, 1775, 1776, 1777, 1778, 1870, 2120, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 275, 276, 279, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 2033, 2037, 2120, 2121, 2124, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(226, 228, 277, 278, 280, 1719, 1869, 1870, 2027, 2029, 2035, 2119, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 206, 209, 210, 211, 213, 214, 215, 216, 217, 219, 220, 265, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 207, 208, 212, 218, 266, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 205, 206, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 207, 208, 209, 210, 266, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 205, 207, 209, 210, 211, 213, 215, 217, 219, 220, 265, 266, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 206, 208, 212, 214, 216, 218, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 71, 72, 73, 130, 131, 132, 140, 141, 176, 178, 179, 180, 182, 223, 225, 229, 230, 233, 234, 236, 243, 244, 245, 247, 248, 249, 250, 271, 272, 281, 282, 284, 285, 287, 289, 290, 292, 294, 296, 1717, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1840, 1863, 1866, 1874, 1875, 1935, 1990, 1991, 1992, 2026, 2032, 2036, 2108, 2109, 2129, 2135, 2136, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2257, 2300, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 142, 143, 175, 177, 181, 221, 227, 231, 235, 246, 273, 274, 283, 286, 288, 291, 293, 295, 1716, 1718, 1839, 1852, 1864, 1865, 1867, 1876, 2028, 2030, 2034, 2128, 2130, 2131, 2132, 2133, 2134, 2222, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 70, 73, 130, 131, 140, 142, 143, 175, 176, 178, 179, 181, 182, 221, 223, 225, 230, 231, 234, 236, 243, 244, 246, 247, 249, 250, 271, 272, 273, 281, 282, 286, 287, 288, 290, 292, 294, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1766, 1863, 1865, 1875, 1876, 1935, 1990, 1992, 2026, 2028, 2030, 2032, 2034, 2108, 2109, 2128, 2130, 2131, 2132, 2134, 2135, 2136, 2137, 2138, 2222, 2223, 2225, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 72, 132, 141, 177, 180, 227, 229, 233, 235, 245, 248, 274, 283, 284, 285, 289, 291, 293, 295, 1718, 1765, 1838, 1839, 1840, 1852, 1864, 1866, 1867, 1874, 1991, 2036, 2129, 2133, 2139, 2194, 2226, 2257, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 130, 131, 132, 140, 175, 176, 179, 180, 182, 221, 223, 227, 229, 231, 233, 234, 236, 243, 244, 245, 247, 248, 250, 273, 274, 281, 282, 286, 291, 293, 295, 1716, 1717, 1718, 1761, 1762, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1864, 1865, 1866, 1874, 1990, 1992, 2028, 2032, 2034, 2036, 2108, 2109, 2130, 2131, 2133, 2135, 2136, 2137, 2139, 2194, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 141, 142, 143, 177, 178, 181, 225, 230, 235, 246, 249, 271, 272, 283, 284, 285, 287, 288, 289, 290, 292, 294, 296, 1760, 1763, 1863, 1867, 1875, 1876, 1935, 1991, 2026, 2030, 2128, 2129, 2132, 2134, 2138, 2223)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 31, 32, 35, 148, 150, 151, 152, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1771, 1772, 1773, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2058, 2179, 2227, 2229, 2282, 2283, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 33, 34, 149, 1652, 1655, 1756, 1757, 1774, 1897, 2056, 2177, 2231, 2279, 2281, 2288, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 31, 32, 34, 35, 148, 152, 1652, 1654, 1655, 1691, 1692, 1750, 1752, 1755, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1900, 2056, 2058, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 33, 149, 150, 151, 1653, 1693, 1751, 1753, 1754, 1756, 1757, 1771, 1898, 2054, 2177, 2229, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 32, 33, 34, 149, 150, 1652, 1653, 1654, 1691, 1692, 1750, 1752, 1753, 1754, 1756, 1771, 1772, 1773, 1774, 1825, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2227, 2229, 2279, 2281, 2282, 2283, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 35, 148, 151, 152, 1655, 1693, 1751, 1755, 1757, 1824, 1826, 1898, 2179, 2231, 2288, 2292)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 224, 226, 276, 277, 278, 279, 280, 1722, 1775, 1777, 1778, 1779, 1868, 1870, 2027, 2029, 2119, 2120, 2121, 2124, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(222, 228, 275, 1719, 1720, 1721, 1727, 1776, 1869, 2033, 2035, 2037, 2125, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 276, 278, 279, 280, 1720, 1721, 1722, 1727, 1777, 1778, 1868, 1870, 2029, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 224, 226, 228, 275, 277, 1719, 1775, 1776, 1779, 1869, 2027, 2033, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 222, 224, 228, 275, 276, 278, 1719, 1721, 1722, 1775, 1776, 1778, 1779, 1869, 1870, 2029, 2033, 2035, 2119, 2121, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 226, 277, 279, 280, 1720, 1727, 1777, 1868, 2027, 2037, 2120, 2124, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 205, 207, 208, 209, 210, 212, 214, 215, 217, 218, 219, 220, 266, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 206, 211, 213, 216, 265, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 206, 207, 208, 211, 212, 213, 215, 216, 217, 219, 265, 266, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 209, 210, 214, 218, 220, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 209, 212, 213, 214, 215, 216, 218, 220, 266, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(208, 210, 211, 217, 219, 265, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 70, 71, 72, 73, 130, 132, 142, 143, 175, 176, 177, 179, 181, 182, 221, 223, 225, 227, 229, 230, 233, 234, 235, 243, 247, 248, 249, 271, 272, 274, 282, 283, 284, 286, 287, 289, 290, 292, 294, 295, 296, 1718, 1761, 1764, 1839, 1840, 1864, 1865, 1867, 1874, 1875, 1990, 1991, 1992, 2028, 2032, 2036, 2108, 2109, 2128, 2129, 2130, 2132, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 131, 140, 141, 178, 180, 231, 236, 244, 245, 246, 250, 273, 281, 285, 288, 291, 293, 1716, 1717, 1760, 1762, 1763, 1765, 1766, 1838, 1852, 1863, 1866, 1876, 1935, 2026, 2030, 2034, 2131, 2133, 2134, 2135, 2300, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 130, 132, 143, 175, 176, 178, 180, 181, 221, 223, 225, 227, 229, 230, 231, 233, 235, 243, 244, 245, 247, 248, 249, 250, 272, 273, 274, 281, 282, 283, 284, 285, 286, 288, 289, 291, 292, 294, 1717, 1718, 1760, 1761, 1763, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2108, 2129, 2131, 2132, 2134, 2135, 2136, 2137, 2138, 2225, 2226, 2257, 2300, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 131, 140, 141, 142, 177, 179, 182, 234, 236, 246, 271, 287, 290, 293, 295, 296, 1716, 1762, 1764, 1765, 1766, 1838, 1840, 1874, 2030, 2109, 2128, 2130, 2133, 2139, 2194, 2222, 2223, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 143, 175, 178, 179, 221, 223, 225, 227, 229, 230, 231, 233, 243, 244, 245, 246, 247, 249, 250, 272, 274, 281, 283, 286, 287, 289, 290, 291, 293, 294, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1838, 1840, 1852, 1863, 1864, 1865, 1874, 1876, 1992, 2026, 2028, 2030, 2032, 2036, 2128, 2130, 2133, 2135, 2136, 2139, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 142, 176, 177, 180, 181, 182, 234, 235, 236, 248, 271, 273, 282, 284, 285, 288, 292, 295, 1717, 1766, 1839, 1866, 1867, 1875, 1935, 1990, 1991, 2034, 2108, 2109, 2129, 2131, 2132, 2134, 2137, 2138, 2194, 2223, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 33, 34, 149, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1751, 1752, 1755, 1756, 1757, 1773, 1774, 1824, 1826, 1898, 2056, 2058, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 35, 148, 150, 1693, 1750, 1753, 1754, 1771, 1772, 1825, 1827, 1897, 1900, 2054, 2177, 2288, 2289, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 31, 32, 33, 35, 148, 149, 150, 151, 1652, 1653, 1691, 1692, 1693, 1752, 1754, 1755, 1756, 1771, 1772, 1774, 1826, 1827, 1897, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2281, 2282, 2283, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 34, 152, 1654, 1655, 1750, 1751, 1753, 1757, 1773, 1824, 1825, 2054, 2179, 2231, 2279, 2288, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 33, 34, 35, 149, 151, 152, 1652, 1653, 1692, 1693, 1750, 1752, 1753, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2229, 2231, 2281, 2282, 2283, 2289, 2290, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 32, 148, 150, 1654, 1655, 1691, 1751, 1754, 1755, 1756, 1826, 1827, 1898, 2227, 2279, 2288, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 226, 275, 277, 278, 280, 1720, 1721, 1727, 1775, 1776, 1778, 1869, 1870, 2029, 2033, 2035, 2120, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(224, 228, 276, 279, 1719, 1722, 1777, 1779, 1868, 2027, 2037, 2119, 2121, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 224, 276, 277, 278, 279, 1719, 1721, 1722, 1727, 1777, 1778, 1868, 1869, 2027, 2033, 2035, 2037, 2119, 2121, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 222, 226, 228, 275, 280, 1720, 1775, 1776, 1779, 1870, 2029, 2120, 2124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 277, 279, 1720, 1721, 1727, 1775, 1776, 1777, 1779, 1868, 1870, 2027, 2029, 2035, 2037, 2120, 2121, 2124, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 275, 276, 278, 280, 1719, 1722, 1778, 1869, 2033, 2119, 2125, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 205, 206, 207, 208, 209, 212, 213, 214, 217, 218, 265, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 210, 211, 215, 216, 219, 220, 266)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 206, 207, 208, 209, 210, 211, 214, 216, 217, 218, 265, 266, 267, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 212, 213, 215, 219, 220, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 207, 209, 210, 212, 213, 215, 217, 218, 219, 220, 265, 266, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 206, 208, 211, 214, 216, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 72, 73, 130, 131, 132, 140, 141, 143, 175, 176, 177, 223, 225, 227, 230, 234, 244, 245, 247, 250, 272, 273, 274, 282, 283, 284, 289, 290, 291, 292, 294, 295, 296, 1717, 1718, 1762, 1763, 1764, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1867, 1874, 1876, 1935, 1990, 1991, 2026, 2028, 2030, 2032, 2034, 2036, 2109, 2128, 2129, 2131, 2132, 2133, 2135, 2137, 2139, 2194, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 142, 178, 179, 180, 181, 182, 221, 229, 231, 233, 235, 236, 243, 246, 248, 249, 271, 281, 285, 286, 287, 288, 293, 1716, 1760, 1761, 1838, 1866, 1875, 1992, 2108, 2130, 2134, 2136, 2138, 2222, 2257, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 73, 131, 132, 140, 141, 142, 143, 175, 176, 177, 181, 221, 223, 225, 227, 230, 234, 243, 248, 249, 250, 271, 272, 273, 282, 286, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1764, 1765, 1838, 1839, 1840, 1863, 1866, 1867, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2108, 2128, 2131, 2132, 2133, 2134, 2135, 2194, 2222, 2223, 2257, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 130, 178, 179, 180, 182, 229, 231, 233, 235, 236, 244, 245, 246, 247, 274, 281, 283, 284, 285, 287, 288, 289, 1761, 1766, 1852, 1864, 1865, 1874, 2030, 2109, 2129, 2130, 2136, 2137, 2138, 2139, 2225, 2226, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 72, 73, 130, 132, 140, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 227, 230, 231, 233, 234, 244, 245, 247, 248, 249, 250, 271, 274, 281, 282, 283, 284, 285, 291, 292, 294, 296, 1716, 1717, 1760, 1761, 1762, 1765, 1766, 1838, 1840, 1852, 1863, 1866, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2108, 2129, 2130, 2131, 2132, 2136, 2137, 2138, 2139, 2194, 2223, 2226, 2300, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 70, 131, 141, 142, 225, 229, 235, 236, 243, 246, 272, 273, 286, 287, 288, 289, 290, 293, 295, 1718, 1763, 1764, 1839, 1864, 1865, 1867, 1874, 1875, 2030, 2036, 2109, 2128, 2133, 2134, 2135, 2222, 2225, 2257, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 32, 33, 34, 150, 151, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1755, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1897, 1900, 2054, 2058, 2179, 2227, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 31, 35, 148, 149, 152, 1652, 1655, 1754, 1756, 1757, 1827, 1898, 2056, 2177, 2229, 2281, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 32, 35, 150, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 1827, 1897, 1898, 2054, 2179, 2227, 2229, 2288, 2289, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 31, 33, 34, 148, 149, 152, 1752, 1825, 1900, 2056, 2058, 2177, 2231, 2279, 2281, 2282, 2283, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 34, 35, 148, 149, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1755, 1756, 1757, 1772, 1773, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2177, 2179, 2231, 2279, 2281, 2283, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 32, 33, 150, 151, 1693, 1751, 1752, 1753, 1754, 1771, 1774, 2056, 2058, 2227, 2229, 2282, 2288, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 224, 226, 228, 276, 277, 278, 279, 280, 1719, 1721, 1722, 1775, 1777, 1778, 1868, 1870, 2027, 2029, 2035, 2119, 2121, 2124, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 275, 1720, 1727, 1776, 1779, 1869, 2033, 2037, 2120, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 224, 275, 276, 277, 278, 279, 1722, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2027, 2029, 2033, 2037, 2119, 2120, 2121, 2124, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 222, 226, 228, 280, 1719, 1720, 1721, 1727, 1868, 2035, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 224, 226, 228, 275, 280, 1720, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 2027, 2029, 2033, 2119, 2120, 2121, 2124, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(222, 276, 277, 278, 279, 1719, 1722, 1869, 1870, 2035, 2037, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 209, 213, 214, 215, 216, 217, 218, 220, 265, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(208, 210, 211, 212, 219, 266, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 205, 206, 208, 209, 210, 212, 215, 217, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 207, 211, 213, 214, 216, 218, 265)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 206, 207, 208, 209, 210, 211, 214, 215, 218, 219, 265, 266, 267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 212, 213, 216, 217, 220, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 72, 130, 132, 141, 175, 177, 178, 179, 180, 181, 182, 225, 231, 233, 234, 235, 243, 244, 248, 271, 272, 273, 274, 281, 283, 284, 287, 288, 289, 290, 291, 292, 293, 294, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1874, 1875, 1876, 1935, 1991, 1992, 2030, 2032, 2034, 2108, 2109, 2128, 2129, 2131, 2132, 2134, 2135, 2137, 2138, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 73, 131, 140, 142, 143, 176, 221, 223, 227, 229, 230, 236, 245, 246, 247, 249, 250, 282, 285, 286, 295, 1761, 1764, 1838, 1866, 1867, 1990, 2026, 2028, 2036, 2130, 2133, 2136, 2139, 2194, 2222, 2223, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 72, 73, 131, 141, 142, 143, 178, 179, 180, 181, 182, 221, 223, 225, 227, 230, 233, 234, 235, 243, 245, 247, 248, 249, 274, 281, 282, 283, 284, 286, 288, 289, 290, 291, 292, 293, 294, 295, 1717, 1718, 1761, 1762, 1765, 1766, 1838, 1840, 1852, 1863, 1864, 1865, 1867, 1874, 1876, 1935, 1990, 1991, 1992, 2028, 2030, 2036, 2108, 2109, 2128, 2129, 2131, 2134, 2136, 2137, 2139, 2194, 2222, 2226, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 71, 130, 132, 140, 175, 176, 177, 229, 231, 236, 244, 246, 250, 271, 272, 273, 285, 287, 296, 1716, 1760, 1763, 1764, 1839, 1866, 1875, 2026, 2032, 2034, 2130, 2132, 2133, 2135, 2138, 2223, 2225, 2257, 2300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 72, 73, 130, 132, 140, 142, 175, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 234, 235, 243, 244, 246, 247, 249, 250, 271, 272, 273, 281, 283, 287, 288, 290, 291, 292, 293, 294, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1838, 1852, 1863, 1866, 1867, 1876, 1935, 1991, 2028, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2132, 2134, 2136, 2139, 2194, 2225, 2257, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 131, 141, 143, 176, 177, 233, 236, 245, 248, 274, 282, 284, 285, 286, 289, 296, 1766, 1839, 1840, 1864, 1865, 1874, 1875, 1990, 1992, 2026, 2030, 2032, 2131, 2133, 2135, 2137, 2138, 2222, 2223, 2226, 2300, 2301, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 32, 34, 35, 148, 149, 150, 151, 152, 1653, 1654, 1655, 1691, 1693, 1750, 1753, 1755, 1756, 1771, 1772, 1773, 1824, 1825, 1826, 1827, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 31, 33, 1652, 1692, 1751, 1752, 1754, 1757, 1774, 1897, 1898, 2177, 2179, 2283, 2288, 2289, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 35, 149, 151, 152, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1773, 1774, 1826, 1897, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2231, 2281, 2282, 2283, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 32, 33, 34, 148, 150, 1652, 1756, 1757, 1771, 1772, 1824, 1825, 1827, 2054, 2179, 2279, 2288, 2289, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 33, 34, 148, 149, 151, 152, 1652, 1653, 1655, 1691, 1751, 1754, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 1898, 1900, 2054, 2056, 2179, 2227, 2229, 2231, 2281, 2283, 2288, 2289, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 35, 150, 1654, 1692, 1693, 1750, 1752, 1753, 1755, 1756, 1825, 1827, 1897, 2058, 2177, 2279, 2282, 2290, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 276, 279, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1870, 2035, 2037, 2119, 2121, 2124, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 224, 226, 228, 275, 277, 278, 1722, 1869, 2027, 2029, 2033, 2120, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 226, 228, 275, 276, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1777, 1778, 1779, 1870, 2027, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 222, 224, 277, 1775, 1776, 1868, 1869, 2029, 2033, 2035, 2037, 2119, 2120)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 224, 226, 228, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1776, 1778, 1869, 2027, 2029, 2033, 2035, 2037, 2121, 2124, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 275, 1727, 1775, 1777, 1779, 1868, 1870, 2119, 2120, 2125, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 210, 213, 215, 217, 218, 219, 220, 265, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 211, 212, 214, 216, 266, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 206, 208, 209, 211, 214, 215, 216, 217, 219, 220, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 207, 210, 212, 213, 218, 265, 266, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 210, 213, 214, 215, 216, 218, 219, 266, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 211, 212, 217, 220, 265, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 73, 130, 140, 141, 142, 143, 177, 178, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 236, 244, 245, 247, 248, 249, 271, 272, 273, 274, 281, 282, 283, 285, 286, 290, 291, 292, 294, 1717, 1718, 1760, 1762, 1764, 1765, 1838, 1840, 1863, 1864, 1865, 1866, 1874, 1876, 1935, 1990, 1991, 2026, 2028, 2030, 2032, 2034, 2036, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2139, 2194, 2223, 2257, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 131, 132, 175, 176, 179, 234, 235, 243, 246, 250, 284, 287, 288, 289, 293, 295, 296, 1716, 1761, 1763, 1766, 1839, 1852, 1867, 1875, 1992, 2108, 2109, 2135, 2136, 2137, 2138, 2222, 2225, 2226, 2300, 2301, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 72, 130, 131, 132, 141, 142, 143, 175, 176, 177, 179, 181, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 246, 247, 249, 272, 273, 274, 281, 282, 284, 285, 287, 291, 292, 293, 294, 295, 296, 1716, 1718, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1865, 1866, 1867, 1875, 1876, 1935, 1991, 2030, 2032, 2034, 2036, 2108, 2128, 2129, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2222, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 73, 140, 178, 180, 182, 221, 244, 245, 248, 250, 271, 283, 286, 288, 289, 290, 1717, 1760, 1762, 1852, 1864, 1874, 1990, 1992, 2026, 2028, 2109, 2130, 2136, 2139, 2194, 2223, 2225, 2226, 2257, 2300, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 72, 73, 131, 132, 140, 141, 142, 143, 175, 176, 177, 179, 180, 182, 221, 225, 230, 231, 233, 236, 243, 244, 245, 247, 249, 271, 272, 273, 274, 281, 282, 284, 286, 287, 289, 290, 291, 1716, 1717, 1718, 1760, 1762, 1765, 1766, 1840, 1852, 1864, 1867, 1875, 1876, 1990, 1992, 2026, 2028, 2032, 2034, 2108, 2109, 2128, 2130, 2132, 2133, 2136, 2137, 2138, 2139, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 71, 130, 178, 181, 223, 227, 229, 234, 235, 246, 248, 250, 283, 285, 288, 292, 293, 294, 295, 296, 1761, 1763, 1764, 1838, 1839, 1863, 1865, 1866, 1874, 1935, 1991, 2030, 2036, 2129, 2131, 2134, 2135, 2194, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 35, 149, 150, 151, 152, 1652, 1654, 1692, 1750, 1751, 1752, 1753, 1756, 1757, 1771, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2283, 2288, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 32, 33, 34, 148, 1653, 1655, 1691, 1693, 1754, 1755, 1772, 1773, 1774, 1897, 2177, 2179, 2281, 2282, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 1655, 1692, 1751, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 151, 152, 1652, 1653, 1654, 1691, 1693, 1750, 1752, 1772, 1773, 1898, 2058, 2177, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 35, 148, 149, 150, 152, 1652, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2179, 2227, 2229, 2231, 2281, 2282, 2283, 2289, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 32, 33, 34, 151, 1653, 1654, 1655, 1692, 1693, 1772, 1773, 1824, 1898, 2058, 2177, 2279, 2288, 2292, 2293)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 43, 222, 224, 226, 275, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 2027, 2029, 2035, 2037, 2120, 2124, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 228, 276, 277, 1868, 1869, 1870, 2033, 2119, 2121, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 224, 228, 275, 276, 278, 279, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1870, 2033, 2035, 2037, 2119, 2120, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 222, 226, 277, 280, 1719, 1720, 1722, 1869, 2027, 2029, 2121, 2124, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 275, 276, 277, 278, 280, 1719, 1721, 1727, 1775, 1776, 1779, 1868, 1870, 2027, 2029, 2035, 2121, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(228, 279, 1720, 1722, 1777, 1778, 1869, 2033, 2037, 2119, 2120, 2124, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 211, 215, 216, 218, 220, 266, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 208, 212, 213, 214, 217, 219, 265, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 207, 210, 211, 213, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 205, 206, 208, 209, 212, 214, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 206, 207, 208, 212, 213, 214, 215, 216, 217, 218, 220, 265, 266, 267, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 209, 210, 211, 219, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 72, 73, 130, 132, 140, 143, 175, 177, 178, 180, 223, 225, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 274, 282, 283, 284, 286, 287, 288, 289, 290, 291, 293, 294, 296, 1716, 1717, 1718, 1760, 1763, 1764, 1765, 1766, 1839, 1840, 1865, 1874, 1875, 1876, 1990, 1991, 1992, 2028, 2030, 2032, 2036, 2108, 2109, 2128, 2129, 2132, 2134, 2135, 2136, 2139, 2194, 2225, 2226, 2257, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 70, 71, 131, 141, 142, 176, 179, 181, 182, 221, 227, 273, 281, 285, 292, 295, 1761, 1762, 1838, 1852, 1863, 1864, 1866, 1867, 1935, 2026, 2034, 2130, 2131, 2133, 2137, 2138, 2222, 2223, 2300, 2301, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 130, 131, 132, 140, 141, 142, 143, 175, 177, 178, 179, 181, 182, 221, 229, 230, 231, 234, 236, 243, 244, 247, 249, 250, 271, 273, 274, 281, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 294, 1717, 1718, 1761, 1764, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1874, 1875, 1876, 1935, 1991, 1992, 2026, 2032, 2034, 2128, 2129, 2130, 2131, 2133, 2134, 2136, 2137, 2139, 2194, 2222, 2257, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 73, 176, 180, 223, 225, 227, 233, 235, 245, 246, 248, 272, 285, 293, 295, 296, 1716, 1760, 1762, 1763, 1765, 1766, 1867, 1990, 2028, 2030, 2036, 2108, 2109, 2132, 2135, 2138, 2223, 2225, 2226, 2300, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 73, 130, 131, 132, 140, 142, 143, 175, 177, 178, 179, 180, 181, 182, 221, 225, 227, 230, 233, 236, 243, 244, 245, 246, 247, 248, 249, 272, 273, 274, 281, 286, 288, 289, 291, 292, 293, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1765, 1766, 1838, 1839, 1840, 1864, 1865, 1867, 1876, 1935, 1990, 1991, 1992, 2028, 2030, 2032, 2034, 2109, 2128, 2129, 2131, 2132, 2134, 2135, 2136, 2139, 2194, 2222, 2223, 2300, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 141, 176, 223, 229, 231, 234, 235, 250, 271, 282, 283, 284, 285, 287, 290, 1717, 1764, 1852, 1863, 1866, 1874, 1875, 2026, 2036, 2108, 2130, 2133, 2137, 2138, 2225, 2226, 2257, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 33, 34, 150, 151, 1652, 1653, 1654, 1655, 1692, 1750, 1751, 1753, 1754, 1756, 1771, 1772, 1774, 1824, 1825, 1826, 1897, 2054, 2058, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 35, 148, 149, 152, 1691, 1693, 1752, 1755, 1757, 1773, 1827, 1898, 1900, 2056, 2229, 2288, 2289, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 34, 35, 148, 150, 151, 1652, 1653, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1754, 1755, 1771, 1772, 1773, 1774, 1825, 1827, 1897, 1900, 2054, 2056, 2179, 2229, 2231, 2279, 2283, 2288, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 33, 149, 152, 1692, 1753, 1756, 1757, 1824, 1826, 1898, 2058, 2177, 2227, 2281, 2282, 2289, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 33, 148, 149, 151, 152, 1652, 1654, 1693, 1752, 1753, 1754, 1756, 1757, 1771, 1772, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2279, 2281, 2283, 2288, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 34, 35, 150, 1653, 1655, 1691, 1692, 1750, 1751, 1755, 1773, 1774, 1824, 1825, 1826, 2231, 2282, 2289, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 222, 226, 228, 276, 277, 278, 279, 280, 1719, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1868, 1870, 2027, 2033, 2035, 2037, 2124, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 224, 275, 1720, 1779, 1869, 2029, 2119, 2120, 2121, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 226, 228, 275, 276, 278, 279, 280, 1721, 1727, 1775, 1776, 1778, 1869, 1870, 2029, 2035, 2037, 2119, 2121, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 224, 277, 1719, 1720, 1722, 1777, 1779, 1868, 2027, 2033, 2120, 2124, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 275, 276, 278, 279, 1719, 1721, 1727, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2119, 2120, 2121, 2124, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 277, 280, 1720, 1722, 1775, 1776, 2033, 2035, 2037, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 209, 210, 212, 213, 215, 217, 218, 219, 220, 265, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 208, 211, 214, 216, 266, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 205, 206, 207, 209, 210, 213, 214, 217, 219, 220, 265, 266, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 208, 211, 212, 215, 216, 218, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 206, 208, 210, 211, 212, 213, 214, 216, 217, 218, 219, 220, 265, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 207, 209, 215, 266, 267, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 70, 73, 131, 140, 141, 142, 143, 176, 178, 179, 180, 181, 225, 229, 230, 231, 233, 234, 236, 243, 244, 245, 246, 248, 249, 250, 271, 274, 281, 282, 284, 285, 286, 287, 288, 291, 292, 294, 1716, 1718, 1760, 1762, 1763, 1764, 1766, 1838, 1839, 1852, 1864, 1865, 1867, 1875, 1876, 1935, 1990, 1991, 2032, 2034, 2036, 2109, 2128, 2129, 2130, 2132, 2134, 2135, 2137, 2138, 2194, 2223, 2225, 2226, 2257, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 72, 130, 132, 175, 177, 182, 221, 223, 227, 235, 247, 272, 273, 283, 289, 290, 293, 295, 296, 1717, 1761, 1765, 1840, 1863, 1866, 1874, 1992, 2026, 2028, 2030, 2108, 2131, 2133, 2136, 2139, 2222, 2300, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 73, 131, 143, 178, 180, 223, 227, 229, 230, 231, 233, 235, 236, 243, 244, 246, 247, 249, 273, 281, 282, 283, 284, 286, 288, 290, 291, 292, 293, 294, 295, 296, 1716, 1761, 1762, 1763, 1764, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1991, 1992, 2026, 2028, 2030, 2032, 2036, 2109, 2128, 2131, 2132, 2134, 2135, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 130, 132, 140, 141, 142, 175, 176, 177, 179, 181, 182, 221, 225, 234, 245, 248, 250, 271, 272, 274, 285, 287, 289, 1717, 1718, 1760, 1765, 1838, 1876, 1935, 1990, 2034, 2108, 2129, 2130, 2133, 2136, 2137, 2300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 72, 73, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 180, 181, 223, 225, 227, 231, 233, 236, 244, 245, 246, 247, 248, 249, 271, 272, 273, 274, 281, 283, 284, 285, 287, 288, 290, 291, 294, 295, 296, 1716, 1718, 1760, 1762, 1763, 1764, 1765, 1766, 1838, 1840, 1852, 1863, 1865, 1866, 1867, 1874, 1990, 1992, 2028, 2032, 2108, 2109, 2128, 2130, 2131, 2132, 2133, 2137, 2194, 2222, 2223, 2257, 2300, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 71, 130, 179, 182, 221, 229, 230, 234, 235, 243, 250, 282, 286, 289, 292, 293, 1717, 1761, 1839, 1864, 1875, 1876, 1935, 1991, 2026, 2030, 2034, 2036, 2129, 2134, 2135, 2136, 2138, 2139, 2225, 2226, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 34, 149, 150, 151, 1653, 1655, 1750, 1752, 1754, 1756, 1757, 1771, 1773, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2058, 2179, 2227, 2229, 2231, 2281, 2282, 2288, 2289, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(31, 35, 148, 152, 1652, 1654, 1691, 1692, 1693, 1751, 1753, 1755, 1772, 1774, 2056, 2177, 2279, 2283, 2290, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 33, 149, 151, 1652, 1653, 1654, 1655, 1691, 1693, 1750, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1825, 1897, 1900, 2054, 2058, 2177, 2229, 2231, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 34, 35, 148, 150, 152, 1692, 1751, 1752, 1772, 1824, 1826, 1827, 1898, 2056, 2179, 2227, 2279, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 33, 35, 148, 149, 151, 1652, 1654, 1655, 1691, 1692, 1693, 1752, 1755, 1756, 1771, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2056, 2177, 2179, 2227, 2229, 2231, 2281, 2282, 2283, 2289, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 32, 34, 150, 152, 1653, 1750, 1751, 1753, 1754, 1757, 1772, 2054, 2058, 2279, 2288, 2293, 2294, 2295)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1727, 1775, 1779, 1868, 1870, 2027, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1721, 1722, 1776, 1777, 1778, 1869, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 1719, 1720, 1721, 1722, 1779, 1868, 1869, 1870, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 1727, 1775, 1776, 1777, 1778, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 1720, 1722, 1727, 1775, 1778, 1868, 1869, 1870, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 1719, 1721, 1776, 1777, 1779, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 205, 206, 208, 212, 213, 214, 215, 217, 218, 220, 265, 266, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 207, 209, 210, 211, 216, 219, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 205, 206, 207, 208, 209, 210, 212, 213, 214, 215, 217, 218, 265, 267, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 211, 216, 219, 220, 266, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 206, 209, 211, 212, 213, 214, 217, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 205, 207, 208, 210, 215, 216, 218, 219)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 131, 141, 142, 143, 177, 233, 234, 235, 236, 281, 283, 284, 287, 288, 289, 292, 293, 294, 295, 296, 1716, 1717, 1764, 1765, 1766, 1838, 1839, 1863, 1864, 1935, 1990, 1991, 1992, 2109, 2137, 2138, 2194, 2222, 2226, 2300, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 130, 132, 140, 229, 230, 231, 282, 285, 286, 290, 291, 1718, 1840, 1852, 1865, 2026, 2030, 2108, 2139, 2223, 2225, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 140, 141, 142, 177, 229, 231, 234, 281, 282, 285, 287, 289, 291, 293, 294, 295, 296, 1716, 1717, 1718, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2138, 2194, 2222, 2223, 2225, 2300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 131, 132, 143, 230, 233, 235, 236, 283, 284, 286, 288, 290, 292, 1764, 1838, 2137, 2139, 2226, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 130, 131, 140, 141, 143, 177, 230, 231, 233, 234, 281, 282, 283, 287, 289, 290, 293, 294, 296, 1717, 1718, 1764, 1766, 1838, 1839, 1840, 1852, 1865, 1935, 1990, 1992, 2108, 2109, 2137, 2138, 2194, 2222, 2223, 2225, 2226, 2300, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 132, 142, 229, 235, 236, 284, 285, 286, 288, 291, 292, 295, 1716, 1765, 1863, 1864, 1991, 2026, 2030, 2139, 2301, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 31, 32, 33, 34, 148, 149, 150, 152, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1753, 1754, 1756, 1771, 1774, 1825, 1827, 1900, 2054, 2056, 2058, 2179, 2229, 2231, 2281, 2282, 2283, 2288, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 35, 151, 1652, 1653, 1752, 1755, 1757, 1772, 1773, 1824, 1826, 1897, 1898, 2177, 2227, 2279, 2289, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 34, 35, 149, 152, 1652, 1653, 1654, 1691, 1693, 1750, 1752, 1753, 1756, 1757, 1771, 1772, 1824, 1825, 1827, 1897, 1898, 1900, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(33, 148, 150, 151, 1655, 1692, 1751, 1754, 1755, 1773, 1774, 1826, 2054, 2056, 2058, 2177, 2179, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 33, 34, 148, 149, 150, 152, 1655, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1757, 1771, 1773, 1774, 1824, 1825, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2279, 2282, 2288, 2289, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 35, 151, 1652, 1653, 1654, 1691, 1755, 1756, 1772, 1826, 1898, 2179, 2227, 2229, 2231, 2281, 2283, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1721, 1727, 1775, 1777, 1778, 1869, 2027, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1720, 1722, 1776, 1779, 1868, 1870, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 1719, 1721, 1727, 1775, 1777, 1778, 1779, 1868, 1870, 2027, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 1720, 1722, 1776, 1869, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 1719, 1721, 1722, 1727, 1777, 1778, 1779, 1869, 2027, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 1720, 1775, 1776, 1868, 1870, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 206, 207, 209, 211, 212, 214, 215, 217, 218, 219, 220, 265, 266, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 208, 210, 213, 216, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 208, 209, 210, 211, 212, 213, 215, 219, 220, 266, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 214, 216, 217, 218, 265, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 265, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 208, 209, 220, 266, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 177, 231, 233, 234, 235, 281, 282, 283, 284, 285, 287, 288, 290, 291, 292, 293, 294, 296, 1716, 1718, 1764, 1765, 1838, 1839, 1863, 1864, 1865, 1935, 1991, 2026, 2108, 2109, 2138, 2139, 2223, 2226, 2300, 2301, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(140, 141, 142, 143, 229, 230, 236, 286, 289, 295, 1717, 1766, 1840, 1852, 1990, 1992, 2030, 2137, 2194, 2222, 2225, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 131, 132, 141, 143, 230, 231, 233, 234, 235, 236, 281, 284, 285, 286, 287, 292, 293, 1716, 1717, 1718, 1764, 1765, 1766, 1839, 1840, 1863, 1864, 1935, 1991, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 130, 140, 142, 177, 229, 282, 283, 288, 289, 290, 291, 294, 295, 296, 1838, 1852, 1865, 1990, 1992, 2026, 2301, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 130, 131, 132, 140, 143, 177, 229, 231, 233, 234, 236, 284, 287, 288, 289, 290, 291, 292, 294, 295, 296, 1717, 1718, 1764, 1766, 1838, 1840, 1864, 1865, 1935, 1990, 1992, 2026, 2030, 2108, 2139, 2194, 2222, 2223, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 141, 142, 230, 235, 281, 282, 283, 285, 286, 293, 1716, 1765, 1839, 1852, 1863, 1991, 2109, 2137, 2138, 2225, 2226, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 34, 35, 148, 149, 150, 152, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1771, 1772, 1774, 1825, 1827, 1897, 1898, 1900, 2056, 2177, 2179, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 31, 32, 33, 151, 1652, 1655, 1755, 1756, 1757, 1773, 1824, 1826, 2054, 2058, 2227, 2289, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 31, 32, 35, 150, 151, 152, 1652, 1654, 1655, 1693, 1750, 1751, 1754, 1756, 1757, 1772, 1773, 1774, 1824, 1826, 1827, 1898, 1900, 2054, 2058, 2177, 2179, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 33, 34, 148, 149, 1653, 1691, 1692, 1752, 1753, 1755, 1771, 1825, 1897, 2056, 2227, 2289, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 31, 32, 35, 150, 152, 1652, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1827, 1898, 2054, 2056, 2058, 2177, 2281, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 33, 34, 148, 149, 151, 1655, 1752, 1754, 1826, 1897, 1900, 2179, 2227, 2229, 2231, 2279, 2292, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 277, 280, 1719, 1721, 1727, 1775, 1776, 1778, 1779, 1868, 2027, 2033, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 275, 276, 278, 279, 1720, 1722, 1777, 1869, 1870, 2029, 2035, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 222, 224, 226, 275, 278, 279, 280, 1719, 1722, 1727, 1775, 1777, 1778, 1869, 1870, 2029, 2033, 2035, 2119, 2121, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 228, 276, 277, 1720, 1721, 1776, 1779, 1868, 2027, 2037, 2120, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 224, 226, 275, 280, 1719, 1720, 1721, 1722, 1775, 1777, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 222, 228, 276, 277, 278, 279, 1727, 1776, 1778, 1779, 1868, 2119, 2120)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 206, 207, 209, 210, 212, 213, 215, 216, 217, 218, 219, 220, 265, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 208, 211, 214, 266, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 205, 207, 209, 210, 213, 214, 215, 216, 219, 220, 265, 266, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 206, 208, 211, 212, 217, 218, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 207, 208, 209, 211, 212, 215, 216, 218, 219, 220, 265, 266, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 205, 206, 210, 213, 214, 217, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 140, 141, 142, 175, 176, 177, 178, 179, 181, 227, 230, 231, 233, 243, 244, 245, 247, 248, 250, 272, 273, 274, 282, 283, 284, 286, 287, 288, 289, 291, 293, 294, 295, 296, 1717, 1718, 1760, 1762, 1764, 1766, 1839, 1840, 1863, 1865, 1867, 1875, 1935, 1990, 2026, 2030, 2032, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2133, 2134, 2135, 2138, 2139, 2222, 2223, 2225, 2257, 2300, 2301, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 143, 180, 182, 221, 223, 225, 229, 234, 235, 236, 246, 249, 271, 281, 285, 290, 292, 1716, 1761, 1763, 1765, 1838, 1852, 1864, 1866, 1874, 1876, 1991, 1992, 2028, 2034, 2132, 2136, 2137, 2194, 2226, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 72, 73, 130, 131, 132, 141, 175, 176, 178, 180, 181, 182, 230, 231, 233, 234, 236, 244, 245, 248, 271, 272, 273, 274, 282, 284, 285, 286, 287, 288, 289, 291, 292, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1874, 1935, 1990, 1991, 2030, 2034, 2036, 2108, 2109, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2257, 2300, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 140, 142, 143, 177, 179, 221, 223, 225, 227, 229, 235, 243, 246, 247, 249, 250, 281, 283, 290, 293, 294, 295, 296, 1718, 1838, 1867, 1875, 1876, 1992, 2026, 2028, 2032, 2128, 2129, 2134, 2222, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 221, 229, 230, 233, 234, 244, 245, 246, 248, 250, 271, 272, 274, 281, 282, 284, 286, 287, 289, 290, 291, 295, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1840, 1852, 1863, 1864, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2108, 2109, 2128, 2132, 2133, 2136, 2137, 2139, 2222, 2226, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 130, 182, 223, 225, 227, 231, 235, 236, 243, 247, 249, 273, 283, 285, 288, 292, 293, 294, 296, 1716, 1839, 1865, 1866, 1867, 1874, 1875, 1876, 2030, 2129, 2130, 2131, 2134, 2135, 2138, 2194, 2223, 2225, 2257, 2300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 33, 34, 149, 151, 152, 1653, 1654, 1655, 1692, 1750, 1751, 1752, 1754, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1897, 1900, 2056, 2177, 2179, 2227, 2229, 2231, 2281, 2288, 2289, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 32, 35, 148, 150, 1652, 1691, 1693, 1753, 1755, 1756, 1827, 1898, 2054, 2058, 2279, 2282, 2283, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 32, 33, 34, 35, 148, 149, 150, 151, 1653, 1655, 1691, 1692, 1750, 1751, 1753, 1756, 1757, 1772, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 31, 152, 1652, 1654, 1693, 1752, 1754, 1755, 1771, 1773, 1774, 1898, 2058, 2177, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 31, 33, 148, 149, 150, 152, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1772, 1773, 1824, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2177, 2227, 2229, 2279, 2281, 2282, 2288, 2289, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 32, 34, 35, 151, 1652, 1653, 1755, 1757, 1771, 1774, 1825, 2058, 2179, 2231, 2283, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 1719, 1720, 1721, 1775, 1776, 1777, 1778, 1869, 1870, 2027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 1722, 1727, 1779, 1868, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 1720, 1721, 1722, 1775, 1776, 1778, 1869, 1870, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1719, 1727, 1777, 1779, 1868, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 1719, 1720, 1722, 1776, 1778, 1779, 1868, 1869, 1870, 2027, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 1721, 1727, 1775, 1777, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 205, 206, 207, 208, 209, 210, 212, 214, 216, 218, 220, 266, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 211, 213, 215, 217, 219, 265, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 208, 210, 211, 214, 215, 216, 217, 218, 220, 266, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 209, 212, 213, 219, 265, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 205, 207, 208, 209, 210, 211, 213, 214, 216, 217, 219, 265, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 206, 212, 215, 218, 220, 266, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 131, 132, 140, 142, 177, 230, 234, 236, 282, 283, 285, 286, 287, 288, 290, 291, 292, 294, 295, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1991, 2030, 2108, 2137, 2138, 2139, 2223, 2225, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 130, 141, 143, 229, 231, 233, 235, 281, 284, 289, 293, 296, 1716, 1865, 1935, 1990, 1992, 2026, 2109, 2194, 2222, 2226, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 130, 140, 141, 143, 177, 234, 281, 282, 283, 284, 285, 287, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1838, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 2026, 2030, 2108, 2137, 2138, 2139, 2194, 2222, 2223, 2301, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 132, 142, 229, 230, 231, 233, 235, 236, 286, 288, 289, 290, 1766, 1839, 1840, 1992, 2109, 2225, 2226, 2300, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 132, 140, 141, 142, 143, 177, 229, 230, 231, 235, 236, 281, 283, 285, 287, 288, 290, 291, 292, 293, 294, 295, 296, 1717, 1718, 1764, 1766, 1839, 1840, 1852, 1863, 1865, 1935, 1990, 1991, 2026, 2108, 2109, 2137, 2139, 2223, 2226, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 130, 131, 233, 234, 282, 284, 286, 289, 1716, 1765, 1838, 1864, 1992, 2030, 2138, 2194, 2222, 2225, 2300, 2301, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 31, 32, 33, 34, 148, 149, 151, 152, 1653, 1654, 1655, 1692, 1693, 1750, 1753, 1754, 1756, 1757, 1771, 1772, 1773, 1774, 1826, 1827, 1897, 1900, 2056, 2058, 2177, 2227, 2229, 2279, 2281, 2282, 2283, 2288, 2290, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 23, 35, 150, 1652, 1691, 1751, 1752, 1755, 1824, 1825, 1898, 2054, 2179, 2231, 2289, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 32, 34, 149, 151, 152, 1653, 1654, 1655, 1692, 1693, 1751, 1753, 1754, 1755, 1771, 1773, 1774, 1824, 1826, 1827, 1898, 1900, 2054, 2058, 2227, 2229, 2231, 2279, 2281, 2283, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 33, 35, 148, 150, 1652, 1691, 1750, 1752, 1756, 1757, 1772, 1825, 1897, 2056, 2177, 2179, 2282, 2288)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 35, 149, 150, 151, 152, 1652, 1653, 1655, 1691, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 1757, 1774, 1825, 1827, 1900, 2054, 2058, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(34, 148, 1654, 1751, 1755, 1771, 1772, 1773, 1824, 1826, 1897, 1898, 2056, 2177, 2179, 2227, 2229, 2289, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1720, 1721, 1722, 1727, 1775, 1776, 1778, 1779, 1868, 1870, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 1719, 1777, 1869, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1719, 1721, 1722, 1727, 1775, 1776, 1778, 1779, 1868, 1870, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 1720, 1777, 1869, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 1719, 1720, 1721, 1727, 1775, 1777, 1778, 1779, 1868, 1869, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 1722, 1776, 1870, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 210, 211, 216, 217, 219, 265, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(208, 209, 212, 213, 214, 215, 218, 220, 266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 206, 207, 208, 209, 210, 212, 213, 214, 215, 216, 218, 219, 220, 265, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 205, 211, 217, 266, 267, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 205, 206, 208, 209, 210, 212, 214, 217, 218, 219, 220, 266, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 207, 211, 213, 215, 216, 265, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 131, 132, 140, 141, 143, 177, 229, 231, 234, 236, 281, 283, 284, 285, 290, 291, 293, 295, 296, 1716, 1717, 1718, 1765, 1766, 1838, 1840, 1852, 1863, 1935, 1990, 2030, 2108, 2109, 2137, 2138, 2139, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 130, 142, 230, 233, 235, 282, 286, 287, 288, 289, 292, 294, 1764, 1839, 1864, 1865, 1991, 1992, 2026, 2194, 2222)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 130, 131, 132, 143, 177, 229, 230, 234, 236, 281, 284, 286, 290, 291, 292, 294, 295, 296, 1716, 1717, 1764, 1765, 1838, 1839, 1840, 1852, 1863, 1865, 1935, 1992, 2026, 2108, 2109, 2137, 2139, 2194, 2222, 2223, 2226, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 140, 141, 142, 231, 233, 235, 282, 283, 285, 287, 288, 289, 293, 1718, 1766, 1864, 1990, 1991, 2030, 2138, 2225, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 131, 132, 140, 141, 142, 143, 229, 230, 234, 235, 236, 281, 283, 284, 285, 287, 290, 291, 292, 295, 296, 1716, 1717, 1764, 1765, 1838, 1840, 1863, 1865, 1990, 1991, 2026, 2108, 2138, 2139, 2222, 2225, 2226, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 130, 177, 231, 233, 282, 286, 288, 289, 293, 294, 1718, 1766, 1839, 1852, 1864, 1935, 1992, 2030, 2109, 2137, 2194, 2223, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 34, 148, 149, 150, 152, 1652, 1654, 1655, 1691, 1692, 1693, 1751, 1752, 1753, 1755, 1756, 1772, 1774, 1826, 1827, 1897, 1898, 1900, 2054, 2058, 2177, 2227, 2229, 2231, 2279, 2281, 2288, 2289, 2290, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 32, 33, 35, 151, 1653, 1750, 1754, 1757, 1771, 1773, 1824, 1825, 2056, 2179, 2282, 2283, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 31, 32, 33, 34, 35, 149, 152, 1652, 1654, 1655, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1827, 1897, 1898, 1900, 2058, 2227, 2229, 2281, 2282, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 148, 150, 151, 1653, 1692, 1693, 1825, 1826, 2054, 2056, 2177, 2179, 2231, 2279, 2283, 2288, 2289, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 23, 31, 32, 33, 148, 150, 152, 1652, 1653, 1654, 1655, 1692, 1750, 1751, 1752, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1826, 1827, 1897, 1898, 2054, 2056, 2058, 2179, 2229, 2231, 2281, 2282, 2283, 2288, 2289, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 34, 35, 149, 151, 1691, 1693, 1753, 1754, 1824, 1825, 1900, 2177, 2227, 2279, 2290, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 222, 224, 226, 228, 275, 276, 278, 1720, 1727, 1776, 1778, 1779, 1868, 1869, 2027, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 277, 279, 280, 1719, 1721, 1722, 1775, 1777, 1870, 2119, 2224)</t>
+    <t xml:space="preserve">c(43, 44, 222, 275, 276, 277, 279, 280, 1719, 1720, 1722, 1727, 1777, 1778, 1779, 1868, 1869, 2027, 2119, 2120, 2124, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 224, 226, 228, 278, 1721, 1775, 1776, 1870, 2121, 2125, 2126)</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 44, 222, 224, 226, 228, 275, 276, 279, 280, 1719, 1720, 1721, 1722, 1775, 1776, 1778, 1779, 1869, 2119, 2120, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 277, 278, 1727, 1777, 1868, 1870, 2027, 2121, 2124, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 224, 226, 228, 276, 278, 279, 1719, 1721, 1722, 1727, 1775, 1777, 1778, 1868, 1869, 1870, 2120, 2121, 2124, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 275, 277, 280, 1720, 1776, 1779, 2027, 2119, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 206, 207, 208, 209, 212, 213, 214, 216, 218, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 210, 211, 215, 217, 219, 220, 265)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 209, 210, 211, 212, 213, 214, 216, 218, 219, 220, 266, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 208, 215, 217, 265, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 206, 207, 208, 209, 210, 211, 214, 216, 217, 218, 219, 265, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 212, 213, 215, 220, 266, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 73, 131, 141, 143, 175, 180, 221, 223, 225, 230, 231, 233, 236, 243, 244, 245, 246, 248, 250, 272, 273, 274, 282, 285, 286, 287, 289, 290, 291, 294, 295, 296, 1716, 1717, 1718, 1761, 1762, 1764, 1765, 1766, 1838, 1839, 1863, 1864, 1865, 1935, 1990, 2030, 2108, 2128, 2129, 2130, 2131, 2132, 2133, 2135, 2137, 2194, 2222, 2223, 2225, 2257, 2300, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 130, 132, 140, 142, 177, 227, 229, 234, 235, 247, 249, 271, 281, 283, 284, 288, 292, 293, 1760, 1763, 1840, 1852, 1866, 1867, 1991, 1992, 2026, 2109, 2134, 2136, 2138, 2139, 2226, 2301, 2302)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 228, 276, 278, 279, 280, 1727, 1777, 1778, 1779, 1868, 1870, 2027, 2120, 2121, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(224, 226, 275, 277, 1719, 1720, 1721, 1722, 1775, 1776, 1869, 2119, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 228, 275, 276, 277, 1719, 1720, 1727, 1775, 1778, 1868, 1869, 2027, 2119, 2121, 2124, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(226, 278, 279, 280, 1721, 1722, 1776, 1777, 1779, 1870, 2120, 2125, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 207, 208, 209, 211, 212, 215, 216, 217, 218, 219, 265, 266, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 205, 206, 210, 213, 214, 220, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 208, 209, 210, 211, 214, 215, 216, 217, 218, 219, 220, 265, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 206, 207, 212, 213, 266, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 206, 207, 209, 212, 213, 215, 216, 217, 265, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 205, 208, 210, 211, 214, 218, 219, 220)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 72, 73, 130, 132, 142, 143, 175, 177, 180, 225, 227, 230, 231, 233, 234, 235, 236, 243, 244, 248, 249, 274, 281, 283, 286, 287, 289, 291, 292, 296, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1840, 1863, 1864, 1866, 1867, 1991, 1992, 2030, 2108, 2109, 2129, 2131, 2133, 2134, 2135, 2136, 2137, 2138, 2194, 2222, 2223, 2225, 2226, 2257, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 131, 140, 141, 221, 223, 229, 245, 246, 247, 250, 271, 272, 273, 282, 284, 285, 288, 290, 293, 294, 295, 1716, 1717, 1838, 1839, 1852, 1865, 1935, 1990, 2026, 2128, 2130, 2132, 2139, 2300)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 130, 131, 132, 140, 141, 142, 177, 180, 221, 227, 229, 236, 244, 245, 246, 250, 273, 281, 282, 283, 284, 285, 288, 289, 290, 294, 295, 296, 1716, 1718, 1760, 1762, 1763, 1765, 1766, 1838, 1839, 1840, 1852, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2030, 2128, 2129, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 143, 175, 223, 225, 230, 231, 233, 234, 235, 243, 247, 248, 249, 271, 272, 274, 286, 287, 291, 292, 293, 1717, 1761, 1764, 1863, 1935, 2026, 2108, 2109, 2130, 2131, 2135, 2300, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 72, 73, 130, 131, 132, 141, 177, 180, 221, 223, 225, 229, 230, 231, 233, 235, 244, 245, 246, 248, 250, 272, 273, 274, 284, 285, 287, 288, 290, 292, 293, 294, 295, 296, 1717, 1761, 1762, 1763, 1765, 1766, 1839, 1840, 1852, 1863, 1865, 1866, 1867, 1990, 1992, 2026, 2030, 2129, 2132, 2133, 2134, 2135, 2136, 2138, 2139, 2194, 2223, 2225, 2226, 2257, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 140, 142, 143, 175, 227, 234, 236, 243, 247, 249, 271, 281, 282, 283, 286, 289, 291, 1716, 1718, 1760, 1764, 1838, 1864, 1935, 1991, 2108, 2109, 2128, 2130, 2131, 2137, 2222, 2300, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 32, 34, 35, 149, 150, 152, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1897, 1898, 1900, 2056, 2058, 2177, 2179, 2279, 2288, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 33, 148, 151, 1654, 1693, 1752, 1826, 1827, 2054, 2227, 2229, 2231, 2281, 2282, 2283, 2289, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 33, 34, 35, 150, 151, 1653, 1655, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1757, 1773, 1824, 1825, 1827, 1898, 1900, 2058, 2177, 2229, 2231, 2279, 2281, 2282, 2288, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 148, 149, 152, 1652, 1654, 1691, 1693, 1756, 1771, 1772, 1774, 1826, 1897, 2054, 2056, 2179, 2227, 2283, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 33, 34, 35, 150, 151, 1652, 1653, 1655, 1691, 1750, 1751, 1755, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1827, 1897, 2054, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 148, 149, 152, 1654, 1692, 1693, 1752, 1753, 1754, 1756, 1826, 1898, 1900, 2056, 2058, 2229, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 228, 275, 276, 277, 278, 279, 1722, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2119, 2120, 2121, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 224, 226, 280, 1719, 1720, 1721, 1727, 1868, 2027, 2124, 2125, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 275, 276, 280, 1719, 1721, 1727, 1775, 1776, 1777, 1779, 1870, 2027, 2119, 2120, 2124, 2125, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(226, 228, 277, 278, 279, 1720, 1722, 1778, 1868, 1869, 2121, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 222, 224, 226, 228, 276, 277, 278, 1719, 1720, 1721, 1722, 1775, 1776, 1777, 1868, 1869, 1870, 2027, 2124, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 275, 279, 280, 1727, 1778, 1779, 2119, 2120, 2121, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 206, 210, 212, 214, 215, 216, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 205, 207, 208, 209, 211, 213, 217)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 206, 208, 209, 210, 211, 212, 213, 217, 218, 220, 265, 266, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 205, 207, 214, 215, 216, 219, 267, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 205, 207, 208, 211, 212, 213, 214, 215, 216, 217, 218, 219, 265, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 206, 209, 210, 220, 266, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 73, 130, 132, 140, 141, 143, 175, 177, 221, 223, 225, 235, 236, 244, 245, 246, 247, 248, 249, 250, 273, 281, 282, 283, 284, 285, 286, 289, 290, 295, 296, 1716, 1717, 1763, 1764, 1766, 1838, 1839, 1840, 1852, 1863, 1865, 1866, 1935, 1990, 1991, 2026, 2108, 2109, 2128, 2129, 2130, 2131, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2257, 2301, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 131, 142, 180, 227, 229, 230, 231, 233, 234, 243, 271, 272, 274, 287, 288, 291, 292, 293, 294, 1718, 1760, 1761, 1762, 1765, 1864, 1867, 1992, 2030, 2132, 2222, 2300, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 72, 73, 130, 131, 132, 140, 142, 143, 177, 180, 221, 223, 230, 231, 233, 236, 245, 246, 247, 249, 272, 273, 274, 281, 282, 285, 286, 287, 288, 290, 291, 292, 293, 294, 296, 1716, 1717, 1760, 1762, 1763, 1765, 1838, 1839, 1840, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2108, 2130, 2133, 2134, 2135, 2136, 2138, 2139, 2222, 2225, 2257, 2300, 2301, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 141, 175, 225, 227, 229, 234, 235, 243, 244, 248, 250, 271, 283, 284, 289, 295, 1718, 1761, 1764, 1766, 1852, 2030, 2109, 2128, 2129, 2131, 2132, 2137, 2194, 2223, 2226, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 131, 132, 141, 142, 143, 177, 180, 223, 225, 227, 230, 231, 233, 234, 243, 244, 245, 246, 248, 249, 272, 273, 281, 283, 284, 285, 286, 287, 288, 290, 291, 295, 296, 1717, 1718, 1760, 1762, 1765, 1766, 1838, 1840, 1852, 1863, 1864, 1865, 1867, 1990, 1992, 2026, 2108, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2135, 2136, 2138, 2139, 2194, 2222, 2223, 2226, 2257, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 72, 73, 130, 140, 175, 221, 229, 235, 236, 247, 250, 271, 274, 282, 289, 292, 293, 294, 1716, 1761, 1763, 1764, 1839, 1866, 1935, 1991, 2030, 2131, 2137, 2225, 2300, 2302, 2312, 2313)</t>
+    <t xml:space="preserve">c(15, 71, 130, 132, 140, 142, 143, 177, 223, 225, 230, 231, 234, 235, 236, 244, 245, 246, 247, 248, 272, 273, 274, 281, 283, 284, 285, 287, 288, 289, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1766, 1838, 1840, 1852, 1865, 1935, 1990, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2134, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 72, 73, 131, 141, 175, 180, 221, 227, 229, 233, 243, 249, 250, 271, 282, 286, 290, 291, 292, 1762, 1765, 1839, 1863, 1864, 1866, 1867, 1991, 1992, 2026, 2133, 2135, 2136, 2222, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 71, 72, 73, 130, 132, 143, 177, 221, 225, 227, 229, 230, 233, 235, 236, 243, 244, 246, 248, 249, 250, 271, 272, 273, 283, 285, 286, 287, 288, 289, 290, 291, 292, 295, 296, 1716, 1717, 1718, 1761, 1762, 1763, 1764, 1766, 1838, 1852, 1867, 1990, 1991, 1992, 2026, 2030, 2109, 2128, 2129, 2131, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2257, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 131, 140, 141, 142, 175, 180, 223, 231, 234, 245, 247, 274, 281, 282, 284, 293, 294, 1760, 1765, 1839, 1840, 1863, 1864, 1865, 1866, 1935, 2108, 2130, 2135, 2226, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 33, 34, 149, 150, 151, 152, 1652, 1653, 1692, 1750, 1751, 1752, 1753, 1755, 1756, 1771, 1772, 1773, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2282, 2283, 2289, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 32, 35, 148, 1654, 1655, 1691, 1693, 1754, 1757, 1774, 2054, 2179, 2231, 2279, 2281, 2288, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 33, 34, 35, 148, 149, 150, 151, 152, 1653, 1654, 1691, 1693, 1750, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1824, 1826, 1898, 1900, 2058, 2179, 2227, 2229, 2279, 2281, 2288, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 32, 1652, 1655, 1692, 1751, 1772, 1773, 1825, 1827, 1897, 2054, 2056, 2177, 2231, 2282, 2283, 2289, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 31, 32, 33, 35, 148, 149, 150, 151, 1654, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1773, 1824, 1825, 1826, 1827, 1900, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2288, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 34, 152, 1652, 1653, 1655, 1692, 1693, 1757, 1772, 1774, 1897, 1898, 2054, 2281, 2282, 2283, 2289, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 226, 275, 279, 280, 1720, 1721, 1722, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 224, 228, 276, 277, 278, 1719, 1727, 1775, 1776, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 224, 226, 228, 277, 1721, 1722, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2027, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 275, 276, 278, 279, 280, 1719, 1720, 1727, 1777, 2119)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 224, 226, 275, 276, 278, 1719, 1720, 1722, 1776, 1777, 1779, 1868, 1869, 1870, 2119, 2121, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 222, 228, 277, 279, 280, 1721, 1727, 1775, 1778, 2027, 2120, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 206, 207, 208, 209, 210, 213, 214, 215, 216, 218, 219, 265, 266, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 211, 212, 217, 220, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 205, 206, 207, 208, 209, 210, 214, 215, 216, 217, 218, 219, 220, 266, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 204, 211, 212, 213, 265, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 206, 209, 211, 212, 213, 214, 216, 217, 219, 220, 265, 266, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 207, 208, 210, 215, 218, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 140, 141, 142, 143, 175, 221, 225, 227, 229, 230, 233, 243, 245, 246, 247, 249, 272, 273, 274, 287, 290, 292, 293, 294, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1765, 1766, 1838, 1840, 1864, 1865, 1867, 1935, 1990, 1991, 1992, 2026, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 130, 131, 132, 177, 180, 223, 231, 234, 235, 236, 244, 248, 250, 271, 281, 282, 283, 284, 285, 286, 288, 289, 291, 295, 1763, 1764, 1839, 1852, 1863, 1866, 2030, 2108, 2131, 2135, 2225)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 130, 132, 141, 142, 143, 175, 177, 180, 221, 223, 227, 229, 230, 231, 234, 244, 246, 247, 249, 271, 273, 274, 281, 282, 283, 284, 286, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1762, 1763, 1765, 1838, 1840, 1852, 1863, 1865, 1866, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2137, 2139, 2194, 2222, 2226, 2257, 2300, 2301, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 131, 140, 225, 233, 235, 236, 243, 245, 248, 250, 272, 285, 287, 288, 1718, 1761, 1764, 1766, 1839, 1864, 1867, 1935, 1990, 1991, 2131, 2135, 2136, 2138, 2223, 2225, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 131, 140, 142, 175, 177, 180, 223, 225, 227, 231, 233, 234, 235, 236, 244, 245, 247, 248, 249, 250, 271, 273, 281, 284, 285, 286, 291, 292, 294, 295, 1716, 1718, 1760, 1761, 1763, 1764, 1765, 1766, 1839, 1840, 1863, 1864, 1865, 1867, 1990, 1992, 2026, 2030, 2108, 2109, 2129, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2223, 2226, 2257, 2300, 2301, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 130, 132, 141, 143, 221, 229, 230, 243, 246, 272, 274, 282, 283, 287, 288, 289, 290, 293, 296, 1717, 1762, 1838, 1852, 1866, 1935, 1991, 2128, 2130, 2136, 2222, 2225, 2302, 2303, 2312)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 20, 31, 32, 35, 148, 150, 151, 152, 1692, 1693, 1750, 1753, 1756, 1897, 1900, 2054, 2058, 2227, 2229, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 33, 34, 149, 1691, 1751, 1752, 1754, 1755, 1757, 1898, 2056, 2231, 2279)</t>
+    <t xml:space="preserve">c(17, 18, 19, 23, 34, 149, 150, 151, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1757, 1897, 1898, 1900, 2058, 2227, 2229, 2231, 2279, 2282, 2283, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 32, 33, 35, 148, 152, 1756, 2054, 2056, 2281, 2288, 2289, 2293, 2294, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 148, 149, 150, 151, 152, 1691, 1692, 1750, 1754, 1755, 1757, 1897, 1898, 2054, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(31, 33, 34, 35, 1693, 1751, 1752, 1753, 1756, 1900, 2056, 2283, 2288, 2289, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 150, 1691, 1692, 1693, 1750, 1752, 1754, 1755, 1756, 1898, 2054, 2056, 2227, 2229, 2231, 2279, 2282, 2283, 2289, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(35, 148, 149, 151, 152, 1751, 1753, 1757, 1897, 1900, 2058, 2281, 2288, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1721, 1722, 1775, 1776, 1868, 1869, 2027, 2121, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 1719, 1720, 1727, 1777, 1778, 1779, 1870, 2119, 2120, 2124, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 224, 226, 228, 277, 278, 280, 1721, 1722, 1727, 1775, 1777, 1779, 1868, 1869, 1870, 2119, 2120, 2121, 2124, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 222, 275, 276, 279, 1719, 1720, 1776, 1778, 2027, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 224, 226, 276, 278, 279, 280, 1719, 1721, 1722, 1727, 1775, 1776, 1777, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 222, 228, 275, 277, 1720, 1778, 1779, 2124, 2125, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 268)</t>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 35, 148, 150, 152, 1691, 1692, 1693, 1752, 1754, 1755, 1757, 1897, 1900, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 32, 34, 149, 151, 1750, 1751, 1753, 1756, 1898, 2054, 2283, 2288, 2289, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 31, 33, 35, 148, 150, 151, 152, 1691, 1750, 1753, 1755, 1756, 1757, 1897, 1898, 2054, 2058, 2227, 2231, 2279, 2281, 2282, 2283, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 32, 34, 149, 1692, 1693, 1751, 1752, 1754, 1900, 2056, 2229, 2288, 2289, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 224, 226, 228, 277, 279, 280, 1719, 1720, 1721, 1775, 1778, 1779, 1868, 1869, 1870, 2119, 2120, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 222, 275, 276, 278, 1722, 1727, 1776, 1777, 2027, 2121, 2124, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 224, 228, 277, 278, 279, 280, 1719, 1721, 1722, 1727, 1776, 1778, 1779, 1869, 2027, 2119, 2120, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 222, 226, 275, 276, 1720, 1775, 1777, 1868, 1870, 2121, 2124, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 224, 228, 275, 279, 280, 1720, 1722, 1776, 1777, 1778, 1779, 1869, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 222, 226, 276, 277, 278, 1719, 1721, 1727, 1775, 1868, 1870, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 266, 2230)</t>
   </si>
   <si>
     <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(266, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 72, 73, 130, 140, 141, 143, 177, 221, 223, 225, 227, 229, 230, 231, 234, 235, 243, 244, 245, 246, 248, 250, 272, 274, 281, 282, 284, 286, 289, 290, 291, 292, 293, 294, 295, 296, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1839, 1863, 1864, 1865, 1866, 1867, 1991, 1992, 2030, 2128, 2129, 2132, 2133, 2135, 2136, 2138, 2223, 2225, 2226, 2257, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 131, 132, 142, 233, 236, 247, 249, 271, 273, 283, 285, 287, 288, 1716, 1717, 1838, 1840, 1852, 1935, 1990, 2026, 2130, 2131, 2134, 2137, 2139, 2194, 2222, 2300, 2301, 2303, 2313)</t>
+    <t xml:space="preserve">c(265, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 132, 140, 141, 177, 221, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 246, 248, 271, 272, 274, 281, 282, 284, 285, 287, 288, 291, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1990, 1992, 2026, 2128, 2130, 2133, 2134, 2135, 2136, 2194, 2222, 2223, 2226, 2300, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 130, 131, 142, 143, 223, 225, 245, 247, 249, 250, 273, 283, 286, 289, 290, 1716, 1840, 1867, 1935, 1991, 2030, 2129, 2131, 2132, 2137, 2138, 2139, 2225, 2257, 2301, 2302, 2303)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(15, 70, 71, 73, 130, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 231, 233, 234, 235, 245, 247, 250, 271, 272, 281, 282, 284, 285, 286, 287, 288, 289, 290, 291, 292, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1839, 1840, 1863, 1864, 1865, 1866, 1867, 1992, 2030, 2128, 2131, 2134, 2135, 2136, 2222, 2223, 2225, 2226, 2257, 2300, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 72, 131, 230, 236, 243, 244, 246, 248, 249, 273, 274, 283, 293, 294, 296, 1766, 1838, 1852, 1935, 1990, 1991, 2026, 2129, 2130, 2132, 2133, 2137, 2138, 2139, 2194, 2301, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 140, 141, 142, 177, 225, 227, 231, 233, 234, 235, 243, 246, 247, 249, 250, 271, 273, 274, 281, 284, 285, 286, 287, 288, 289, 291, 292, 293, 295, 296, 1716, 1718, 1760, 1761, 1764, 1765, 1766, 1840, 1852, 1865, 1867, 1935, 1992, 2026, 2030, 2128, 2129, 2131, 2135, 2136, 2137, 2139, 2194, 2223, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 132, 143, 221, 223, 229, 230, 236, 244, 245, 248, 272, 282, 283, 290, 294, 1717, 1762, 1763, 1838, 1839, 1863, 1864, 1866, 1990, 1991, 2130, 2132, 2133, 2134, 2138, 2222, 2225, 2257)</t>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 141, 143, 223, 225, 227, 229, 231, 234, 243, 244, 245, 246, 247, 249, 250, 272, 273, 274, 281, 282, 284, 286, 288, 289, 290, 291, 293, 294, 1716, 1717, 1760, 1763, 1765, 1766, 1838, 1839, 1840, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 2128, 2129, 2132, 2133, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 131, 132, 140, 142, 177, 221, 230, 233, 235, 236, 248, 271, 283, 285, 287, 292, 295, 296, 1718, 1761, 1762, 1764, 1852, 1935, 1992, 2026, 2030, 2130, 2131, 2134, 2135, 2138, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 73, 130, 131, 141, 143, 221, 227, 229, 230, 231, 234, 236, 243, 244, 245, 246, 247, 248, 249, 271, 272, 273, 274, 281, 282, 284, 285, 286, 287, 289, 292, 293, 296, 1761, 1763, 1764, 1765, 1766, 1839, 1840, 1863, 1865, 1867, 1935, 1990, 1991, 1992, 2128, 2129, 2130, 2131, 2134, 2135, 2136, 2137, 2138, 2194, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 132, 140, 142, 177, 223, 225, 233, 235, 250, 283, 288, 290, 291, 294, 295, 1716, 1717, 1718, 1760, 1762, 1838, 1852, 1864, 1866, 2026, 2030, 2132, 2133, 2139, 2222, 2223, 2257)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 149, 150, 151, 152, 1692, 1693, 1752, 1754, 1755, 1757, 1898, 1900, 2054, 2056, 2058, 2227, 2283, 2288, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(35, 148, 1691, 1750, 1751, 1753, 1756, 1897, 2229, 2231, 2279, 2281, 2282, 2289, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 31, 32, 35, 149, 150, 152, 1691, 1751, 1752, 1753, 1754, 1757, 1897, 1898, 1900, 2054, 2056, 2227, 2231, 2279, 2281, 2282, 2288, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 33, 34, 148, 151, 1692, 1693, 1750, 1755, 1756, 2058, 2229, 2283, 2289, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 31, 33, 34, 148, 149, 150, 151, 1691, 1693, 1750, 1751, 1752, 1753, 1756, 1757, 1900, 2054, 2056, 2058, 2227, 2229, 2281, 2282, 2288, 2289, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 32, 35, 152, 1692, 1754, 1755, 1897, 1898, 2231, 2279, 2283, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1777, 1779, 1868, 1869, 2119, 2120, 2124, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 224, 226, 228, 1776, 1778, 1870, 2027, 2121, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 279, 280, 1720, 1721, 1722, 1727, 1776, 1779, 1869, 1870, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(228, 275, 276, 277, 278, 1719, 1775, 1777, 1778, 1868, 2027, 2119, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 222, 224, 226, 228, 276, 277, 278, 280, 1720, 1722, 1727, 1775, 1776, 1868, 2027, 2119, 2120, 2121, 2124, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 275, 279, 1719, 1721, 1777, 1778, 1779, 1869, 1870, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265:267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 266, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 72, 73, 130, 141, 177, 223, 225, 227, 230, 231, 233, 234, 236, 243, 244, 245, 248, 250, 272, 273, 281, 282, 283, 284, 285, 289, 290, 291, 293, 294, 296, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1766, 1838, 1839, 1840, 1863, 1864, 1865, 1866, 1935, 1990, 1991, 2026, 2030, 2128, 2129, 2132, 2133, 2134, 2135, 2136, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 131, 132, 140, 142, 143, 221, 229, 235, 246, 247, 249, 271, 274, 286, 287, 288, 292, 295, 1762, 1765, 1852, 1867, 1992, 2130, 2131, 2137, 2138, 2139, 2194, 2223, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 132, 140, 141, 177, 221, 223, 231, 233, 234, 235, 236, 245, 246, 247, 248, 249, 250, 271, 273, 281, 282, 283, 284, 285, 286, 287, 288, 289, 292, 293, 294, 296, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1839, 1852, 1863, 1865, 1866, 1867, 1992, 2026, 2129, 2130, 2131, 2133, 2135, 2137, 2139, 2194, 2223, 2225, 2226, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 131, 142, 143, 225, 227, 229, 230, 243, 244, 272, 274, 290, 291, 295, 1716, 1838, 1840, 1864, 1935, 1990, 1991, 2030, 2128, 2132, 2134, 2136, 2138, 2222, 2257, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 73, 130, 131, 140, 141, 142, 143, 177, 223, 229, 231, 233, 234, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 281, 283, 284, 285, 286, 288, 289, 293, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1838, 1839, 1863, 1864, 1865, 1935, 1990, 1992, 2026, 2030, 2128, 2129, 2130, 2134, 2137, 2194, 2257, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 132, 221, 225, 227, 230, 235, 273, 274, 282, 287, 290, 291, 292, 1717, 1766, 1840, 1852, 1866, 1867, 1991, 2131, 2132, 2133, 2135, 2136, 2138, 2139, 2222, 2223, 2225, 2226, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 19, 23, 31, 32, 33, 34, 35, 148, 150, 151, 1691, 1692, 1750, 1752, 1755, 1756, 1897, 1898, 1900, 2054, 2058, 2227, 2282, 2283, 2288, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 149, 152, 1693, 1751, 1753, 1754, 1757, 2056, 2229, 2231, 2279, 2281, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 32, 33, 34, 35, 148, 150, 151, 1691, 1692, 1693, 1750, 1751, 1754, 1755, 1898, 2054, 2056, 2058, 2227, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 31, 149, 152, 1752, 1753, 1756, 1757, 1897, 1900, 2229, 2231, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1693, 1750, 1752, 1754, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 31, 1691, 1692, 1751, 1753, 1755, 1756, 1757, 1897, 2281, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 275, 276, 277, 278, 279, 1719, 1720, 1721, 1722, 1727, 1776, 1778, 1779, 1868, 2120, 2121, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 228, 280, 1775, 1777, 1869, 1870, 2027, 2119, 2124, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 226, 276, 278, 279, 280, 1721, 1722, 1727, 1775, 1777, 1778, 1779, 1870, 2027, 2120, 2124, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 228, 275, 277, 1719, 1720, 1776, 1868, 1869, 2119, 2121, 2125, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 276, 277, 278, 279, 280, 1719, 1720, 1722, 1727, 1775, 1776, 1777, 1779, 1868, 1870, 2027, 2119, 2124, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 224, 226, 228, 275, 1721, 1778, 1869, 2120, 2121, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265:268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 131, 132, 141, 143, 177, 223, 225, 227, 229, 230, 231, 233, 234, 235, 243, 245, 247, 248, 249, 271, 281, 282, 284, 285, 286, 288, 289, 290, 292, 293, 294, 295, 1716, 1717, 1718, 1763, 1764, 1766, 1839, 1852, 1863, 1864, 1865, 1935, 1990, 1992, 2026, 2030, 2131, 2132, 2134, 2136, 2138, 2139, 2194, 2222, 2223, 2226, 2257, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 140, 142, 221, 236, 244, 246, 250, 272, 273, 274, 283, 287, 291, 296, 1760, 1761, 1762, 1765, 1838, 1840, 1866, 1867, 1991, 2128, 2129, 2130, 2133, 2135, 2137, 2225, 2300, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 71, 73, 130, 131, 141, 177, 221, 223, 225, 227, 231, 233, 235, 244, 245, 246, 247, 250, 271, 272, 281, 282, 283, 284, 285, 286, 287, 289, 291, 292, 294, 295, 1716, 1717, 1718, 1760, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2030, 2128, 2129, 2130, 2132, 2133, 2134, 2139, 2222, 2223, 2225, 2257, 2300, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 72, 132, 140, 142, 143, 229, 230, 234, 236, 243, 248, 249, 273, 274, 288, 290, 293, 296, 1761, 1863, 1864, 2026, 2131, 2135, 2136, 2137, 2138, 2194, 2226, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 73, 131, 132, 140, 141, 177, 223, 225, 229, 233, 234, 236, 243, 244, 245, 246, 248, 249, 250, 271, 272, 273, 284, 285, 286, 287, 288, 289, 292, 293, 294, 296, 1760, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1864, 1867, 1935, 1992, 2026, 2030, 2128, 2129, 2130, 2133, 2134, 2135, 2136, 2137, 2194, 2225, 2257, 2300, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 130, 142, 143, 221, 227, 230, 231, 235, 247, 274, 281, 282, 283, 290, 291, 295, 1716, 1717, 1718, 1762, 1852, 1865, 1866, 1990, 1991, 2131, 2132, 2138, 2139, 2222, 2223, 2226, 2303)</t>
+    <t xml:space="preserve">c(17, 19, 23, 32, 34, 35, 1691, 1692, 1750, 1751, 1753, 1754, 1755, 1771, 1772, 1774, 1824, 1825, 1826, 1827, 2058, 2177, 2179, 2289, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 31, 33, 1693, 1752, 1756, 1757, 1773, 2054, 2056, 2288, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 32, 33, 34, 35, 1691, 1692, 1750, 1752, 1753, 1755, 1756, 1757, 1772, 1773, 1824, 1825, 1827, 2054, 2056, 2177, 2179, 2288, 2289, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 1693, 1751, 1754, 1771, 1774, 1826, 2058, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 31, 32, 33, 34, 35, 1691, 1750, 1751, 1752, 1754, 1756, 1757, 1771, 1772, 1774, 1825, 1826, 2054, 2056, 2179, 2289, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 1692, 1693, 1753, 1755, 1773, 1824, 1827, 2058, 2177, 2288, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 175, 180, 230, 233, 234, 236, 271, 272, 273, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 177, 229, 231, 235, 274, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 175, 177, 230, 231, 233, 234, 272, 274, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 180, 229, 235, 236, 271, 273, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 175, 229, 231, 234, 235, 236, 272, 273, 274, 1764, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 177, 180, 230, 233, 271, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1753, 1756, 1757, 1774, 1826, 2054, 2058, 2177, 2288, 2289, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 1752, 1754, 1755, 1771, 1772, 1773, 1824, 1825, 1827, 2056, 2179, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 31, 32, 33, 34, 1691, 1693, 1752, 1755, 1757, 1772, 1774, 1826, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 35, 1692, 1750, 1751, 1753, 1754, 1756, 1771, 1773, 1824, 1825, 1827)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 32, 33, 35, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 31, 34, 1691, 1772, 1825, 2288, 2289, 2290, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 175, 177, 180, 229, 230, 231, 233, 235, 236, 271, 273, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 234, 272, 274, 1764, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 177, 180, 229, 230, 233, 234, 273, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 175, 231, 235, 236, 271, 272, 274)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 175, 177, 229, 233, 234, 235, 236, 271, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 180, 230, 231, 272, 273, 274, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 34, 1691, 1692, 1693, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1774, 1825, 1826, 1827, 2054, 2177, 2288, 2289, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 32, 33, 35, 1750, 1751, 1773, 1824, 2056, 2058, 2179, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 31, 33, 35, 1691, 1692, 1693, 1750, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 2054, 2179, 2289, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 32, 34, 1751, 1752, 1753, 1827, 2056, 2058, 2177, 2288, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 31, 32, 35, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1772, 1774, 1824, 1827, 2054, 2177, 2179, 2288, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 33, 34, 1692, 1755, 1757, 1773, 1825, 1826, 2056, 2058, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 177, 180, 229, 233, 235, 271, 273, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(175, 230, 231, 234, 236, 272, 274, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 230, 233, 236, 271, 273, 274, 1764, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 229, 231, 234, 235, 272, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 177, 180, 230, 231, 234, 236, 273, 274, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 175, 229, 233, 235, 271, 272, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1773, 1824, 1825, 1826, 1827, 2058, 2179, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 1753, 1757, 1771, 1772, 1774, 2054, 2056, 2177, 2288, 2289, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 35, 1693, 1750, 1752, 1755, 1756, 1757, 1772, 1773, 1824, 1826, 1827, 2054, 2058, 2177, 2179, 2288, 2289, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 34, 1691, 1692, 1751, 1753, 1754, 1771, 1774, 1825, 2056, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 33, 34, 1692, 1693, 1752, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1827, 2054, 2056, 2179, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 31, 32, 35, 1691, 1750, 1751, 1754, 1825, 1826, 2058, 2177, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 177, 230, 231, 234, 235, 271, 272, 274, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 175, 180, 229, 233, 236, 273, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 175, 180, 230, 233, 235, 236, 272, 274, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 177, 229, 231, 234, 271, 273, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 175, 177, 229, 231, 233, 234, 235, 271, 272, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 180, 230, 236, 273, 274, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 35, 1691, 1692, 1751, 1752, 1753, 1754, 2054, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(33, 34, 1693, 1750, 1755, 1756, 1757, 2056, 2058, 2288, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 35, 1692, 1751, 1752, 1756, 1757, 2056, 2058, 2288, 2289, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 1691, 1693, 1750, 1753, 1754, 1755, 2054, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 32, 34, 35, 1691, 1692, 1751, 1753, 1754, 1755, 1756, 2054, 2058, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 33, 1693, 1750, 1752, 1757, 2056, 2288, 2289, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 180, 229, 230, 231, 233, 235, 236, 272, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 175, 177, 234, 271, 273, 274, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 177, 180, 229, 230, 231, 234, 235, 273, 274, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 175, 233, 236, 271, 272)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 175, 180, 229, 230, 234, 235, 273, 274, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 177, 231, 233, 236, 271, 272, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 31, 32, 33, 34, 1691, 1692, 1693, 1751, 1752, 1754, 1757, 2054, 2056, 2058, 2289, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 35, 1750, 1753, 1755, 1756, 2288, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 31, 32, 34, 1691, 1692, 1750, 1753, 1755, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 33, 35, 1693, 1751, 1752, 1754, 1756, 1757, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 31, 33, 34, 35, 1692, 1750, 1752, 1753, 1755, 1756, 2054, 2056, 2288, 2289, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 32, 1691, 1693, 1751, 1754, 1757, 2058, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 175, 180, 229, 234, 235, 236, 271, 272, 273, 274, 1764, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 177, 230, 231, 233, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 175, 180, 229, 230, 233, 234, 235, 271, 272, 273, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 177, 231, 236, 274, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 175, 180, 229, 230, 231, 234, 236, 273, 1764, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 177, 233, 235, 271, 272, 274, 1765)</t>
   </si>
 </sst>
 </file>
@@ -2294,19 +2522,19 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
         <v>62</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="s">
-        <v>63</v>
       </c>
       <c r="N17" t="n">
         <v>27</v>
       </c>
       <c r="O17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P17" t="n">
         <v>14</v>
@@ -2350,19 +2578,19 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N18" t="n">
         <v>27</v>
       </c>
       <c r="O18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P18" t="n">
         <v>14</v>
@@ -2406,19 +2634,19 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N19" t="n">
         <v>27</v>
       </c>
       <c r="O19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P19" t="n">
         <v>14</v>
@@ -2453,7 +2681,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2468,13 +2696,13 @@
         <v>1</v>
       </c>
       <c r="M20" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18</v>
+      </c>
+      <c r="O20" t="s">
         <v>70</v>
-      </c>
-      <c r="N20" t="n">
-        <v>18</v>
-      </c>
-      <c r="O20" t="s">
-        <v>71</v>
       </c>
       <c r="P20" t="n">
         <v>9</v>
@@ -2509,7 +2737,7 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2524,13 +2752,13 @@
         <v>2</v>
       </c>
       <c r="M21" t="s">
+        <v>71</v>
+      </c>
+      <c r="N21" t="n">
+        <v>18</v>
+      </c>
+      <c r="O21" t="s">
         <v>72</v>
-      </c>
-      <c r="N21" t="n">
-        <v>18</v>
-      </c>
-      <c r="O21" t="s">
-        <v>73</v>
       </c>
       <c r="P21" t="n">
         <v>9</v>
@@ -2565,7 +2793,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -2580,13 +2808,13 @@
         <v>3</v>
       </c>
       <c r="M22" t="s">
+        <v>73</v>
+      </c>
+      <c r="N22" t="n">
+        <v>18</v>
+      </c>
+      <c r="O22" t="s">
         <v>74</v>
-      </c>
-      <c r="N22" t="n">
-        <v>18</v>
-      </c>
-      <c r="O22" t="s">
-        <v>75</v>
       </c>
       <c r="P22" t="n">
         <v>9</v>
@@ -2621,28 +2849,28 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
         <v>76</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="s">
-        <v>62</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="s">
-        <v>77</v>
       </c>
       <c r="N23" t="n">
         <v>79</v>
       </c>
       <c r="O23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P23" t="n">
         <v>40</v>
@@ -2677,7 +2905,7 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -2686,19 +2914,19 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
       </c>
       <c r="M24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N24" t="n">
         <v>79</v>
       </c>
       <c r="O24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P24" t="n">
         <v>40</v>
@@ -2733,7 +2961,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -2742,19 +2970,19 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
       </c>
       <c r="M25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N25" t="n">
         <v>79</v>
       </c>
       <c r="O25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P25" t="n">
         <v>40</v>
@@ -2798,19 +3026,19 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
+        <v>82</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
         <v>83</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="s">
-        <v>84</v>
       </c>
       <c r="N26" t="n">
         <v>40</v>
       </c>
       <c r="O26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P26" t="n">
         <v>20</v>
@@ -2854,19 +3082,19 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
       </c>
       <c r="M27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P27" t="n">
         <v>20</v>
@@ -2910,19 +3138,19 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N28" t="n">
         <v>40</v>
       </c>
       <c r="O28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P28" t="n">
         <v>20</v>
@@ -2966,19 +3194,19 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
+        <v>89</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
         <v>90</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="s">
-        <v>91</v>
       </c>
       <c r="N29" t="n">
         <v>27</v>
       </c>
       <c r="O29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P29" t="n">
         <v>14</v>
@@ -3022,19 +3250,19 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
       </c>
       <c r="M30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N30" t="n">
         <v>27</v>
       </c>
       <c r="O30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P30" t="n">
         <v>14</v>
@@ -3078,19 +3306,19 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N31" t="n">
         <v>27</v>
       </c>
       <c r="O31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P31" t="n">
         <v>14</v>
@@ -3134,19 +3362,19 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="s">
+        <v>96</v>
+      </c>
+      <c r="N32" t="n">
+        <v>18</v>
+      </c>
+      <c r="O32" t="s">
         <v>97</v>
-      </c>
-      <c r="N32" t="n">
-        <v>18</v>
-      </c>
-      <c r="O32" t="s">
-        <v>98</v>
       </c>
       <c r="P32" t="n">
         <v>9</v>
@@ -3190,19 +3418,19 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
       </c>
       <c r="M33" t="s">
+        <v>98</v>
+      </c>
+      <c r="N33" t="n">
+        <v>18</v>
+      </c>
+      <c r="O33" t="s">
         <v>99</v>
-      </c>
-      <c r="N33" t="n">
-        <v>18</v>
-      </c>
-      <c r="O33" t="s">
-        <v>100</v>
       </c>
       <c r="P33" t="n">
         <v>9</v>
@@ -3246,19 +3474,19 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
       </c>
       <c r="M34" t="s">
+        <v>100</v>
+      </c>
+      <c r="N34" t="n">
+        <v>18</v>
+      </c>
+      <c r="O34" t="s">
         <v>101</v>
-      </c>
-      <c r="N34" t="n">
-        <v>18</v>
-      </c>
-      <c r="O34" t="s">
-        <v>102</v>
       </c>
       <c r="P34" t="n">
         <v>9</v>
@@ -3302,19 +3530,19 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N35" t="n">
         <v>79</v>
       </c>
       <c r="O35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P35" t="n">
         <v>40</v>
@@ -3358,19 +3586,19 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N36" t="n">
         <v>79</v>
       </c>
       <c r="O36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P36" t="n">
         <v>40</v>
@@ -3414,19 +3642,19 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
       </c>
       <c r="O37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P37" t="n">
         <v>40</v>
@@ -3470,19 +3698,19 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N38" t="n">
         <v>40</v>
       </c>
       <c r="O38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P38" t="n">
         <v>20</v>
@@ -3526,19 +3754,19 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N39" t="n">
         <v>40</v>
       </c>
       <c r="O39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P39" t="n">
         <v>20</v>
@@ -3582,19 +3810,19 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
       </c>
       <c r="M40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N40" t="n">
         <v>40</v>
       </c>
       <c r="O40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P40" t="n">
         <v>20</v>
@@ -3638,19 +3866,19 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N41" t="n">
         <v>27</v>
       </c>
       <c r="O41" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P41" t="n">
         <v>14</v>
@@ -3694,19 +3922,19 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
       </c>
       <c r="M42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N42" t="n">
         <v>27</v>
       </c>
       <c r="O42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P42" t="n">
         <v>14</v>
@@ -3750,19 +3978,19 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
       </c>
       <c r="M43" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N43" t="n">
         <v>27</v>
       </c>
       <c r="O43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P43" t="n">
         <v>14</v>
@@ -3797,7 +4025,7 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
@@ -3806,19 +4034,19 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N44" t="n">
         <v>18</v>
       </c>
       <c r="O44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="P44" t="n">
         <v>9</v>
@@ -3853,7 +4081,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
@@ -3862,19 +4090,19 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N45" t="n">
         <v>18</v>
       </c>
       <c r="O45" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P45" t="n">
         <v>9</v>
@@ -3909,7 +4137,7 @@
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
@@ -3918,19 +4146,19 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
       </c>
       <c r="M46" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N46" t="n">
         <v>18</v>
       </c>
       <c r="O46" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P46" t="n">
         <v>9</v>
@@ -3965,7 +4193,7 @@
         <v>2</v>
       </c>
       <c r="H47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -3974,19 +4202,19 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N47" t="n">
         <v>79</v>
       </c>
       <c r="O47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P47" t="n">
         <v>40</v>
@@ -4021,7 +4249,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -4030,19 +4258,19 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N48" t="n">
         <v>79</v>
       </c>
       <c r="O48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P48" t="n">
         <v>40</v>
@@ -4077,7 +4305,7 @@
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
@@ -4086,19 +4314,19 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
       </c>
       <c r="M49" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N49" t="n">
         <v>79</v>
       </c>
       <c r="O49" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P49" t="n">
         <v>40</v>
@@ -4142,19 +4370,19 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N50" t="n">
         <v>40</v>
       </c>
       <c r="O50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P50" t="n">
         <v>20</v>
@@ -4198,19 +4426,19 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N51" t="n">
         <v>40</v>
       </c>
       <c r="O51" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="P51" t="n">
         <v>20</v>
@@ -4254,19 +4482,19 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
       </c>
       <c r="M52" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N52" t="n">
         <v>40</v>
       </c>
       <c r="O52" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P52" t="n">
         <v>20</v>
@@ -4310,19 +4538,19 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N53" t="n">
         <v>27</v>
       </c>
       <c r="O53" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P53" t="n">
         <v>14</v>
@@ -4366,19 +4594,19 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N54" t="n">
         <v>27</v>
       </c>
       <c r="O54" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P54" t="n">
         <v>14</v>
@@ -4422,19 +4650,19 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
       </c>
       <c r="M55" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N55" t="n">
         <v>27</v>
       </c>
       <c r="O55" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P55" t="n">
         <v>14</v>
@@ -4478,19 +4706,19 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N56" t="n">
         <v>18</v>
       </c>
       <c r="O56" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P56" t="n">
         <v>9</v>
@@ -4534,19 +4762,19 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N57" t="n">
         <v>18</v>
       </c>
       <c r="O57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P57" t="n">
         <v>9</v>
@@ -4590,19 +4818,19 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
       </c>
       <c r="M58" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N58" t="n">
         <v>18</v>
       </c>
       <c r="O58" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P58" t="n">
         <v>9</v>
@@ -4646,19 +4874,19 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N59" t="n">
         <v>79</v>
       </c>
       <c r="O59" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P59" t="n">
         <v>40</v>
@@ -4702,19 +4930,19 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N60" t="n">
         <v>79</v>
       </c>
       <c r="O60" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P60" t="n">
         <v>40</v>
@@ -4758,19 +4986,19 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N61" t="n">
         <v>79</v>
       </c>
       <c r="O61" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P61" t="n">
         <v>40</v>
@@ -4814,19 +5042,19 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N62" t="n">
         <v>40</v>
       </c>
       <c r="O62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P62" t="n">
         <v>20</v>
@@ -4870,19 +5098,19 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
       </c>
       <c r="M63" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N63" t="n">
         <v>40</v>
       </c>
       <c r="O63" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P63" t="n">
         <v>20</v>
@@ -4926,19 +5154,19 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
       </c>
       <c r="M64" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N64" t="n">
         <v>40</v>
       </c>
       <c r="O64" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P64" t="n">
         <v>20</v>
@@ -4982,19 +5210,19 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N65" t="n">
         <v>27</v>
       </c>
       <c r="O65" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="P65" t="n">
         <v>14</v>
@@ -5038,19 +5266,19 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
+        <v>139</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2</v>
+      </c>
+      <c r="M66" t="s">
         <v>166</v>
-      </c>
-      <c r="L66" t="n">
-        <v>2</v>
-      </c>
-      <c r="M66" t="s">
-        <v>169</v>
       </c>
       <c r="N66" t="n">
         <v>27</v>
       </c>
       <c r="O66" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P66" t="n">
         <v>14</v>
@@ -5094,19 +5322,19 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
       </c>
       <c r="M67" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N67" t="n">
         <v>27</v>
       </c>
       <c r="O67" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P67" t="n">
         <v>14</v>
@@ -5141,7 +5369,7 @@
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I68" t="n">
         <v>3</v>
@@ -5150,19 +5378,19 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N68" t="n">
         <v>18</v>
       </c>
       <c r="O68" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P68" t="n">
         <v>9</v>
@@ -5197,7 +5425,7 @@
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I69" t="n">
         <v>3</v>
@@ -5206,19 +5434,19 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N69" t="n">
         <v>18</v>
       </c>
       <c r="O69" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P69" t="n">
         <v>9</v>
@@ -5253,7 +5481,7 @@
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I70" t="n">
         <v>3</v>
@@ -5262,19 +5490,19 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
       </c>
       <c r="M70" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="N70" t="n">
         <v>18</v>
       </c>
       <c r="O70" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P70" t="n">
         <v>9</v>
@@ -5309,7 +5537,7 @@
         <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I71" t="n">
         <v>3</v>
@@ -5318,19 +5546,19 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N71" t="n">
         <v>79</v>
       </c>
       <c r="O71" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P71" t="n">
         <v>40</v>
@@ -5365,7 +5593,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I72" t="n">
         <v>3</v>
@@ -5374,19 +5602,19 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
       </c>
       <c r="M72" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="N72" t="n">
         <v>79</v>
       </c>
       <c r="O72" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P72" t="n">
         <v>40</v>
@@ -5421,7 +5649,7 @@
         <v>2</v>
       </c>
       <c r="H73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I73" t="n">
         <v>3</v>
@@ -5430,19 +5658,19 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
       </c>
       <c r="M73" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="N73" t="n">
         <v>79</v>
       </c>
       <c r="O73" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P73" t="n">
         <v>40</v>
@@ -5486,19 +5714,19 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="N74" t="n">
         <v>40</v>
       </c>
       <c r="O74" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P74" t="n">
         <v>20</v>
@@ -5542,19 +5770,19 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
+        <v>182</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" t="s">
         <v>185</v>
-      </c>
-      <c r="L75" t="n">
-        <v>2</v>
-      </c>
-      <c r="M75" t="s">
-        <v>188</v>
       </c>
       <c r="N75" t="n">
         <v>40</v>
       </c>
       <c r="O75" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P75" t="n">
         <v>20</v>
@@ -5598,19 +5826,19 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
       </c>
       <c r="M76" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="N76" t="n">
         <v>40</v>
       </c>
       <c r="O76" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P76" t="n">
         <v>20</v>
@@ -5654,28 +5882,28 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N77" t="n">
         <v>13</v>
       </c>
       <c r="O77" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P77" t="n">
         <v>7</v>
       </c>
       <c r="Q77" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R77" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78">
@@ -5710,28 +5938,28 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N78" t="n">
         <v>13</v>
       </c>
       <c r="O78" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P78" t="n">
         <v>7</v>
       </c>
       <c r="Q78" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R78" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79">
@@ -5766,28 +5994,28 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N79" t="n">
         <v>13</v>
       </c>
       <c r="O79" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P79" t="n">
         <v>7</v>
       </c>
       <c r="Q79" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R79" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80">
@@ -5822,19 +6050,19 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N80" t="n">
         <v>18</v>
       </c>
       <c r="O80" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P80" t="n">
         <v>9</v>
@@ -5878,19 +6106,19 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
       </c>
       <c r="M81" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N81" t="n">
         <v>18</v>
       </c>
       <c r="O81" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P81" t="n">
         <v>9</v>
@@ -5934,19 +6162,19 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
       </c>
       <c r="M82" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N82" t="n">
         <v>18</v>
       </c>
       <c r="O82" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P82" t="n">
         <v>9</v>
@@ -5990,28 +6218,28 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N83" t="n">
         <v>46</v>
       </c>
       <c r="O83" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P83" t="n">
         <v>24</v>
       </c>
       <c r="Q83" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R83" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84">
@@ -6046,28 +6274,28 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N84" t="n">
         <v>46</v>
       </c>
       <c r="O84" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P84" t="n">
         <v>24</v>
       </c>
       <c r="Q84" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R84" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85">
@@ -6102,28 +6330,28 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N85" t="n">
         <v>46</v>
       </c>
       <c r="O85" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P85" t="n">
         <v>24</v>
       </c>
       <c r="Q85" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R85" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86">
@@ -6158,19 +6386,19 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="N86" t="n">
         <v>40</v>
       </c>
       <c r="O86" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P86" t="n">
         <v>20</v>
@@ -6214,19 +6442,19 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
+        <v>182</v>
+      </c>
+      <c r="L87" t="n">
+        <v>2</v>
+      </c>
+      <c r="M87" t="s">
         <v>212</v>
-      </c>
-      <c r="L87" t="n">
-        <v>2</v>
-      </c>
-      <c r="M87" t="s">
-        <v>215</v>
       </c>
       <c r="N87" t="n">
         <v>40</v>
       </c>
       <c r="O87" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P87" t="n">
         <v>20</v>
@@ -6270,19 +6498,19 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
       </c>
       <c r="M88" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N88" t="n">
         <v>40</v>
       </c>
       <c r="O88" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P88" t="n">
         <v>20</v>
@@ -6326,28 +6554,28 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N89" t="n">
         <v>13</v>
       </c>
       <c r="O89" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P89" t="n">
         <v>7</v>
       </c>
       <c r="Q89" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R89" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="90">
@@ -6382,28 +6610,28 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="N90" t="n">
         <v>13</v>
       </c>
       <c r="O90" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P90" t="n">
         <v>7</v>
       </c>
       <c r="Q90" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R90" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91">
@@ -6438,28 +6666,28 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N91" t="n">
         <v>13</v>
       </c>
       <c r="O91" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="P91" t="n">
         <v>7</v>
       </c>
       <c r="Q91" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R91" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="92">
@@ -6467,7 +6695,7 @@
         <v>184</v>
       </c>
       <c r="B92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
@@ -6485,7 +6713,7 @@
         <v>2</v>
       </c>
       <c r="H92" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I92" t="n">
         <v>4</v>
@@ -6494,19 +6722,19 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="N92" t="n">
         <v>18</v>
       </c>
       <c r="O92" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="P92" t="n">
         <v>9</v>
@@ -6523,7 +6751,7 @@
         <v>185</v>
       </c>
       <c r="B93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="s">
         <v>18</v>
@@ -6541,7 +6769,7 @@
         <v>2</v>
       </c>
       <c r="H93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I93" t="n">
         <v>4</v>
@@ -6550,19 +6778,19 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N93" t="n">
         <v>18</v>
       </c>
       <c r="O93" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P93" t="n">
         <v>9</v>
@@ -6579,7 +6807,7 @@
         <v>186</v>
       </c>
       <c r="B94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" t="s">
         <v>18</v>
@@ -6597,7 +6825,7 @@
         <v>2</v>
       </c>
       <c r="H94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I94" t="n">
         <v>4</v>
@@ -6606,19 +6834,19 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
       </c>
       <c r="M94" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="N94" t="n">
         <v>18</v>
       </c>
       <c r="O94" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="P94" t="n">
         <v>9</v>
@@ -6653,7 +6881,7 @@
         <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I95" t="n">
         <v>4</v>
@@ -6662,28 +6890,28 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="N95" t="n">
         <v>46</v>
       </c>
       <c r="O95" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="P95" t="n">
         <v>24</v>
       </c>
       <c r="Q95" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R95" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96">
@@ -6709,7 +6937,7 @@
         <v>2</v>
       </c>
       <c r="H96" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I96" t="n">
         <v>4</v>
@@ -6718,28 +6946,28 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N96" t="n">
         <v>46</v>
       </c>
       <c r="O96" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P96" t="n">
         <v>24</v>
       </c>
       <c r="Q96" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R96" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97">
@@ -6765,7 +6993,7 @@
         <v>2</v>
       </c>
       <c r="H97" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I97" t="n">
         <v>4</v>
@@ -6774,28 +7002,28 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N97" t="n">
         <v>46</v>
       </c>
       <c r="O97" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="P97" t="n">
         <v>24</v>
       </c>
       <c r="Q97" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R97" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98">
@@ -6830,19 +7058,19 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N98" t="n">
         <v>40</v>
       </c>
       <c r="O98" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="P98" t="n">
         <v>20</v>
@@ -6886,19 +7114,19 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="N99" t="n">
         <v>40</v>
       </c>
       <c r="O99" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="P99" t="n">
         <v>20</v>
@@ -6942,19 +7170,19 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N100" t="n">
         <v>40</v>
       </c>
       <c r="O100" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P100" t="n">
         <v>20</v>
@@ -6998,28 +7226,28 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N101" t="n">
         <v>24</v>
       </c>
       <c r="O101" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="P101" t="n">
         <v>13</v>
       </c>
       <c r="Q101" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R101" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102">
@@ -7054,28 +7282,28 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N102" t="n">
         <v>24</v>
       </c>
       <c r="O102" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P102" t="n">
         <v>13</v>
       </c>
       <c r="Q102" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R102" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103">
@@ -7110,28 +7338,28 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N103" t="n">
         <v>24</v>
       </c>
       <c r="O103" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P103" t="n">
         <v>13</v>
       </c>
       <c r="Q103" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R103" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104">
@@ -7166,19 +7394,19 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N104" t="n">
         <v>18</v>
       </c>
       <c r="O104" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P104" t="n">
         <v>9</v>
@@ -7222,19 +7450,19 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
       </c>
       <c r="M105" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N105" t="n">
         <v>18</v>
       </c>
       <c r="O105" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P105" t="n">
         <v>9</v>
@@ -7278,19 +7506,19 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
       </c>
       <c r="M106" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N106" t="n">
         <v>18</v>
       </c>
       <c r="O106" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P106" t="n">
         <v>9</v>
@@ -7334,28 +7562,28 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N107" t="n">
         <v>70</v>
       </c>
       <c r="O107" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P107" t="n">
         <v>36</v>
       </c>
       <c r="Q107" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R107" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="108">
@@ -7390,28 +7618,28 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N108" t="n">
         <v>70</v>
       </c>
       <c r="O108" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P108" t="n">
         <v>36</v>
       </c>
       <c r="Q108" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R108" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109">
@@ -7446,28 +7674,28 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="N109" t="n">
         <v>70</v>
       </c>
       <c r="O109" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P109" t="n">
         <v>36</v>
       </c>
       <c r="Q109" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R109" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="110">
@@ -7502,19 +7730,19 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N110" t="n">
         <v>40</v>
       </c>
       <c r="O110" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="P110" t="n">
         <v>20</v>
@@ -7558,19 +7786,19 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="N111" t="n">
         <v>40</v>
       </c>
       <c r="O111" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="P111" t="n">
         <v>20</v>
@@ -7614,19 +7842,19 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="N112" t="n">
         <v>40</v>
       </c>
       <c r="O112" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P112" t="n">
         <v>20</v>
@@ -7670,28 +7898,28 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="N113" t="n">
         <v>24</v>
       </c>
       <c r="O113" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="P113" t="n">
         <v>13</v>
       </c>
       <c r="Q113" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R113" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114">
@@ -7726,28 +7954,28 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="N114" t="n">
         <v>24</v>
       </c>
       <c r="O114" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="P114" t="n">
         <v>13</v>
       </c>
       <c r="Q114" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R114" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115">
@@ -7782,28 +8010,28 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
+        <v>241</v>
+      </c>
+      <c r="L115" t="n">
+        <v>3</v>
+      </c>
+      <c r="M115" t="s">
         <v>272</v>
-      </c>
-      <c r="L115" t="n">
-        <v>3</v>
-      </c>
-      <c r="M115" t="s">
-        <v>277</v>
       </c>
       <c r="N115" t="n">
         <v>24</v>
       </c>
       <c r="O115" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="P115" t="n">
         <v>13</v>
       </c>
       <c r="Q115" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R115" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116">
@@ -7811,7 +8039,7 @@
         <v>232</v>
       </c>
       <c r="B116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" t="s">
         <v>18</v>
@@ -7829,7 +8057,7 @@
         <v>2</v>
       </c>
       <c r="H116" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I116" t="n">
         <v>5</v>
@@ -7838,19 +8066,19 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="N116" t="n">
         <v>18</v>
       </c>
       <c r="O116" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="P116" t="n">
         <v>9</v>
@@ -7867,7 +8095,7 @@
         <v>233</v>
       </c>
       <c r="B117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="s">
         <v>18</v>
@@ -7885,7 +8113,7 @@
         <v>2</v>
       </c>
       <c r="H117" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I117" t="n">
         <v>5</v>
@@ -7894,19 +8122,19 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
       </c>
       <c r="M117" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="N117" t="n">
         <v>18</v>
       </c>
       <c r="O117" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="P117" t="n">
         <v>9</v>
@@ -7923,7 +8151,7 @@
         <v>234</v>
       </c>
       <c r="B118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118" t="s">
         <v>18</v>
@@ -7941,7 +8169,7 @@
         <v>2</v>
       </c>
       <c r="H118" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I118" t="n">
         <v>5</v>
@@ -7950,19 +8178,19 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
       </c>
       <c r="M118" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="N118" t="n">
         <v>18</v>
       </c>
       <c r="O118" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="P118" t="n">
         <v>9</v>
@@ -7997,7 +8225,7 @@
         <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I119" t="n">
         <v>5</v>
@@ -8006,28 +8234,28 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N119" t="n">
         <v>70</v>
       </c>
       <c r="O119" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="P119" t="n">
         <v>36</v>
       </c>
       <c r="Q119" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R119" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="120">
@@ -8053,7 +8281,7 @@
         <v>2</v>
       </c>
       <c r="H120" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I120" t="n">
         <v>5</v>
@@ -8062,28 +8290,28 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="N120" t="n">
         <v>70</v>
       </c>
       <c r="O120" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P120" t="n">
         <v>36</v>
       </c>
       <c r="Q120" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R120" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121">
@@ -8109,7 +8337,7 @@
         <v>2</v>
       </c>
       <c r="H121" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I121" t="n">
         <v>5</v>
@@ -8118,28 +8346,28 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="N121" t="n">
         <v>70</v>
       </c>
       <c r="O121" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P121" t="n">
         <v>36</v>
       </c>
       <c r="Q121" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R121" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="122">
@@ -8174,28 +8402,28 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="N122" t="n">
         <v>30</v>
       </c>
       <c r="O122" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P122" t="n">
         <v>16</v>
       </c>
       <c r="Q122" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="R122" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="123">
@@ -8230,28 +8458,28 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N123" t="n">
         <v>30</v>
       </c>
       <c r="O123" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="P123" t="n">
         <v>16</v>
       </c>
       <c r="Q123" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="R123" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="124">
@@ -8286,28 +8514,28 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="N124" t="n">
         <v>30</v>
       </c>
       <c r="O124" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="P124" t="n">
         <v>16</v>
       </c>
       <c r="Q124" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="R124" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="125">
@@ -8342,28 +8570,28 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="N125" t="n">
         <v>24</v>
       </c>
       <c r="O125" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="P125" t="n">
         <v>13</v>
       </c>
       <c r="Q125" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R125" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="126">
@@ -8398,28 +8626,28 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="N126" t="n">
         <v>24</v>
       </c>
       <c r="O126" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="P126" t="n">
         <v>13</v>
       </c>
       <c r="Q126" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R126" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127">
@@ -8454,28 +8682,28 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="N127" t="n">
         <v>24</v>
       </c>
       <c r="O127" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="P127" t="n">
         <v>13</v>
       </c>
       <c r="Q127" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R127" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128">
@@ -8510,28 +8738,28 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="N128" t="n">
         <v>4</v>
       </c>
       <c r="O128" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="P128" t="n">
         <v>3</v>
       </c>
       <c r="Q128" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="R128" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="129">
@@ -8566,28 +8794,28 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="N129" t="n">
         <v>4</v>
       </c>
       <c r="O129" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P129" t="n">
         <v>3</v>
       </c>
       <c r="Q129" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="R129" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="130">
@@ -8622,28 +8850,28 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="N130" t="n">
         <v>4</v>
       </c>
       <c r="O130" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="P130" t="n">
         <v>3</v>
       </c>
       <c r="Q130" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="R130" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="131">
@@ -8678,28 +8906,28 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N131" t="n">
         <v>68</v>
       </c>
       <c r="O131" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="P131" t="n">
         <v>34</v>
       </c>
       <c r="Q131" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="R131" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="132">
@@ -8734,28 +8962,28 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N132" t="n">
         <v>68</v>
       </c>
       <c r="O132" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P132" t="n">
         <v>34</v>
       </c>
       <c r="Q132" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="R132" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="133">
@@ -8790,28 +9018,28 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>62</v>
+        <v>294</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="N133" t="n">
         <v>68</v>
       </c>
       <c r="O133" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="P133" t="n">
         <v>34</v>
       </c>
       <c r="Q133" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="R133" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="134">
@@ -8846,28 +9074,28 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="N134" t="n">
         <v>30</v>
       </c>
       <c r="O134" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="P134" t="n">
         <v>16</v>
       </c>
       <c r="Q134" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="R134" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="135">
@@ -8902,28 +9130,28 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="N135" t="n">
         <v>30</v>
       </c>
       <c r="O135" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P135" t="n">
         <v>16</v>
       </c>
       <c r="Q135" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="R135" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="136">
@@ -8958,28 +9186,28 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
+        <v>286</v>
+      </c>
+      <c r="L136" t="n">
+        <v>3</v>
+      </c>
+      <c r="M136" t="s">
         <v>319</v>
-      </c>
-      <c r="L136" t="n">
-        <v>3</v>
-      </c>
-      <c r="M136" t="s">
-        <v>324</v>
       </c>
       <c r="N136" t="n">
         <v>30</v>
       </c>
       <c r="O136" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="P136" t="n">
         <v>16</v>
       </c>
       <c r="Q136" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="R136" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="137">
@@ -9014,28 +9242,28 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N137" t="n">
         <v>24</v>
       </c>
       <c r="O137" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="P137" t="n">
         <v>13</v>
       </c>
       <c r="Q137" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R137" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="138">
@@ -9070,28 +9298,28 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="N138" t="n">
         <v>24</v>
       </c>
       <c r="O138" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P138" t="n">
         <v>13</v>
       </c>
       <c r="Q138" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R138" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139">
@@ -9126,28 +9354,28 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="N139" t="n">
         <v>24</v>
       </c>
       <c r="O139" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="P139" t="n">
         <v>13</v>
       </c>
       <c r="Q139" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R139" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140">
@@ -9173,7 +9401,7 @@
         <v>2</v>
       </c>
       <c r="H140" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I140" t="n">
         <v>6</v>
@@ -9182,28 +9410,28 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N140" t="n">
         <v>4</v>
       </c>
       <c r="O140" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P140" t="n">
         <v>3</v>
       </c>
       <c r="Q140" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="R140" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="141">
@@ -9229,7 +9457,7 @@
         <v>2</v>
       </c>
       <c r="H141" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I141" t="n">
         <v>6</v>
@@ -9238,28 +9466,28 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="N141" t="n">
         <v>4</v>
       </c>
       <c r="O141" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="P141" t="n">
         <v>3</v>
       </c>
       <c r="Q141" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="R141" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="142">
@@ -9285,7 +9513,7 @@
         <v>2</v>
       </c>
       <c r="H142" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I142" t="n">
         <v>6</v>
@@ -9294,28 +9522,28 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N142" t="n">
         <v>4</v>
       </c>
       <c r="O142" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="P142" t="n">
         <v>3</v>
       </c>
       <c r="Q142" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="R142" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="143">
@@ -9341,7 +9569,7 @@
         <v>2</v>
       </c>
       <c r="H143" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I143" t="n">
         <v>6</v>
@@ -9350,28 +9578,28 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="N143" t="n">
         <v>68</v>
       </c>
       <c r="O143" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="P143" t="n">
         <v>34</v>
       </c>
       <c r="Q143" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="R143" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="144">
@@ -9397,7 +9625,7 @@
         <v>2</v>
       </c>
       <c r="H144" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I144" t="n">
         <v>6</v>
@@ -9406,28 +9634,28 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="N144" t="n">
         <v>68</v>
       </c>
       <c r="O144" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P144" t="n">
         <v>34</v>
       </c>
       <c r="Q144" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="R144" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145">
@@ -9453,7 +9681,7 @@
         <v>2</v>
       </c>
       <c r="H145" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I145" t="n">
         <v>6</v>
@@ -9462,28 +9690,3916 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N145" t="n">
         <v>68</v>
       </c>
       <c r="O145" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="P145" t="n">
         <v>34</v>
       </c>
       <c r="Q145" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="R145" t="s">
-        <v>314</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>292</v>
+      </c>
+      <c r="B146" t="b">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>18</v>
+      </c>
+      <c r="D146" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="s">
+        <v>20</v>
+      </c>
+      <c r="I146" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" t="s">
+        <v>337</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="s">
+        <v>338</v>
+      </c>
+      <c r="N146" t="n">
+        <v>27</v>
+      </c>
+      <c r="O146" t="s">
+        <v>339</v>
+      </c>
+      <c r="P146" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>340</v>
+      </c>
+      <c r="R146" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>293</v>
+      </c>
+      <c r="B147" t="b">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>18</v>
+      </c>
+      <c r="D147" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="s">
+        <v>20</v>
+      </c>
+      <c r="I147" t="n">
+        <v>7</v>
+      </c>
+      <c r="J147" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" t="s">
+        <v>337</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" t="s">
+        <v>341</v>
+      </c>
+      <c r="N147" t="n">
+        <v>27</v>
+      </c>
+      <c r="O147" t="s">
+        <v>342</v>
+      </c>
+      <c r="P147" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>340</v>
+      </c>
+      <c r="R147" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>294</v>
+      </c>
+      <c r="B148" t="b">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
+        <v>18</v>
+      </c>
+      <c r="D148" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="s">
+        <v>20</v>
+      </c>
+      <c r="I148" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="s">
+        <v>337</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" t="s">
+        <v>343</v>
+      </c>
+      <c r="N148" t="n">
+        <v>27</v>
+      </c>
+      <c r="O148" t="s">
+        <v>344</v>
+      </c>
+      <c r="P148" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>340</v>
+      </c>
+      <c r="R148" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>298</v>
+      </c>
+      <c r="B149" t="b">
+        <v>1</v>
+      </c>
+      <c r="C149" t="s">
+        <v>18</v>
+      </c>
+      <c r="D149" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="s">
+        <v>29</v>
+      </c>
+      <c r="I149" t="n">
+        <v>7</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="s">
+        <v>345</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="s">
+        <v>346</v>
+      </c>
+      <c r="N149"/>
+      <c r="O149" t="s">
+        <v>346</v>
+      </c>
+      <c r="P149"/>
+      <c r="Q149" t="s">
+        <v>346</v>
+      </c>
+      <c r="R149" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>299</v>
+      </c>
+      <c r="B150" t="b">
+        <v>1</v>
+      </c>
+      <c r="C150" t="s">
+        <v>18</v>
+      </c>
+      <c r="D150" t="s">
+        <v>19</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="s">
+        <v>29</v>
+      </c>
+      <c r="I150" t="n">
+        <v>7</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="s">
+        <v>345</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" t="s">
+        <v>346</v>
+      </c>
+      <c r="N150"/>
+      <c r="O150" t="s">
+        <v>346</v>
+      </c>
+      <c r="P150"/>
+      <c r="Q150" t="s">
+        <v>346</v>
+      </c>
+      <c r="R150" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>300</v>
+      </c>
+      <c r="B151" t="b">
+        <v>1</v>
+      </c>
+      <c r="C151" t="s">
+        <v>18</v>
+      </c>
+      <c r="D151" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="s">
+        <v>29</v>
+      </c>
+      <c r="I151" t="n">
+        <v>7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="s">
+        <v>345</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" t="s">
+        <v>346</v>
+      </c>
+      <c r="N151"/>
+      <c r="O151" t="s">
+        <v>346</v>
+      </c>
+      <c r="P151"/>
+      <c r="Q151" t="s">
+        <v>346</v>
+      </c>
+      <c r="R151" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>304</v>
+      </c>
+      <c r="B152" t="b">
+        <v>1</v>
+      </c>
+      <c r="C152" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" t="s">
+        <v>19</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="s">
+        <v>38</v>
+      </c>
+      <c r="I152" t="n">
+        <v>7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="s">
+        <v>337</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="s">
+        <v>346</v>
+      </c>
+      <c r="N152"/>
+      <c r="O152" t="s">
+        <v>346</v>
+      </c>
+      <c r="P152"/>
+      <c r="Q152" t="s">
+        <v>346</v>
+      </c>
+      <c r="R152" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>305</v>
+      </c>
+      <c r="B153" t="b">
+        <v>1</v>
+      </c>
+      <c r="C153" t="s">
+        <v>18</v>
+      </c>
+      <c r="D153" t="s">
+        <v>19</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="s">
+        <v>38</v>
+      </c>
+      <c r="I153" t="n">
+        <v>7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="s">
+        <v>337</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2</v>
+      </c>
+      <c r="M153" t="s">
+        <v>346</v>
+      </c>
+      <c r="N153"/>
+      <c r="O153" t="s">
+        <v>346</v>
+      </c>
+      <c r="P153"/>
+      <c r="Q153" t="s">
+        <v>346</v>
+      </c>
+      <c r="R153" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>306</v>
+      </c>
+      <c r="B154" t="b">
+        <v>1</v>
+      </c>
+      <c r="C154" t="s">
+        <v>18</v>
+      </c>
+      <c r="D154" t="s">
+        <v>19</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="s">
+        <v>38</v>
+      </c>
+      <c r="I154" t="n">
+        <v>7</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" t="s">
+        <v>337</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" t="s">
+        <v>346</v>
+      </c>
+      <c r="N154"/>
+      <c r="O154" t="s">
+        <v>346</v>
+      </c>
+      <c r="P154"/>
+      <c r="Q154" t="s">
+        <v>346</v>
+      </c>
+      <c r="R154" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>310</v>
+      </c>
+      <c r="B155" t="b">
+        <v>0</v>
+      </c>
+      <c r="C155" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155" t="s">
+        <v>19</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="s">
+        <v>46</v>
+      </c>
+      <c r="I155" t="n">
+        <v>7</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="s">
+        <v>345</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="s">
+        <v>347</v>
+      </c>
+      <c r="N155" t="n">
+        <v>14</v>
+      </c>
+      <c r="O155" t="s">
+        <v>348</v>
+      </c>
+      <c r="P155" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>349</v>
+      </c>
+      <c r="R155" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>311</v>
+      </c>
+      <c r="B156" t="b">
+        <v>0</v>
+      </c>
+      <c r="C156" t="s">
+        <v>18</v>
+      </c>
+      <c r="D156" t="s">
+        <v>19</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="s">
+        <v>46</v>
+      </c>
+      <c r="I156" t="n">
+        <v>7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="s">
+        <v>345</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="s">
+        <v>350</v>
+      </c>
+      <c r="N156" t="n">
+        <v>14</v>
+      </c>
+      <c r="O156" t="s">
+        <v>351</v>
+      </c>
+      <c r="P156" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>349</v>
+      </c>
+      <c r="R156" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>312</v>
+      </c>
+      <c r="B157" t="b">
+        <v>0</v>
+      </c>
+      <c r="C157" t="s">
+        <v>18</v>
+      </c>
+      <c r="D157" t="s">
+        <v>19</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>46</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="s">
+        <v>345</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3</v>
+      </c>
+      <c r="M157" t="s">
+        <v>352</v>
+      </c>
+      <c r="N157" t="n">
+        <v>14</v>
+      </c>
+      <c r="O157" t="s">
+        <v>353</v>
+      </c>
+      <c r="P157" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>349</v>
+      </c>
+      <c r="R157" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>316</v>
+      </c>
+      <c r="B158" t="b">
+        <v>0</v>
+      </c>
+      <c r="C158" t="s">
+        <v>18</v>
+      </c>
+      <c r="D158" t="s">
+        <v>19</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="s">
+        <v>54</v>
+      </c>
+      <c r="I158" t="n">
+        <v>7</v>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" t="s">
+        <v>337</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="s">
+        <v>354</v>
+      </c>
+      <c r="N158" t="n">
+        <v>27</v>
+      </c>
+      <c r="O158" t="s">
+        <v>355</v>
+      </c>
+      <c r="P158" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>340</v>
+      </c>
+      <c r="R158" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>317</v>
+      </c>
+      <c r="B159" t="b">
+        <v>0</v>
+      </c>
+      <c r="C159" t="s">
+        <v>18</v>
+      </c>
+      <c r="D159" t="s">
+        <v>19</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="s">
+        <v>54</v>
+      </c>
+      <c r="I159" t="n">
+        <v>7</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="s">
+        <v>337</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="s">
+        <v>356</v>
+      </c>
+      <c r="N159" t="n">
+        <v>27</v>
+      </c>
+      <c r="O159" t="s">
+        <v>357</v>
+      </c>
+      <c r="P159" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>340</v>
+      </c>
+      <c r="R159" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>318</v>
+      </c>
+      <c r="B160" t="b">
+        <v>0</v>
+      </c>
+      <c r="C160" t="s">
+        <v>18</v>
+      </c>
+      <c r="D160" t="s">
+        <v>19</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="s">
+        <v>54</v>
+      </c>
+      <c r="I160" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="s">
+        <v>337</v>
+      </c>
+      <c r="L160" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" t="s">
+        <v>358</v>
+      </c>
+      <c r="N160" t="n">
+        <v>27</v>
+      </c>
+      <c r="O160" t="s">
+        <v>359</v>
+      </c>
+      <c r="P160" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>340</v>
+      </c>
+      <c r="R160" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>322</v>
+      </c>
+      <c r="B161" t="b">
+        <v>1</v>
+      </c>
+      <c r="C161" t="s">
+        <v>18</v>
+      </c>
+      <c r="D161" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="s">
+        <v>61</v>
+      </c>
+      <c r="I161" t="n">
+        <v>7</v>
+      </c>
+      <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="s">
+        <v>345</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="s">
+        <v>346</v>
+      </c>
+      <c r="N161"/>
+      <c r="O161" t="s">
+        <v>346</v>
+      </c>
+      <c r="P161"/>
+      <c r="Q161" t="s">
+        <v>346</v>
+      </c>
+      <c r="R161" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>323</v>
+      </c>
+      <c r="B162" t="b">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>18</v>
+      </c>
+      <c r="D162" t="s">
+        <v>19</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" t="s">
+        <v>61</v>
+      </c>
+      <c r="I162" t="n">
+        <v>7</v>
+      </c>
+      <c r="J162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" t="s">
+        <v>345</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" t="s">
+        <v>346</v>
+      </c>
+      <c r="N162"/>
+      <c r="O162" t="s">
+        <v>346</v>
+      </c>
+      <c r="P162"/>
+      <c r="Q162" t="s">
+        <v>346</v>
+      </c>
+      <c r="R162" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>324</v>
+      </c>
+      <c r="B163" t="b">
+        <v>1</v>
+      </c>
+      <c r="C163" t="s">
+        <v>18</v>
+      </c>
+      <c r="D163" t="s">
+        <v>19</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="s">
+        <v>61</v>
+      </c>
+      <c r="I163" t="n">
+        <v>7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="s">
+        <v>345</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="s">
+        <v>346</v>
+      </c>
+      <c r="N163"/>
+      <c r="O163" t="s">
+        <v>346</v>
+      </c>
+      <c r="P163"/>
+      <c r="Q163" t="s">
+        <v>346</v>
+      </c>
+      <c r="R163" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>328</v>
+      </c>
+      <c r="B164" t="b">
+        <v>1</v>
+      </c>
+      <c r="C164" t="s">
+        <v>18</v>
+      </c>
+      <c r="D164" t="s">
+        <v>19</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="s">
+        <v>68</v>
+      </c>
+      <c r="I164" t="n">
+        <v>7</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="s">
+        <v>337</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="s">
+        <v>346</v>
+      </c>
+      <c r="N164"/>
+      <c r="O164" t="s">
+        <v>346</v>
+      </c>
+      <c r="P164"/>
+      <c r="Q164" t="s">
+        <v>346</v>
+      </c>
+      <c r="R164" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>329</v>
+      </c>
+      <c r="B165" t="b">
+        <v>1</v>
+      </c>
+      <c r="C165" t="s">
+        <v>18</v>
+      </c>
+      <c r="D165" t="s">
+        <v>19</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H165" t="s">
+        <v>68</v>
+      </c>
+      <c r="I165" t="n">
+        <v>7</v>
+      </c>
+      <c r="J165" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" t="s">
+        <v>337</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="s">
+        <v>346</v>
+      </c>
+      <c r="N165"/>
+      <c r="O165" t="s">
+        <v>346</v>
+      </c>
+      <c r="P165"/>
+      <c r="Q165" t="s">
+        <v>346</v>
+      </c>
+      <c r="R165" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>330</v>
+      </c>
+      <c r="B166" t="b">
+        <v>1</v>
+      </c>
+      <c r="C166" t="s">
+        <v>18</v>
+      </c>
+      <c r="D166" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="s">
+        <v>68</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7</v>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="s">
+        <v>337</v>
+      </c>
+      <c r="L166" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" t="s">
+        <v>346</v>
+      </c>
+      <c r="N166"/>
+      <c r="O166" t="s">
+        <v>346</v>
+      </c>
+      <c r="P166"/>
+      <c r="Q166" t="s">
+        <v>346</v>
+      </c>
+      <c r="R166" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>334</v>
+      </c>
+      <c r="B167" t="b">
+        <v>0</v>
+      </c>
+      <c r="C167" t="s">
+        <v>18</v>
+      </c>
+      <c r="D167" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="s">
+        <v>75</v>
+      </c>
+      <c r="I167" t="n">
+        <v>7</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" t="s">
+        <v>345</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="s">
+        <v>360</v>
+      </c>
+      <c r="N167" t="n">
+        <v>14</v>
+      </c>
+      <c r="O167" t="s">
+        <v>361</v>
+      </c>
+      <c r="P167" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>349</v>
+      </c>
+      <c r="R167" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>335</v>
+      </c>
+      <c r="B168" t="b">
+        <v>0</v>
+      </c>
+      <c r="C168" t="s">
+        <v>18</v>
+      </c>
+      <c r="D168" t="s">
+        <v>19</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="s">
+        <v>75</v>
+      </c>
+      <c r="I168" t="n">
+        <v>7</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="s">
+        <v>345</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" t="s">
+        <v>362</v>
+      </c>
+      <c r="N168" t="n">
+        <v>14</v>
+      </c>
+      <c r="O168" t="s">
+        <v>363</v>
+      </c>
+      <c r="P168" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>349</v>
+      </c>
+      <c r="R168" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>336</v>
+      </c>
+      <c r="B169" t="b">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s">
+        <v>18</v>
+      </c>
+      <c r="D169" t="s">
+        <v>19</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="s">
+        <v>75</v>
+      </c>
+      <c r="I169" t="n">
+        <v>7</v>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="s">
+        <v>345</v>
+      </c>
+      <c r="L169" t="n">
+        <v>3</v>
+      </c>
+      <c r="M169" t="s">
+        <v>364</v>
+      </c>
+      <c r="N169" t="n">
+        <v>14</v>
+      </c>
+      <c r="O169" t="s">
+        <v>365</v>
+      </c>
+      <c r="P169" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>349</v>
+      </c>
+      <c r="R169" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>340</v>
+      </c>
+      <c r="B170" t="b">
+        <v>0</v>
+      </c>
+      <c r="C170" t="s">
+        <v>18</v>
+      </c>
+      <c r="D170" t="s">
+        <v>19</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="s">
+        <v>20</v>
+      </c>
+      <c r="I170" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="s">
+        <v>366</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="s">
+        <v>367</v>
+      </c>
+      <c r="N170" t="n">
+        <v>27</v>
+      </c>
+      <c r="O170" t="s">
+        <v>368</v>
+      </c>
+      <c r="P170" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>340</v>
+      </c>
+      <c r="R170" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>341</v>
+      </c>
+      <c r="B171" t="b">
+        <v>0</v>
+      </c>
+      <c r="C171" t="s">
+        <v>18</v>
+      </c>
+      <c r="D171" t="s">
+        <v>19</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="s">
+        <v>20</v>
+      </c>
+      <c r="I171" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="s">
+        <v>366</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="s">
+        <v>369</v>
+      </c>
+      <c r="N171" t="n">
+        <v>27</v>
+      </c>
+      <c r="O171" t="s">
+        <v>370</v>
+      </c>
+      <c r="P171" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>340</v>
+      </c>
+      <c r="R171" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>342</v>
+      </c>
+      <c r="B172" t="b">
+        <v>0</v>
+      </c>
+      <c r="C172" t="s">
+        <v>18</v>
+      </c>
+      <c r="D172" t="s">
+        <v>19</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="s">
+        <v>20</v>
+      </c>
+      <c r="I172" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3</v>
+      </c>
+      <c r="K172" t="s">
+        <v>366</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" t="s">
+        <v>371</v>
+      </c>
+      <c r="N172" t="n">
+        <v>27</v>
+      </c>
+      <c r="O172" t="s">
+        <v>372</v>
+      </c>
+      <c r="P172" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>340</v>
+      </c>
+      <c r="R172" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>346</v>
+      </c>
+      <c r="B173" t="b">
+        <v>1</v>
+      </c>
+      <c r="C173" t="s">
+        <v>18</v>
+      </c>
+      <c r="D173" t="s">
+        <v>19</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="s">
+        <v>29</v>
+      </c>
+      <c r="I173" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="s">
+        <v>345</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="s">
+        <v>346</v>
+      </c>
+      <c r="N173"/>
+      <c r="O173" t="s">
+        <v>346</v>
+      </c>
+      <c r="P173"/>
+      <c r="Q173" t="s">
+        <v>346</v>
+      </c>
+      <c r="R173" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>347</v>
+      </c>
+      <c r="B174" t="b">
+        <v>1</v>
+      </c>
+      <c r="C174" t="s">
+        <v>18</v>
+      </c>
+      <c r="D174" t="s">
+        <v>19</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="s">
+        <v>29</v>
+      </c>
+      <c r="I174" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="s">
+        <v>345</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" t="s">
+        <v>346</v>
+      </c>
+      <c r="N174"/>
+      <c r="O174" t="s">
+        <v>346</v>
+      </c>
+      <c r="P174"/>
+      <c r="Q174" t="s">
+        <v>346</v>
+      </c>
+      <c r="R174" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>348</v>
+      </c>
+      <c r="B175" t="b">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
+        <v>18</v>
+      </c>
+      <c r="D175" t="s">
+        <v>19</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="s">
+        <v>29</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="s">
+        <v>345</v>
+      </c>
+      <c r="L175" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" t="s">
+        <v>346</v>
+      </c>
+      <c r="N175"/>
+      <c r="O175" t="s">
+        <v>346</v>
+      </c>
+      <c r="P175"/>
+      <c r="Q175" t="s">
+        <v>346</v>
+      </c>
+      <c r="R175" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>352</v>
+      </c>
+      <c r="B176" t="b">
+        <v>1</v>
+      </c>
+      <c r="C176" t="s">
+        <v>18</v>
+      </c>
+      <c r="D176" t="s">
+        <v>19</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="s">
+        <v>38</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="s">
+        <v>366</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="s">
+        <v>346</v>
+      </c>
+      <c r="N176"/>
+      <c r="O176" t="s">
+        <v>346</v>
+      </c>
+      <c r="P176"/>
+      <c r="Q176" t="s">
+        <v>346</v>
+      </c>
+      <c r="R176" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>353</v>
+      </c>
+      <c r="B177" t="b">
+        <v>1</v>
+      </c>
+      <c r="C177" t="s">
+        <v>18</v>
+      </c>
+      <c r="D177" t="s">
+        <v>19</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="s">
+        <v>38</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="s">
+        <v>366</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="s">
+        <v>346</v>
+      </c>
+      <c r="N177"/>
+      <c r="O177" t="s">
+        <v>346</v>
+      </c>
+      <c r="P177"/>
+      <c r="Q177" t="s">
+        <v>346</v>
+      </c>
+      <c r="R177" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>354</v>
+      </c>
+      <c r="B178" t="b">
+        <v>1</v>
+      </c>
+      <c r="C178" t="s">
+        <v>18</v>
+      </c>
+      <c r="D178" t="s">
+        <v>19</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="s">
+        <v>38</v>
+      </c>
+      <c r="I178" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="s">
+        <v>366</v>
+      </c>
+      <c r="L178" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" t="s">
+        <v>346</v>
+      </c>
+      <c r="N178"/>
+      <c r="O178" t="s">
+        <v>346</v>
+      </c>
+      <c r="P178"/>
+      <c r="Q178" t="s">
+        <v>346</v>
+      </c>
+      <c r="R178" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>358</v>
+      </c>
+      <c r="B179" t="b">
+        <v>0</v>
+      </c>
+      <c r="C179" t="s">
+        <v>18</v>
+      </c>
+      <c r="D179" t="s">
+        <v>19</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="s">
+        <v>46</v>
+      </c>
+      <c r="I179" t="n">
+        <v>8</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="s">
+        <v>345</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="s">
+        <v>373</v>
+      </c>
+      <c r="N179" t="n">
+        <v>14</v>
+      </c>
+      <c r="O179" t="s">
+        <v>374</v>
+      </c>
+      <c r="P179" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>349</v>
+      </c>
+      <c r="R179" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>359</v>
+      </c>
+      <c r="B180" t="b">
+        <v>0</v>
+      </c>
+      <c r="C180" t="s">
+        <v>18</v>
+      </c>
+      <c r="D180" t="s">
+        <v>19</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="s">
+        <v>46</v>
+      </c>
+      <c r="I180" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="s">
+        <v>345</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" t="s">
+        <v>375</v>
+      </c>
+      <c r="N180" t="n">
+        <v>14</v>
+      </c>
+      <c r="O180" t="s">
+        <v>376</v>
+      </c>
+      <c r="P180" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>349</v>
+      </c>
+      <c r="R180" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>360</v>
+      </c>
+      <c r="B181" t="b">
+        <v>0</v>
+      </c>
+      <c r="C181" t="s">
+        <v>18</v>
+      </c>
+      <c r="D181" t="s">
+        <v>19</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>46</v>
+      </c>
+      <c r="I181" t="n">
+        <v>8</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="s">
+        <v>345</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3</v>
+      </c>
+      <c r="M181" t="s">
+        <v>377</v>
+      </c>
+      <c r="N181" t="n">
+        <v>14</v>
+      </c>
+      <c r="O181" t="s">
+        <v>378</v>
+      </c>
+      <c r="P181" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>349</v>
+      </c>
+      <c r="R181" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>364</v>
+      </c>
+      <c r="B182" t="b">
+        <v>0</v>
+      </c>
+      <c r="C182" t="s">
+        <v>18</v>
+      </c>
+      <c r="D182" t="s">
+        <v>19</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="s">
+        <v>54</v>
+      </c>
+      <c r="I182" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="s">
+        <v>366</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="s">
+        <v>379</v>
+      </c>
+      <c r="N182" t="n">
+        <v>27</v>
+      </c>
+      <c r="O182" t="s">
+        <v>380</v>
+      </c>
+      <c r="P182" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>340</v>
+      </c>
+      <c r="R182" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>365</v>
+      </c>
+      <c r="B183" t="b">
+        <v>0</v>
+      </c>
+      <c r="C183" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183" t="s">
+        <v>19</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="s">
+        <v>54</v>
+      </c>
+      <c r="I183" t="n">
+        <v>8</v>
+      </c>
+      <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="s">
+        <v>366</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="s">
+        <v>381</v>
+      </c>
+      <c r="N183" t="n">
+        <v>27</v>
+      </c>
+      <c r="O183" t="s">
+        <v>382</v>
+      </c>
+      <c r="P183" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>340</v>
+      </c>
+      <c r="R183" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>366</v>
+      </c>
+      <c r="B184" t="b">
+        <v>0</v>
+      </c>
+      <c r="C184" t="s">
+        <v>18</v>
+      </c>
+      <c r="D184" t="s">
+        <v>19</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="s">
+        <v>54</v>
+      </c>
+      <c r="I184" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="s">
+        <v>366</v>
+      </c>
+      <c r="L184" t="n">
+        <v>3</v>
+      </c>
+      <c r="M184" t="s">
+        <v>383</v>
+      </c>
+      <c r="N184" t="n">
+        <v>27</v>
+      </c>
+      <c r="O184" t="s">
+        <v>384</v>
+      </c>
+      <c r="P184" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>340</v>
+      </c>
+      <c r="R184" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>370</v>
+      </c>
+      <c r="B185" t="b">
+        <v>1</v>
+      </c>
+      <c r="C185" t="s">
+        <v>18</v>
+      </c>
+      <c r="D185" t="s">
+        <v>19</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="s">
+        <v>61</v>
+      </c>
+      <c r="I185" t="n">
+        <v>8</v>
+      </c>
+      <c r="J185" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" t="s">
+        <v>345</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="s">
+        <v>346</v>
+      </c>
+      <c r="N185"/>
+      <c r="O185" t="s">
+        <v>346</v>
+      </c>
+      <c r="P185"/>
+      <c r="Q185" t="s">
+        <v>346</v>
+      </c>
+      <c r="R185" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>371</v>
+      </c>
+      <c r="B186" t="b">
+        <v>1</v>
+      </c>
+      <c r="C186" t="s">
+        <v>18</v>
+      </c>
+      <c r="D186" t="s">
+        <v>19</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="s">
+        <v>61</v>
+      </c>
+      <c r="I186" t="n">
+        <v>8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>3</v>
+      </c>
+      <c r="K186" t="s">
+        <v>345</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+      <c r="M186" t="s">
+        <v>346</v>
+      </c>
+      <c r="N186"/>
+      <c r="O186" t="s">
+        <v>346</v>
+      </c>
+      <c r="P186"/>
+      <c r="Q186" t="s">
+        <v>346</v>
+      </c>
+      <c r="R186" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>372</v>
+      </c>
+      <c r="B187" t="b">
+        <v>1</v>
+      </c>
+      <c r="C187" t="s">
+        <v>18</v>
+      </c>
+      <c r="D187" t="s">
+        <v>19</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" t="s">
+        <v>61</v>
+      </c>
+      <c r="I187" t="n">
+        <v>8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="s">
+        <v>345</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3</v>
+      </c>
+      <c r="M187" t="s">
+        <v>346</v>
+      </c>
+      <c r="N187"/>
+      <c r="O187" t="s">
+        <v>346</v>
+      </c>
+      <c r="P187"/>
+      <c r="Q187" t="s">
+        <v>346</v>
+      </c>
+      <c r="R187" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>376</v>
+      </c>
+      <c r="B188" t="b">
+        <v>1</v>
+      </c>
+      <c r="C188" t="s">
+        <v>18</v>
+      </c>
+      <c r="D188" t="s">
+        <v>19</v>
+      </c>
+      <c r="E188" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2</v>
+      </c>
+      <c r="H188" t="s">
+        <v>68</v>
+      </c>
+      <c r="I188" t="n">
+        <v>8</v>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="s">
+        <v>366</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="s">
+        <v>346</v>
+      </c>
+      <c r="N188"/>
+      <c r="O188" t="s">
+        <v>346</v>
+      </c>
+      <c r="P188"/>
+      <c r="Q188" t="s">
+        <v>346</v>
+      </c>
+      <c r="R188" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>377</v>
+      </c>
+      <c r="B189" t="b">
+        <v>1</v>
+      </c>
+      <c r="C189" t="s">
+        <v>18</v>
+      </c>
+      <c r="D189" t="s">
+        <v>19</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="s">
+        <v>68</v>
+      </c>
+      <c r="I189" t="n">
+        <v>8</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="s">
+        <v>366</v>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+      <c r="M189" t="s">
+        <v>346</v>
+      </c>
+      <c r="N189"/>
+      <c r="O189" t="s">
+        <v>346</v>
+      </c>
+      <c r="P189"/>
+      <c r="Q189" t="s">
+        <v>346</v>
+      </c>
+      <c r="R189" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>378</v>
+      </c>
+      <c r="B190" t="b">
+        <v>1</v>
+      </c>
+      <c r="C190" t="s">
+        <v>18</v>
+      </c>
+      <c r="D190" t="s">
+        <v>19</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="s">
+        <v>68</v>
+      </c>
+      <c r="I190" t="n">
+        <v>8</v>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="s">
+        <v>366</v>
+      </c>
+      <c r="L190" t="n">
+        <v>3</v>
+      </c>
+      <c r="M190" t="s">
+        <v>346</v>
+      </c>
+      <c r="N190"/>
+      <c r="O190" t="s">
+        <v>346</v>
+      </c>
+      <c r="P190"/>
+      <c r="Q190" t="s">
+        <v>346</v>
+      </c>
+      <c r="R190" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>382</v>
+      </c>
+      <c r="B191" t="b">
+        <v>0</v>
+      </c>
+      <c r="C191" t="s">
+        <v>18</v>
+      </c>
+      <c r="D191" t="s">
+        <v>19</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" t="s">
+        <v>75</v>
+      </c>
+      <c r="I191" t="n">
+        <v>8</v>
+      </c>
+      <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="s">
+        <v>345</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="s">
+        <v>385</v>
+      </c>
+      <c r="N191" t="n">
+        <v>14</v>
+      </c>
+      <c r="O191" t="s">
+        <v>386</v>
+      </c>
+      <c r="P191" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>349</v>
+      </c>
+      <c r="R191" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>383</v>
+      </c>
+      <c r="B192" t="b">
+        <v>0</v>
+      </c>
+      <c r="C192" t="s">
+        <v>18</v>
+      </c>
+      <c r="D192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" t="s">
+        <v>75</v>
+      </c>
+      <c r="I192" t="n">
+        <v>8</v>
+      </c>
+      <c r="J192" t="n">
+        <v>3</v>
+      </c>
+      <c r="K192" t="s">
+        <v>345</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+      <c r="M192" t="s">
+        <v>387</v>
+      </c>
+      <c r="N192" t="n">
+        <v>14</v>
+      </c>
+      <c r="O192" t="s">
+        <v>388</v>
+      </c>
+      <c r="P192" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>349</v>
+      </c>
+      <c r="R192" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>384</v>
+      </c>
+      <c r="B193" t="b">
+        <v>0</v>
+      </c>
+      <c r="C193" t="s">
+        <v>18</v>
+      </c>
+      <c r="D193" t="s">
+        <v>19</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="s">
+        <v>75</v>
+      </c>
+      <c r="I193" t="n">
+        <v>8</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="s">
+        <v>345</v>
+      </c>
+      <c r="L193" t="n">
+        <v>3</v>
+      </c>
+      <c r="M193" t="s">
+        <v>389</v>
+      </c>
+      <c r="N193" t="n">
+        <v>14</v>
+      </c>
+      <c r="O193" t="s">
+        <v>390</v>
+      </c>
+      <c r="P193" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>349</v>
+      </c>
+      <c r="R193" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>388</v>
+      </c>
+      <c r="B194" t="b">
+        <v>0</v>
+      </c>
+      <c r="C194" t="s">
+        <v>18</v>
+      </c>
+      <c r="D194" t="s">
+        <v>19</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="s">
+        <v>20</v>
+      </c>
+      <c r="I194" t="n">
+        <v>9</v>
+      </c>
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="s">
+        <v>391</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="s">
+        <v>392</v>
+      </c>
+      <c r="N194" t="n">
+        <v>20</v>
+      </c>
+      <c r="O194" t="s">
+        <v>393</v>
+      </c>
+      <c r="P194" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>394</v>
+      </c>
+      <c r="R194" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>389</v>
+      </c>
+      <c r="B195" t="b">
+        <v>0</v>
+      </c>
+      <c r="C195" t="s">
+        <v>18</v>
+      </c>
+      <c r="D195" t="s">
+        <v>19</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="s">
+        <v>20</v>
+      </c>
+      <c r="I195" t="n">
+        <v>9</v>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="s">
+        <v>391</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+      <c r="M195" t="s">
+        <v>395</v>
+      </c>
+      <c r="N195" t="n">
+        <v>20</v>
+      </c>
+      <c r="O195" t="s">
+        <v>396</v>
+      </c>
+      <c r="P195" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>394</v>
+      </c>
+      <c r="R195" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>390</v>
+      </c>
+      <c r="B196" t="b">
+        <v>0</v>
+      </c>
+      <c r="C196" t="s">
+        <v>18</v>
+      </c>
+      <c r="D196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="s">
+        <v>20</v>
+      </c>
+      <c r="I196" t="n">
+        <v>9</v>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="s">
+        <v>391</v>
+      </c>
+      <c r="L196" t="n">
+        <v>3</v>
+      </c>
+      <c r="M196" t="s">
+        <v>397</v>
+      </c>
+      <c r="N196" t="n">
+        <v>20</v>
+      </c>
+      <c r="O196" t="s">
+        <v>398</v>
+      </c>
+      <c r="P196" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>394</v>
+      </c>
+      <c r="R196" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>394</v>
+      </c>
+      <c r="B197" t="b">
+        <v>1</v>
+      </c>
+      <c r="C197" t="s">
+        <v>18</v>
+      </c>
+      <c r="D197" t="s">
+        <v>19</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="s">
+        <v>29</v>
+      </c>
+      <c r="I197" t="n">
+        <v>9</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="s">
+        <v>345</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="s">
+        <v>346</v>
+      </c>
+      <c r="N197"/>
+      <c r="O197" t="s">
+        <v>346</v>
+      </c>
+      <c r="P197"/>
+      <c r="Q197" t="s">
+        <v>346</v>
+      </c>
+      <c r="R197" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>395</v>
+      </c>
+      <c r="B198" t="b">
+        <v>1</v>
+      </c>
+      <c r="C198" t="s">
+        <v>18</v>
+      </c>
+      <c r="D198" t="s">
+        <v>19</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="s">
+        <v>29</v>
+      </c>
+      <c r="I198" t="n">
+        <v>9</v>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="s">
+        <v>345</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+      <c r="M198" t="s">
+        <v>346</v>
+      </c>
+      <c r="N198"/>
+      <c r="O198" t="s">
+        <v>346</v>
+      </c>
+      <c r="P198"/>
+      <c r="Q198" t="s">
+        <v>346</v>
+      </c>
+      <c r="R198" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>396</v>
+      </c>
+      <c r="B199" t="b">
+        <v>1</v>
+      </c>
+      <c r="C199" t="s">
+        <v>18</v>
+      </c>
+      <c r="D199" t="s">
+        <v>19</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="s">
+        <v>29</v>
+      </c>
+      <c r="I199" t="n">
+        <v>9</v>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="s">
+        <v>345</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="s">
+        <v>346</v>
+      </c>
+      <c r="N199"/>
+      <c r="O199" t="s">
+        <v>346</v>
+      </c>
+      <c r="P199"/>
+      <c r="Q199" t="s">
+        <v>346</v>
+      </c>
+      <c r="R199" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>400</v>
+      </c>
+      <c r="B200" t="b">
+        <v>1</v>
+      </c>
+      <c r="C200" t="s">
+        <v>18</v>
+      </c>
+      <c r="D200" t="s">
+        <v>19</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="s">
+        <v>38</v>
+      </c>
+      <c r="I200" t="n">
+        <v>9</v>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="s">
+        <v>391</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="s">
+        <v>346</v>
+      </c>
+      <c r="N200"/>
+      <c r="O200" t="s">
+        <v>346</v>
+      </c>
+      <c r="P200"/>
+      <c r="Q200" t="s">
+        <v>346</v>
+      </c>
+      <c r="R200" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>401</v>
+      </c>
+      <c r="B201" t="b">
+        <v>1</v>
+      </c>
+      <c r="C201" t="s">
+        <v>18</v>
+      </c>
+      <c r="D201" t="s">
+        <v>19</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="s">
+        <v>38</v>
+      </c>
+      <c r="I201" t="n">
+        <v>9</v>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="s">
+        <v>391</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="s">
+        <v>346</v>
+      </c>
+      <c r="N201"/>
+      <c r="O201" t="s">
+        <v>346</v>
+      </c>
+      <c r="P201"/>
+      <c r="Q201" t="s">
+        <v>346</v>
+      </c>
+      <c r="R201" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>402</v>
+      </c>
+      <c r="B202" t="b">
+        <v>1</v>
+      </c>
+      <c r="C202" t="s">
+        <v>18</v>
+      </c>
+      <c r="D202" t="s">
+        <v>19</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="s">
+        <v>38</v>
+      </c>
+      <c r="I202" t="n">
+        <v>9</v>
+      </c>
+      <c r="J202" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" t="s">
+        <v>391</v>
+      </c>
+      <c r="L202" t="n">
+        <v>3</v>
+      </c>
+      <c r="M202" t="s">
+        <v>346</v>
+      </c>
+      <c r="N202"/>
+      <c r="O202" t="s">
+        <v>346</v>
+      </c>
+      <c r="P202"/>
+      <c r="Q202" t="s">
+        <v>346</v>
+      </c>
+      <c r="R202" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>406</v>
+      </c>
+      <c r="B203" t="b">
+        <v>0</v>
+      </c>
+      <c r="C203" t="s">
+        <v>18</v>
+      </c>
+      <c r="D203" t="s">
+        <v>19</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="s">
+        <v>46</v>
+      </c>
+      <c r="I203" t="n">
+        <v>9</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="s">
+        <v>345</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="s">
+        <v>399</v>
+      </c>
+      <c r="N203" t="n">
+        <v>14</v>
+      </c>
+      <c r="O203" t="s">
+        <v>400</v>
+      </c>
+      <c r="P203" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>349</v>
+      </c>
+      <c r="R203" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>407</v>
+      </c>
+      <c r="B204" t="b">
+        <v>0</v>
+      </c>
+      <c r="C204" t="s">
+        <v>18</v>
+      </c>
+      <c r="D204" t="s">
+        <v>19</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="s">
+        <v>46</v>
+      </c>
+      <c r="I204" t="n">
+        <v>9</v>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="s">
+        <v>345</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="s">
+        <v>401</v>
+      </c>
+      <c r="N204" t="n">
+        <v>14</v>
+      </c>
+      <c r="O204" t="s">
+        <v>402</v>
+      </c>
+      <c r="P204" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>349</v>
+      </c>
+      <c r="R204" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>408</v>
+      </c>
+      <c r="B205" t="b">
+        <v>0</v>
+      </c>
+      <c r="C205" t="s">
+        <v>18</v>
+      </c>
+      <c r="D205" t="s">
+        <v>19</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="s">
+        <v>46</v>
+      </c>
+      <c r="I205" t="n">
+        <v>9</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="s">
+        <v>345</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3</v>
+      </c>
+      <c r="M205" t="s">
+        <v>403</v>
+      </c>
+      <c r="N205" t="n">
+        <v>14</v>
+      </c>
+      <c r="O205" t="s">
+        <v>404</v>
+      </c>
+      <c r="P205" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>349</v>
+      </c>
+      <c r="R205" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>412</v>
+      </c>
+      <c r="B206" t="b">
+        <v>0</v>
+      </c>
+      <c r="C206" t="s">
+        <v>18</v>
+      </c>
+      <c r="D206" t="s">
+        <v>19</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>2</v>
+      </c>
+      <c r="H206" t="s">
+        <v>54</v>
+      </c>
+      <c r="I206" t="n">
+        <v>9</v>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="s">
+        <v>391</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="s">
+        <v>405</v>
+      </c>
+      <c r="N206" t="n">
+        <v>20</v>
+      </c>
+      <c r="O206" t="s">
+        <v>406</v>
+      </c>
+      <c r="P206" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>394</v>
+      </c>
+      <c r="R206" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>413</v>
+      </c>
+      <c r="B207" t="b">
+        <v>0</v>
+      </c>
+      <c r="C207" t="s">
+        <v>18</v>
+      </c>
+      <c r="D207" t="s">
+        <v>19</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="s">
+        <v>54</v>
+      </c>
+      <c r="I207" t="n">
+        <v>9</v>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="s">
+        <v>391</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="s">
+        <v>407</v>
+      </c>
+      <c r="N207" t="n">
+        <v>20</v>
+      </c>
+      <c r="O207" t="s">
+        <v>408</v>
+      </c>
+      <c r="P207" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>394</v>
+      </c>
+      <c r="R207" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>414</v>
+      </c>
+      <c r="B208" t="b">
+        <v>0</v>
+      </c>
+      <c r="C208" t="s">
+        <v>18</v>
+      </c>
+      <c r="D208" t="s">
+        <v>19</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H208" t="s">
+        <v>54</v>
+      </c>
+      <c r="I208" t="n">
+        <v>9</v>
+      </c>
+      <c r="J208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" t="s">
+        <v>391</v>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="s">
+        <v>409</v>
+      </c>
+      <c r="N208" t="n">
+        <v>20</v>
+      </c>
+      <c r="O208" t="s">
+        <v>410</v>
+      </c>
+      <c r="P208" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>394</v>
+      </c>
+      <c r="R208" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>418</v>
+      </c>
+      <c r="B209" t="b">
+        <v>1</v>
+      </c>
+      <c r="C209" t="s">
+        <v>18</v>
+      </c>
+      <c r="D209" t="s">
+        <v>19</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="s">
+        <v>61</v>
+      </c>
+      <c r="I209" t="n">
+        <v>9</v>
+      </c>
+      <c r="J209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" t="s">
+        <v>345</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="s">
+        <v>346</v>
+      </c>
+      <c r="N209"/>
+      <c r="O209" t="s">
+        <v>346</v>
+      </c>
+      <c r="P209"/>
+      <c r="Q209" t="s">
+        <v>346</v>
+      </c>
+      <c r="R209" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>419</v>
+      </c>
+      <c r="B210" t="b">
+        <v>1</v>
+      </c>
+      <c r="C210" t="s">
+        <v>18</v>
+      </c>
+      <c r="D210" t="s">
+        <v>19</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="s">
+        <v>61</v>
+      </c>
+      <c r="I210" t="n">
+        <v>9</v>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="s">
+        <v>345</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="s">
+        <v>346</v>
+      </c>
+      <c r="N210"/>
+      <c r="O210" t="s">
+        <v>346</v>
+      </c>
+      <c r="P210"/>
+      <c r="Q210" t="s">
+        <v>346</v>
+      </c>
+      <c r="R210" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>420</v>
+      </c>
+      <c r="B211" t="b">
+        <v>1</v>
+      </c>
+      <c r="C211" t="s">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>19</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="s">
+        <v>61</v>
+      </c>
+      <c r="I211" t="n">
+        <v>9</v>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="s">
+        <v>345</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3</v>
+      </c>
+      <c r="M211" t="s">
+        <v>346</v>
+      </c>
+      <c r="N211"/>
+      <c r="O211" t="s">
+        <v>346</v>
+      </c>
+      <c r="P211"/>
+      <c r="Q211" t="s">
+        <v>346</v>
+      </c>
+      <c r="R211" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>424</v>
+      </c>
+      <c r="B212" t="b">
+        <v>1</v>
+      </c>
+      <c r="C212" t="s">
+        <v>18</v>
+      </c>
+      <c r="D212" t="s">
+        <v>19</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H212" t="s">
+        <v>68</v>
+      </c>
+      <c r="I212" t="n">
+        <v>9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="s">
+        <v>391</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="s">
+        <v>346</v>
+      </c>
+      <c r="N212"/>
+      <c r="O212" t="s">
+        <v>346</v>
+      </c>
+      <c r="P212"/>
+      <c r="Q212" t="s">
+        <v>346</v>
+      </c>
+      <c r="R212" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>425</v>
+      </c>
+      <c r="B213" t="b">
+        <v>1</v>
+      </c>
+      <c r="C213" t="s">
+        <v>18</v>
+      </c>
+      <c r="D213" t="s">
+        <v>19</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H213" t="s">
+        <v>68</v>
+      </c>
+      <c r="I213" t="n">
+        <v>9</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="s">
+        <v>391</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="s">
+        <v>346</v>
+      </c>
+      <c r="N213"/>
+      <c r="O213" t="s">
+        <v>346</v>
+      </c>
+      <c r="P213"/>
+      <c r="Q213" t="s">
+        <v>346</v>
+      </c>
+      <c r="R213" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>426</v>
+      </c>
+      <c r="B214" t="b">
+        <v>1</v>
+      </c>
+      <c r="C214" t="s">
+        <v>18</v>
+      </c>
+      <c r="D214" t="s">
+        <v>19</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="s">
+        <v>68</v>
+      </c>
+      <c r="I214" t="n">
+        <v>9</v>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="s">
+        <v>391</v>
+      </c>
+      <c r="L214" t="n">
+        <v>3</v>
+      </c>
+      <c r="M214" t="s">
+        <v>346</v>
+      </c>
+      <c r="N214"/>
+      <c r="O214" t="s">
+        <v>346</v>
+      </c>
+      <c r="P214"/>
+      <c r="Q214" t="s">
+        <v>346</v>
+      </c>
+      <c r="R214" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>430</v>
+      </c>
+      <c r="B215" t="b">
+        <v>0</v>
+      </c>
+      <c r="C215" t="s">
+        <v>18</v>
+      </c>
+      <c r="D215" t="s">
+        <v>19</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H215" t="s">
+        <v>75</v>
+      </c>
+      <c r="I215" t="n">
+        <v>9</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="s">
+        <v>345</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="s">
+        <v>411</v>
+      </c>
+      <c r="N215" t="n">
+        <v>14</v>
+      </c>
+      <c r="O215" t="s">
+        <v>412</v>
+      </c>
+      <c r="P215" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>349</v>
+      </c>
+      <c r="R215" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>431</v>
+      </c>
+      <c r="B216" t="b">
+        <v>0</v>
+      </c>
+      <c r="C216" t="s">
+        <v>18</v>
+      </c>
+      <c r="D216" t="s">
+        <v>19</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H216" t="s">
+        <v>75</v>
+      </c>
+      <c r="I216" t="n">
+        <v>9</v>
+      </c>
+      <c r="J216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K216" t="s">
+        <v>345</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2</v>
+      </c>
+      <c r="M216" t="s">
+        <v>413</v>
+      </c>
+      <c r="N216" t="n">
+        <v>14</v>
+      </c>
+      <c r="O216" t="s">
+        <v>414</v>
+      </c>
+      <c r="P216" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>349</v>
+      </c>
+      <c r="R216" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>432</v>
+      </c>
+      <c r="B217" t="b">
+        <v>0</v>
+      </c>
+      <c r="C217" t="s">
+        <v>18</v>
+      </c>
+      <c r="D217" t="s">
+        <v>19</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="s">
+        <v>75</v>
+      </c>
+      <c r="I217" t="n">
+        <v>9</v>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="s">
+        <v>345</v>
+      </c>
+      <c r="L217" t="n">
+        <v>3</v>
+      </c>
+      <c r="M217" t="s">
+        <v>415</v>
+      </c>
+      <c r="N217" t="n">
+        <v>14</v>
+      </c>
+      <c r="O217" t="s">
+        <v>416</v>
+      </c>
+      <c r="P217" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>349</v>
+      </c>
+      <c r="R217" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 32, 33, 34, 148, 149, 150, 152, 1652, 1653, 1654, 1692, 1693, 1750, 1751, 1754, 1755, 1772, 1773, 1774, 1825, 1826, 2054, 2058, 2177, 2179, 2227, 2229, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 35, 151, 1655, 1691, 1752, 1753, 1756, 1757, 1771, 1824, 1827, 1897, 1898, 1900, 2056, 2231, 2279, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 31, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1754, 1773, 1774, 1824, 1897, 2054, 2056, 2177, 2179, 2229, 2231, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 23, 32, 1653, 1692, 1753, 1755, 1756, 1757, 1771, 1772, 1825, 1826, 1827, 1898, 1900, 2058, 2227, 2279)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 34, 35, 148, 149, 150, 151, 152, 1653, 1654, 1655, 1692, 1693, 1751, 1752, 1753, 1755, 1757, 1771, 1774, 1824, 1825, 1826, 1897, 1900, 2054, 2177, 2179, 2227, 2231, 2281, 2282, 2283, 2288, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 32, 33, 1652, 1691, 1750, 1754, 1756, 1772, 1773, 1827, 1898, 2056, 2058, 2229, 2279, 2289, 2290, 2294)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 148, 150, 151, 152, 1652, 1653, 1654, 1692, 1751, 1752, 1754, 1755, 1824, 1897, 1898, 1900, 2054, 2227, 2231, 2281, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 149, 1655, 1691, 1693, 1750, 1753, 1756, 1757, 1773, 2056, 2058, 2229, 2279)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 148, 149, 150, 152, 1652, 1691, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 151, 1653, 1654, 1655, 1692, 1693, 1753, 1898, 2281, 2282, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 148, 150, 151, 1652, 1653, 1654, 1691, 1692, 1693, 1751, 1752, 1753, 1757, 1773, 1898, 2054, 2056, 2058, 2227, 2231, 2281, 2282, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 149, 152, 1655, 1750, 1754, 1755, 1756, 1824, 1897, 1900, 2229, 2279, 2283)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
@@ -107,1165 +107,1118 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 275, 276, 277, 278, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2033, 2037, 2119, 2120, 2121, 2124, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 222, 224, 226, 228, 279, 1722, 1868, 2027, 2029, 2035, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 222, 226, 228, 275, 276, 278, 279, 280, 1720, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 2029, 2033, 2035, 2037, 2120, 2121, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 224, 277, 1719, 1721, 1722, 1870, 2027, 2119, 2124, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 222, 224, 226, 275, 278, 279, 280, 1719, 1720, 1727, 1775, 1776, 1779, 1868, 1869, 1870, 2029, 2035, 2037, 2120, 2124, 2125, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 228, 276, 277, 1721, 1722, 1777, 1778, 2027, 2033, 2119, 2121, 2127, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 43, 222, 226, 1719, 1720, 1721, 1722, 1778, 1869, 1870, 2027, 2033, 2119, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(224, 228, 1727, 1775, 1776, 1777, 1779, 1868, 2029, 2035, 2037, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 222, 228, 1719, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2033, 2120, 2121, 2124, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 224, 226, 1720, 1722, 2029, 2035, 2037, 2119, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 226, 228, 1720, 1722, 1775, 1776, 1777, 1779, 1870, 2027, 2029, 2033, 2035, 2119, 2120, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 222, 224, 1719, 1721, 1727, 1778, 1868, 1869, 2037, 2121, 2224)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 210, 211, 212, 213, 214, 216, 217, 218, 219, 265, 267, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 207, 208, 209, 215, 220, 266, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 206, 207, 208, 210, 211, 212, 213, 214, 216, 217, 219, 220, 265, 266, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 209, 215, 218, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 206, 208, 209, 210, 211, 212, 215, 216, 217, 218, 219, 220, 267, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 205, 207, 213, 214, 265, 266, 1899, 2230)</t>
+    <t xml:space="preserve">c(201, 203, 206, 207, 208, 209, 210, 211, 212, 213, 214, 216, 218, 219, 266, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 205, 217, 220, 267, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 216, 217, 218, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 207, 211, 213, 214, 217, 218, 219, 220, 267, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 206, 208, 209, 210, 212, 216, 266, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 204, 206, 207, 209, 210, 211, 212, 213, 214, 217, 219, 220, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 205, 208, 216, 218, 266, 267, 1899)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 130, 131, 132, 141, 142, 143, 177, 179, 180, 182, 227, 229, 230, 231, 233, 234, 235, 243, 245, 246, 247, 248, 250, 272, 273, 274, 282, 283, 284, 285, 286, 287, 289, 290, 291, 293, 294, 295, 296, 1718, 1760, 1762, 1763, 1764, 1765, 1766, 1840, 1852, 1863, 1864, 1865, 1866, 1874, 1875, 1935, 1990, 1991, 2028, 2036, 2108, 2129, 2130, 2133, 2134, 2135, 2136, 2138, 2139, 2222, 2223, 2225, 2300, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 140, 175, 176, 178, 181, 221, 223, 225, 236, 244, 249, 271, 281, 288, 292, 1716, 1717, 1761, 1838, 1839, 1867, 1876, 1992, 2026, 2030, 2032, 2034, 2109, 2128, 2131, 2132, 2137, 2194, 2226, 2257, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 
-2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 70, 71, 72, 73, 131, 132, 141, 142, 175, 177, 178, 179, 180, 182, 223, 231, 234, 235, 244, 245, 246, 247, 248, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 289, 291, 293, 295, 296, 1716, 1717, 1718, 1761, 1763, 1766, 1838, 1852, 1863, 1866, 1874, 1876, 1935, 1991, 1992, 2028, 2030, 2032, 2034, 2109, 2128, 2129, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2222, 2225, 2226, 2257, 2300, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 130, 140, 143, 176, 181, 221, 225, 227, 229, 230, 233, 236, 243, 249, 250, 288, 290, 292, 294, 1760, 1762, 1764, 1765, 1839, 1840, 1864, 1865, 1867, 1875, 1990, 2026, 2036, 2108, 2130, 2136, 2223, 2301, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 71, 73, 140, 141, 142, 143, 175, 176, 177, 178, 180, 181, 221, 223, 225, 227, 229, 231, 233, 234, 236, 243, 246, 249, 271, 272, 273, 274, 282, 283, 284, 287, 292, 294, 295, 1716, 1717, 1718, 1760, 1761, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1867, 1874, 1876, 1935, 1990, 1991, 2028, 2030, 2032, 2034, 2108, 2130, 2132, 2133, 2134, 2135, 2136, 2138, 2139, 2194, 2222, 2223, 2226, 2257, 2300, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 72, 130, 131, 132, 179, 182, 230, 235, 244, 245, 247, 248, 250, 281, 285, 286, 288, 289, 290, 291, 293, 296, 1762, 1763, 1865, 1866, 1875, 1992, 2026, 2036, 2109, 2128, 2129, 2131, 2137, 2225, 2301, 2313)</t>
+    <t xml:space="preserve">c(13, 15, 130, 131, 132, 141, 177, 179, 221, 223, 225, 227, 229, 230, 231, 234, 235, 236, 244, 245, 248, 249, 281, 282, 283, 285, 286, 287, 288, 289, 290, 291, 293, 294, 295, 296, 1717, 1763, 1838, 1839, 1864, 1865, 1866, 1874, 1875, 1991, 1992, 2028, 2030, 2032, 2036, 2108, 2109, 2131, 2132, 2133, 2135, 2137, 2138, 2139, 2222, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 140, 142, 143, 176, 178, 180, 181, 182, 233, 243, 246, 250, 284, 292, 1716, 1718, 1760, 1761, 1762, 1840, 1852, 1863, 1867, 1876, 1990, 2026, 2034, 2128, 2129, 2130, 2134, 2136, 2194, 2223)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 130, 131, 132, 140, 141, 142, 143, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
+2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 131, 140, 141, 142, 143, 177, 179, 180, 182, 223, 227, 231, 233, 234, 235, 236, 243, 244, 245, 246, 249, 250, 281, 282, 283, 285, 286, 287, 290, 291, 292, 293, 294, 295, 296, 1716, 1760, 1763, 1839, 1840, 1863, 1864, 1866, 1867, 1874, 1991, 1992, 2026, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2133, 2134, 2139, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 130, 132, 176, 178, 181, 221, 225, 229, 230, 248, 284, 288, 289, 1717, 1718, 1761, 1762, 1838, 1852, 1865, 1875, 1876, 1990, 2028, 2030, 2132, 2135, 2136, 2137, 2138, 2194, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 130, 131, 132, 142, 143, 177, 178, 179, 180, 182, 221, 225, 227, 231, 233, 235, 236, 243, 244, 246, 249, 250, 281, 282, 283, 284, 285, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1864, 1866, 1874, 1876, 1990, 2026, 2028, 2030, 2108, 2109, 2128, 2129, 2131, 2132, 2133, 2134, 2137, 2138, 2139, 2222, 2223, 2225, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 140, 141, 176, 181, 223, 229, 230, 234, 245, 248, 286, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1865, 1867, 1875, 1991, 1992, 2032, 2034, 2036, 2130, 2135, 2136, 2194, 2226, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 34, 148, 149, 152, 1654, 1655, 1692, 1693, 1750, 1753, 1754, 1756, 1757, 1771, 1774, 1824, 1825, 1826, 1897, 1900, 2054, 2056, 2058, 2179, 2229, 2279, 2281, 2282, 2283, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 32, 33, 35, 150, 151, 1652, 1653, 1691, 1751, 1752, 1755, 1772, 1773, 1827, 1898, 2177, 2227, 2231, 2288)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 23, 31, 32, 33, 34, 35, 149, 151, 1652, 1653, 1655, 1691, 1752, 1754, 1755, 1756, 1757, 1773, 1774, 1824, 1825, 1827, 1897, 1898, 1900, 2054, 2058, 2177, 2227, 2231, 2281, 2282, 2283, 2288, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 148, 150, 152, 1654, 1692, 1693, 1750, 1751, 1753, 1771, 1772, 1826, 2056, 2179, 2229, 2279, 2289, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 148, 149, 150, 152, 1652, 1653, 1655, 1691, 1692, 1693, 1751, 1754, 1755, 1756, 1757, 1772, 1773, 1774, 1825, 1826, 1827, 1897, 1900, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2288, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 34, 35, 151, 1654, 1750, 1752, 1753, 1771, 1824, 1898, 2054, 2281, 2283, 2289, 2290, 2292, 2293, 2295)</t>
+    <t xml:space="preserve">c(17, 23, 150, 151, 152, 1652, 1653, 1655, 1692, 1693, 1750, 1751, 1755, 1756, 1773, 1824, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 148, 149, 1654, 1691, 1752, 1753, 1754, 1757, 1897, 1898, 2282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 148, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1897, 1898, 1900, 2054, 2058, 2229, 2231, 2281, 2282, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 149, 150, 1757, 1773, 1824, 2056, 2227, 2279, 2283, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 148, 150, 151, 152, 1652, 1654, 1692, 1693, 1752, 1753, 1754, 1755, 1756, 1757, 1824, 1897, 2054, 2056, 2227, 2229, 2279, 2281, 2282, 2283, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 149, 1653, 1655, 1691, 1750, 1751, 1773, 1898, 1900, 2058, 2231, 2290)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 226, 228, 275, 278, 279, 280, 1722, 1727, 1775, 1776, 1779, 1868, 1869, 2033, 2035, 2037, 2120, 2121, 2124, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 224, 276, 277, 1719, 1720, 1721, 1777, 1778, 1870, 2027, 2029, 2119, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 275, 276, 1719, 1721, 1722, 1727, 1776, 1777, 1779, 1868, 1869, 2029, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 277, 278, 279, 280, 1720, 1775, 1778, 1870, 2027, 2033, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 224, 226, 275, 276, 277, 279, 280, 1719, 1776, 1777, 1779, 1868, 1869, 2027, 2033, 2035, 2037, 2119, 2121, 2124, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 228, 278, 1720, 1721, 1722, 1727, 1775, 1778, 1870, 2029, 2120, 2125, 2224)</t>
+    <t xml:space="preserve">c(42, 43, 226, 228, 1719, 1720, 1722, 1727, 1777, 1868, 1869, 1870, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2125, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 222, 224, 1721, 1775, 1776, 1778, 1779, 2027, 2124, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 226, 228, 1719, 1720, 1727, 1775, 1777, 1778, 1779, 1868, 2033, 2037, 2121, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(224, 1721, 1722, 1776, 1869, 1870, 2027, 2029, 2035, 2119, 2120, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 222, 224, 226, 1719, 1722, 1727, 1775, 1776, 1777, 1779, 1869, 2033, 2035, 2037, 2119, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 228, 1720, 1721, 1778, 1868, 1870, 2027, 2029, 2120, 2121, 2126)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 203, 204, 206, 208, 209, 210, 212, 214, 215, 216, 218, 220, 265, 266, 267, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 207, 211, 213, 217, 219, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 208, 209, 210, 211, 212, 214, 215, 216, 217, 218, 220, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 213, 219, 265, 266, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 205, 206, 207, 210, 211, 213, 214, 216, 217, 219, 265, 266, 267, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 208, 209, 212, 215, 218, 220, 1899, 2230)</t>
+    <t xml:space="preserve">c(201, 202, 203, 206, 207, 208, 210, 211, 213, 217, 219, 220, 266, 267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 209, 212, 214, 216, 218, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 207, 208, 210, 212, 213, 216, 217, 266, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 206, 209, 211, 214, 218, 219, 220, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 210, 211, 212, 216, 217, 219, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 213, 214, 218, 220, 266, 267, 2232)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 71, 72, 73, 131, 132, 141, 142, 143, 175, 176, 177, 179, 181, 182, 223, 225, 227, 229, 230, 231, 234, 235, 236, 243, 244, 245, 248, 249, 250, 271, 274, 281, 282, 284, 286, 287, 288, 289, 290, 294, 296, 1717, 1718, 1762, 1764, 1765, 1766, 1838, 1863, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2222, 2223, 2225, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 70, 130, 140, 178, 180, 221, 233, 246, 247, 272, 273, 283, 285, 291, 292, 293, 295, 1716, 1760, 1761, 1763, 1839, 1840, 1852, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 2036, 2194, 2226, 2257, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 70, 71, 73, 131, 132, 140, 142, 143, 175, 177, 178, 179, 181, 182, 225, 227, 229, 230, 231, 235, 236, 243, 244, 245, 248, 250, 272, 273, 281, 282, 283, 285, 286, 288, 289, 290, 291, 293, 294, 295, 296, 1716, 1717, 1761, 1764, 1838, 1852, 1863, 1865, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2030, 2032, 2034, 2036, 2128, 2129, 2130, 2132, 2133, 2135, 2136, 2137, 2138, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 72, 130, 141, 176, 180, 221, 223, 233, 234, 246, 247, 249, 271, 274, 284, 287, 292, 1718, 1760, 1762, 1763, 1765, 1766, 1839, 1840, 1864, 1866, 1867, 1935, 2028, 2108, 2109, 2131, 2134, 2139, 2194, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 73, 132, 140, 143, 177, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 234, 235, 236, 244, 245, 246, 247, 250, 274, 283, 284, 285, 287, 288, 291, 292, 293, 294, 295, 296, 1716, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1852, 1863, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2108, 2129, 2130, 2131, 2133, 2134, 2135, 2136, 2137, 2222, 2223, 2225, 2300, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 71, 130, 131, 141, 142, 175, 176, 178, 179, 233, 243, 248, 249, 271, 272, 273, 281, 282, 286, 289, 290, 1717, 1718, 1760, 1840, 1864, 1865, 1935, 2036, 2109, 2128, 2132, 2138, 2139, 2194, 2226, 2257, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 23, 33, 34, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1692, 1693, 1751, 1752, 1754, 1755, 1771, 1772, 1824, 1825, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 31, 32, 35, 1653, 1691, 1750, 1753, 1756, 1757, 1773, 1774, 1826, 1827, 1897, 2279, 2281, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 31, 32, 35, 148, 149, 152, 1652, 1653, 1655, 1691, 1692, 1693, 1751, 1754, 1755, 1756, 1771, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 1900, 2056, 2058, 2177, 2229, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 33, 34, 150, 151, 1654, 1750, 1752, 1753, 1757, 1772, 1827, 2054, 2179, 2227, 2231, 2283, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 33, 34, 35, 148, 149, 150, 152, 1652, 1654, 1691, 1692, 1693, 1753, 1756, 1757, 1771, 1773, 1824, 1825, 1826, 1897, 1898, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 31, 32, 151, 1653, 1655, 1750, 1751, 1752, 1754, 1755, 1772, 1774, 1827, 1900, 2054, 2056, 2281, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 224, 226, 276, 277, 278, 279, 280, 1722, 1775, 1777, 1778, 1779, 1868, 1870, 2027, 2029, 2119, 2120, 2121, 2124, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(222, 228, 275, 1719, 1720, 1721, 1727, 1776, 1869, 2033, 2035, 2037, 2125, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 276, 278, 279, 280, 1720, 1721, 1722, 1727, 1777, 1778, 1868, 1870, 2029, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 224, 226, 228, 275, 277, 1719, 1775, 1776, 1779, 1869, 2027, 2033, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 222, 224, 228, 275, 276, 278, 1719, 1721, 1722, 1775, 1776, 1778, 1779, 1869, 1870, 2029, 2033, 2035, 2119, 2121, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 226, 277, 279, 280, 1720, 1727, 1777, 1868, 2027, 2037, 2120, 2124, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 205, 207, 208, 209, 210, 212, 214, 215, 217, 218, 219, 220, 266, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 206, 211, 213, 216, 265, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 206, 207, 208, 211, 212, 213, 215, 216, 217, 219, 265, 266, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 209, 210, 214, 218, 220, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 209, 212, 213, 214, 215, 216, 218, 220, 266, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(208, 210, 211, 217, 219, 265, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 70, 71, 72, 73, 130, 132, 142, 143, 175, 176, 177, 179, 181, 182, 221, 223, 225, 227, 229, 230, 233, 234, 235, 243, 247, 248, 249, 271, 272, 274, 282, 283, 284, 286, 287, 289, 290, 292, 294, 295, 296, 1718, 1761, 1764, 1839, 1840, 1864, 1865, 1867, 1874, 1875, 1990, 1991, 1992, 2028, 2032, 2036, 2108, 2109, 2128, 2129, 2130, 2132, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 131, 140, 141, 178, 180, 231, 236, 244, 245, 246, 250, 273, 281, 285, 288, 291, 293, 1716, 1717, 1760, 1762, 1763, 1765, 1766, 1838, 1852, 1863, 1866, 1876, 1935, 2026, 2030, 2034, 2131, 2133, 2134, 2135, 2300, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 130, 132, 143, 175, 176, 178, 180, 181, 221, 223, 225, 227, 229, 230, 231, 233, 235, 243, 244, 245, 247, 248, 249, 250, 272, 273, 274, 281, 282, 283, 284, 285, 286, 288, 289, 291, 292, 294, 1717, 1718, 1760, 1761, 1763, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2108, 2129, 2131, 2132, 2134, 2135, 2136, 2137, 2138, 2225, 2226, 2257, 2300, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 131, 140, 141, 142, 177, 179, 182, 234, 236, 246, 271, 287, 290, 293, 295, 296, 1716, 1762, 1764, 1765, 1766, 1838, 1840, 1874, 2030, 2109, 2128, 2130, 2133, 2139, 2194, 2222, 2223, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 143, 175, 178, 179, 221, 223, 225, 227, 229, 230, 231, 233, 243, 244, 245, 246, 247, 249, 250, 272, 274, 281, 283, 286, 287, 289, 290, 291, 293, 294, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1838, 1840, 1852, 1863, 1864, 1865, 1874, 1876, 1992, 2026, 2028, 2030, 2032, 2036, 2128, 2130, 2133, 2135, 2136, 2139, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 142, 176, 177, 180, 181, 182, 234, 235, 236, 248, 271, 273, 282, 284, 285, 288, 292, 295, 1717, 1766, 1839, 1866, 1867, 1875, 1935, 1990, 1991, 2034, 2108, 2109, 2129, 2131, 2132, 2134, 2137, 2138, 2194, 2223, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 33, 34, 149, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1751, 1752, 1755, 1756, 1757, 1773, 1774, 1824, 1826, 1898, 2056, 2058, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 35, 148, 150, 1693, 1750, 1753, 1754, 1771, 1772, 1825, 1827, 1897, 1900, 2054, 2177, 2288, 2289, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 31, 32, 33, 35, 148, 149, 150, 151, 1652, 1653, 1691, 1692, 1693, 1752, 1754, 1755, 1756, 1771, 1772, 1774, 1826, 1827, 1897, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2281, 2282, 2283, 2289, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 34, 152, 1654, 1655, 1750, 1751, 1753, 1757, 1773, 1824, 1825, 2054, 2179, 2231, 2279, 2288, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 33, 34, 35, 149, 151, 152, 1652, 1653, 1692, 1693, 1750, 1752, 1753, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2229, 2231, 2281, 2282, 2283, 2289, 2290, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 32, 148, 150, 1654, 1655, 1691, 1751, 1754, 1755, 1756, 1826, 1827, 1898, 2227, 2279, 2288, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 226, 275, 277, 278, 280, 1720, 1721, 1727, 1775, 1776, 1778, 1869, 1870, 2029, 2033, 2035, 2120, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 228, 276, 279, 1719, 1722, 1777, 1779, 1868, 2027, 2037, 2119, 2121, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 224, 276, 277, 278, 279, 1719, 1721, 1722, 1727, 1777, 1778, 1868, 1869, 2027, 2033, 2035, 2037, 2119, 2121, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 222, 226, 228, 275, 280, 1720, 1775, 1776, 1779, 1870, 2029, 2120, 2124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 277, 279, 1720, 1721, 1727, 1775, 1776, 1777, 1779, 1868, 1870, 2027, 2029, 2035, 2037, 2120, 2121, 2124, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 275, 276, 278, 280, 1719, 1722, 1778, 1869, 2033, 2119, 2125, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 205, 206, 207, 208, 209, 212, 213, 214, 217, 218, 265, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 210, 211, 215, 216, 219, 220, 266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 206, 207, 208, 209, 210, 211, 214, 216, 217, 218, 265, 266, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 212, 213, 215, 219, 220, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 207, 209, 210, 212, 213, 215, 217, 218, 219, 220, 265, 266, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 206, 208, 211, 214, 216, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 73, 130, 131, 132, 140, 141, 143, 175, 176, 177, 223, 225, 227, 230, 234, 244, 245, 247, 250, 272, 273, 274, 282, 283, 284, 289, 290, 291, 292, 294, 295, 296, 1717, 1718, 1762, 1763, 1764, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1867, 1874, 1876, 1935, 1990, 1991, 2026, 2028, 2030, 2032, 2034, 2036, 2109, 2128, 2129, 2131, 2132, 2133, 2135, 2137, 2139, 2194, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 142, 178, 179, 180, 181, 182, 221, 229, 231, 233, 235, 236, 243, 246, 248, 249, 271, 281, 285, 286, 287, 288, 293, 1716, 1760, 1761, 1838, 1866, 1875, 1992, 2108, 2130, 2134, 2136, 2138, 2222, 2257, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 73, 131, 132, 140, 141, 142, 143, 175, 176, 177, 181, 221, 223, 225, 227, 230, 234, 243, 248, 249, 250, 271, 272, 273, 282, 286, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1764, 1765, 1838, 1839, 1840, 1863, 1866, 1867, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2108, 2128, 2131, 2132, 2133, 2134, 2135, 2194, 2222, 2223, 2257, 2300, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 130, 178, 179, 180, 182, 229, 231, 233, 235, 236, 244, 245, 246, 247, 274, 281, 283, 284, 285, 287, 288, 289, 1761, 1766, 1852, 1864, 1865, 1874, 2030, 2109, 2129, 2130, 2136, 2137, 2138, 2139, 2225, 2226, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 71, 72, 73, 130, 132, 140, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 227, 230, 231, 233, 234, 244, 245, 247, 248, 249, 250, 271, 274, 281, 282, 283, 284, 285, 291, 292, 294, 296, 1716, 1717, 1760, 1761, 1762, 1765, 1766, 1838, 1840, 1852, 1863, 1866, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2108, 2129, 2130, 2131, 2132, 2136, 2137, 2138, 2139, 2194, 2223, 2226, 2300, 2301, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 70, 131, 141, 142, 225, 229, 235, 236, 243, 246, 272, 273, 286, 287, 288, 289, 290, 293, 295, 1718, 1763, 1764, 1839, 1864, 1865, 1867, 1874, 1875, 2030, 2036, 2109, 2128, 2133, 2134, 2135, 2222, 2225, 2257, 2302)</t>
+    <t xml:space="preserve">c(14, 15, 130, 131, 142, 143, 176, 179, 180, 181, 182, 229, 233, 236, 244, 245, 246, 250, 281, 282, 283, 285, 288, 290, 291, 292, 293, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1840, 1852, 1863, 1864, 1865, 1866, 1874, 1875, 1876, 1992, 2026, 2028, 2030, 2034, 2036, 2108, 2109, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 132, 140, 141, 177, 178, 221, 223, 225, 227, 230, 231, 234, 235, 243, 248, 249, 284, 286, 287, 289, 294, 296, 1763, 1838, 1839, 1867, 1990, 1991, 2032, 2128, 2129, 2130, 2134, 2223)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 130, 131, 140, 141, 142, 143, 176, 178, 179, 180, 182, 223, 225, 230, 231, 233, 236, 244, 245, 246, 248, 249, 250, 281, 282, 283, 285, 287, 288, 290, 291, 294, 295, 296, 1718, 1762, 1840, 1852, 1863, 1864, 1866, 1867, 1874, 1875, 2026, 2030, 2034, 2036, 2108, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 132, 177, 181, 221, 227, 229, 234, 235, 243, 284, 286, 289, 292, 293, 1716, 1717, 1760, 1761, 1763, 1838, 1839, 1865, 1876, 1990, 1991, 1992, 2028, 2032, 2109, 2128, 2136, 2226, 2300, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 131, 132, 141, 142, 143, 178, 180, 181, 182, 221, 223, 229, 230, 231, 234, 235, 243, 245, 248, 250, 285, 286, 288, 289, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1852, 1863, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2034, 2036, 2109, 2128, 2129, 2132, 2133, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2300, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 130, 140, 176, 177, 179, 225, 227, 233, 236, 244, 246, 249, 281, 282, 283, 284, 287, 290, 291, 1716, 1839, 1840, 1864, 1865, 2030, 2032, 2108, 2130, 2131, 2134, 2135, 2225, 2301, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 149, 150, 151, 152, 1653, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1897, 1898, 2054, 2056, 2058, 2227, 2281, 2282, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 148, 1652, 1692, 1757, 1773, 1824, 1900, 2229, 2231, 2279, 2283, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 150, 152, 1652, 1653, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1753, 1755, 1756, 1757, 1897, 2054, 2229, 2231, 2279, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 148, 149, 151, 1692, 1754, 1773, 1824, 1898, 1900, 2056, 2058, 2227, 2281)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 148, 151, 152, 1652, 1653, 1691, 1693, 1750, 1751, 1754, 1755, 1756, 1773, 1824, 1897, 1900, 2054, 2056, 2058, 2227, 2229, 2281, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 149, 150, 1654, 1655, 1692, 1752, 1753, 1757, 1898, 2231, 2279)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 224, 226, 1719, 1720, 1721, 1722, 1778, 1779, 1868, 1869, 2027, 2033, 2035, 2119, 2120, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 222, 228, 1727, 1775, 1776, 1777, 1870, 2029, 2037, 2121, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 226, 228, 1719, 1720, 1722, 1775, 1776, 1777, 1869, 1870, 2027, 2029, 2119, 2121, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 224, 1721, 1727, 1778, 1779, 1868, 2033, 2035, 2037, 2120, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 226, 228, 1720, 1721, 1722, 1727, 1777, 1868, 1869, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 224, 1719, 1775, 1776, 1778, 1779, 1870, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 205, 207, 208, 211, 213, 214, 216, 217, 218, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 206, 209, 210, 212, 219, 220)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 205, 206, 207, 210, 211, 212, 213, 216, 217, 219, 266, 267, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 208, 209, 214, 218, 220, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 206, 207, 208, 209, 210, 212, 217, 218, 219, 220, 266, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 211, 213, 214, 216, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 130, 132, 140, 141, 142, 143, 176, 179, 180, 223, 225, 229, 230, 231, 233, 235, 236, 243, 244, 246, 249, 281, 282, 284, 285, 286, 287, 289, 291, 292, 294, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1840, 1863, 1864, 1865, 1867, 1875, 1876, 1990, 1991, 2026, 2030, 2032, 2034, 2036, 2108, 2128, 2129, 2131, 2132, 2133, 2135, 2137, 2139, 2194, 2222, 2226, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 131, 177, 178, 181, 182, 221, 227, 234, 245, 248, 250, 283, 288, 290, 293, 296, 1763, 1838, 1839, 1852, 1866, 1874, 1992, 2028, 2109, 2130, 2134, 2136, 2138, 2223, 2225, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 130, 131, 132, 140, 142, 143, 176, 178, 180, 182, 225, 227, 229, 230, 235, 243, 244, 246, 248, 250, 282, 283, 284, 285, 286, 287, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1838, 1839, 1852, 1865, 1867, 1991, 1992, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2133, 2134, 2136, 2137, 2138, 2194, 2222, 2223, 2225, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(141, 177, 179, 181, 221, 223, 231, 233, 234, 236, 245, 249, 281, 288, 289, 290, 291, 292, 1716, 1763, 1840, 1863, 1864, 1866, 1874, 1875, 1876, 1990, 2026, 2131, 2132, 2135, 2139, 2226, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 130, 132, 140, 141, 143, 177, 178, 182, 221, 223, 227, 229, 233, 234, 235, 243, 245, 246, 282, 285, 286, 287, 288, 289, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1867, 1874, 1875, 1991, 1992, 2030, 2032, 2034, 2036, 2109, 2128, 2129, 2130, 2133, 2134, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2301, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(131, 142, 176, 179, 180, 181, 225, 230, 231, 236, 244, 248, 249, 250, 281, 283, 284, 290, 291, 1716, 1762, 1865, 1876, 1990, 2026, 2028, 2108, 2131, 2132, 2135, 2136, 2222, 2300, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 148, 149, 150, 152, 1653, 1654, 1655, 1691, 1692, 1750, 1751, 1753, 1755, 1757, 1824, 1897, 1900, 2056, 2058, 2231, 2279, 2281, 2283, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 151, 1652, 1693, 1752, 1754, 1756, 1773, 1898, 2054, 2227, 2229, 2282, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 149, 150, 151, 152, 1652, 1653, 1655, 1692, 1750, 1753, 1754, 1756, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2279, 2281, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(148, 1654, 1691, 1693, 1751, 1752, 1755, 1757, 1773, 1824, 2231, 2282, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1752, 1754, 1756, 1757, 1773, 1897, 2054, 2056, 2058, 2227, 2229, 2231, 2281, 2282, 2283, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 148, 149, 1693, 1751, 1753, 1755, 1824, 1898, 1900, 2279, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 224, 226, 1719, 1720, 1776, 1777, 1778, 1868, 1869, 2029, 2033, 2035, 2037, 2120, 2124, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 228, 1721, 1722, 1727, 1775, 1779, 1870, 2027, 2119, 2121, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 226, 1719, 1721, 1775, 1777, 1778, 1779, 2027, 2029, 2033, 2035, 2119, 2120, 2121, 2124, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(224, 228, 1720, 1722, 1727, 1776, 1868, 1869, 1870, 2037, 2125, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 1719, 1720, 1721, 1775, 1776, 1868, 1870, 2027, 2033, 2119, 2121, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(228, 1722, 1727, 1777, 1778, 1779, 1869, 2029, 2035, 2037, 2120, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 207, 208, 209, 210, 211, 213, 214, 216, 218, 220, 266, 267, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 212, 217, 219, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 209, 212, 214, 216, 217, 218, 219, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 207, 208, 210, 211, 213, 220, 266, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 213, 214, 217, 218, 220, 266, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 208, 211, 212, 216, 219, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 140, 142, 143, 177, 178, 179, 180, 181, 221, 223, 225, 227, 229, 230, 231, 233, 234, 236, 243, 245, 246, 248, 249, 250, 281, 282, 283, 285, 286, 289, 291, 292, 293, 295, 296, 1716, 1718, 1760, 1763, 1838, 1839, 1852, 1863, 1865, 1876, 1990, 2030, 2032, 2034, 2108, 2109, 2130, 2131, 2132, 2133, 2135, 2136, 2138, 2139, 2222, 2223, 2226, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 130, 131, 132, 141, 176, 182, 235, 244, 284, 287, 288, 290, 294, 1717, 1761, 1762, 1840, 1864, 1866, 1867, 1874, 1875, 1991, 1992, 2026, 2028, 2036, 2128, 2129, 2134, 2137, 2194, 2225, 2300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 130, 131, 142, 176, 177, 178, 181, 182, 221, 223, 227, 229, 233, 234, 235, 236, 243, 244, 246, 248, 250, 281, 282, 283, 284, 285, 286, 287, 289, 290, 291, 294, 296, 1716, 1717, 1718, 1761, 1762, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1875, 1876, 1990, 1991, 2026, 2030, 2034, 2108, 2109, 2128, 2129, 2133, 2135, 2136, 2138, 2194, 2223, 2226, 2300, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 132, 140, 141, 143, 179, 180, 225, 230, 231, 245, 249, 288, 292, 293, 295, 1760, 1763, 1840, 1874, 1992, 2028, 2032, 2036, 2130, 2131, 2132, 2134, 2137, 2139, 2222, 2225, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 130, 140, 141, 142, 177, 178, 179, 180, 181, 223, 225, 227, 229, 231, 236, 244, 245, 248, 249, 250, 281, 282, 283, 287, 288, 290, 292, 293, 295, 296, 1716, 1717, 1718, 1760, 1838, 1839, 1840, 1864, 1865, 1866, 1867, 1874, 1876, 1991, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2132, 2134, 2135, 2136, 2137, 2139, 2222, 2223, 2225, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 131, 132, 143, 176, 182, 221, 230, 233, 234, 235, 243, 246, 284, 285, 286, 289, 291, 294, 1761, 1762, 1763, 1852, 1863, 1875, 1990, 1992, 2131, 2133, 2138, 2194, 2226, 2303, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(20, 23, 32, 33, 34, 150, 151, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1755, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1897, 1900, 2054, 2058, 2179, 2227, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 35, 148, 149, 152, 1652, 1655, 1754, 1756, 1757, 1827, 1898, 2056, 2177, 2229, 2281, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 32, 35, 150, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 1827, 1897, 1898, 2054, 2179, 2227, 2229, 2288, 2289, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 31, 33, 34, 148, 149, 152, 1752, 1825, 1900, 2056, 2058, 2177, 2231, 2279, 2281, 2282, 2283, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 34, 35, 148, 149, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1755, 1756, 1757, 1772, 1773, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2177, 2179, 2231, 2279, 2281, 2283, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 32, 33, 150, 151, 1693, 1751, 1752, 1753, 1754, 1771, 1774, 2056, 2058, 2227, 2229, 2282, 2288, 2289)</t>
+    <t xml:space="preserve">c(17, 18, 20, 150, 151, 152, 1653, 1655, 1691, 1692, 1751, 1752, 1753, 1754, 1756, 1757, 1824, 1898, 1900, 2054, 2056, 2058, 2227, 2231, 2279, 2282, 2283, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 23, 148, 149, 1652, 1654, 1693, 1750, 1755, 1773, 1897, 2229, 2281, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 150, 151, 152, 1652, 1654, 1655, 1691, 1692, 1750, 1752, 1753, 1754, 1755, 1773, 1824, 1897, 1900, 2054, 2058, 2227, 2229, 2279, 2281, 2282, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 148, 149, 1653, 1693, 1751, 1756, 1757, 1898, 2056, 2231, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 148, 149, 151, 1652, 1655, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1773, 1824, 2054, 2056, 2058, 2229, 2231, 2279, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 150, 152, 1653, 1654, 1691, 1692, 1756, 1757, 1897, 1898, 1900, 2227, 2281)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(44, 224, 226, 228, 276, 277, 278, 279, 280, 1719, 1721, 1722, 1775, 1777, 1778, 1868, 1870, 2027, 2029, 2035, 2119, 2121, 2124, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 275, 1720, 1727, 1776, 1779, 1869, 2033, 2037, 2120, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 224, 275, 276, 277, 278, 279, 1722, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2027, 2029, 2033, 2037, 2119, 2120, 2121, 2124, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 222, 226, 228, 280, 1719, 1720, 1721, 1727, 1868, 2035, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 224, 226, 228, 275, 280, 1720, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 2027, 2029, 2033, 2119, 2120, 2121, 2124, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(222, 276, 277, 278, 279, 1719, 1722, 1869, 1870, 2035, 2037, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 209, 213, 214, 215, 216, 217, 218, 220, 265, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(208, 210, 211, 212, 219, 266, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 205, 206, 208, 209, 210, 212, 215, 217, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 207, 211, 213, 214, 216, 218, 265)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 206, 207, 208, 209, 210, 211, 214, 215, 218, 219, 265, 266, 267, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 212, 213, 216, 217, 220, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 130, 132, 141, 175, 177, 178, 179, 180, 181, 182, 225, 231, 233, 234, 235, 243, 244, 248, 271, 272, 273, 274, 281, 283, 284, 287, 288, 289, 290, 291, 292, 293, 294, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1874, 1875, 1876, 1935, 1991, 1992, 2030, 2032, 2034, 2108, 2109, 2128, 2129, 2131, 2132, 2134, 2135, 2137, 2138, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 73, 131, 140, 142, 143, 176, 221, 223, 227, 229, 230, 236, 245, 246, 247, 249, 250, 282, 285, 286, 295, 1761, 1764, 1838, 1866, 1867, 1990, 2026, 2028, 2036, 2130, 2133, 2136, 2139, 2194, 2222, 2223, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 72, 73, 131, 141, 142, 143, 178, 179, 180, 181, 182, 221, 223, 225, 227, 230, 233, 234, 235, 243, 245, 247, 248, 249, 274, 281, 282, 283, 284, 286, 288, 289, 290, 291, 292, 293, 294, 295, 1717, 1718, 1761, 1762, 1765, 1766, 1838, 1840, 1852, 1863, 1864, 1865, 1867, 1874, 1876, 1935, 1990, 1991, 1992, 2028, 2030, 2036, 2108, 2109, 2128, 2129, 2131, 2134, 2136, 2137, 2139, 2194, 2222, 2226, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 71, 130, 132, 140, 175, 176, 177, 229, 231, 236, 244, 246, 250, 271, 272, 273, 285, 287, 296, 1716, 1760, 1763, 1764, 1839, 1866, 1875, 2026, 2032, 2034, 2130, 2132, 2133, 2135, 2138, 2223, 2225, 2257, 2300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 72, 73, 130, 132, 140, 142, 175, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 234, 235, 243, 244, 246, 247, 249, 250, 271, 272, 273, 281, 283, 287, 288, 290, 291, 292, 293, 294, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1838, 1852, 1863, 1866, 1867, 1876, 1935, 1991, 2028, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2132, 2134, 2136, 2139, 2194, 2225, 2257, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 131, 141, 143, 176, 177, 233, 236, 245, 248, 274, 282, 284, 285, 286, 289, 296, 1766, 1839, 1840, 1864, 1865, 1874, 1875, 1990, 1992, 2026, 2030, 2032, 2131, 2133, 2135, 2137, 2138, 2222, 2223, 2226, 2300, 2301, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 32, 34, 35, 148, 149, 150, 151, 152, 1653, 1654, 1655, 1691, 1693, 1750, 1753, 1755, 1756, 1771, 1772, 1773, 1824, 1825, 1826, 1827, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 31, 33, 1652, 1692, 1751, 1752, 1754, 1757, 1774, 1897, 1898, 2177, 2179, 2283, 2288, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 35, 149, 151, 152, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1773, 1774, 1826, 1897, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2231, 2281, 2282, 2283, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 32, 33, 34, 148, 150, 1652, 1756, 1757, 1771, 1772, 1824, 1825, 1827, 2054, 2179, 2279, 2288, 2289, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 33, 34, 148, 149, 151, 152, 1652, 1653, 1655, 1691, 1751, 1754, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 1898, 1900, 2054, 2056, 2179, 2227, 2229, 2231, 2281, 2283, 2288, 2289, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 35, 150, 1654, 1692, 1693, 1750, 1752, 1753, 1755, 1756, 1825, 1827, 1897, 2058, 2177, 2279, 2282, 2290, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 276, 279, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1870, 2035, 2037, 2119, 2121, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 224, 226, 228, 275, 277, 278, 1722, 1869, 2027, 2029, 2033, 2120, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 226, 228, 275, 276, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1777, 1778, 1779, 1870, 2027, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 224, 277, 1775, 1776, 1868, 1869, 2029, 2033, 2035, 2037, 2119, 2120)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 222, 224, 226, 228, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1776, 1778, 1869, 2027, 2029, 2033, 2035, 2037, 2121, 2124, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 275, 1727, 1775, 1777, 1779, 1868, 1870, 2119, 2120, 2125, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 210, 213, 215, 217, 218, 219, 220, 265, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 207, 211, 212, 214, 216, 266, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 206, 208, 209, 211, 214, 215, 216, 217, 219, 220, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 207, 210, 212, 213, 218, 265, 266, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 210, 213, 214, 215, 216, 218, 219, 266, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 207, 211, 212, 217, 220, 265, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 73, 130, 140, 141, 142, 143, 177, 178, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 236, 244, 245, 247, 248, 249, 271, 272, 273, 274, 281, 282, 283, 285, 286, 290, 291, 292, 294, 1717, 1718, 1760, 1762, 1764, 1765, 1838, 1840, 1863, 1864, 1865, 1866, 1874, 1876, 1935, 1990, 1991, 2026, 2028, 2030, 2032, 2034, 2036, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2139, 2194, 2223, 2257, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 131, 132, 175, 176, 179, 234, 235, 243, 246, 250, 284, 287, 288, 289, 293, 295, 296, 1716, 1761, 1763, 1766, 1839, 1852, 1867, 1875, 1992, 2108, 2109, 2135, 2136, 2137, 2138, 2222, 2225, 2226, 2300, 2301, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 130, 131, 132, 141, 142, 143, 175, 176, 177, 179, 181, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 246, 247, 249, 272, 273, 274, 281, 282, 284, 285, 287, 291, 292, 293, 294, 295, 296, 1716, 1718, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1865, 1866, 1867, 1875, 1876, 1935, 1991, 2030, 2032, 2034, 2036, 2108, 2128, 2129, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2222, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 73, 140, 178, 180, 182, 221, 244, 245, 248, 250, 271, 283, 286, 288, 289, 290, 1717, 1760, 1762, 1852, 1864, 1874, 1990, 1992, 2026, 2028, 2109, 2130, 2136, 2139, 2194, 2223, 2225, 2226, 2257, 2300, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 73, 131, 132, 140, 141, 142, 143, 175, 176, 177, 179, 180, 182, 221, 225, 230, 231, 233, 236, 243, 244, 245, 247, 249, 271, 272, 273, 274, 281, 282, 284, 286, 287, 289, 290, 291, 1716, 1717, 1718, 1760, 1762, 1765, 1766, 1840, 1852, 1864, 1867, 1875, 1876, 1990, 1992, 2026, 2028, 2032, 2034, 2108, 2109, 2128, 2130, 2132, 2133, 2136, 2137, 2138, 2139, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 71, 130, 178, 181, 223, 227, 229, 234, 235, 246, 248, 250, 283, 285, 288, 292, 293, 294, 295, 296, 1761, 1763, 1764, 1838, 1839, 1863, 1865, 1866, 1874, 1935, 1991, 2030, 2036, 2129, 2131, 2134, 2135, 2194, 2302)</t>
+    <t xml:space="preserve">c(42, 43, 222, 228, 1719, 1720, 1721, 1775, 1776, 1778, 1779, 1868, 1870, 2027, 2029, 2033, 2035, 2119, 2120, 2124, 2125, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 224, 226, 1722, 1727, 1777, 1869, 2037, 2121, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 228, 1719, 1720, 1721, 1722, 1776, 1777, 1779, 1868, 1869, 2029, 2033, 2035, 2037, 2119, 2120, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 224, 226, 1727, 1775, 1778, 1870, 2027, 2121, 2124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 224, 226, 228, 1720, 1721, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 2027, 2033, 2035, 2037, 2119, 2120, 2121, 2125, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 222, 1719, 1722, 1727, 1870, 2029, 2124, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 205, 206, 210, 212, 216, 217, 218, 220, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 204, 207, 208, 209, 211, 213, 214, 219)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 208, 213, 216, 217, 218, 266, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 209, 210, 211, 212, 214, 219, 220, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 208, 210, 213, 217, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(207, 209, 211, 212, 214, 216, 218, 219, 220)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 130, 131, 132, 140, 141, 142, 178, 179, 180, 181, 182, 221, 225, 229, 231, 233, 234, 235, 243, 244, 245, 246, 248, 250, 281, 282, 284, 286, 287, 290, 291, 292, 293, 296, 1760, 1761, 1762, 1763, 1838, 1840, 1852, 1863, 1864, 1865, 1867, 1874, 1876, 1991, 2026, 2028, 2032, 2108, 2109, 2128, 2130, 2131, 2133, 2134, 2136, 2138, 2139, 2225, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(143, 176, 177, 223, 227, 230, 236, 249, 283, 285, 288, 289, 294, 295, 1716, 1717, 1718, 1839, 1866, 1875, 1990, 1992, 2030, 2034, 2036, 2129, 2132, 2135, 2137, 2194, 2222, 2223, 2226, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 130, 132, 140, 142, 143, 176, 177, 180, 182, 221, 225, 227, 231, 233, 235, 236, 243, 246, 249, 250, 282, 283, 284, 285, 286, 287, 288, 290, 294, 295, 1717, 1718, 1760, 1761, 1763, 1839, 1840, 1852, 1864, 1865, 1867, 1874, 1875, 1991, 1992, 2030, 2032, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2223, 2226, 2300, 2301, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 131, 141, 178, 179, 181, 223, 229, 230, 234, 244, 245, 248, 281, 289, 291, 292, 293, 296, 1716, 1762, 1838, 1863, 1866, 1876, 1990, 2026, 2028, 2034, 2134, 2222, 2225, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 131, 140, 141, 142, 143, 176, 177, 178, 180, 182, 221, 223, 225, 227, 231, 233, 234, 236, 243, 244, 245, 246, 281, 282, 284, 285, 286, 287, 290, 291, 292, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1865, 1876, 1990, 2032, 2034, 2108, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2139, 2225, 2226, 2300, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 132, 179, 181, 229, 230, 235, 248, 249, 250, 283, 288, 289, 293, 294, 296, 1863, 1864, 1866, 1867, 1874, 1875, 1991, 1992, 2026, 2028, 2030, 2036, 2109, 2138, 2194, 2222, 2223, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 148, 149, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1757, 1773, 1824, 1897, 1898, 1900, 2054, 2056, 2227, 2231, 2282, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 150, 151, 152, 1652, 1753, 1755, 1756, 2058, 2229, 2279, 2281, 2283, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 148, 149, 150, 151, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1753, 1755, 1756, 1757, 1773, 1824, 1897, 2054, 2056, 2227, 2231, 2282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 152, 1654, 1693, 1754, 1898, 1900, 2058, 2229, 2279, 2281, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 149, 151, 152, 1652, 1654, 1655, 1692, 1693, 1750, 1751, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1900, 2054, 2227, 2231, 2279, 2281, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 148, 150, 1653, 1691, 1752, 1753, 1898, 2056, 2058, 2229, 2282, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 224, 1719, 1722, 1775, 1776, 1777, 1778, 1779, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2121, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 226, 228, 1720, 1721, 1727, 1868, 1869, 2120, 2124, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 224, 226, 228, 1719, 1721, 1775, 1776, 1778, 1868, 2027, 2037, 2119, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 1720, 1722, 1727, 1777, 1779, 1869, 1870, 2029, 2033, 2035, 2120)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 1719, 1721, 1722, 1727, 1778, 1868, 1869, 1870, 2027, 2029, 2035, 2037, 2119, 2121, 2124, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(226, 228, 1720, 1775, 1776, 1777, 1779, 2033, 2120, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 207, 208, 209, 210, 211, 212, 213, 216, 217, 220, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 206, 214, 218, 219, 266, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 211, 212, 216, 218, 219, 220, 266, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 208, 210, 213, 214, 217, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 206, 207, 208, 209, 210, 212, 214, 216, 217, 218, 266, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 205, 211, 213, 219, 220, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 131, 132, 141, 142, 176, 177, 178, 181, 182, 223, 229, 230, 231, 233, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 284, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1838, 1839, 1852, 1863, 1864, 1865, 1867, 1874, 1876, 1991, 1992, 2026, 2032, 2034, 2036, 2108, 2132, 2133, 2134, 2136, 2225, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 130, 140, 143, 179, 180, 221, 225, 227, 234, 235, 283, 285, 296, 1763, 1840, 1866, 1875, 1990, 2028, 2030, 2109, 2128, 2129, 2130, 2131, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 130, 132, 140, 142, 143, 176, 178, 179, 221, 225, 227, 229, 230, 233, 234, 235, 236, 243, 244, 248, 281, 282, 283, 285, 286, 287, 288, 292, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1838, 1840, 1852, 1864, 1865, 1866, 1874, 1875, 1876, 1992, 2028, 2030, 2108, 2128, 2129, 2130, 2132, 2133, 2134, 2137, 2138, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 131, 141, 177, 180, 181, 182, 223, 231, 245, 246, 249, 250, 284, 289, 290, 291, 293, 1763, 1839, 1863, 1867, 1990, 1991, 2026, 2032, 2034, 2036, 2109, 2131, 2135, 2136, 2139, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 130, 131, 140, 142, 177, 178, 179, 180, 181, 182, 221, 223, 234, 235, 236, 244, 248, 249, 250, 284, 285, 286, 287, 288, 290, 291, 293, 294, 296, 1716, 1760, 1761, 1838, 1839, 1840, 1863, 1865, 1866, 1867, 1875, 1990, 1991, 1992, 2028, 2032, 2034, 2036, 2108, 2129, 2131, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 132, 141, 143, 176, 225, 227, 229, 230, 231, 233, 243, 245, 246, 281, 282, 283, 289, 292, 295, 1717, 1718, 1762, 1763, 1852, 1864, 1874, 1876, 2026, 2030, 2109, 2128, 2130, 2132, 2136)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 35, 149, 150, 151, 152, 1652, 1654, 1692, 1750, 1751, 1752, 1753, 1756, 1757, 1771, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2283, 2288, 2289, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(31, 32, 33, 34, 148, 1653, 1655, 1691, 1693, 1754, 1755, 1772, 1773, 1774, 1897, 2177, 2179, 2281, 2282, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 1655, 1692, 1751, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 151, 152, 1652, 1653, 1654, 1691, 1693, 1750, 1752, 1772, 1773, 1898, 2058, 2177, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 35, 148, 149, 150, 152, 1652, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2179, 2227, 2229, 2231, 2281, 2282, 2283, 2289, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 32, 33, 34, 151, 1653, 1654, 1655, 1692, 1693, 1772, 1773, 1824, 1898, 2058, 2177, 2279, 2288, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1727, 1775, 1779, 1868, 1870, 2027, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1721, 1722, 1776, 1777, 1778, 1869, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 1719, 1720, 1721, 1722, 1779, 1868, 1869, 1870, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 1727, 1775, 1776, 1777, 1778, 2027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 1720, 1722, 1727, 1775, 1778, 1868, 1869, 1870, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 1719, 1721, 1776, 1777, 1779, 2027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 205, 206, 208, 212, 213, 214, 215, 217, 218, 220, 265, 266, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 207, 209, 210, 211, 216, 219, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 205, 206, 207, 208, 209, 210, 212, 213, 214, 215, 217, 218, 265, 267, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 211, 216, 219, 220, 266, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 206, 209, 211, 212, 213, 214, 217, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 207, 208, 210, 215, 216, 218, 219)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 131, 141, 142, 143, 177, 233, 234, 235, 236, 281, 283, 284, 287, 288, 289, 292, 293, 294, 295, 296, 1716, 1717, 1764, 1765, 1766, 1838, 1839, 1863, 1864, 1935, 1990, 1991, 1992, 2109, 2137, 2138, 2194, 2222, 2226, 2300, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 130, 132, 140, 229, 230, 231, 282, 285, 286, 290, 291, 1718, 1840, 1852, 1865, 2026, 2030, 2108, 2139, 2223, 2225, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 140, 141, 142, 177, 229, 231, 234, 281, 282, 285, 287, 289, 291, 293, 294, 295, 296, 1716, 1717, 1718, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2138, 2194, 2222, 2223, 2225, 2300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 131, 132, 143, 230, 233, 235, 236, 283, 284, 286, 288, 290, 292, 1764, 1838, 2137, 2139, 2226, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 130, 131, 140, 141, 143, 177, 230, 231, 233, 234, 281, 282, 283, 287, 289, 290, 293, 294, 296, 1717, 1718, 1764, 1766, 1838, 1839, 1840, 1852, 1865, 1935, 1990, 1992, 2108, 2109, 2137, 2138, 2194, 2222, 2223, 2225, 2226, 2300, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 132, 142, 229, 235, 236, 284, 285, 286, 288, 291, 292, 295, 1716, 1765, 1863, 1864, 1991, 2026, 2030, 2139, 2301, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 31, 32, 33, 34, 148, 149, 150, 152, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1753, 1754, 1756, 1771, 1774, 1825, 1827, 1900, 2054, 2056, 2058, 2179, 2229, 2231, 2281, 2282, 2283, 2288, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 35, 151, 1652, 1653, 1752, 1755, 1757, 1772, 1773, 1824, 1826, 1897, 1898, 2177, 2227, 2279, 2289, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 34, 35, 149, 152, 1652, 1653, 1654, 1691, 1693, 1750, 1752, 1753, 1756, 1757, 1771, 1772, 1824, 1825, 1827, 1897, 1898, 1900, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(33, 148, 150, 151, 1655, 1692, 1751, 1754, 1755, 1773, 1774, 1826, 2054, 2056, 2058, 2177, 2179, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 33, 34, 148, 149, 150, 152, 1655, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1757, 1771, 1773, 1774, 1824, 1825, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2279, 2282, 2288, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 35, 151, 1652, 1653, 1654, 1691, 1755, 1756, 1772, 1826, 1898, 2179, 2227, 2229, 2231, 2281, 2283, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1721, 1727, 1775, 1777, 1778, 1869, 2027, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1720, 1722, 1776, 1779, 1868, 1870, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 1719, 1721, 1727, 1775, 1777, 1778, 1779, 1868, 1870, 2027, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 1720, 1722, 1776, 1869, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 1719, 1721, 1722, 1727, 1777, 1778, 1779, 1869, 2027, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 1720, 1775, 1776, 1868, 1870, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 206, 207, 209, 211, 212, 214, 215, 217, 218, 219, 220, 265, 266, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 208, 210, 213, 216, 267, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 208, 209, 210, 211, 212, 213, 215, 219, 220, 266, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 214, 216, 217, 218, 265, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 265, 267, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 207, 208, 209, 220, 266, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 177, 231, 233, 234, 235, 281, 282, 283, 284, 285, 287, 288, 290, 291, 292, 293, 294, 296, 1716, 1718, 1764, 1765, 1838, 1839, 1863, 1864, 1865, 1935, 1991, 2026, 2108, 2109, 2138, 2139, 2223, 2226, 2300, 2301, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(140, 141, 142, 143, 229, 230, 236, 286, 289, 295, 1717, 1766, 1840, 1852, 1990, 1992, 2030, 2137, 2194, 2222, 2225, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 131, 132, 141, 143, 230, 231, 233, 234, 235, 236, 281, 284, 285, 286, 287, 292, 293, 1716, 1717, 1718, 1764, 1765, 1766, 1839, 1840, 1863, 1864, 1935, 1991, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 130, 140, 142, 177, 229, 282, 283, 288, 289, 290, 291, 294, 295, 296, 1838, 1852, 1865, 1990, 1992, 2026, 2301, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 130, 131, 132, 140, 143, 177, 229, 231, 233, 234, 236, 284, 287, 288, 289, 290, 291, 292, 294, 295, 296, 1717, 1718, 1764, 1766, 1838, 1840, 1864, 1865, 1935, 1990, 1992, 2026, 2030, 2108, 2139, 2194, 2222, 2223, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 141, 142, 230, 235, 281, 282, 283, 285, 286, 293, 1716, 1765, 1839, 1852, 1863, 1991, 2109, 2137, 2138, 2225, 2226, 2312)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 149, 150, 151, 1654, 1655, 1692, 1693, 1750, 1752, 1754, 1773, 1824, 1897, 1898, 1900, 2058, 2229, 2231, 2279, 2281, 2282, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(148, 152, 1652, 1653, 1691, 1751, 1753, 1755, 1756, 1757, 2054, 2056, 2227, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 149, 151, 1652, 1653, 1692, 1693, 1751, 1752, 1755, 1757, 1773, 1824, 1897, 1898, 1900, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 148, 150, 152, 1654, 1655, 1691, 1750, 1753, 1754, 1756, 2054, 2282, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 149, 151, 152, 1653, 1654, 1655, 1691, 1692, 1750, 1751, 1752, 1755, 1756, 1773, 1898, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 148, 150, 1652, 1693, 1753, 1754, 1757, 1824, 1897, 1900, 2054, 2283, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + ADF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 1719, 1720, 1722, 1727, 1777, 1779, 1869, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 1721, 1775, 1776, 1778, 1868)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 1719, 1721, 1727, 1775, 1776, 1777, 1868, 1869, 1870, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 1720, 1722, 1778, 1779, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 1719, 1720, 1721, 1775, 1776, 1777, 1779, 1868, 1869, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 1722, 1727, 1778, 1870, 2027, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 206, 207, 208, 209, 210, 211, 212, 213, 216, 218, 219, 266, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 214, 217, 220, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 207, 210, 212, 214, 216, 217, 219, 220, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 206, 208, 209, 211, 213, 218, 266)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 207, 209, 210, 211, 212, 213, 216, 217, 218, 219, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 205, 206, 208, 214, 220, 266, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 142, 143, 229, 230, 231, 234, 235, 236, 282, 286, 287, 288, 290, 292, 293, 294, 295, 1716, 1717, 1718, 1838, 1840, 1852, 1863, 1864, 1990, 1991, 1992, 2026, 2108, 2109, 2137, 2138, 2139, 2194, 2225, 2226, 2300, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(131, 132, 140, 141, 177, 233, 281, 283, 284, 285, 289, 291, 296, 1839, 1865, 2030, 2222, 2223, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 131, 132, 141, 142, 229, 230, 233, 236, 282, 283, 285, 286, 288, 289, 291, 292, 293, 295, 296, 1716, 1717, 1718, 1838, 1840, 1863, 1864, 1865, 1991, 1992, 2030, 2109, 2137, 2139, 2223, 2225, 2226, 2300, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(140, 143, 177, 231, 234, 235, 281, 284, 287, 290, 294, 1839, 1852, 1990, 2026, 2108, 2138, 2194, 2222, 2301, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(131, 140, 141, 142, 143, 177, 231, 234, 283, 284, 286, 287, 288, 290, 291, 292, 294, 295, 296, 1716, 1717, 1718, 1838, 1839, 1852, 1863, 1864, 1865, 1990, 2026, 2108, 2109, 2138, 2139, 2194, 2223, 2225, 2226, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 132, 229, 230, 233, 235, 236, 281, 282, 285, 289, 293, 1840, 1991, 1992, 2030, 2137, 2222, 2300, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 149, 150, 151, 152, 1653, 1655, 1691, 1750, 1751, 1753, 1755, 1756, 1757, 1824, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2281, 2283, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 148, 1652, 1654, 1692, 1693, 1752, 1754, 1773, 2231, 2279, 2282, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 148, 150, 151, 152, 1652, 1653, 1654, 1655, 1692, 1750, 1751, 1752, 1753, 1755, 1756, 1897, 1900, 2058, 2229, 2231, 2281, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 149, 1691, 1693, 1754, 1757, 1773, 1824, 1898, 2054, 2056, 2227, 2279)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 149, 150, 151, 152, 1652, 1653, 1655, 1691, 1692, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1898, 2054, 2227, 2229, 2231, 2279, 2281, 2282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 148, 1654, 1693, 1750, 1751, 1752, 1900, 2056, 2058, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 1719, 1721, 1776, 1777, 1778, 1869, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 1720, 1722, 1727, 1775, 1779, 1868)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 1720, 1727, 1775, 1776, 1777, 1779, 1868, 1870, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1719, 1721, 1722, 1778, 1869, 2027, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1868, 2027, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 1777, 1778, 1779, 1869, 1870, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 207, 209, 213, 216, 218, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 206, 208, 210, 211, 212, 214, 217)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 210, 211, 214, 217, 218, 219, 220, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(208, 209, 212, 213, 216, 266, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 209, 210, 211, 213, 216, 218, 220, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 206, 207, 208, 212, 214, 217, 219, 266)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(131, 140, 142, 143, 230, 231, 234, 235, 281, 285, 286, 287, 288, 289, 290, 291, 293, 294, 296, 1716, 1717, 1718, 1838, 1839, 1840, 1991, 2030, 2108, 2109, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 132, 141, 177, 229, 233, 236, 282, 283, 284, 292, 295, 1852, 1863, 1864, 1865, 1990, 1992, 2026, 2137, 2138)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 140, 143, 177, 229, 233, 234, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 293, 294, 1716, 1717, 1718, 1838, 1840, 1852, 1864, 1865, 1990, 1991, 1992, 2108, 2109, 2137, 2138, 2194, 2222, 2223, 2300, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(131, 132, 141, 142, 230, 231, 235, 236, 281, 285, 295, 296, 1839, 1863, 2026, 2030, 2139, 2225, 2226, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 132, 140, 142, 143, 177, 229, 230, 233, 284, 285, 288, 289, 290, 291, 292, 293, 295, 296, 1716, 1717, 1838, 1839, 1840, 1863, 1864, 1991, 1992, 2026, 2030, 2109, 2138, 2139, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(131, 141, 231, 234, 235, 236, 281, 282, 283, 286, 287, 294, 1718, 1852, 1865, 1990, 2108, 2137, 2194, 2222, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 19, 20, 34, 35, 148, 149, 150, 152, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1771, 1772, 1774, 1825, 1827, 1897, 1898, 1900, 2056, 2177, 2179, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 31, 32, 33, 151, 1652, 1655, 1755, 1756, 1757, 1773, 1824, 1826, 2054, 2058, 2227, 2289, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 31, 32, 35, 150, 151, 152, 1652, 1654, 1655, 1693, 1750, 1751, 1754, 1756, 1757, 1772, 1773, 1774, 1824, 1826, 1827, 1898, 1900, 2054, 2058, 2177, 2179, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 33, 34, 148, 149, 1653, 1691, 1692, 1752, 1753, 1755, 1771, 1825, 1897, 2056, 2227, 2289, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 31, 32, 35, 150, 152, 1652, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1827, 1898, 2054, 2056, 2058, 2177, 2281, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 33, 34, 148, 149, 151, 1655, 1752, 1754, 1826, 1897, 1900, 2179, 2227, 2229, 2231, 2279, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 222, 275, 276, 277, 279, 280, 1719, 1720, 1722, 1727, 1777, 1778, 1779, 1868, 1869, 2027, 2119, 2120, 2124, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 224, 226, 228, 278, 1721, 1775, 1776, 1870, 2121, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 228, 276, 278, 279, 280, 1727, 1777, 1778, 1779, 1868, 1870, 2027, 2120, 2121, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 226, 275, 277, 1719, 1720, 1721, 1722, 1775, 1776, 1869, 2119, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 228, 275, 276, 277, 1719, 1720, 1727, 1775, 1778, 1868, 1869, 2027, 2119, 2121, 2124, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(226, 278, 279, 280, 1721, 1722, 1776, 1777, 1779, 1870, 2120, 2125, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 207, 208, 209, 211, 212, 215, 216, 217, 218, 219, 265, 266, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 205, 206, 210, 213, 214, 220, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 208, 209, 210, 211, 214, 215, 216, 217, 218, 219, 220, 265, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 206, 207, 212, 213, 266, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 206, 207, 209, 212, 213, 215, 216, 217, 265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 208, 210, 211, 214, 218, 219, 220)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 73, 130, 132, 142, 143, 175, 177, 180, 225, 227, 230, 231, 233, 234, 235, 236, 243, 244, 248, 249, 274, 281, 283, 286, 287, 289, 291, 292, 296, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1840, 1863, 1864, 1866, 1867, 1991, 1992, 2030, 2108, 2109, 2129, 2131, 2133, 2134, 2135, 2136, 2137, 2138, 2194, 2222, 2223, 2225, 2226, 2257, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 131, 140, 141, 221, 223, 229, 245, 246, 247, 250, 271, 272, 273, 282, 284, 285, 288, 290, 293, 294, 295, 1716, 1717, 1838, 1839, 1852, 1865, 1935, 1990, 2026, 2128, 2130, 2132, 2139, 2300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
-2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 130, 132, 140, 142, 143, 177, 223, 225, 230, 231, 234, 235, 236, 244, 245, 246, 247, 248, 272, 273, 274, 281, 283, 284, 285, 287, 288, 289, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1766, 1838, 1840, 1852, 1865, 1935, 1990, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2134, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 72, 73, 131, 141, 175, 180, 221, 227, 229, 233, 243, 249, 250, 271, 282, 286, 290, 291, 292, 1762, 1765, 1839, 1863, 1864, 1866, 1867, 1991, 1992, 2026, 2133, 2135, 2136, 2222, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 72, 73, 130, 132, 143, 177, 221, 225, 227, 229, 230, 233, 235, 236, 243, 244, 246, 248, 249, 250, 271, 272, 273, 283, 285, 286, 287, 288, 289, 290, 291, 292, 295, 296, 1716, 1717, 1718, 1761, 1762, 1763, 1764, 1766, 1838, 1852, 1867, 1990, 1991, 1992, 2026, 2030, 2109, 2128, 2129, 2131, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2257, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 131, 140, 141, 142, 175, 180, 223, 231, 234, 245, 247, 274, 281, 282, 284, 293, 294, 1760, 1765, 1839, 1840, 1863, 1864, 1865, 1866, 1935, 2108, 2130, 2135, 2226, 2300, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 33, 34, 149, 150, 151, 152, 1652, 1653, 1692, 1750, 1751, 1752, 1753, 1755, 1756, 1771, 1772, 1773, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2282, 2283, 2289, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(31, 32, 35, 148, 1654, 1655, 1691, 1693, 1754, 1757, 1774, 2054, 2179, 2231, 2279, 2281, 2288, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 33, 34, 35, 148, 149, 150, 151, 152, 1653, 1654, 1691, 1693, 1750, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1824, 1826, 1898, 1900, 2058, 2179, 2227, 2229, 2279, 2281, 2288, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 32, 1652, 1655, 1692, 1751, 1772, 1773, 1825, 1827, 1897, 2054, 2056, 2177, 2231, 2282, 2283, 2289, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 31, 32, 33, 35, 148, 149, 150, 151, 1654, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1773, 1824, 1825, 1826, 1827, 1900, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2288, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 34, 152, 1652, 1653, 1655, 1692, 1693, 1757, 1772, 1774, 1897, 1898, 2054, 2281, 2282, 2283, 2289, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 226, 275, 279, 280, 1720, 1721, 1722, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 224, 228, 276, 277, 278, 1719, 1727, 1775, 1776, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 224, 226, 228, 277, 1721, 1722, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2027, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 222, 275, 276, 278, 279, 280, 1719, 1720, 1727, 1777, 2119)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 224, 226, 275, 276, 278, 1719, 1720, 1722, 1776, 1777, 1779, 1868, 1869, 1870, 2119, 2121, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 228, 277, 279, 280, 1721, 1727, 1775, 1778, 2027, 2120, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 206, 207, 208, 209, 210, 213, 214, 215, 216, 218, 219, 265, 266, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 205, 211, 212, 217, 220, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 205, 206, 207, 208, 209, 210, 214, 215, 216, 217, 218, 219, 220, 266, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 211, 212, 213, 265, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 206, 209, 211, 212, 213, 214, 216, 217, 219, 220, 265, 266, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 207, 208, 210, 215, 218, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 140, 141, 142, 143, 175, 221, 225, 227, 229, 230, 233, 243, 245, 246, 247, 249, 272, 273, 274, 287, 290, 292, 293, 294, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1765, 1766, 1838, 1840, 1864, 1865, 1867, 1935, 1990, 1991, 1992, 2026, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 130, 131, 132, 177, 180, 223, 231, 234, 235, 236, 244, 248, 250, 271, 281, 282, 283, 284, 285, 286, 288, 289, 291, 295, 1763, 1764, 1839, 1852, 1863, 1866, 2030, 2108, 2131, 2135, 2225)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 130, 132, 141, 142, 143, 175, 177, 180, 221, 223, 227, 229, 230, 231, 234, 244, 246, 247, 249, 271, 273, 274, 281, 282, 283, 284, 286, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1762, 1763, 1765, 1838, 1840, 1852, 1863, 1865, 1866, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2137, 2139, 2194, 2222, 2226, 2257, 2300, 2301, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 71, 131, 140, 225, 233, 235, 236, 243, 245, 248, 250, 272, 285, 287, 288, 1718, 1761, 1764, 1766, 1839, 1864, 1867, 1935, 1990, 1991, 2131, 2135, 2136, 2138, 2223, 2225, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 131, 140, 142, 175, 177, 180, 223, 225, 227, 231, 233, 234, 235, 236, 244, 245, 247, 248, 249, 250, 271, 273, 281, 284, 285, 286, 291, 292, 294, 295, 1716, 1718, 1760, 1761, 1763, 1764, 1765, 1766, 1839, 1840, 1863, 1864, 1865, 1867, 1990, 1992, 2026, 2030, 2108, 2109, 2129, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2223, 2226, 2257, 2300, 2301, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 130, 132, 141, 143, 221, 229, 230, 243, 246, 272, 274, 282, 283, 287, 288, 289, 290, 293, 296, 1717, 1762, 1838, 1852, 1866, 1935, 1991, 2128, 2130, 2136, 2222, 2225, 2302, 2303, 2312)</t>
+    <t xml:space="preserve">c(18, 20, 23, 149, 152, 1652, 1653, 1655, 1691, 1692, 1693, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 1898, 1900, 2058, 2227, 2229, 2279, 2281, 2282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 148, 150, 151, 1654, 1750, 1897, 2054, 2056, 2231, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 23, 148, 149, 150, 151, 152, 1652, 1654, 1691, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1897, 2054, 2056, 2058, 2279, 2281, 2282, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 1653, 1655, 1692, 1753, 1773, 1824, 1898, 1900, 2227, 2229, 2231, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 149, 152, 1652, 1654, 1655, 1692, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 2058, 2227, 2229, 2231, 2279, 2281, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 148, 150, 151, 1653, 1691, 1753, 1898, 1900, 2054, 2056, 2282, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + CP_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 1720, 1722, 1775, 1776, 1778, 1779, 1868, 1870, 2027, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 1719, 1721, 1727, 1777, 1869, 2119, 2120, 2121, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 224, 228, 1719, 1720, 1721, 1722, 1775, 1776, 1777, 1779, 1869, 1870, 2119, 2120, 2124, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 226, 1727, 1778, 1868, 2027, 2121, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 226, 228, 1720, 1721, 1776, 1777, 1778, 1868, 1869, 1870, 2027, 2120, 2121, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(224, 1719, 1722, 1727, 1775, 1779, 2119, 2124, 2125, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 207, 208, 211, 212, 216, 217, 218, 220, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 206, 209, 210, 213, 214, 219, 266, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 204, 205, 206, 208, 209, 211, 212, 213, 214, 216, 217, 220, 267, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 207, 210, 218, 219, 266, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 206, 209, 210, 211, 212, 213, 214, 217, 220, 266, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 205, 207, 208, 216, 218, 219, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 130, 131, 141, 142, 143, 221, 223, 225, 227, 230, 234, 236, 243, 244, 246, 250, 281, 282, 283, 286, 289, 290, 291, 292, 293, 296, 1716, 1718, 1760, 1761, 1763, 1838, 1840, 1852, 1865, 1867, 1990, 1991, 2026, 2030, 2108, 2128, 2129, 2130, 2131, 2132, 2133, 2137, 2138, 2139, 2194, 2222, 2226, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(132, 140, 177, 180, 229, 231, 233, 235, 245, 248, 249, 284, 285, 287, 288, 294, 295, 1717, 1762, 1839, 1863, 1864, 1866, 1992, 2109, 2134, 2135, 2136, 2223, 2225, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 130, 131, 132, 140, 141, 142, 143, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 130, 131, 141, 143, 223, 229, 230, 231, 233, 235, 244, 245, 246, 249, 282, 283, 285, 287, 288, 289, 293, 294, 295, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1863, 1864, 1865, 1990, 2030, 2108, 2128, 2129, 2130, 2132, 2133, 2134, 2135, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 132, 140, 142, 177, 180, 221, 225, 227, 234, 236, 243, 248, 250, 281, 284, 286, 290, 291, 292, 1718, 1852, 1866, 1867, 1991, 1992, 2026, 2109, 2131, 2138, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 130, 131, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 233, 236, 243, 244, 246, 248, 249, 250, 281, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 1760, 1762, 1838, 1840, 1852, 1866, 1867, 1990, 2026, 2030, 2129, 2131, 2132, 2133, 2135, 2137, 2139, 2223, 2225, 2226, 2300, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(132, 180, 230, 231, 234, 235, 245, 285, 296, 1716, 1717, 1718, 1761, 1763, 1839, 1863, 1864, 1865, 1991, 1992, 2108, 2109, 2128, 2130, 2134, 2136, 2138, 2194, 2222, 2301, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 150, 1652, 1653, 1655, 1691, 1692, 1693, 1751, 1752, 1754, 1756, 1757, 1824, 1897, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2281, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 148, 149, 151, 152, 1654, 1750, 1753, 1755, 1773, 1898, 2279, 2282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1755, 1756, 1757, 1898, 1900, 2054, 2229, 2231, 2281, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(152, 1693, 1751, 1752, 1753, 1754, 1773, 1824, 1897, 2056, 2058, 2227, 2279, 2282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 23, 150, 151, 1653, 1654, 1655, 1692, 1693, 1750, 1754, 1755, 1756, 1757, 1824, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2231, 2279, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 148, 149, 152, 1652, 1691, 1751, 1752, 1753, 1773, 2229, 2281, 2282)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1776, 1777, 1868, 2027, 2119, 2121, 2124, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 1727, 1775, 1778, 1779, 1869, 1870, 2120, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1727, 1776, 1777, 1779, 1868, 1869, 2027, 2119, 2121, 2124, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1720, 1721, 1722, 1775, 1778, 1870, 2120, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 228, 1719, 1720, 1721, 1775, 1778, 1779, 1869, 1870, 2027, 2120, 2121, 2124, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(226, 1722, 1727, 1776, 1777, 1868, 2119, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 208, 209, 210, 216, 217, 218, 219, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 211, 212, 213, 214, 220, 266, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 208, 209, 211, 214, 217, 219, 266, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 210, 212, 213, 216, 218, 220, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 207, 208, 209, 210, 217, 218, 219, 220, 266, 267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 206, 211, 212, 213, 214, 216, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 131, 132, 140, 221, 223, 227, 230, 231, 233, 235, 236, 243, 245, 282, 283, 284, 285, 286, 287, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1838, 1852, 1865, 1866, 1867, 1990, 1991, 2109, 2128, 2129, 2130, 2131, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 130, 141, 142, 143, 177, 180, 225, 229, 234, 244, 246, 248, 249, 250, 281, 288, 289, 1718, 1839, 1840, 1863, 1864, 1992, 2026, 2030, 2108, 2132, 2134, 2222, 2223)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 130, 131, 140, 143, 177, 223, 227, 229, 231, 233, 235, 236, 243, 245, 246, 248, 249, 281, 283, 285, 286, 289, 290, 292, 295, 1716, 1718, 1760, 1761, 1762, 1763, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 2026, 2108, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2136, 2138, 2139, 2194, 2226, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 132, 141, 142, 180, 221, 225, 230, 234, 244, 250, 282, 284, 287, 288, 291, 293, 294, 296, 1717, 1838, 1992, 2030, 2131, 2135, 2137, 2222, 2223, 2225, 2300, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 130, 131, 132, 143, 180, 221, 223, 229, 230, 233, 234, 235, 236, 243, 245, 246, 248, 249, 281, 282, 283, 284, 286, 288, 289, 290, 292, 293, 295, 1717, 1718, 1760, 1840, 1863, 1864, 1865, 1866, 1867, 1991, 1992, 2026, 2030, 2109, 2128, 2129, 2130, 2131, 2133, 2134, 2136, 2137, 2222, 2223, 2225, 2300, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(140, 141, 142, 177, 225, 227, 231, 244, 250, 285, 287, 291, 294, 296, 1716, 1761, 1762, 1763, 1838, 1839, 1852, 1990, 2108, 2132, 2135, 2138, 2139, 2194, 2226, 2301, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 34, 149, 150, 151, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1757, 1897, 1898, 1900, 2058, 2227, 2229, 2231, 2279, 2282, 2283, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 32, 33, 35, 148, 152, 1756, 2054, 2056, 2281, 2288, 2289, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 35, 148, 150, 152, 1691, 1692, 1693, 1752, 1754, 1755, 1757, 1897, 1900, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 32, 34, 149, 151, 1750, 1751, 1753, 1756, 1898, 2054, 2283, 2288, 2289, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 31, 33, 35, 148, 150, 151, 152, 1691, 1750, 1753, 1755, 1756, 1757, 1897, 1898, 2054, 2058, 2227, 2231, 2279, 2281, 2282, 2283, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 32, 34, 149, 1692, 1693, 1751, 1752, 1754, 1900, 2056, 2229, 2288, 2289, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 224, 226, 228, 277, 279, 280, 1719, 1720, 1721, 1775, 1778, 1779, 1868, 1869, 1870, 2119, 2120, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 222, 275, 276, 278, 1722, 1727, 1776, 1777, 2027, 2121, 2124, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 224, 228, 277, 278, 279, 280, 1719, 1721, 1722, 1727, 1776, 1778, 1779, 1869, 2027, 2119, 2120, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 222, 226, 275, 276, 1720, 1775, 1777, 1868, 1870, 2121, 2124, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 224, 228, 275, 279, 280, 1720, 1722, 1776, 1777, 1778, 1779, 1869, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 226, 276, 277, 278, 1719, 1721, 1727, 1775, 1868, 1870, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 132, 140, 141, 177, 221, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 246, 248, 271, 272, 274, 281, 282, 284, 285, 287, 288, 291, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1990, 1992, 2026, 2128, 2130, 2133, 2134, 2135, 2136, 2194, 2222, 2223, 2226, 2300, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 130, 131, 142, 143, 223, 225, 245, 247, 249, 250, 273, 283, 286, 289, 290, 1716, 1840, 1867, 1935, 1991, 2030, 2129, 2131, 2132, 2137, 2138, 2139, 2225, 2257, 2301, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
-2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 141, 143, 223, 225, 227, 229, 231, 234, 243, 244, 245, 246, 247, 249, 250, 272, 273, 274, 281, 282, 284, 286, 288, 289, 290, 291, 293, 294, 1716, 1717, 1760, 1763, 1765, 1766, 1838, 1839, 1840, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 2128, 2129, 2132, 2133, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 131, 132, 140, 142, 177, 221, 230, 233, 235, 236, 248, 271, 283, 285, 287, 292, 295, 296, 1718, 1761, 1762, 1764, 1852, 1935, 1992, 2026, 2030, 2130, 2131, 2134, 2135, 2138, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 73, 130, 131, 141, 143, 221, 227, 229, 230, 231, 234, 236, 243, 244, 245, 246, 247, 248, 249, 271, 272, 273, 274, 281, 282, 284, 285, 286, 287, 289, 292, 293, 296, 1761, 1763, 1764, 1765, 1766, 1839, 1840, 1863, 1865, 1867, 1935, 1990, 1991, 1992, 2128, 2129, 2130, 2131, 2134, 2135, 2136, 2137, 2138, 2194, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 132, 140, 142, 177, 223, 225, 233, 235, 250, 283, 288, 290, 291, 294, 295, 1716, 1717, 1718, 1760, 1762, 1838, 1852, 1864, 1866, 2026, 2030, 2132, 2133, 2139, 2222, 2223, 2257)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 149, 150, 151, 152, 1692, 1693, 1752, 1754, 1755, 1757, 1898, 1900, 2054, 2056, 2058, 2227, 2283, 2288, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(35, 148, 1691, 1750, 1751, 1753, 1756, 1897, 2229, 2231, 2279, 2281, 2282, 2289, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 31, 32, 35, 149, 150, 152, 1691, 1751, 1752, 1753, 1754, 1757, 1897, 1898, 1900, 2054, 2056, 2227, 2231, 2279, 2281, 2282, 2288, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 33, 34, 148, 151, 1692, 1693, 1750, 1755, 1756, 2058, 2229, 2283, 2289, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 33, 34, 148, 149, 150, 151, 1691, 1693, 1750, 1751, 1752, 1753, 1756, 1757, 1900, 2054, 2056, 2058, 2227, 2229, 2281, 2282, 2288, 2289, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 32, 35, 152, 1692, 1754, 1755, 1897, 1898, 2231, 2279, 2283, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1777, 1779, 1868, 1869, 2119, 2120, 2124, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 224, 226, 228, 1776, 1778, 1870, 2027, 2121, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 279, 280, 1720, 1721, 1722, 1727, 1776, 1779, 1869, 1870, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(228, 275, 276, 277, 278, 1719, 1775, 1777, 1778, 1868, 2027, 2119, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 222, 224, 226, 228, 276, 277, 278, 280, 1720, 1722, 1727, 1775, 1776, 1868, 2027, 2119, 2120, 2121, 2124, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 275, 279, 1719, 1721, 1777, 1778, 1779, 1869, 1870, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265:267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 72, 73, 130, 141, 177, 223, 225, 227, 230, 231, 233, 234, 236, 243, 244, 245, 248, 250, 272, 273, 281, 282, 283, 284, 285, 289, 290, 291, 293, 294, 296, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1766, 1838, 1839, 1840, 1863, 1864, 1865, 1866, 1935, 1990, 1991, 2026, 2030, 2128, 2129, 2132, 2133, 2134, 2135, 2136, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 131, 132, 140, 142, 143, 221, 229, 235, 246, 247, 249, 271, 274, 286, 287, 288, 292, 295, 1762, 1765, 1852, 1867, 1992, 2130, 2131, 2137, 2138, 2139, 2194, 2223, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 132, 140, 141, 177, 221, 223, 231, 233, 234, 235, 236, 245, 246, 247, 248, 249, 250, 271, 273, 281, 282, 283, 284, 285, 286, 287, 288, 289, 292, 293, 294, 296, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1839, 1852, 1863, 1865, 1866, 1867, 1992, 2026, 2129, 2130, 2131, 2133, 2135, 2137, 2139, 2194, 2223, 2225, 2226, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 131, 142, 143, 225, 227, 229, 230, 243, 244, 272, 274, 290, 291, 295, 1716, 1838, 1840, 1864, 1935, 1990, 1991, 2030, 2128, 2132, 2134, 2136, 2138, 2222, 2257, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 73, 130, 131, 140, 141, 142, 143, 177, 223, 229, 231, 233, 234, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 281, 283, 284, 285, 286, 288, 289, 293, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1838, 1839, 1863, 1864, 1865, 1935, 1990, 1992, 2026, 2030, 2128, 2129, 2130, 2134, 2137, 2194, 2257, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 132, 221, 225, 227, 230, 235, 273, 274, 282, 287, 290, 291, 292, 1717, 1766, 1840, 1852, 1866, 1867, 1991, 2131, 2132, 2133, 2135, 2136, 2138, 2139, 2222, 2223, 2225, 2226, 2313)</t>
+    <t xml:space="preserve">c(19, 20, 149, 150, 151, 152, 1691, 1692, 1693, 1752, 1753, 1754, 1755, 1897, 1900, 2054, 2056, 2058, 2227, 2231, 2279, 2281, 2282, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 23, 148, 1750, 1751, 1756, 1757, 1898, 2229, 2283, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 149, 150, 151, 1691, 1692, 1693, 1751, 1755, 1756, 1757, 1897, 1898, 1900, 2056, 2058, 2231, 2279, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 148, 152, 1750, 1752, 1753, 1754, 2054, 2227, 2229, 2281)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 149, 150, 1692, 1693, 1750, 1752, 1753, 1754, 1757, 1900, 2056, 2058, 2227, 2231, 2281, 2282, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(148, 151, 152, 1691, 1751, 1755, 1756, 1897, 1898, 2054, 2229, 2279)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 1720, 1721, 1722, 1778, 1868, 1869, 1870, 2027, 2119, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(228, 1719, 1727, 1775, 1776, 1777, 1779, 2120, 2121, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1775, 1777, 1778, 1779, 1868, 1869, 2027, 2119, 2120, 2121, 2124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 1722, 1727, 1776, 1870, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 222, 224, 226, 228, 1722, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2027, 2119, 2120, 2121, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 1719, 1720, 1721, 1727, 1868, 2124, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 132, 140, 142, 143, 177, 221, 223, 225, 230, 231, 233, 234, 235, 236, 248, 249, 250, 281, 283, 284, 285, 286, 289, 291, 293, 294, 295, 1761, 1762, 1838, 1840, 1852, 1863, 1864, 1865, 1867, 1990, 1991, 1992, 2026, 2030, 2129, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2139, 2222, 2225, 2226, 2300, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 130, 131, 141, 227, 229, 243, 244, 245, 246, 282, 287, 288, 290, 292, 296, 1716, 1717, 1718, 1760, 1763, 1839, 1866, 2128, 2134, 2138, 2194, 2223, 2301, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 132, 140, 141, 143, 177, 221, 223, 225, 229, 230, 231, 233, 234, 236, 243, 248, 249, 282, 283, 284, 285, 286, 288, 290, 291, 292, 294, 1716, 1717, 1761, 1762, 1763, 1838, 1839, 1840, 1863, 1864, 1867, 1991, 2026, 2030, 2128, 2130, 2132, 2134, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2300, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 131, 142, 227, 235, 244, 245, 246, 250, 281, 287, 289, 293, 295, 296, 1718, 1760, 1852, 1865, 1866, 1990, 1992, 2129, 2131, 2133, 2136, 2225, 2301, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 130, 131, 132, 143, 177, 221, 223, 225, 227, 229, 230, 231, 235, 243, 246, 248, 250, 285, 289, 290, 291, 292, 293, 294, 295, 1717, 1718, 1760, 1763, 1838, 1839, 1852, 1864, 1865, 1867, 1990, 1992, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2223, 2225, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(140, 141, 142, 233, 234, 236, 244, 245, 249, 281, 282, 283, 284, 286, 287, 288, 296, 1716, 1761, 1762, 1840, 1863, 1866, 1991, 2026, 2134, 2194, 2222, 2226, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 148, 149, 150, 1691, 1692, 1693, 1751, 1752, 1754, 1755, 1897, 1898, 1900, 2054, 2056, 2229, 2231, 2279, 2281, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 151, 152, 1750, 1753, 1756, 1757, 2058, 2227, 2282, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 148, 149, 151, 152, 1693, 1751, 1752, 1753, 1754, 1756, 1757, 1897, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 150, 1691, 1692, 1750, 1755, 1898, 1900, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 148, 149, 150, 152, 1691, 1692, 1751, 1752, 1754, 1755, 1757, 1897, 1898, 1900, 2054, 2227, 2229, 2231, 2279, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 151, 1693, 1750, 1753, 1756, 2056, 2058, 2281, 2282, 2283, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 222, 226, 1720, 1721, 1727, 1776, 1777, 1778, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 224, 228, 1719, 1722, 1775, 1779, 2124, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 222, 224, 226, 228, 1719, 1721, 1722, 1727, 1775, 1779, 1868, 2027, 2119, 2121, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 1720, 1776, 1777, 1778, 1869, 1870, 2120, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 222, 228, 1719, 1720, 1721, 1727, 1775, 1778, 1779, 1869, 1870, 2120, 2121, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 224, 226, 1722, 1776, 1777, 1868, 2027, 2119, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 130, 140, 141, 142, 143, 177, 223, 225, 227, 229, 230, 231, 234, 235, 236, 243, 244, 249, 250, 284, 286, 288, 289, 290, 292, 293, 294, 295, 1760, 1762, 1763, 1838, 1839, 1852, 1866, 1990, 1991, 1992, 2030, 2128, 2130, 2131, 2132, 2133, 2135, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(131, 132, 221, 233, 245, 246, 248, 281, 282, 283, 285, 287, 291, 296, 1716, 1717, 1718, 1761, 1840, 1863, 1864, 1865, 1867, 2026, 2129, 2134, 2136, 2137, 2138, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 141, 142, 143, 177, 221, 225, 227, 229, 230, 231, 234, 235, 243, 244, 245, 248, 250, 285, 286, 287, 288, 289, 291, 292, 293, 294, 295, 296, 1716, 1718, 1760, 1761, 1763, 1839, 1863, 1865, 1866, 1867, 1990, 1991, 2030, 2128, 2132, 2133, 2134, 2135, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 131, 132, 140, 223, 233, 236, 246, 249, 281, 282, 283, 284, 290, 1717, 1762, 1838, 1840, 1852, 1864, 1992, 2026, 2129, 2130, 2131, 2138, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 130, 131, 140, 142, 143, 177, 225, 227, 229, 231, 233, 235, 236, 243, 245, 248, 249, 250, 282, 283, 289, 291, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1852, 1863, 1864, 1865, 1866, 1990, 1991, 1992, 2026, 2128, 2132, 2134, 2135, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2300, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(132, 141, 221, 223, 230, 234, 244, 246, 281, 284, 285, 286, 287, 288, 290, 292, 293, 1763, 1838, 1839, 1840, 1867, 2030, 2129, 2130, 2131, 2133, 2138, 2226, 2301)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 19, 23, 32, 34, 35, 1691, 1692, 1750, 1751, 1753, 1754, 1755, 1771, 1772, 1774, 1824, 1825, 1826, 1827, 2058, 2177, 2179, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 31, 33, 1693, 1752, 1756, 1757, 1773, 2054, 2056, 2288, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 32, 33, 34, 35, 1691, 1692, 1750, 1752, 1753, 1755, 1756, 1757, 1772, 1773, 1824, 1825, 1827, 2054, 2056, 2177, 2179, 2288, 2289, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 1693, 1751, 1754, 1771, 1774, 1826, 2058, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 31, 32, 33, 34, 35, 1691, 1750, 1751, 1752, 1754, 1756, 1757, 1771, 1772, 1774, 1825, 1826, 2054, 2056, 2179, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 1692, 1693, 1753, 1755, 1773, 1824, 1827, 2058, 2177, 2288, 2292, 2294)</t>
+    <t xml:space="preserve">c(17, 19, 20, 23, 1692, 1693, 1751, 1752, 1753, 1757, 1773, 1824, 2054, 2056, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 1691, 1750, 1754, 1755, 1756, 2058, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 2054, 2056, 2058, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1757, 1773, 2056, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 1753, 1755, 1756, 1824, 2054, 2058, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 1691, 1692, 1693, 1750, 1753, 1755, 1756, 1773, 2054, 2058, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 1751, 1752, 1754, 1757, 1824, 2056, 2289)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 175, 180, 230, 233, 234, 236, 271, 272, 273, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 177, 229, 231, 235, 274, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 175, 177, 230, 231, 233, 234, 272, 274, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 180, 229, 235, 236, 271, 273, 1764)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 175, 229, 231, 234, 235, 236, 272, 273, 274, 1764, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 177, 180, 230, 233, 271, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1753, 1756, 1757, 1774, 1826, 2054, 2058, 2177, 2288, 2289, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 1752, 1754, 1755, 1771, 1772, 1773, 1824, 1825, 1827, 2056, 2179, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 31, 32, 33, 34, 1691, 1693, 1752, 1755, 1757, 1772, 1774, 1826, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 35, 1692, 1750, 1751, 1753, 1754, 1756, 1771, 1773, 1824, 1825, 1827)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 32, 33, 35, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 34, 1691, 1772, 1825, 2288, 2289, 2290, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 175, 177, 180, 229, 230, 231, 233, 235, 236, 271, 273, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 234, 272, 274, 1764, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 177, 180, 229, 230, 233, 234, 273, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 175, 231, 235, 236, 271, 272, 274)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 175, 177, 229, 233, 234, 235, 236, 271, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 180, 230, 231, 272, 273, 274, 1766)</t>
+    <t xml:space="preserve">c(229, 230, 231, 233, 234, 235)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 180, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 180, 229, 230, 231, 233, 234, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 229, 230, 233, 234, 235)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 231, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 229, 231, 233, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 230, 234)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 1691, 1750, 1752, 1755, 1756, 1757, 1824, 2054, 2058, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 1692, 1693, 1751, 1753, 1754, 1773, 2056)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1755, 1756, 1824, 2054, 2058, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 1753, 1754, 1757, 1773, 2056, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 1691, 1692, 1751, 1754, 1755, 1756, 1773, 1824, 2054, 2056, 2058)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 1693, 1750, 1752, 1753, 1757, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 229, 233, 234, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 230, 231)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 229, 230, 231, 234, 235)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 233, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 180, 229, 230, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(231, 233, 234)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 34, 1691, 1692, 1693, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1774, 1825, 1826, 1827, 2054, 2177, 2288, 2289, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 32, 33, 35, 1750, 1751, 1773, 1824, 2056, 2058, 2179, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 31, 33, 35, 1691, 1692, 1693, 1750, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 2054, 2179, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 32, 34, 1751, 1752, 1753, 1827, 2056, 2058, 2177, 2288, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 32, 35, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1772, 1774, 1824, 1827, 2054, 2177, 2179, 2288, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 33, 34, 1692, 1755, 1757, 1773, 1825, 1826, 2056, 2058, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 177, 180, 229, 233, 235, 271, 273, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(175, 230, 231, 234, 236, 272, 274, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 230, 233, 236, 271, 273, 274, 1764, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 229, 231, 234, 235, 272, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 177, 180, 230, 231, 234, 236, 273, 274, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 175, 229, 233, 235, 271, 272, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1773, 1824, 1825, 1826, 1827, 2058, 2179, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 1753, 1757, 1771, 1772, 1774, 2054, 2056, 2177, 2288, 2289, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 35, 1693, 1750, 1752, 1755, 1756, 1757, 1772, 1773, 1824, 1826, 1827, 2054, 2058, 2177, 2179, 2288, 2289, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 34, 1691, 1692, 1751, 1753, 1754, 1771, 1774, 1825, 2056, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 33, 34, 1692, 1693, 1752, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1827, 2054, 2056, 2179, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 31, 32, 35, 1691, 1750, 1751, 1754, 1825, 1826, 2058, 2177, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 177, 230, 231, 234, 235, 271, 272, 274, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 175, 180, 229, 233, 236, 273, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 175, 180, 230, 233, 235, 236, 272, 274, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 177, 229, 231, 234, 271, 273, 1764)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 175, 177, 229, 231, 233, 234, 235, 271, 272, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 180, 230, 236, 273, 274, 1764)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1751, 1752, 1753, 1754, 1755, 1757, 1773, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1693, 1750, 1756, 1824, 2054, 2056, 2058, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 1691, 1692, 1693, 1751, 1752, 1753, 1754, 1773, 2054, 2058, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 1750, 1755, 1756, 1757, 1824, 2056)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 1691, 1692, 1693, 1751, 1753, 1773, 1824, 2056, 2058, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 1750, 1752, 1754, 1755, 1756, 1757, 2054)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 229, 230, 231, 233, 234)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 180, 230, 231, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(229, 233, 234)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 230, 231, 233, 234, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 229, 235)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 1693, 1750, 1752, 1755, 1757, 1773, 1824, 2054, 2056, 2058, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 1691, 1692, 1751, 1753, 1754, 1756)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 1691, 1693, 1751, 1752, 1757, 1773, 1824, 2054, 2056, 2058, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 1692, 1750, 1753, 1754, 1755, 1756)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 1692, 1693, 1750, 1754, 1755, 1757, 1773, 1824, 2054, 2056, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 1691, 1751, 1752, 1753, 1756, 2058, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 180, 233, 234, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229:231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 230, 231, 233, 234, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 229, 235)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(229, 230, 233, 234, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 180, 231)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 35, 1691, 1692, 1751, 1752, 1753, 1754, 2054, 2289, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(33, 34, 1693, 1750, 1755, 1756, 1757, 2056, 2058, 2288, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 35, 1692, 1751, 1752, 1756, 1757, 2056, 2058, 2288, 2289, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 1691, 1693, 1750, 1753, 1754, 1755, 2054, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 32, 34, 35, 1691, 1692, 1751, 1753, 1754, 1755, 1756, 2054, 2058, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 33, 1693, 1750, 1752, 1757, 2056, 2288, 2289, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 180, 229, 230, 231, 233, 235, 236, 272, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 175, 177, 234, 271, 273, 274, 1764)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 177, 180, 229, 230, 231, 234, 235, 273, 274, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 175, 233, 236, 271, 272)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 175, 180, 229, 230, 234, 235, 273, 274, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 177, 231, 233, 236, 271, 272, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 31, 32, 33, 34, 1691, 1692, 1693, 1751, 1752, 1754, 1757, 2054, 2056, 2058, 2289, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 35, 1750, 1753, 1755, 1756, 2288, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 31, 32, 34, 1691, 1692, 1750, 1753, 1755, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 33, 35, 1693, 1751, 1752, 1754, 1756, 1757, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 33, 34, 35, 1692, 1750, 1752, 1753, 1755, 1756, 2054, 2056, 2288, 2289, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 32, 1691, 1693, 1751, 1754, 1757, 2058, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 175, 180, 229, 234, 235, 236, 271, 272, 273, 274, 1764, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 177, 230, 231, 233, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 175, 180, 229, 230, 233, 234, 235, 271, 272, 273, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 177, 231, 236, 274, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 175, 180, 229, 230, 231, 234, 236, 273, 1764, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 177, 233, 235, 271, 272, 274, 1765)</t>
+    <t xml:space="preserve">c(17, 19, 20, 23, 1691, 1692, 1693, 1751, 1753, 1754, 1755, 1756, 2058, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 1750, 1752, 1757, 2054, 2056, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 1691, 1750, 1752, 1753, 1754, 1755, 1757, 2054, 2056, 2058, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 1692, 1693, 1751, 1756, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 1692, 1750, 1751, 1752, 1753, 1754, 1757, 2054, 2056, 2058)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 1691, 1693, 1755, 1756, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 180, 231, 233, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(229, 230, 234)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 229, 231, 233, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 230, 234)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 180, 229, 231, 233, 234)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(230, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1751, 1754, 1755, 1756, 1757, 2054, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1693, 1750, 1752, 1753, 2056, 2058, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 2054, 2058, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 1691, 1751, 1755, 1757, 2056, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 1691, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 2056, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 1692, 1752, 1757, 2054, 2058, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 229, 230, 231, 233, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 234, 235)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(177, 229, 230, 233, 235, 236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(180, 231, 234)</t>
   </si>
 </sst>
 </file>
@@ -1691,13 +1644,13 @@
         <v>22</v>
       </c>
       <c r="N2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
         <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="s">
         <v>24</v>
@@ -1747,13 +1700,13 @@
         <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="s">
         <v>24</v>
@@ -1803,13 +1756,13 @@
         <v>27</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="s">
         <v>24</v>
@@ -1859,13 +1812,13 @@
         <v>31</v>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O5" t="s">
         <v>32</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="s">
         <v>33</v>
@@ -1915,13 +1868,13 @@
         <v>34</v>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O6" t="s">
         <v>35</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="s">
         <v>33</v>
@@ -1971,13 +1924,13 @@
         <v>36</v>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O7" t="s">
         <v>37</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="s">
         <v>33</v>
@@ -2027,7 +1980,7 @@
         <v>39</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O8" t="s">
         <v>40</v>
@@ -2083,7 +2036,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O9" t="s">
         <v>43</v>
@@ -2139,7 +2092,7 @@
         <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O10" t="s">
         <v>45</v>
@@ -2195,13 +2148,13 @@
         <v>47</v>
       </c>
       <c r="N11" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O11" t="s">
         <v>48</v>
       </c>
       <c r="P11" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="s">
         <v>49</v>
@@ -2251,13 +2204,13 @@
         <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O12" t="s">
         <v>51</v>
       </c>
       <c r="P12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q12" t="s">
         <v>49</v>
@@ -2307,13 +2260,13 @@
         <v>52</v>
       </c>
       <c r="N13" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O13" t="s">
         <v>53</v>
       </c>
       <c r="P13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q13" t="s">
         <v>49</v>
@@ -2363,13 +2316,13 @@
         <v>55</v>
       </c>
       <c r="N14" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O14" t="s">
         <v>56</v>
       </c>
       <c r="P14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="s">
         <v>24</v>
@@ -2419,13 +2372,13 @@
         <v>57</v>
       </c>
       <c r="N15" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O15" t="s">
         <v>58</v>
       </c>
       <c r="P15" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="s">
         <v>24</v>
@@ -2475,13 +2428,13 @@
         <v>59</v>
       </c>
       <c r="N16" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O16" t="s">
         <v>60</v>
       </c>
       <c r="P16" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="s">
         <v>24</v>
@@ -2531,13 +2484,13 @@
         <v>62</v>
       </c>
       <c r="N17" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O17" t="s">
         <v>63</v>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="s">
         <v>33</v>
@@ -2587,13 +2540,13 @@
         <v>64</v>
       </c>
       <c r="N18" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O18" t="s">
         <v>65</v>
       </c>
       <c r="P18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="s">
         <v>33</v>
@@ -2643,13 +2596,13 @@
         <v>66</v>
       </c>
       <c r="N19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O19" t="s">
         <v>67</v>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="s">
         <v>33</v>
@@ -2699,7 +2652,7 @@
         <v>69</v>
       </c>
       <c r="N20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
@@ -2755,7 +2708,7 @@
         <v>71</v>
       </c>
       <c r="N21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O21" t="s">
         <v>72</v>
@@ -2811,7 +2764,7 @@
         <v>73</v>
       </c>
       <c r="N22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O22" t="s">
         <v>74</v>
@@ -2867,13 +2820,13 @@
         <v>76</v>
       </c>
       <c r="N23" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O23" t="s">
         <v>77</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q23" t="s">
         <v>49</v>
@@ -2923,13 +2876,13 @@
         <v>78</v>
       </c>
       <c r="N24" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O24" t="s">
         <v>79</v>
       </c>
       <c r="P24" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q24" t="s">
         <v>49</v>
@@ -2979,13 +2932,13 @@
         <v>80</v>
       </c>
       <c r="N25" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O25" t="s">
         <v>81</v>
       </c>
       <c r="P25" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q25" t="s">
         <v>49</v>
@@ -3026,22 +2979,22 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
         <v>82</v>
       </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="s">
+      <c r="N26" t="n">
+        <v>28</v>
+      </c>
+      <c r="O26" t="s">
         <v>83</v>
       </c>
-      <c r="N26" t="n">
-        <v>40</v>
-      </c>
-      <c r="O26" t="s">
-        <v>84</v>
-      </c>
       <c r="P26" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q26" t="s">
         <v>24</v>
@@ -3082,22 +3035,22 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
       </c>
       <c r="M27" t="s">
+        <v>84</v>
+      </c>
+      <c r="N27" t="n">
+        <v>28</v>
+      </c>
+      <c r="O27" t="s">
         <v>85</v>
       </c>
-      <c r="N27" t="n">
-        <v>40</v>
-      </c>
-      <c r="O27" t="s">
-        <v>86</v>
-      </c>
       <c r="P27" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q27" t="s">
         <v>24</v>
@@ -3138,22 +3091,22 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
       </c>
       <c r="M28" t="s">
+        <v>86</v>
+      </c>
+      <c r="N28" t="n">
+        <v>28</v>
+      </c>
+      <c r="O28" t="s">
         <v>87</v>
       </c>
-      <c r="N28" t="n">
-        <v>40</v>
-      </c>
-      <c r="O28" t="s">
-        <v>88</v>
-      </c>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q28" t="s">
         <v>24</v>
@@ -3194,22 +3147,22 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>88</v>
+      </c>
+      <c r="N29" t="n">
+        <v>22</v>
+      </c>
+      <c r="O29" t="s">
         <v>89</v>
       </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="s">
-        <v>90</v>
-      </c>
-      <c r="N29" t="n">
-        <v>27</v>
-      </c>
-      <c r="O29" t="s">
-        <v>91</v>
-      </c>
       <c r="P29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="s">
         <v>33</v>
@@ -3250,22 +3203,22 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
       </c>
       <c r="M30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N30" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q30" t="s">
         <v>33</v>
@@ -3306,22 +3259,22 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N31" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q31" t="s">
         <v>33</v>
@@ -3362,19 +3315,19 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P32" t="n">
         <v>9</v>
@@ -3418,19 +3371,19 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N33" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P33" t="n">
         <v>9</v>
@@ -3474,19 +3427,19 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N34" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P34" t="n">
         <v>9</v>
@@ -3530,22 +3483,22 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O35" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q35" t="s">
         <v>49</v>
@@ -3586,22 +3539,22 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N36" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P36" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q36" t="s">
         <v>49</v>
@@ -3642,22 +3595,22 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N37" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P37" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q37" t="s">
         <v>49</v>
@@ -3698,22 +3651,22 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N38" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O38" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P38" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q38" t="s">
         <v>24</v>
@@ -3754,22 +3707,22 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N39" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O39" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P39" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q39" t="s">
         <v>24</v>
@@ -3810,22 +3763,22 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
       </c>
       <c r="M40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N40" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P40" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q40" t="s">
         <v>24</v>
@@ -3866,22 +3819,22 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N41" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O41" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P41" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="s">
         <v>33</v>
@@ -3922,22 +3875,22 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
       </c>
       <c r="M42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N42" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P42" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q42" t="s">
         <v>33</v>
@@ -3978,22 +3931,22 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
       </c>
       <c r="M43" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N43" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P43" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="s">
         <v>33</v>
@@ -4034,19 +3987,19 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N44" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O44" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P44" t="n">
         <v>9</v>
@@ -4090,19 +4043,19 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O45" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="P45" t="n">
         <v>9</v>
@@ -4146,19 +4099,19 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
       </c>
       <c r="M46" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N46" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P46" t="n">
         <v>9</v>
@@ -4202,22 +4155,22 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N47" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P47" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q47" t="s">
         <v>49</v>
@@ -4258,22 +4211,22 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N48" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P48" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q48" t="s">
         <v>49</v>
@@ -4314,22 +4267,22 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
       </c>
       <c r="M49" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N49" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P49" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q49" t="s">
         <v>49</v>
@@ -4370,22 +4323,22 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
+        <v>130</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>131</v>
+      </c>
+      <c r="N50" t="n">
+        <v>28</v>
+      </c>
+      <c r="O50" t="s">
         <v>132</v>
       </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="s">
-        <v>133</v>
-      </c>
-      <c r="N50" t="n">
-        <v>40</v>
-      </c>
-      <c r="O50" t="s">
-        <v>134</v>
-      </c>
       <c r="P50" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q50" t="s">
         <v>24</v>
@@ -4426,22 +4379,22 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N51" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P51" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q51" t="s">
         <v>24</v>
@@ -4482,22 +4435,22 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
       </c>
       <c r="M52" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N52" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O52" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="P52" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q52" t="s">
         <v>24</v>
@@ -4538,22 +4491,22 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
+        <v>137</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>138</v>
+      </c>
+      <c r="N53" t="n">
+        <v>22</v>
+      </c>
+      <c r="O53" t="s">
         <v>139</v>
       </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="s">
-        <v>140</v>
-      </c>
-      <c r="N53" t="n">
-        <v>27</v>
-      </c>
-      <c r="O53" t="s">
-        <v>141</v>
-      </c>
       <c r="P53" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q53" t="s">
         <v>33</v>
@@ -4594,22 +4547,22 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N54" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O54" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P54" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q54" t="s">
         <v>33</v>
@@ -4650,22 +4603,22 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
       </c>
       <c r="M55" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N55" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O55" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P55" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q55" t="s">
         <v>33</v>
@@ -4706,19 +4659,19 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N56" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O56" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P56" t="n">
         <v>9</v>
@@ -4762,19 +4715,19 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P57" t="n">
         <v>9</v>
@@ -4818,19 +4771,19 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
       </c>
       <c r="M58" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N58" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O58" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P58" t="n">
         <v>9</v>
@@ -4874,22 +4827,22 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N59" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O59" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P59" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q59" t="s">
         <v>49</v>
@@ -4930,22 +4883,22 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N60" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O60" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P60" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q60" t="s">
         <v>49</v>
@@ -4986,22 +4939,22 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N61" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O61" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P61" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q61" t="s">
         <v>49</v>
@@ -5042,22 +4995,22 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N62" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P62" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q62" t="s">
         <v>24</v>
@@ -5098,22 +5051,22 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
       </c>
       <c r="M63" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N63" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O63" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P63" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q63" t="s">
         <v>24</v>
@@ -5154,22 +5107,22 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
       </c>
       <c r="M64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N64" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O64" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P64" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q64" t="s">
         <v>24</v>
@@ -5210,22 +5163,22 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N65" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O65" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P65" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q65" t="s">
         <v>33</v>
@@ -5266,22 +5219,22 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
       </c>
       <c r="M66" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N66" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O66" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P66" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q66" t="s">
         <v>33</v>
@@ -5322,22 +5275,22 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
       </c>
       <c r="M67" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N67" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O67" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P67" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q67" t="s">
         <v>33</v>
@@ -5378,19 +5331,19 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N68" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O68" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P68" t="n">
         <v>9</v>
@@ -5434,19 +5387,19 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N69" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O69" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P69" t="n">
         <v>9</v>
@@ -5490,19 +5443,19 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
       </c>
       <c r="M70" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N70" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O70" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P70" t="n">
         <v>9</v>
@@ -5546,22 +5499,22 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N71" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O71" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P71" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q71" t="s">
         <v>49</v>
@@ -5602,22 +5555,22 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
       </c>
       <c r="M72" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N72" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O72" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P72" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q72" t="s">
         <v>49</v>
@@ -5658,22 +5611,22 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
       </c>
       <c r="M73" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N73" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="O73" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P73" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q73" t="s">
         <v>49</v>
@@ -5714,22 +5667,22 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
+        <v>180</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="s">
+        <v>181</v>
+      </c>
+      <c r="N74" t="n">
+        <v>28</v>
+      </c>
+      <c r="O74" t="s">
         <v>182</v>
       </c>
-      <c r="L74" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" t="s">
-        <v>183</v>
-      </c>
-      <c r="N74" t="n">
-        <v>40</v>
-      </c>
-      <c r="O74" t="s">
-        <v>184</v>
-      </c>
       <c r="P74" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q74" t="s">
         <v>24</v>
@@ -5770,22 +5723,22 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
       </c>
       <c r="M75" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N75" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O75" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="P75" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q75" t="s">
         <v>24</v>
@@ -5826,22 +5779,22 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
       </c>
       <c r="M76" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N76" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O76" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P76" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q76" t="s">
         <v>24</v>
@@ -5882,28 +5835,28 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
+        <v>187</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="s">
+        <v>188</v>
+      </c>
+      <c r="N77" t="n">
+        <v>12</v>
+      </c>
+      <c r="O77" t="s">
         <v>189</v>
-      </c>
-      <c r="L77" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" t="s">
-        <v>190</v>
-      </c>
-      <c r="N77" t="n">
-        <v>13</v>
-      </c>
-      <c r="O77" t="s">
-        <v>191</v>
       </c>
       <c r="P77" t="n">
         <v>7</v>
       </c>
       <c r="Q77" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R77" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78">
@@ -5938,28 +5891,28 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O78" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P78" t="n">
         <v>7</v>
       </c>
       <c r="Q78" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R78" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79">
@@ -5994,28 +5947,28 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N79" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O79" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P79" t="n">
         <v>7</v>
       </c>
       <c r="Q79" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R79" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80">
@@ -6050,19 +6003,19 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N80" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O80" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P80" t="n">
         <v>9</v>
@@ -6106,19 +6059,19 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
       </c>
       <c r="M81" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N81" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O81" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P81" t="n">
         <v>9</v>
@@ -6162,19 +6115,19 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
       </c>
       <c r="M82" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N82" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O82" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P82" t="n">
         <v>9</v>
@@ -6218,28 +6171,28 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
+        <v>201</v>
+      </c>
+      <c r="N83" t="n">
+        <v>41</v>
+      </c>
+      <c r="O83" t="s">
+        <v>202</v>
+      </c>
+      <c r="P83" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q83" t="s">
         <v>203</v>
       </c>
-      <c r="N83" t="n">
-        <v>46</v>
-      </c>
-      <c r="O83" t="s">
-        <v>204</v>
-      </c>
-      <c r="P83" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>205</v>
-      </c>
       <c r="R83" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84">
@@ -6274,28 +6227,28 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N84" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O84" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P84" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q84" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R84" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="85">
@@ -6330,28 +6283,28 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N85" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O85" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P85" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q85" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R85" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86">
@@ -6386,22 +6339,22 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N86" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O86" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P86" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q86" t="s">
         <v>24</v>
@@ -6442,22 +6395,22 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
       </c>
       <c r="M87" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N87" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O87" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P87" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q87" t="s">
         <v>24</v>
@@ -6498,22 +6451,22 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
       </c>
       <c r="M88" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="N88" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O88" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P88" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q88" t="s">
         <v>24</v>
@@ -6554,28 +6507,28 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N89" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O89" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P89" t="n">
         <v>7</v>
       </c>
       <c r="Q89" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R89" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90">
@@ -6610,28 +6563,28 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N90" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O90" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P90" t="n">
         <v>7</v>
       </c>
       <c r="Q90" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R90" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91">
@@ -6666,28 +6619,28 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O91" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P91" t="n">
         <v>7</v>
       </c>
       <c r="Q91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92">
@@ -6722,19 +6675,19 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N92" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O92" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P92" t="n">
         <v>9</v>
@@ -6778,19 +6731,19 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N93" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O93" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P93" t="n">
         <v>9</v>
@@ -6834,19 +6787,19 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
       </c>
       <c r="M94" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N94" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O94" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P94" t="n">
         <v>9</v>
@@ -6890,28 +6843,28 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N95" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O95" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P95" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q95" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R95" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96">
@@ -6946,28 +6899,28 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N96" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O96" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P96" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q96" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R96" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97">
@@ -7002,28 +6955,28 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N97" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O97" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P97" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q97" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R97" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98">
@@ -7058,22 +7011,22 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
+        <v>232</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="s">
+        <v>233</v>
+      </c>
+      <c r="N98" t="n">
+        <v>28</v>
+      </c>
+      <c r="O98" t="s">
         <v>234</v>
       </c>
-      <c r="L98" t="n">
-        <v>1</v>
-      </c>
-      <c r="M98" t="s">
-        <v>235</v>
-      </c>
-      <c r="N98" t="n">
-        <v>40</v>
-      </c>
-      <c r="O98" t="s">
-        <v>236</v>
-      </c>
       <c r="P98" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q98" t="s">
         <v>24</v>
@@ -7114,22 +7067,22 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N99" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O99" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P99" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q99" t="s">
         <v>24</v>
@@ -7170,22 +7123,22 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N100" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O100" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P100" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q100" t="s">
         <v>24</v>
@@ -7226,28 +7179,28 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
+        <v>239</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="s">
+        <v>240</v>
+      </c>
+      <c r="N101" t="n">
+        <v>20</v>
+      </c>
+      <c r="O101" t="s">
         <v>241</v>
       </c>
-      <c r="L101" t="n">
-        <v>1</v>
-      </c>
-      <c r="M101" t="s">
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="s">
         <v>242</v>
       </c>
-      <c r="N101" t="n">
-        <v>24</v>
-      </c>
-      <c r="O101" t="s">
-        <v>243</v>
-      </c>
-      <c r="P101" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>244</v>
-      </c>
       <c r="R101" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="102">
@@ -7282,28 +7235,28 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="N102" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O102" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P102" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q102" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R102" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="103">
@@ -7338,28 +7291,28 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="N103" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O103" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P103" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q103" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R103" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="104">
@@ -7394,19 +7347,19 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N104" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O104" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P104" t="n">
         <v>9</v>
@@ -7450,19 +7403,19 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
       </c>
       <c r="M105" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N105" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O105" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P105" t="n">
         <v>9</v>
@@ -7506,19 +7459,19 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
       </c>
       <c r="M106" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N106" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O106" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P106" t="n">
         <v>9</v>
@@ -7562,28 +7515,28 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
+        <v>253</v>
+      </c>
+      <c r="N107" t="n">
+        <v>60</v>
+      </c>
+      <c r="O107" t="s">
+        <v>254</v>
+      </c>
+      <c r="P107" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q107" t="s">
         <v>255</v>
       </c>
-      <c r="N107" t="n">
-        <v>70</v>
-      </c>
-      <c r="O107" t="s">
-        <v>256</v>
-      </c>
-      <c r="P107" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>257</v>
-      </c>
       <c r="R107" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="108">
@@ -7618,28 +7571,28 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N108" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O108" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P108" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q108" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R108" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="109">
@@ -7674,28 +7627,28 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N109" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O109" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P109" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q109" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R109" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="110">
@@ -7730,22 +7683,22 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N110" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O110" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P110" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q110" t="s">
         <v>24</v>
@@ -7786,22 +7739,22 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N111" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O111" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P111" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q111" t="s">
         <v>24</v>
@@ -7842,22 +7795,22 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N112" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O112" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P112" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q112" t="s">
         <v>24</v>
@@ -7898,28 +7851,28 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N113" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O113" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P113" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q113" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R113" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="114">
@@ -7954,28 +7907,28 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N114" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O114" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P114" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q114" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R114" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="115">
@@ -8010,28 +7963,28 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N115" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O115" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P115" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q115" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R115" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="116">
@@ -8066,19 +8019,19 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N116" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O116" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P116" t="n">
         <v>9</v>
@@ -8122,19 +8075,19 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
       </c>
       <c r="M117" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="N117" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O117" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P117" t="n">
         <v>9</v>
@@ -8178,19 +8131,19 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
       </c>
       <c r="M118" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N118" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O118" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P118" t="n">
         <v>9</v>
@@ -8234,28 +8187,28 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N119" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O119" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P119" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q119" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R119" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="120">
@@ -8290,28 +8243,28 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N120" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O120" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P120" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q120" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R120" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="121">
@@ -8346,28 +8299,28 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N121" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O121" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P121" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q121" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R121" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="122">
@@ -8402,28 +8355,28 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
+        <v>284</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="s">
+        <v>285</v>
+      </c>
+      <c r="N122" t="n">
+        <v>24</v>
+      </c>
+      <c r="O122" t="s">
         <v>286</v>
       </c>
-      <c r="L122" t="n">
-        <v>1</v>
-      </c>
-      <c r="M122" t="s">
+      <c r="P122" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q122" t="s">
         <v>287</v>
       </c>
-      <c r="N122" t="n">
-        <v>30</v>
-      </c>
-      <c r="O122" t="s">
-        <v>288</v>
-      </c>
-      <c r="P122" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>289</v>
-      </c>
       <c r="R122" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="123">
@@ -8458,28 +8411,28 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N123" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="O123" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P123" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q123" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R123" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="124">
@@ -8514,28 +8467,28 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N124" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="O124" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P124" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q124" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R124" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="125">
@@ -8570,28 +8523,28 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
+        <v>292</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="s">
+        <v>293</v>
+      </c>
+      <c r="N125" t="n">
+        <v>20</v>
+      </c>
+      <c r="O125" t="s">
         <v>294</v>
       </c>
-      <c r="L125" t="n">
-        <v>1</v>
-      </c>
-      <c r="M125" t="s">
-        <v>295</v>
-      </c>
-      <c r="N125" t="n">
-        <v>24</v>
-      </c>
-      <c r="O125" t="s">
-        <v>296</v>
-      </c>
       <c r="P125" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q125" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R125" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="126">
@@ -8626,28 +8579,28 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="N126" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O126" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P126" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q126" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R126" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="127">
@@ -8682,28 +8635,28 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N127" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O127" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P127" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q127" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R127" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="128">
@@ -8711,7 +8664,7 @@
         <v>256</v>
       </c>
       <c r="B128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -8738,28 +8691,24 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>301</v>
-      </c>
-      <c r="N128" t="n">
-        <v>4</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N128"/>
       <c r="O128" t="s">
-        <v>302</v>
-      </c>
-      <c r="P128" t="n">
-        <v>3</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="P128"/>
       <c r="Q128" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="R128" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="129">
@@ -8767,7 +8716,7 @@
         <v>257</v>
       </c>
       <c r="B129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -8794,28 +8743,24 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>304</v>
-      </c>
-      <c r="N129" t="n">
-        <v>4</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N129"/>
       <c r="O129" t="s">
-        <v>305</v>
-      </c>
-      <c r="P129" t="n">
-        <v>3</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="P129"/>
       <c r="Q129" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="R129" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="130">
@@ -8823,7 +8768,7 @@
         <v>258</v>
       </c>
       <c r="B130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -8850,28 +8795,24 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>306</v>
-      </c>
-      <c r="N130" t="n">
-        <v>4</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N130"/>
       <c r="O130" t="s">
-        <v>307</v>
-      </c>
-      <c r="P130" t="n">
-        <v>3</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="P130"/>
       <c r="Q130" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="R130" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="131">
@@ -8906,28 +8847,28 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="N131" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="O131" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="P131" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q131" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="R131" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="132">
@@ -8962,28 +8903,28 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="N132" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="O132" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="P132" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q132" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="R132" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="133">
@@ -9018,28 +8959,28 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N133" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="O133" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="P133" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q133" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="R133" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="134">
@@ -9074,28 +9015,28 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N134" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="O134" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="P134" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q134" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R134" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="135">
@@ -9130,28 +9071,28 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="N135" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="O135" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="P135" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q135" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R135" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="136">
@@ -9186,28 +9127,28 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="N136" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="O136" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="P136" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q136" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R136" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="137">
@@ -9242,28 +9183,28 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="N137" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O137" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="P137" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q137" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R137" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="138">
@@ -9298,28 +9239,28 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="N138" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O138" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="P138" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q138" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R138" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="139">
@@ -9354,28 +9295,28 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="N139" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O139" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="P139" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q139" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R139" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140">
@@ -9410,28 +9351,24 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>306</v>
-      </c>
-      <c r="N140" t="n">
-        <v>4</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N140"/>
       <c r="O140" t="s">
-        <v>307</v>
-      </c>
-      <c r="P140" t="n">
-        <v>3</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="P140"/>
       <c r="Q140" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="R140" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="141">
@@ -9466,28 +9403,24 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>327</v>
-      </c>
-      <c r="N141" t="n">
-        <v>4</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N141"/>
       <c r="O141" t="s">
-        <v>328</v>
-      </c>
-      <c r="P141" t="n">
-        <v>3</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="P141"/>
       <c r="Q141" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="R141" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="142">
@@ -9522,28 +9455,24 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>329</v>
-      </c>
-      <c r="N142" t="n">
-        <v>4</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N142"/>
       <c r="O142" t="s">
-        <v>330</v>
-      </c>
-      <c r="P142" t="n">
-        <v>3</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="P142"/>
       <c r="Q142" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="R142" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="143">
@@ -9578,28 +9507,28 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="N143" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="O143" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="P143" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q143" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="R143" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="144">
@@ -9634,28 +9563,28 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="N144" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="O144" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="P144" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q144" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="R144" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="145">
@@ -9690,28 +9619,28 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="N145" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="O145" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="P145" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q145" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="R145" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="146">
@@ -9746,28 +9675,28 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="N146" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O146" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="P146" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q146" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R146" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="147">
@@ -9802,28 +9731,28 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="N147" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O147" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="P147" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q147" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R147" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="148">
@@ -9858,28 +9787,28 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="N148" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O148" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="P148" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q148" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R148" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="149">
@@ -9914,24 +9843,24 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N149"/>
       <c r="O149" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P149"/>
       <c r="Q149" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R149" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="150">
@@ -9966,24 +9895,24 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
       </c>
       <c r="M150" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N150"/>
       <c r="O150" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P150"/>
       <c r="Q150" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R150" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="151">
@@ -10018,24 +9947,24 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
       </c>
       <c r="M151" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N151"/>
       <c r="O151" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P151"/>
       <c r="Q151" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R151" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="152">
@@ -10070,24 +9999,24 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N152"/>
       <c r="O152" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P152"/>
       <c r="Q152" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R152" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="153">
@@ -10122,24 +10051,24 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
       </c>
       <c r="M153" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N153"/>
       <c r="O153" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P153"/>
       <c r="Q153" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R153" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="154">
@@ -10174,24 +10103,24 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
       </c>
       <c r="M154" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N154"/>
       <c r="O154" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P154"/>
       <c r="Q154" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R154" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="155">
@@ -10226,28 +10155,28 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="N155" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O155" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="P155" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q155" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R155" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="156">
@@ -10282,28 +10211,28 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="N156" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O156" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="P156" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q156" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R156" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="157">
@@ -10338,28 +10267,28 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="N157" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O157" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="P157" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q157" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R157" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="158">
@@ -10394,28 +10323,28 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="N158" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O158" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="P158" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q158" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R158" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="159">
@@ -10450,28 +10379,28 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="N159" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O159" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="P159" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q159" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R159" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="160">
@@ -10506,28 +10435,28 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="N160" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O160" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="P160" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q160" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R160" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="161">
@@ -10562,24 +10491,24 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N161"/>
       <c r="O161" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P161"/>
       <c r="Q161" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R161" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="162">
@@ -10614,24 +10543,24 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
       </c>
       <c r="M162" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N162"/>
       <c r="O162" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P162"/>
       <c r="Q162" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R162" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="163">
@@ -10666,24 +10595,24 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
       </c>
       <c r="M163" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N163"/>
       <c r="O163" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P163"/>
       <c r="Q163" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R163" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="164">
@@ -10718,24 +10647,24 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
       </c>
       <c r="M164" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N164"/>
       <c r="O164" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P164"/>
       <c r="Q164" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R164" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="165">
@@ -10770,24 +10699,24 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
       </c>
       <c r="M165" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N165"/>
       <c r="O165" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P165"/>
       <c r="Q165" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R165" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="166">
@@ -10822,24 +10751,24 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
       </c>
       <c r="M166" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N166"/>
       <c r="O166" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P166"/>
       <c r="Q166" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R166" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="167">
@@ -10874,28 +10803,28 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="N167" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O167" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="P167" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q167" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R167" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="168">
@@ -10930,28 +10859,28 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="N168" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O168" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="P168" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q168" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R168" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="169">
@@ -10986,28 +10915,28 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="N169" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O169" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="P169" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q169" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R169" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="170">
@@ -11042,28 +10971,28 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="N170" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O170" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="P170" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q170" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R170" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="171">
@@ -11098,28 +11027,28 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="N171" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O171" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="P171" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q171" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R171" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="172">
@@ -11154,28 +11083,28 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="N172" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O172" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="P172" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q172" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R172" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="173">
@@ -11210,24 +11139,24 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N173"/>
       <c r="O173" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P173"/>
       <c r="Q173" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R173" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="174">
@@ -11262,24 +11191,24 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
       </c>
       <c r="M174" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N174"/>
       <c r="O174" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P174"/>
       <c r="Q174" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R174" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="175">
@@ -11314,24 +11243,24 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
       </c>
       <c r="M175" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N175"/>
       <c r="O175" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P175"/>
       <c r="Q175" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R175" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="176">
@@ -11366,24 +11295,24 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
       </c>
       <c r="M176" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N176"/>
       <c r="O176" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P176"/>
       <c r="Q176" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R176" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177">
@@ -11418,24 +11347,24 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
       </c>
       <c r="M177" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N177"/>
       <c r="O177" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P177"/>
       <c r="Q177" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R177" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178">
@@ -11470,24 +11399,24 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
       </c>
       <c r="M178" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N178"/>
       <c r="O178" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P178"/>
       <c r="Q178" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R178" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="179">
@@ -11522,28 +11451,28 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="N179" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O179" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="P179" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q179" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R179" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="180">
@@ -11578,28 +11507,28 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="N180" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O180" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="P180" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q180" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R180" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="181">
@@ -11634,28 +11563,28 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="N181" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O181" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="P181" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q181" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R181" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="182">
@@ -11690,28 +11619,28 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
+        <v>353</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="s">
         <v>366</v>
       </c>
-      <c r="L182" t="n">
-        <v>1</v>
-      </c>
-      <c r="M182" t="s">
-        <v>379</v>
-      </c>
       <c r="N182" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O182" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="P182" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q182" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R182" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="183">
@@ -11746,28 +11675,28 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="N183" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O183" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="P183" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q183" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R183" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="184">
@@ -11802,28 +11731,28 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="N184" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O184" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="P184" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q184" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="R184" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="185">
@@ -11858,24 +11787,24 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
       </c>
       <c r="M185" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N185"/>
       <c r="O185" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P185"/>
       <c r="Q185" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R185" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="186">
@@ -11910,24 +11839,24 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
       </c>
       <c r="M186" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N186"/>
       <c r="O186" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P186"/>
       <c r="Q186" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R186" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="187">
@@ -11962,24 +11891,24 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
       </c>
       <c r="M187" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N187"/>
       <c r="O187" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P187"/>
       <c r="Q187" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R187" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="188">
@@ -12014,24 +11943,24 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
       </c>
       <c r="M188" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N188"/>
       <c r="O188" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P188"/>
       <c r="Q188" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R188" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="189">
@@ -12066,24 +11995,24 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
       </c>
       <c r="M189" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N189"/>
       <c r="O189" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P189"/>
       <c r="Q189" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R189" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="190">
@@ -12118,24 +12047,24 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
       </c>
       <c r="M190" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N190"/>
       <c r="O190" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P190"/>
       <c r="Q190" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R190" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="191">
@@ -12170,28 +12099,28 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="N191" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O191" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="P191" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q191" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R191" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="192">
@@ -12226,28 +12155,28 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="N192" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O192" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="P192" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q192" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R192" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="193">
@@ -12282,28 +12211,28 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="N193" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O193" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="P193" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q193" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R193" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="194">
@@ -12338,28 +12267,28 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="N194" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O194" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="P194" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q194" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="R194" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="195">
@@ -12394,28 +12323,28 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="N195" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O195" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="P195" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q195" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="R195" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="196">
@@ -12450,28 +12379,28 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="N196" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O196" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="P196" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q196" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="R196" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="197">
@@ -12506,24 +12435,24 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
       </c>
       <c r="M197" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N197"/>
       <c r="O197" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P197"/>
       <c r="Q197" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R197" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="198">
@@ -12558,24 +12487,24 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
       </c>
       <c r="M198" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N198"/>
       <c r="O198" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P198"/>
       <c r="Q198" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R198" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="199">
@@ -12610,24 +12539,24 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
       </c>
       <c r="M199" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N199"/>
       <c r="O199" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P199"/>
       <c r="Q199" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R199" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="200">
@@ -12662,24 +12591,24 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
       </c>
       <c r="M200" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N200"/>
       <c r="O200" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P200"/>
       <c r="Q200" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R200" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="201">
@@ -12714,24 +12643,24 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
       </c>
       <c r="M201" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N201"/>
       <c r="O201" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P201"/>
       <c r="Q201" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R201" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="202">
@@ -12766,24 +12695,24 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
       </c>
       <c r="M202" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N202"/>
       <c r="O202" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P202"/>
       <c r="Q202" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R202" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="203">
@@ -12818,28 +12747,28 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="N203" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O203" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="P203" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q203" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R203" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="204">
@@ -12874,28 +12803,28 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="N204" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O204" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="P204" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q204" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R204" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="205">
@@ -12930,28 +12859,28 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="N205" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O205" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="P205" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q205" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R205" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="206">
@@ -12986,28 +12915,28 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="N206" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O206" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="P206" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q206" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="R206" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="207">
@@ -13042,28 +12971,28 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="N207" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O207" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="P207" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q207" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="R207" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="208">
@@ -13098,28 +13027,28 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="N208" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O208" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="P208" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q208" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="R208" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="209">
@@ -13154,24 +13083,24 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
       </c>
       <c r="M209" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N209"/>
       <c r="O209" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P209"/>
       <c r="Q209" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R209" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="210">
@@ -13206,24 +13135,24 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
       </c>
       <c r="M210" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N210"/>
       <c r="O210" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P210"/>
       <c r="Q210" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R210" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="211">
@@ -13258,24 +13187,24 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
       </c>
       <c r="M211" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N211"/>
       <c r="O211" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P211"/>
       <c r="Q211" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R211" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="212">
@@ -13310,24 +13239,24 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
       </c>
       <c r="M212" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N212"/>
       <c r="O212" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P212"/>
       <c r="Q212" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R212" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="213">
@@ -13362,24 +13291,24 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
       </c>
       <c r="M213" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N213"/>
       <c r="O213" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P213"/>
       <c r="Q213" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R213" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="214">
@@ -13414,24 +13343,24 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
       </c>
       <c r="M214" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N214"/>
       <c r="O214" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="P214"/>
       <c r="Q214" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="R214" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
     </row>
     <row r="215">
@@ -13466,28 +13395,28 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="N215" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O215" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="P215" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q215" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R215" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="216">
@@ -13522,28 +13451,28 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="N216" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O216" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="P216" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q216" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R216" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="217">
@@ -13578,28 +13507,28 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="N217" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O217" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="P217" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q217" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="R217" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -80,1145 +80,1192 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 148, 150, 151, 152, 1652, 1653, 1654, 1692, 1751, 1752, 1754, 1755, 1824, 1897, 1898, 1900, 2054, 2227, 2231, 2281, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 149, 1655, 1691, 1693, 1750, 1753, 1756, 1757, 1773, 2056, 2058, 2229, 2279)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 148, 149, 150, 152, 1652, 1691, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 151, 1653, 1654, 1655, 1692, 1693, 1753, 1898, 2281, 2282, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 148, 150, 151, 1652, 1653, 1654, 1691, 1692, 1693, 1751, 1752, 1753, 1757, 1773, 1898, 2054, 2056, 2058, 2227, 2231, 2281, 2282, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 149, 152, 1655, 1750, 1754, 1755, 1756, 1824, 1897, 1900, 2229, 2279, 2283)</t>
+    <t xml:space="preserve">c(17, 18, 19, 23, 33, 34, 35, 151, 152, 1652, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1773, 1774, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2179, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 32, 148, 149, 150, 1653, 1654, 1655, 1691, 1755, 1757, 1772, 1824, 2177, 2229, 2283, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 34, 35, 149, 150, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1756, 1772, 1773, 1774, 1826, 1827, 1897, 1898, 1900, 2058, 2179, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 31, 32, 33, 148, 152, 1753, 1754, 1755, 1757, 1771, 1824, 1825, 2054, 2056, 2177, 2229, 2283, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 33, 34, 148, 149, 150, 152, 1655, 1691, 1693, 1751, 1757, 1771, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 1900, 2054, 2056, 2058, 2179, 2227, 2229, 2231, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 35, 151, 1652, 1653, 1654, 1692, 1750, 1752, 1753, 1754, 1755, 1756, 1772, 1827, 2177, 2279, 2281, 2292, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 226, 1719, 1720, 1721, 1722, 1778, 1869, 1870, 2027, 2033, 2119, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 228, 1727, 1775, 1776, 1777, 1779, 1868, 2029, 2035, 2037, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 228, 1719, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2033, 2120, 2121, 2124, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 224, 226, 1720, 1722, 2029, 2035, 2037, 2119, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 226, 228, 1720, 1722, 1775, 1776, 1777, 1779, 1870, 2027, 2029, 2033, 2035, 2119, 2120, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 222, 224, 1719, 1721, 1727, 1778, 1868, 1869, 2037, 2121, 2224)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 226, 275, 276, 277, 278, 279, 280, 1719, 1720, 1722, 1775, 1777, 1778, 1779, 1868, 1869, 2027, 2035, 2037, 2120, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 224, 228, 1721, 1727, 1776, 1870, 2029, 2033, 2119, 2121, 2124, 2125, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 224, 228, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1777, 1778, 1868, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2124, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 226, 275, 276, 277, 1776, 1779, 1869, 2120, 2121, 2125, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 228, 275, 276, 277, 278, 280, 1719, 1722, 1777, 1778, 1779, 1869, 1870, 2027, 2029, 2033, 2035, 2119, 2120, 2121, 2124, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 224, 226, 279, 1720, 1721, 1727, 1775, 1776, 1868, 2037, 2125, 2221)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 203, 206, 207, 208, 209, 210, 211, 212, 213, 214, 216, 218, 219, 266, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 205, 217, 220, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 216, 217, 218, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 207, 211, 213, 214, 217, 218, 219, 220, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 206, 208, 209, 210, 212, 216, 266, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 206, 207, 209, 210, 211, 212, 213, 214, 217, 219, 220, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 205, 208, 216, 218, 266, 267, 1899)</t>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 208, 211, 212, 215, 216, 217, 218, 219, 265, 266, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 209, 210, 213, 214, 220, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 208, 210, 211, 212, 213, 214, 215, 216, 217, 219, 265, 266, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 207, 209, 218, 220, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 205, 206, 209, 210, 211, 212, 214, 216, 218, 219, 220, 266, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 207, 208, 213, 215, 217, 265, 2230)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 132, 141, 177, 179, 221, 223, 225, 227, 229, 230, 231, 234, 235, 236, 244, 245, 248, 249, 281, 282, 283, 285, 286, 287, 288, 289, 290, 291, 293, 294, 295, 296, 1717, 1763, 1838, 1839, 1864, 1865, 1866, 1874, 1875, 1991, 1992, 2028, 2030, 2032, 2036, 2108, 2109, 2131, 2132, 2133, 2135, 2137, 2138, 2139, 2222, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 140, 142, 143, 176, 178, 180, 181, 182, 233, 243, 246, 250, 284, 292, 1716, 1718, 1760, 1761, 1762, 1840, 1852, 1863, 1867, 1876, 1990, 2026, 2034, 2128, 2129, 2130, 2134, 2136, 2194, 2223)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 130, 131, 132, 140, 141, 142, 143, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
-2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 131, 140, 141, 142, 143, 177, 179, 180, 182, 223, 227, 231, 233, 234, 235, 236, 243, 244, 245, 246, 249, 250, 281, 282, 283, 285, 286, 287, 290, 291, 292, 293, 294, 295, 296, 1716, 1760, 1763, 1839, 1840, 1863, 1864, 1866, 1867, 1874, 1991, 1992, 2026, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2133, 2134, 2139, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 130, 132, 176, 178, 181, 221, 225, 229, 230, 248, 284, 288, 289, 1717, 1718, 1761, 1762, 1838, 1852, 1865, 1875, 1876, 1990, 2028, 2030, 2132, 2135, 2136, 2137, 2138, 2194, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 130, 131, 132, 142, 143, 177, 178, 179, 180, 182, 221, 225, 227, 231, 233, 235, 236, 243, 244, 246, 249, 250, 281, 282, 283, 284, 285, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1864, 1866, 1874, 1876, 1990, 2026, 2028, 2030, 2108, 2109, 2128, 2129, 2131, 2132, 2133, 2134, 2137, 2138, 2139, 2222, 2223, 2225, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 140, 141, 176, 181, 223, 229, 230, 234, 245, 248, 286, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1865, 1867, 1875, 1991, 1992, 2032, 2034, 2036, 2130, 2135, 2136, 2194, 2226, 2313)</t>
+    <t xml:space="preserve">c(15, 70, 72, 73, 141, 142, 176, 177, 178, 179, 180, 221, 225, 227, 229, 230, 231, 233, 234, 236, 243, 244, 245, 246, 247, 248, 249, 271, 273, 281, 282, 283, 286, 287, 290, 292, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1839, 1840, 1863, 1864, 1865, 1867, 1874, 1875, 1935, 1990, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2131, 2134, 2138, 2194, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 71, 130, 131, 132, 140, 143, 175, 181, 182, 223, 235, 250, 272, 274, 284, 285, 288, 289, 291, 293, 1717, 1766, 1838, 1852, 1866, 1876, 1991, 1992, 2129, 2130, 2132, 2133, 2135, 2136, 2137, 2139, 2222, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 
+2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 73, 130, 131, 132, 142, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 230, 234, 235, 236, 244, 245, 246, 248, 249, 250, 271, 272, 281, 282, 283, 286, 287, 288, 290, 291, 292, 296, 1760, 1762, 1763, 1764, 1765, 1766, 1839, 1840, 1852, 1864, 1875, 1876, 1935, 1990, 1991, 1992, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2132, 2134, 2136, 2138, 2194, 2222, 2223, 2257, 2300, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 140, 141, 143, 175, 229, 231, 233, 243, 247, 273, 274, 284, 285, 289, 293, 294, 295, 1716, 1717, 1718, 1761, 1838, 1863, 1865, 1866, 1867, 1874, 2026, 2028, 2130, 2131, 2133, 2135, 2137, 2139, 2225, 2226, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 132, 141, 142, 143, 175, 176, 180, 182, 221, 223, 225, 227, 230, 233, 234, 235, 236, 243, 244, 245, 246, 247, 249, 271, 272, 273, 274, 281, 283, 286, 292, 293, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1766, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 2026, 2028, 2030, 2034, 2036, 2108, 2109, 2128, 2132, 2135, 2136, 2137, 2139, 2223, 2226, 2257, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 130, 131, 140, 177, 178, 179, 181, 229, 231, 248, 250, 282, 284, 285, 287, 288, 289, 290, 291, 294, 295, 1717, 1764, 1765, 1840, 1875, 1992, 2032, 2129, 2130, 2131, 2133, 2134, 2138, 2194, 2222, 2225, 2302, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 23, 150, 151, 152, 1652, 1653, 1655, 1692, 1693, 1750, 1751, 1755, 1756, 1773, 1824, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 148, 149, 1654, 1691, 1752, 1753, 1754, 1757, 1897, 1898, 2282)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 148, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1897, 1898, 1900, 2054, 2058, 2229, 2231, 2281, 2282, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 149, 150, 1757, 1773, 1824, 2056, 2227, 2279, 2283, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 148, 150, 151, 152, 1652, 1654, 1692, 1693, 1752, 1753, 1754, 1755, 1756, 1757, 1824, 1897, 2054, 2056, 2227, 2229, 2279, 2281, 2282, 2283, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 149, 1653, 1655, 1691, 1750, 1751, 1773, 1898, 1900, 2058, 2231, 2290)</t>
+    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 35, 152, 1653, 1654, 1655, 1692, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1774, 1825, 1898, 2054, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 148, 149, 150, 151, 1652, 1691, 1753, 1771, 1772, 1773, 1824, 1826, 1827, 1897, 1900, 2056, 2281, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 148, 149, 1652, 1654, 1655, 1691, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1824, 1825, 1827, 1897, 1898, 1900, 2058, 2179, 2227, 2229, 2231, 2281, 2282, 2289, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 33, 34, 35, 150, 151, 152, 1653, 1693, 1772, 1773, 1826, 2054, 2056, 2177, 2279, 2283, 2288, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 31, 32, 33, 34, 35, 151, 152, 1652, 1653, 1655, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1771, 1772, 1774, 1824, 1826, 1827, 1897, 2054, 2056, 2058, 2177, 2179, 2227, 2231, 2281, 2282, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 148, 149, 150, 1654, 1691, 1693, 1753, 1757, 1773, 1825, 1898, 1900, 2229, 2279, 2283, 2288, 2292)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 43, 226, 228, 1719, 1720, 1722, 1727, 1777, 1868, 1869, 1870, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2125, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 222, 224, 1721, 1775, 1776, 1778, 1779, 2027, 2124, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 226, 228, 1719, 1720, 1727, 1775, 1777, 1778, 1779, 1868, 2033, 2037, 2121, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 1721, 1722, 1776, 1869, 1870, 2027, 2029, 2035, 2119, 2120, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 222, 224, 226, 1719, 1722, 1727, 1775, 1776, 1777, 1779, 1869, 2033, 2035, 2037, 2119, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 228, 1720, 1721, 1778, 1868, 1870, 2027, 2029, 2120, 2121, 2126)</t>
+    <t xml:space="preserve">c(41, 222, 224, 226, 228, 275, 278, 279, 1719, 1720, 1721, 1727, 1775, 1776, 1868, 1869, 1870, 2027, 2029, 2033, 2119, 2120, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 276, 277, 280, 1722, 1777, 1778, 1779, 2035, 2037, 2121, 2124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 226, 228, 275, 276, 277, 279, 1719, 1721, 1722, 1727, 1775, 1777, 1779, 1868, 1869, 1870, 2035, 2037, 2119, 2120, 2121, 2125, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(222, 224, 278, 280, 1720, 1776, 1778, 2027, 2029, 2033, 2124, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 222, 224, 277, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1778, 1868, 1869, 2027, 2029, 2033, 2119, 2120, 2121, 2124, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 226, 228, 275, 276, 278, 1777, 1779, 1870, 2035, 2037, 2126, 2221)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 206, 207, 208, 210, 211, 213, 217, 219, 220, 266, 267, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 209, 212, 214, 216, 218, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 207, 208, 210, 212, 213, 216, 217, 266, 267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 206, 209, 211, 214, 218, 219, 220, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 210, 211, 212, 216, 217, 219, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 207, 213, 214, 218, 220, 266, 267, 2232)</t>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 208, 209, 212, 215, 217, 220, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(207, 210, 211, 213, 214, 216, 218, 219, 265)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 207, 208, 209, 210, 211, 212, 214, 215, 216, 219, 266, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 206, 213, 217, 218, 220, 265, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 205, 206, 207, 208, 209, 211, 214, 215, 216, 218, 219, 220, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 210, 212, 213, 217, 265, 266, 2232)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(14, 15, 130, 131, 142, 143, 176, 179, 180, 181, 182, 229, 233, 236, 244, 245, 246, 250, 281, 282, 283, 285, 288, 290, 291, 292, 293, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1840, 1852, 1863, 1864, 1865, 1866, 1874, 1875, 1876, 1992, 2026, 2028, 2030, 2034, 2036, 2108, 2109, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 132, 140, 141, 177, 178, 221, 223, 225, 227, 230, 231, 234, 235, 243, 248, 249, 284, 286, 287, 289, 294, 296, 1763, 1838, 1839, 1867, 1990, 1991, 2032, 2128, 2129, 2130, 2134, 2223)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 130, 131, 140, 141, 142, 143, 176, 178, 179, 180, 182, 223, 225, 230, 231, 233, 236, 244, 245, 246, 248, 249, 250, 281, 282, 283, 285, 287, 288, 290, 291, 294, 295, 296, 1718, 1762, 1840, 1852, 1863, 1864, 1866, 1867, 1874, 1875, 2026, 2030, 2034, 2036, 2108, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2301, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 132, 177, 181, 221, 227, 229, 234, 235, 243, 284, 286, 289, 292, 293, 1716, 1717, 1760, 1761, 1763, 1838, 1839, 1865, 1876, 1990, 1991, 1992, 2028, 2032, 2109, 2128, 2136, 2226, 2300, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 131, 132, 141, 142, 143, 178, 180, 181, 182, 221, 223, 229, 230, 231, 234, 235, 243, 245, 248, 250, 285, 286, 288, 289, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1852, 1863, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2034, 2036, 2109, 2128, 2129, 2132, 2133, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2300, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 130, 140, 176, 177, 179, 225, 227, 233, 236, 244, 246, 249, 281, 282, 283, 284, 287, 290, 291, 1716, 1839, 1840, 1864, 1865, 2030, 2032, 2108, 2130, 2131, 2134, 2135, 2225, 2301, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 149, 150, 151, 152, 1653, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1897, 1898, 2054, 2056, 2058, 2227, 2281, 2282, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 148, 1652, 1692, 1757, 1773, 1824, 1900, 2229, 2231, 2279, 2283, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 150, 152, 1652, 1653, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1753, 1755, 1756, 1757, 1897, 2054, 2229, 2231, 2279, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 148, 149, 151, 1692, 1754, 1773, 1824, 1898, 1900, 2056, 2058, 2227, 2281)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 148, 151, 152, 1652, 1653, 1691, 1693, 1750, 1751, 1754, 1755, 1756, 1773, 1824, 1897, 1900, 2054, 2056, 2058, 2227, 2229, 2281, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 149, 150, 1654, 1655, 1692, 1752, 1753, 1757, 1898, 2231, 2279)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 224, 226, 1719, 1720, 1721, 1722, 1778, 1779, 1868, 1869, 2027, 2033, 2035, 2119, 2120, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 228, 1727, 1775, 1776, 1777, 1870, 2029, 2037, 2121, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 226, 228, 1719, 1720, 1722, 1775, 1776, 1777, 1869, 1870, 2027, 2029, 2119, 2121, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 224, 1721, 1727, 1778, 1779, 1868, 2033, 2035, 2037, 2120, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 226, 228, 1720, 1721, 1722, 1727, 1777, 1868, 1869, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 224, 1719, 1775, 1776, 1778, 1779, 1870, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 207, 208, 211, 213, 214, 216, 217, 218, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 206, 209, 210, 212, 219, 220)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 206, 207, 210, 211, 212, 213, 216, 217, 219, 266, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 208, 209, 214, 218, 220, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 206, 207, 208, 209, 210, 212, 217, 218, 219, 220, 266, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 211, 213, 214, 216, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 130, 132, 140, 141, 142, 143, 176, 179, 180, 223, 225, 229, 230, 231, 233, 235, 236, 243, 244, 246, 249, 281, 282, 284, 285, 286, 287, 289, 291, 292, 294, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1840, 1863, 1864, 1865, 1867, 1875, 1876, 1990, 1991, 2026, 2030, 2032, 2034, 2036, 2108, 2128, 2129, 2131, 2132, 2133, 2135, 2137, 2139, 2194, 2222, 2226, 2300, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 131, 177, 178, 181, 182, 221, 227, 234, 245, 248, 250, 283, 288, 290, 293, 296, 1763, 1838, 1839, 1852, 1866, 1874, 1992, 2028, 2109, 2130, 2134, 2136, 2138, 2223, 2225, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 130, 131, 132, 140, 142, 143, 176, 178, 180, 182, 225, 227, 229, 230, 235, 243, 244, 246, 248, 250, 282, 283, 284, 285, 286, 287, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1838, 1839, 1852, 1865, 1867, 1991, 1992, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2133, 2134, 2136, 2137, 2138, 2194, 2222, 2223, 2225, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(141, 177, 179, 181, 221, 223, 231, 233, 234, 236, 245, 249, 281, 288, 289, 290, 291, 292, 1716, 1763, 1840, 1863, 1864, 1866, 1874, 1875, 1876, 1990, 2026, 2131, 2132, 2135, 2139, 2226, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 130, 132, 140, 141, 143, 177, 178, 182, 221, 223, 227, 229, 233, 234, 235, 243, 245, 246, 282, 285, 286, 287, 288, 289, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1867, 1874, 1875, 1991, 1992, 2030, 2032, 2034, 2036, 2109, 2128, 2129, 2130, 2133, 2134, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2301, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 142, 176, 179, 180, 181, 225, 230, 231, 236, 244, 248, 249, 250, 281, 283, 284, 290, 291, 1716, 1762, 1865, 1876, 1990, 2026, 2028, 2108, 2131, 2132, 2135, 2136, 2222, 2300, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 148, 149, 150, 152, 1653, 1654, 1655, 1691, 1692, 1750, 1751, 1753, 1755, 1757, 1824, 1897, 1900, 2056, 2058, 2231, 2279, 2281, 2283, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 151, 1652, 1693, 1752, 1754, 1756, 1773, 1898, 2054, 2227, 2229, 2282, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 149, 150, 151, 152, 1652, 1653, 1655, 1692, 1750, 1753, 1754, 1756, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2279, 2281, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(148, 1654, 1691, 1693, 1751, 1752, 1755, 1757, 1773, 1824, 2231, 2282, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1752, 1754, 1756, 1757, 1773, 1897, 2054, 2056, 2058, 2227, 2229, 2231, 2281, 2282, 2283, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 148, 149, 1693, 1751, 1753, 1755, 1824, 1898, 1900, 2279, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 224, 226, 1719, 1720, 1776, 1777, 1778, 1868, 1869, 2029, 2033, 2035, 2037, 2120, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 228, 1721, 1722, 1727, 1775, 1779, 1870, 2027, 2119, 2121, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 226, 1719, 1721, 1775, 1777, 1778, 1779, 2027, 2029, 2033, 2035, 2119, 2120, 2121, 2124, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 228, 1720, 1722, 1727, 1776, 1868, 1869, 1870, 2037, 2125, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 1719, 1720, 1721, 1775, 1776, 1868, 1870, 2027, 2033, 2119, 2121, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(228, 1722, 1727, 1777, 1778, 1779, 1869, 2029, 2035, 2037, 2120, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 207, 208, 209, 210, 211, 213, 214, 216, 218, 220, 266, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 212, 217, 219, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 209, 212, 214, 216, 217, 218, 219, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 207, 208, 210, 211, 213, 220, 266, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 213, 214, 217, 218, 220, 266, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 208, 211, 212, 216, 219, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 140, 142, 143, 177, 178, 179, 180, 181, 221, 223, 225, 227, 229, 230, 231, 233, 234, 236, 243, 245, 246, 248, 249, 250, 281, 282, 283, 285, 286, 289, 291, 292, 293, 295, 296, 1716, 1718, 1760, 1763, 1838, 1839, 1852, 1863, 1865, 1876, 1990, 2030, 2032, 2034, 2108, 2109, 2130, 2131, 2132, 2133, 2135, 2136, 2138, 2139, 2222, 2223, 2226, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 130, 131, 132, 141, 176, 182, 235, 244, 284, 287, 288, 290, 294, 1717, 1761, 1762, 1840, 1864, 1866, 1867, 1874, 1875, 1991, 1992, 2026, 2028, 2036, 2128, 2129, 2134, 2137, 2194, 2225, 2300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 130, 131, 142, 176, 177, 178, 181, 182, 221, 223, 227, 229, 233, 234, 235, 236, 243, 244, 246, 248, 250, 281, 282, 283, 284, 285, 286, 287, 289, 290, 291, 294, 296, 1716, 1717, 1718, 1761, 1762, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1875, 1876, 1990, 1991, 2026, 2030, 2034, 2108, 2109, 2128, 2129, 2133, 2135, 2136, 2138, 2194, 2223, 2226, 2300, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 132, 140, 141, 143, 179, 180, 225, 230, 231, 245, 249, 288, 292, 293, 295, 1760, 1763, 1840, 1874, 1992, 2028, 2032, 2036, 2130, 2131, 2132, 2134, 2137, 2139, 2222, 2225, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 130, 140, 141, 142, 177, 178, 179, 180, 181, 223, 225, 227, 229, 231, 236, 244, 245, 248, 249, 250, 281, 282, 283, 287, 288, 290, 292, 293, 295, 296, 1716, 1717, 1718, 1760, 1838, 1839, 1840, 1864, 1865, 1866, 1867, 1874, 1876, 1991, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2132, 2134, 2135, 2136, 2137, 2139, 2222, 2223, 2225, 2300, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 131, 132, 143, 176, 182, 221, 230, 233, 234, 235, 243, 246, 284, 285, 286, 289, 291, 294, 1761, 1762, 1763, 1852, 1863, 1875, 1990, 1992, 2131, 2133, 2138, 2194, 2226, 2303, 2313)</t>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 132, 140, 141, 142, 175, 176, 177, 178, 179, 180, 181, 182, 223, 227, 230, 231, 233, 235, 236, 244, 246, 248, 249, 271, 272, 274, 281, 282, 284, 287, 291, 292, 295, 296, 1717, 1718, 1760, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1852, 1863, 1867, 1874, 1875, 1991, 2026, 2034, 2109, 2129, 2130, 2131, 2132, 2134, 2136, 2137, 2139, 2194, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(131, 143, 221, 225, 229, 234, 243, 245, 247, 250, 273, 283, 285, 286, 288, 289, 290, 293, 294, 1716, 1762, 1840, 1864, 1865, 1866, 1876, 1935, 1990, 1992, 2028, 2030, 2032, 2036, 2108, 2128, 2133, 2135, 2138, 2222, 2223)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 72, 130, 143, 175, 176, 177, 178, 179, 180, 181, 223, 225, 227, 229, 231, 234, 235, 243, 244, 246, 248, 250, 271, 272, 273, 274, 281, 283, 284, 285, 286, 289, 290, 291, 292, 293, 296, 1716, 1717, 1761, 1762, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1874, 1875, 1876, 1935, 1992, 2026, 2028, 2030, 2036, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2138, 2139, 2194, 2225, 2226, 2257, 2300, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 70, 73, 131, 132, 140, 141, 142, 182, 221, 230, 233, 236, 245, 247, 249, 282, 287, 288, 294, 295, 1718, 1760, 1763, 1764, 1765, 1867, 1990, 1991, 2032, 2034, 2108, 2109, 2136, 2137, 2222, 2223, 2301, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 72, 131, 140, 141, 142, 175, 177, 178, 179, 181, 182, 221, 223, 229, 233, 234, 235, 236, 243, 244, 246, 247, 248, 250, 271, 272, 273, 274, 281, 282, 283, 284, 288, 289, 291, 293, 294, 296, 1717, 1718, 1760, 1761, 1764, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1875, 1876, 1935, 1991, 2026, 2028, 2032, 2034, 2036, 2108, 2109, 2129, 2130, 2132, 2133, 2134, 2138, 2139, 2194, 2223, 2225, 2226, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 71, 73, 130, 132, 143, 176, 180, 225, 227, 230, 231, 245, 249, 285, 286, 287, 290, 292, 295, 1716, 1762, 1763, 1765, 1865, 1867, 1874, 1990, 1992, 2030, 2128, 2131, 2135, 2136, 2137, 2222, 2257, 2300, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 33, 150, 151, 1653, 1654, 1655, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1772, 1773, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2229, 2231, 2279, 2282, 2283, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 32, 34, 35, 148, 149, 152, 1652, 1691, 1692, 1755, 1757, 1774, 1898, 2227, 2281, 2288, 2289, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 34, 148, 150, 151, 1654, 1655, 1691, 1692, 1693, 1751, 1754, 1771, 1772, 1773, 1774, 1825, 1826, 1900, 2054, 2056, 2058, 2177, 2227, 2229, 2231, 2279, 2282, 2283, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(33, 35, 149, 152, 1652, 1653, 1750, 1752, 1753, 1755, 1756, 1757, 1824, 1827, 1897, 1898, 2179, 2281, 2288, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 34, 148, 149, 150, 1653, 1654, 1691, 1750, 1752, 1754, 1755, 1756, 1771, 1772, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2058, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 33, 35, 151, 152, 1652, 1655, 1692, 1693, 1751, 1753, 1757, 1773, 1774, 1898, 2056, 2177, 2179, 2227, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 224, 228, 275, 277, 279, 280, 1720, 1721, 1722, 1775, 1777, 1778, 1779, 1868, 1869, 2027, 2035, 2037, 2120, 2121, 2124, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 226, 276, 278, 1719, 1727, 1776, 1870, 2029, 2033, 2119, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 224, 226, 228, 275, 276, 278, 279, 280, 1719, 1720, 1721, 1775, 1776, 1778, 1868, 2027, 2029, 2033, 2037, 2120, 2125, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 277, 1722, 1727, 1777, 1779, 1869, 1870, 2035, 2119, 2121, 2124, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 275, 278, 280, 1720, 1722, 1776, 1778, 1779, 1868, 1870, 2033, 2035, 2037, 2119, 2120, 2121, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 276, 277, 279, 1719, 1721, 1727, 1775, 1777, 1869, 2027, 2029, 2124, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 207, 208, 210, 211, 214, 215, 217, 218, 219, 266, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 206, 209, 212, 213, 216, 220, 265, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 206, 207, 211, 212, 214, 215, 216, 217, 218, 219, 220, 266, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 208, 209, 210, 213, 265, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 208, 211, 212, 215, 216, 217, 218, 265, 266, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 209, 210, 213, 214, 219, 220, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 70, 72, 73, 130, 131, 132, 140, 142, 143, 176, 177, 178, 179, 180, 181, 182, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 244, 245, 247, 249, 250, 271, 272, 274, 283, 284, 285, 287, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1765, 1766, 1838, 1839, 1852, 1863, 1864, 1867, 1874, 1875, 1876, 1991, 2028, 2034, 2109, 2128, 2129, 2131, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 141, 175, 221, 243, 246, 248, 273, 281, 282, 286, 288, 289, 1760, 1761, 1762, 1763, 1764, 1840, 1865, 1866, 1935, 1990, 1992, 2026, 2030, 2032, 2036, 2108, 2130, 2132, 2225, 2257, 2300, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 70, 72, 130, 141, 143, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 233, 234, 235, 236, 244, 245, 246, 247, 249, 271, 272, 274, 281, 282, 283, 285, 286, 289, 290, 293, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1839, 1863, 1864, 1866, 1867, 1874, 1875, 1935, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2300, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 71, 73, 131, 132, 140, 142, 175, 227, 229, 230, 231, 243, 248, 250, 273, 284, 287, 288, 291, 292, 294, 295, 1718, 1765, 1766, 1838, 1840, 1852, 1865, 1876, 1990, 2108, 2109, 2128, 2129, 2138, 2226, 2257, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 72, 130, 131, 132, 141, 142, 176, 177, 178, 179, 180, 181, 225, 227, 231, 234, 235, 245, 246, 247, 248, 250, 271, 273, 281, 282, 283, 287, 288, 290, 291, 292, 294, 296, 1760, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1865, 1866, 1867, 1874, 1875, 1990, 1991, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2129, 2130, 2131, 2132, 2134, 2135, 2137, 2139, 2194, 2222, 2223, 2225, 2257, 2300, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 140, 143, 175, 182, 221, 223, 229, 230, 233, 236, 243, 244, 249, 272, 274, 284, 285, 286, 289, 293, 295, 1716, 1717, 1718, 1762, 1864, 1876, 1935, 1992, 2026, 2128, 2133, 2136, 2138, 2226, 2301, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 148, 149, 151, 152, 1652, 1654, 1655, 1692, 1693, 1750, 1751, 1752, 1753, 1756, 1757, 1771, 1772, 1824, 1825, 1826, 1897, 1898, 2058, 2179, 2229, 2231, 2281, 2282, 2288, 2289, 2290, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 34, 35, 150, 1653, 1691, 1754, 1755, 1773, 1774, 1827, 1900, 2054, 2056, 2177, 2227, 2279, 2283, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 148, 149, 151, 1652, 1653, 1655, 1691, 1692, 1752, 1753, 1754, 1756, 1771, 1773, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 31, 32, 33, 34, 35, 150, 152, 1654, 1693, 1750, 1751, 1755, 1757, 1772, 1774, 1897, 2281, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 150, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1824, 1825, 1827, 1898, 1900, 2054, 2056, 2058, 2177, 2279, 2283, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(35, 148, 149, 151, 152, 1654, 1693, 1753, 1774, 1826, 1897, 2179, 2227, 2229, 2231, 2281, 2282, 2288, 2289, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 224, 226, 228, 275, 276, 279, 280, 1719, 1721, 1722, 1775, 1778, 1779, 1869, 2027, 2029, 2035, 2037, 2119, 2120, 2124, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 277, 278, 1720, 1727, 1776, 1777, 1868, 1870, 2033, 2121, 2125, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 228, 275, 276, 277, 278, 279, 280, 1719, 1721, 1722, 1776, 1777, 1778, 1870, 2027, 2029, 2033, 2120, 2121, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 226, 1720, 1727, 1775, 1779, 1868, 1869, 2035, 2037, 2119, 2124, 2125, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 222, 224, 226, 275, 277, 279, 1720, 1721, 1722, 1727, 1775, 1776, 1778, 1869, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 228, 276, 278, 280, 1719, 1777, 1779, 1868, 1870, 2124, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 209, 212, 213, 215, 216, 219, 220, 265, 266, 267, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 207, 208, 210, 211, 214, 217, 218, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 206, 208, 209, 212, 213, 215, 217, 218, 265, 266, 267, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 207, 210, 211, 214, 216, 219, 220, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 207, 208, 209, 210, 212, 213, 214, 215, 216, 219, 265, 266, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 205, 206, 211, 217, 218, 220, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 71, 72, 73, 130, 140, 141, 142, 176, 177, 179, 181, 182, 223, 225, 227, 229, 233, 234, 235, 236, 244, 246, 247, 248, 271, 272, 273, 274, 282, 284, 287, 289, 291, 293, 294, 295, 296, 1718, 1760, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2109, 2128, 2129, 2130, 2132, 2133, 2135, 2137, 2138, 2139, 2223, 2225, 2226, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 131, 132, 143, 175, 178, 180, 221, 230, 231, 243, 245, 249, 250, 281, 283, 285, 286, 288, 290, 292, 1716, 1717, 1761, 1865, 1867, 1874, 1875, 1876, 2030, 2108, 2131, 2134, 2136, 2194, 2222, 2257, 2300, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 70, 71, 72, 73, 130, 132, 140, 141, 142, 143, 177, 178, 179, 180, 181, 182, 221, 225, 227, 230, 231, 234, 235, 236, 245, 247, 249, 250, 271, 272, 273, 274, 281, 282, 284, 286, 287, 288, 289, 290, 291, 293, 294, 295, 1716, 1760, 1762, 1763, 1764, 1840, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1992, 2028, 2032, 2036, 2109, 2129, 2130, 2132, 2138, 2139, 2222, 2223, 2225, 2257, 2300, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 131, 175, 176, 223, 229, 233, 243, 244, 246, 248, 283, 285, 292, 296, 1717, 1718, 1761, 1765, 1766, 1838, 1839, 1852, 1863, 1935, 1991, 2026, 2030, 2034, 2108, 2128, 2131, 2133, 2134, 2135, 2136, 2137, 2194, 2226, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 71, 72, 131, 132, 140, 141, 142, 176, 177, 178, 179, 180, 181, 182, 225, 229, 230, 231, 233, 234, 235, 236, 245, 249, 250, 271, 272, 273, 282, 283, 285, 287, 291, 292, 293, 295, 296, 1718, 1760, 1762, 1764, 1765, 1838, 1840, 1863, 1864, 1865, 1867, 1874, 1875, 1876, 1935, 1991, 1992, 2028, 2032, 2034, 2036, 2108, 2109, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2194, 2222, 2223, 2226, 2257, 2300, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 130, 143, 175, 221, 223, 227, 243, 244, 246, 247, 248, 274, 281, 284, 286, 288, 289, 290, 294, 1716, 1717, 1761, 1763, 1766, 1839, 1852, 1866, 1990, 2026, 2030, 2128, 2129, 2134, 2139, 2225, 2302, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 20, 150, 151, 152, 1653, 1655, 1691, 1692, 1751, 1752, 1753, 1754, 1756, 1757, 1824, 1898, 1900, 2054, 2056, 2058, 2227, 2231, 2279, 2282, 2283, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 23, 148, 149, 1652, 1654, 1693, 1750, 1755, 1773, 1897, 2229, 2281, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 150, 151, 152, 1652, 1654, 1655, 1691, 1692, 1750, 1752, 1753, 1754, 1755, 1773, 1824, 1897, 1900, 2054, 2058, 2227, 2229, 2279, 2281, 2282, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 148, 149, 1653, 1693, 1751, 1756, 1757, 1898, 2056, 2231, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 148, 149, 151, 1652, 1655, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1773, 1824, 2054, 2056, 2058, 2229, 2231, 2279, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 150, 152, 1653, 1654, 1691, 1692, 1756, 1757, 1897, 1898, 1900, 2227, 2281)</t>
+    <t xml:space="preserve">c(19, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1655, 1691, 1692, 1752, 1753, 1756, 1757, 1771, 1772, 1774, 1824, 1897, 1898, 1900, 2054, 2056, 2177, 2179, 2227, 2231, 2279, 2281, 2288, 2289, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 1653, 1654, 1693, 1750, 1751, 1754, 1755, 1773, 1825, 1826, 1827, 2058, 2229, 2282, 2283, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 32, 33, 34, 148, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1751, 1752, 1753, 1754, 1755, 1772, 1773, 1824, 1826, 1827, 1897, 1900, 2177, 2179, 2229, 2279, 2281, 2282, 2283, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 31, 35, 149, 1750, 1756, 1757, 1771, 1774, 1825, 1898, 2054, 2056, 2058, 2227, 2231, 2288, 2289, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 148, 149, 150, 151, 1652, 1654, 1655, 1692, 1693, 1751, 1752, 1754, 1755, 1771, 1773, 1774, 1900, 2056, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(35, 152, 1653, 1691, 1750, 1753, 1756, 1757, 1772, 1824, 1825, 1826, 1827, 1897, 1898, 2054, 2058, 2229, 2283, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 43, 222, 228, 1719, 1720, 1721, 1775, 1776, 1778, 1779, 1868, 1870, 2027, 2029, 2033, 2035, 2119, 2120, 2124, 2125, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 224, 226, 1722, 1727, 1777, 1869, 2037, 2121, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 228, 1719, 1720, 1721, 1722, 1776, 1777, 1779, 1868, 1869, 2029, 2033, 2035, 2037, 2119, 2120, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 226, 1727, 1775, 1778, 1870, 2027, 2121, 2124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 224, 226, 228, 1720, 1721, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 2027, 2033, 2035, 2037, 2119, 2120, 2121, 2125, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 222, 1719, 1722, 1727, 1870, 2029, 2124, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 205, 206, 210, 212, 216, 217, 218, 220, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 207, 208, 209, 211, 213, 214, 219)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 208, 213, 216, 217, 218, 266, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 209, 210, 211, 212, 214, 219, 220, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 208, 210, 213, 217, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(207, 209, 211, 212, 214, 216, 218, 219, 220)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 130, 131, 132, 140, 141, 142, 178, 179, 180, 181, 182, 221, 225, 229, 231, 233, 234, 235, 243, 244, 245, 246, 248, 250, 281, 282, 284, 286, 287, 290, 291, 292, 293, 296, 1760, 1761, 1762, 1763, 1838, 1840, 1852, 1863, 1864, 1865, 1867, 1874, 1876, 1991, 2026, 2028, 2032, 2108, 2109, 2128, 2130, 2131, 2133, 2134, 2136, 2138, 2139, 2225, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(143, 176, 177, 223, 227, 230, 236, 249, 283, 285, 288, 289, 294, 295, 1716, 1717, 1718, 1839, 1866, 1875, 1990, 1992, 2030, 2034, 2036, 2129, 2132, 2135, 2137, 2194, 2222, 2223, 2226, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 130, 132, 140, 142, 143, 176, 177, 180, 182, 221, 225, 227, 231, 233, 235, 236, 243, 246, 249, 250, 282, 283, 284, 285, 286, 287, 288, 290, 294, 295, 1717, 1718, 1760, 1761, 1763, 1839, 1840, 1852, 1864, 1865, 1867, 1874, 1875, 1991, 1992, 2030, 2032, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2223, 2226, 2300, 2301, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 131, 141, 178, 179, 181, 223, 229, 230, 234, 244, 245, 248, 281, 289, 291, 292, 293, 296, 1716, 1762, 1838, 1863, 1866, 1876, 1990, 2026, 2028, 2034, 2134, 2222, 2225, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 131, 140, 141, 142, 143, 176, 177, 178, 180, 182, 221, 223, 225, 227, 231, 233, 234, 236, 243, 244, 245, 246, 281, 282, 284, 285, 286, 287, 290, 291, 292, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1865, 1876, 1990, 2032, 2034, 2108, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2139, 2225, 2226, 2300, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 132, 179, 181, 229, 230, 235, 248, 249, 250, 283, 288, 289, 293, 294, 296, 1863, 1864, 1866, 1867, 1874, 1875, 1991, 1992, 2026, 2028, 2030, 2036, 2109, 2138, 2194, 2222, 2223, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 148, 149, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1757, 1773, 1824, 1897, 1898, 1900, 2054, 2056, 2227, 2231, 2282, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 150, 151, 152, 1652, 1753, 1755, 1756, 2058, 2229, 2279, 2281, 2283, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 148, 149, 150, 151, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1753, 1755, 1756, 1757, 1773, 1824, 1897, 2054, 2056, 2227, 2231, 2282)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 152, 1654, 1693, 1754, 1898, 1900, 2058, 2229, 2279, 2281, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 149, 151, 152, 1652, 1654, 1655, 1692, 1693, 1750, 1751, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1900, 2054, 2227, 2231, 2279, 2281, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 148, 150, 1653, 1691, 1752, 1753, 1898, 2056, 2058, 2229, 2282, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 224, 1719, 1722, 1775, 1776, 1777, 1778, 1779, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2121, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 226, 228, 1720, 1721, 1727, 1868, 1869, 2120, 2124, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 224, 226, 228, 1719, 1721, 1775, 1776, 1778, 1868, 2027, 2037, 2119, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 1720, 1722, 1727, 1777, 1779, 1869, 1870, 2029, 2033, 2035, 2120)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 1719, 1721, 1722, 1727, 1778, 1868, 1869, 1870, 2027, 2029, 2035, 2037, 2119, 2121, 2124, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(226, 228, 1720, 1775, 1776, 1777, 1779, 2033, 2120, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 207, 208, 209, 210, 211, 212, 213, 216, 217, 220, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 206, 214, 218, 219, 266, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 211, 212, 216, 218, 219, 220, 266, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 208, 210, 213, 214, 217, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 206, 207, 208, 209, 210, 212, 214, 216, 217, 218, 266, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 211, 213, 219, 220, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 131, 132, 141, 142, 176, 177, 178, 181, 182, 223, 229, 230, 231, 233, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 284, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1838, 1839, 1852, 1863, 1864, 1865, 1867, 1874, 1876, 1991, 1992, 2026, 2032, 2034, 2036, 2108, 2132, 2133, 2134, 2136, 2225, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 130, 140, 143, 179, 180, 221, 225, 227, 234, 235, 283, 285, 296, 1763, 1840, 1866, 1875, 1990, 2028, 2030, 2109, 2128, 2129, 2130, 2131, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 130, 132, 140, 142, 143, 176, 178, 179, 221, 225, 227, 229, 230, 233, 234, 235, 236, 243, 244, 248, 281, 282, 283, 285, 286, 287, 288, 292, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1838, 1840, 1852, 1864, 1865, 1866, 1874, 1875, 1876, 1992, 2028, 2030, 2108, 2128, 2129, 2130, 2132, 2133, 2134, 2137, 2138, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 131, 141, 177, 180, 181, 182, 223, 231, 245, 246, 249, 250, 284, 289, 290, 291, 293, 1763, 1839, 1863, 1867, 1990, 1991, 2026, 2032, 2034, 2036, 2109, 2131, 2135, 2136, 2139, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 130, 131, 140, 142, 177, 178, 179, 180, 181, 182, 221, 223, 234, 235, 236, 244, 248, 249, 250, 284, 285, 286, 287, 288, 290, 291, 293, 294, 296, 1716, 1760, 1761, 1838, 1839, 1840, 1863, 1865, 1866, 1867, 1875, 1990, 1991, 1992, 2028, 2032, 2034, 2036, 2108, 2129, 2131, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 132, 141, 143, 176, 225, 227, 229, 230, 231, 233, 243, 245, 246, 281, 282, 283, 289, 292, 295, 1717, 1718, 1762, 1763, 1852, 1864, 1874, 1876, 2026, 2030, 2109, 2128, 2130, 2132, 2136)</t>
+    <t xml:space="preserve">c(42, 44, 222, 224, 226, 275, 277, 279, 280, 1720, 1722, 1727, 1779, 1868, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 228, 276, 278, 1719, 1721, 1775, 1776, 1777, 1778, 1869, 2120, 2121)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 222, 224, 228, 277, 279, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2029, 2033, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 226, 275, 276, 278, 280, 1719, 1720, 1722, 1868, 2027, 2035, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 224, 277, 279, 280, 1720, 1722, 1727, 1775, 1776, 1777, 1779, 1869, 1870, 2027, 2029, 2035, 2037, 2119, 2120, 2121, 2124, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 226, 228, 275, 276, 278, 1719, 1721, 1778, 1868, 2033, 2125, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 206, 207, 208, 209, 211, 212, 213, 216, 217, 219, 220, 265, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 210, 214, 215, 218, 266, 267, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 205, 206, 208, 209, 210, 211, 214, 215, 216, 217, 218, 265, 266, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 207, 212, 213, 219, 220, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 208, 209, 210, 211, 212, 214, 215, 218, 220, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 213, 216, 217, 219, 265, 266, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 71, 73, 130, 131, 132, 141, 176, 177, 179, 181, 182, 221, 223, 225, 227, 229, 231, 233, 234, 235, 236, 243, 246, 247, 248, 250, 271, 273, 281, 284, 286, 287, 288, 289, 290, 292, 293, 294, 295, 296, 1760, 1761, 1763, 1764, 1765, 1766, 1863, 1865, 1866, 1874, 1875, 1876, 1991, 1992, 2026, 2032, 2034, 2036, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2226, 2257, 2300, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 72, 140, 142, 143, 175, 178, 180, 230, 244, 245, 249, 272, 274, 282, 283, 285, 291, 1716, 1717, 1718, 1762, 1838, 1839, 1840, 1852, 1864, 1867, 1935, 1990, 2028, 2030, 2108, 2131, 2136, 2222, 2223, 2225, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 71, 73, 130, 131, 132, 140, 141, 143, 175, 176, 177, 179, 180, 181, 182, 225, 229, 230, 231, 236, 243, 245, 246, 247, 248, 249, 250, 271, 272, 273, 281, 282, 283, 284, 286, 287, 288, 289, 290, 291, 295, 296, 1718, 1761, 1762, 1763, 1765, 1766, 1838, 1852, 1863, 1864, 1866, 1867, 1874, 1875, 1935, 1990, 2028, 2030, 2032, 2034, 2129, 2131, 2133, 2134, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 72, 142, 178, 221, 223, 227, 233, 234, 235, 244, 274, 285, 292, 293, 294, 1716, 1717, 1760, 1764, 1839, 1840, 1865, 1876, 1991, 1992, 2026, 2036, 2108, 2109, 2128, 2130, 2132, 2135, 2136, 2222, 2257, 2300, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 131, 132, 140, 141, 143, 177, 181, 182, 223, 225, 229, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 273, 274, 281, 283, 284, 286, 287, 288, 290, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1763, 1764, 1765, 1838, 1852, 1864, 1866, 1867, 1874, 1875, 1990, 1992, 2026, 2028, 2032, 2034, 2036, 2109, 2131, 2132, 2133, 2137, 2138, 2139, 2222, 2223, 2225, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 130, 142, 175, 176, 178, 179, 180, 221, 227, 230, 231, 233, 234, 272, 282, 285, 289, 291, 292, 1716, 1762, 1766, 1839, 1840, 1863, 1865, 1876, 1935, 1991, 2030, 2108, 2128, 2129, 2130, 2134, 2135, 2136, 2194, 2226)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 31, 32, 33, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1692, 1693, 1750, 1751, 1753, 1755, 1756, 1771, 1773, 1824, 1825, 1897, 1900, 2054, 2058, 2177, 2179, 2227, 2229, 2279, 2281, 2282, 2288, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 34, 35, 1653, 1691, 1752, 1754, 1757, 1772, 1774, 1826, 1827, 1898, 2056, 2231, 2283, 2289, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 34, 149, 150, 151, 1654, 1655, 1691, 1750, 1751, 1753, 1754, 1755, 1772, 1773, 1824, 1826, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 33, 35, 148, 152, 1652, 1653, 1692, 1693, 1752, 1756, 1757, 1771, 1774, 1825, 1827, 2179, 2229, 2283, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 31, 33, 34, 35, 148, 150, 151, 152, 1654, 1655, 1692, 1693, 1751, 1752, 1753, 1754, 1755, 1757, 1772, 1824, 1825, 1827, 1897, 1898, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 23, 32, 149, 1652, 1653, 1691, 1750, 1756, 1771, 1773, 1774, 1826, 1900, 2054, 2056, 2058, 2281, 2289, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 226, 228, 275, 277, 278, 280, 1719, 1720, 1722, 1776, 1777, 1778, 1870, 2029, 2033, 2035, 2037, 2121, 2124, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(224, 276, 279, 1721, 1727, 1775, 1779, 1868, 1869, 2027, 2119, 2120, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 222, 224, 275, 276, 277, 278, 279, 280, 1719, 1721, 1722, 1727, 1775, 1777, 1778, 1779, 1869, 1870, 2037, 2119, 2120, 2121, 2124, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 226, 228, 1720, 1776, 1868, 2027, 2029, 2033, 2035, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 226, 275, 277, 280, 1719, 1720, 1721, 1775, 1778, 1779, 1868, 1869, 1870, 2029, 2033, 2037, 2119, 2120, 2124, 2125, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(224, 228, 276, 278, 279, 1722, 1727, 1776, 1777, 2027, 2035, 2121, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 207, 210, 211, 212, 213, 214, 215, 217, 218, 219, 220, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 206, 208, 209, 216, 265, 266, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 205, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 219, 220, 266, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 206, 218, 265, 267, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 209, 212, 213, 215, 216, 217, 220, 266, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 208, 210, 211, 214, 218, 219, 265, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 140, 141, 143, 175, 176, 177, 178, 180, 181, 182, 221, 223, 227, 230, 231, 233, 236, 243, 246, 247, 248, 249, 271, 272, 273, 281, 284, 286, 287, 290, 293, 294, 296, 1717, 1718, 1761, 1762, 1763, 1765, 1766, 1839, 1864, 1874, 1876, 1935, 1991, 1992, 2026, 2028, 2030, 2034, 2036, 2108, 2109, 2128, 2130, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2222, 2223, 2225, 2257, 2301, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(132, 142, 179, 225, 229, 234, 235, 244, 245, 250, 274, 282, 283, 285, 288, 289, 291, 292, 295, 1716, 1760, 1764, 1838, 1840, 1852, 1863, 1865, 1866, 1867, 1875, 1990, 2032, 2129, 2136, 2194, 2226, 2300, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 71, 73, 132, 140, 142, 143, 175, 176, 182, 221, 223, 225, 227, 229, 231, 233, 236, 243, 246, 247, 248, 249, 250, 271, 273, 274, 281, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 293, 295, 1716, 1718, 1761, 1762, 1763, 1765, 1766, 1840, 1852, 1864, 1865, 1867, 1875, 1876, 1935, 1990, 2026, 2028, 2030, 2034, 2108, 2109, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2226, 2257, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 72, 130, 131, 141, 177, 178, 179, 180, 181, 230, 234, 235, 244, 245, 272, 285, 294, 296, 1717, 1760, 1764, 1838, 1839, 1863, 1866, 1874, 1991, 1992, 2032, 2036, 2128, 2223, 2225, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 131, 132, 140, 142, 175, 178, 179, 182, 223, 225, 229, 231, 233, 234, 235, 236, 244, 245, 246, 247, 248, 249, 271, 281, 284, 285, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1761, 1763, 1764, 1765, 1766, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 2026, 2028, 2030, 2036, 2128, 2129, 2131, 2133, 2135, 2136, 2137, 2138, 2194, 2223, 2225, 2300, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 141, 143, 176, 177, 180, 181, 221, 227, 230, 243, 250, 272, 273, 274, 282, 283, 286, 287, 1718, 1762, 1838, 1839, 1875, 1992, 2032, 2034, 2108, 2109, 2130, 2132, 2134, 2139, 2222, 2226, 2257, 2301, 2302, 2303, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 149, 150, 151, 1654, 1655, 1692, 1693, 1750, 1752, 1754, 1773, 1824, 1897, 1898, 1900, 2058, 2229, 2231, 2279, 2281, 2282, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(148, 152, 1652, 1653, 1691, 1751, 1753, 1755, 1756, 1757, 2054, 2056, 2227, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 149, 151, 1652, 1653, 1692, 1693, 1751, 1752, 1755, 1757, 1773, 1824, 1897, 1898, 1900, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 148, 150, 152, 1654, 1655, 1691, 1750, 1753, 1754, 1756, 2054, 2282, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 149, 151, 152, 1653, 1654, 1655, 1691, 1692, 1750, 1751, 1752, 1755, 1756, 1773, 1898, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 148, 150, 1652, 1693, 1753, 1754, 1757, 1824, 1897, 1900, 2054, 2283, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1719, 1720, 1722, 1727, 1777, 1779, 1869, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 1721, 1775, 1776, 1778, 1868)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 1719, 1721, 1727, 1775, 1776, 1777, 1868, 1869, 1870, 2027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1720, 1722, 1778, 1779, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 1719, 1720, 1721, 1775, 1776, 1777, 1779, 1868, 1869, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 1722, 1727, 1778, 1870, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 206, 207, 208, 209, 210, 211, 212, 213, 216, 218, 219, 266, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 214, 217, 220, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 207, 210, 212, 214, 216, 217, 219, 220, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 206, 208, 209, 211, 213, 218, 266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 207, 209, 210, 211, 212, 213, 216, 217, 218, 219, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 206, 208, 214, 220, 266, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 142, 143, 229, 230, 231, 234, 235, 236, 282, 286, 287, 288, 290, 292, 293, 294, 295, 1716, 1717, 1718, 1838, 1840, 1852, 1863, 1864, 1990, 1991, 1992, 2026, 2108, 2109, 2137, 2138, 2139, 2194, 2225, 2226, 2300, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 132, 140, 141, 177, 233, 281, 283, 284, 285, 289, 291, 296, 1839, 1865, 2030, 2222, 2223, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 131, 132, 141, 142, 229, 230, 233, 236, 282, 283, 285, 286, 288, 289, 291, 292, 293, 295, 296, 1716, 1717, 1718, 1838, 1840, 1863, 1864, 1865, 1991, 1992, 2030, 2109, 2137, 2139, 2223, 2225, 2226, 2300, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(140, 143, 177, 231, 234, 235, 281, 284, 287, 290, 294, 1839, 1852, 1990, 2026, 2108, 2138, 2194, 2222, 2301, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 140, 141, 142, 143, 177, 231, 234, 283, 284, 286, 287, 288, 290, 291, 292, 294, 295, 296, 1716, 1717, 1718, 1838, 1839, 1852, 1863, 1864, 1865, 1990, 2026, 2108, 2109, 2138, 2139, 2194, 2223, 2225, 2226, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 132, 229, 230, 233, 235, 236, 281, 282, 285, 289, 293, 1840, 1991, 1992, 2030, 2137, 2222, 2300, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 149, 150, 151, 152, 1653, 1655, 1691, 1750, 1751, 1753, 1755, 1756, 1757, 1824, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2281, 2283, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 148, 1652, 1654, 1692, 1693, 1752, 1754, 1773, 2231, 2279, 2282, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 148, 150, 151, 152, 1652, 1653, 1654, 1655, 1692, 1750, 1751, 1752, 1753, 1755, 1756, 1897, 1900, 2058, 2229, 2231, 2281, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 149, 1691, 1693, 1754, 1757, 1773, 1824, 1898, 2054, 2056, 2227, 2279)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 149, 150, 151, 152, 1652, 1653, 1655, 1691, 1692, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1898, 2054, 2227, 2229, 2231, 2279, 2281, 2282)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 148, 1654, 1693, 1750, 1751, 1752, 1900, 2056, 2058, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 1719, 1721, 1776, 1777, 1778, 1869, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 1720, 1722, 1727, 1775, 1779, 1868)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 1720, 1727, 1775, 1776, 1777, 1779, 1868, 1870, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1719, 1721, 1722, 1778, 1869, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1868, 2027, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1777, 1778, 1779, 1869, 1870, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 207, 209, 213, 216, 218, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 206, 208, 210, 211, 212, 214, 217)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 210, 211, 214, 217, 218, 219, 220, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(208, 209, 212, 213, 216, 266, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 205, 209, 210, 211, 213, 216, 218, 220, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 206, 207, 208, 212, 214, 217, 219, 266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 140, 142, 143, 230, 231, 234, 235, 281, 285, 286, 287, 288, 289, 290, 291, 293, 294, 296, 1716, 1717, 1718, 1838, 1839, 1840, 1991, 2030, 2108, 2109, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 132, 141, 177, 229, 233, 236, 282, 283, 284, 292, 295, 1852, 1863, 1864, 1865, 1990, 1992, 2026, 2137, 2138)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 140, 143, 177, 229, 233, 234, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 293, 294, 1716, 1717, 1718, 1838, 1840, 1852, 1864, 1865, 1990, 1991, 1992, 2108, 2109, 2137, 2138, 2194, 2222, 2223, 2300, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 132, 141, 142, 230, 231, 235, 236, 281, 285, 295, 296, 1839, 1863, 2026, 2030, 2139, 2225, 2226, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 132, 140, 142, 143, 177, 229, 230, 233, 284, 285, 288, 289, 290, 291, 292, 293, 295, 296, 1716, 1717, 1838, 1839, 1840, 1863, 1864, 1991, 1992, 2026, 2030, 2109, 2138, 2139, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 141, 231, 234, 235, 236, 281, 282, 283, 286, 287, 294, 1718, 1852, 1865, 1990, 2108, 2137, 2194, 2222, 2313)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 34, 35, 149, 151, 152, 1652, 1653, 1693, 1750, 1751, 1752, 1753, 1756, 1757, 1774, 1824, 1825, 1827, 1897, 1898, 2054, 2058, 2177, 2179, 2227, 2229, 2281, 2283, 2288, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 148, 150, 1654, 1655, 1691, 1692, 1754, 1755, 1771, 1772, 1773, 1826, 1900, 2056, 2231, 2279, 2282, 2289, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 34, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1691, 1692, 1752, 1757, 1771, 1773, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2177, 2179, 2227, 2229, 2281, 2282, 2283, 2289, 2290, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 33, 35, 1653, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 1772, 1774, 1824, 2058, 2231, 2279, 2288, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 32, 34, 35, 148, 149, 151, 152, 1652, 1653, 1655, 1691, 1693, 1750, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1898, 2054, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 31, 33, 150, 1654, 1692, 1751, 1752, 1772, 1825, 1826, 1827, 1897, 1900, 2056, 2282, 2283)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 1720, 1722, 1775, 1776, 1779, 1869, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 1719, 1721, 1727, 1777, 1778, 1868)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 1719, 1721, 1722, 1727, 1775, 1777, 1779, 1868, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 1720, 1776, 1778, 1869)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 1719, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 2027, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 1720, 1721, 1868, 1869, 1870, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 210, 212, 213, 214, 216, 217, 218, 220, 266, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 211, 215, 219, 265, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 208, 209, 210, 212, 213, 214, 215, 217, 220, 266, 267, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 206, 207, 211, 216, 218, 219, 265, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 209, 210, 211, 213, 217, 218, 219, 220, 265, 266, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 208, 212, 214, 215, 216, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 131, 132, 140, 141, 177, 230, 231, 233, 234, 235, 281, 283, 284, 285, 286, 290, 291, 293, 294, 295, 296, 1716, 1717, 1718, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1992, 2026, 2030, 2108, 2137, 2138, 2139, 2194, 2223, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 130, 142, 143, 229, 236, 282, 287, 288, 289, 292, 1764, 1865, 1935, 1990, 1991, 2109, 2222, 2225, 2226, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 141, 143, 177, 229, 230, 231, 233, 234, 235, 236, 282, 283, 284, 286, 288, 291, 292, 295, 296, 1716, 1717, 1718, 1765, 1838, 1840, 1863, 1935, 1990, 1992, 2109, 2137, 2138, 2139, 2222, 2223, 2225, 2226, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(132, 140, 142, 281, 285, 287, 289, 290, 293, 294, 1764, 1766, 1839, 1852, 1864, 1865, 1991, 2026, 2030, 2108, 2194, 2300, 2301, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 131, 132, 140, 142, 229, 231, 233, 234, 236, 281, 283, 285, 286, 288, 289, 291, 292, 295, 296, 1716, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1865, 1990, 1991, 2026, 2030, 2108, 2109, 2137, 2139, 2194, 2222, 2225, 2226, 2300, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 130, 141, 143, 177, 230, 235, 282, 284, 287, 290, 293, 294, 1717, 1718, 1852, 1864, 1935, 1992, 2138, 2223, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 149, 150, 152, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1772, 1773, 1774, 1825, 1827, 1897, 2054, 2056, 2177, 2179, 2227, 2229, 2231, 2283, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 34, 35, 148, 151, 1654, 1693, 1757, 1824, 1826, 1898, 1900, 2058, 2279, 2281, 2282, 2288, 2289, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 34, 148, 149, 150, 152, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 1757, 1773, 1774, 1824, 1827, 1897, 2056, 2058, 2177, 2179, 2227, 2229, 2281, 2282, 2283, 2288, 2289, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 32, 33, 35, 151, 1652, 1751, 1755, 1771, 1772, 1825, 1826, 1898, 1900, 2054, 2231, 2279, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 150, 152, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1774, 1824, 1827, 1898, 1900, 2054, 2058, 2179, 2227, 2231, 2279, 2281, 2282, 2288, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 33, 34, 35, 148, 149, 151, 1654, 1693, 1773, 1825, 1826, 1897, 2056, 2177, 2229, 2283, 2289, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 1720, 1721, 1722, 1727, 1776, 1868, 1869, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 1719, 1775, 1777, 1778, 1779)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 1721, 1722, 1727, 1776, 1777, 1778, 1779, 1870, 2027, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 1719, 1720, 1775, 1868, 1869, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 1719, 1721, 1727, 1775, 1776, 1777, 1779, 1868, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 1720, 1722, 1778, 1869, 1870)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 205, 206, 207, 208, 210, 211, 214, 216, 217, 218, 219, 265, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 209, 212, 213, 215, 220, 266, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 208, 209, 210, 213, 214, 215, 216, 218, 219, 265, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 207, 211, 212, 217, 220, 266, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 209, 210, 212, 213, 214, 215, 216, 220, 265, 266, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 207, 208, 211, 217, 218, 219, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 130, 132, 140, 141, 142, 177, 230, 231, 233, 234, 286, 288, 289, 290, 291, 292, 293, 294, 295, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1852, 1863, 1864, 1935, 1990, 1991, 2026, 2030, 2108, 2109, 2138, 2139, 2194, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 131, 143, 229, 235, 236, 281, 282, 283, 284, 285, 287, 296, 1840, 1865, 1992, 2137, 2222, 2223, 2225, 2226, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 130, 131, 132, 142, 177, 229, 230, 236, 281, 283, 284, 286, 287, 288, 289, 290, 292, 293, 295, 296, 1717, 1718, 1766, 1838, 1839, 1840, 1852, 1863, 1865, 1935, 1990, 1992, 2026, 2030, 2108, 2138, 2194, 2225, 2226, 2300, 2301, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 140, 141, 143, 231, 233, 234, 235, 282, 285, 291, 294, 1716, 1764, 1765, 1864, 1991, 2109, 2137, 2139, 2222, 2223, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 131, 132, 140, 141, 142, 177, 229, 233, 234, 236, 281, 282, 283, 284, 285, 286, 287, 290, 291, 292, 295, 296, 1716, 1717, 1765, 1838, 1839, 1840, 1865, 1935, 1991, 1992, 2030, 2108, 2109, 2138, 2139, 2223, 2225, 2226, 2300, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 130, 143, 230, 231, 235, 288, 289, 293, 294, 1718, 1764, 1766, 1852, 1863, 1864, 1990, 2026, 2137, 2194, 2222, 2301, 2312)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 20, 23, 149, 152, 1652, 1653, 1655, 1691, 1692, 1693, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 1898, 1900, 2058, 2227, 2229, 2279, 2281, 2282)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 148, 150, 151, 1654, 1750, 1897, 2054, 2056, 2231, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 23, 148, 149, 150, 151, 152, 1652, 1654, 1691, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1897, 2054, 2056, 2058, 2279, 2281, 2282, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 1653, 1655, 1692, 1753, 1773, 1824, 1898, 1900, 2227, 2229, 2231, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 149, 152, 1652, 1654, 1655, 1692, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 2058, 2227, 2229, 2231, 2279, 2281, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 148, 150, 151, 1653, 1691, 1753, 1898, 1900, 2054, 2056, 2282, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 1720, 1722, 1775, 1776, 1778, 1779, 1868, 1870, 2027, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1719, 1721, 1727, 1777, 1869, 2119, 2120, 2121, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 224, 228, 1719, 1720, 1721, 1722, 1775, 1776, 1777, 1779, 1869, 1870, 2119, 2120, 2124, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 226, 1727, 1778, 1868, 2027, 2121, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 226, 228, 1720, 1721, 1776, 1777, 1778, 1868, 1869, 1870, 2027, 2120, 2121, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 1719, 1722, 1727, 1775, 1779, 2119, 2124, 2125, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 207, 208, 211, 212, 216, 217, 218, 220, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 206, 209, 210, 213, 214, 219, 266, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 205, 206, 208, 209, 211, 212, 213, 214, 216, 217, 220, 267, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 207, 210, 218, 219, 266, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 206, 209, 210, 211, 212, 213, 214, 217, 220, 266, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 205, 207, 208, 216, 218, 219, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 141, 142, 143, 221, 223, 225, 227, 230, 234, 236, 243, 244, 246, 250, 281, 282, 283, 286, 289, 290, 291, 292, 293, 296, 1716, 1718, 1760, 1761, 1763, 1838, 1840, 1852, 1865, 1867, 1990, 1991, 2026, 2030, 2108, 2128, 2129, 2130, 2131, 2132, 2133, 2137, 2138, 2139, 2194, 2222, 2226, 2300, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 140, 177, 180, 229, 231, 233, 235, 245, 248, 249, 284, 285, 287, 288, 294, 295, 1717, 1762, 1839, 1863, 1864, 1866, 1992, 2109, 2134, 2135, 2136, 2223, 2225, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 132, 140, 141, 142, 143, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 130, 131, 141, 143, 223, 229, 230, 231, 233, 235, 244, 245, 246, 249, 282, 283, 285, 287, 288, 289, 293, 294, 295, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1863, 1864, 1865, 1990, 2030, 2108, 2128, 2129, 2130, 2132, 2133, 2134, 2135, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 132, 140, 142, 177, 180, 221, 225, 227, 234, 236, 243, 248, 250, 281, 284, 286, 290, 291, 292, 1718, 1852, 1866, 1867, 1991, 1992, 2026, 2109, 2131, 2138, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 233, 236, 243, 244, 246, 248, 249, 250, 281, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 1760, 1762, 1838, 1840, 1852, 1866, 1867, 1990, 2026, 2030, 2129, 2131, 2132, 2133, 2135, 2137, 2139, 2223, 2225, 2226, 2300, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 180, 230, 231, 234, 235, 245, 285, 296, 1716, 1717, 1718, 1761, 1763, 1839, 1863, 1864, 1865, 1991, 1992, 2108, 2109, 2128, 2130, 2134, 2136, 2138, 2194, 2222, 2301, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 150, 1652, 1653, 1655, 1691, 1692, 1693, 1751, 1752, 1754, 1756, 1757, 1824, 1897, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2281, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 148, 149, 151, 152, 1654, 1750, 1753, 1755, 1773, 1898, 2279, 2282)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1755, 1756, 1757, 1898, 1900, 2054, 2229, 2231, 2281, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(152, 1693, 1751, 1752, 1753, 1754, 1773, 1824, 1897, 2056, 2058, 2227, 2279, 2282)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 23, 150, 151, 1653, 1654, 1655, 1692, 1693, 1750, 1754, 1755, 1756, 1757, 1824, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2231, 2279, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 148, 149, 152, 1652, 1691, 1751, 1752, 1753, 1773, 2229, 2281, 2282)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1776, 1777, 1868, 2027, 2119, 2121, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 1727, 1775, 1778, 1779, 1869, 1870, 2120, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1727, 1776, 1777, 1779, 1868, 1869, 2027, 2119, 2121, 2124, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1720, 1721, 1722, 1775, 1778, 1870, 2120, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 228, 1719, 1720, 1721, 1775, 1778, 1779, 1869, 1870, 2027, 2120, 2121, 2124, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(226, 1722, 1727, 1776, 1777, 1868, 2119, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 208, 209, 210, 216, 217, 218, 219, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 211, 212, 213, 214, 220, 266, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 208, 209, 211, 214, 217, 219, 266, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 210, 212, 213, 216, 218, 220, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 207, 208, 209, 210, 217, 218, 219, 220, 266, 267, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 206, 211, 212, 213, 214, 216, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 131, 132, 140, 221, 223, 227, 230, 231, 233, 235, 236, 243, 245, 282, 283, 284, 285, 286, 287, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1838, 1852, 1865, 1866, 1867, 1990, 1991, 2109, 2128, 2129, 2130, 2131, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 130, 141, 142, 143, 177, 180, 225, 229, 234, 244, 246, 248, 249, 250, 281, 288, 289, 1718, 1839, 1840, 1863, 1864, 1992, 2026, 2030, 2108, 2132, 2134, 2222, 2223)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 130, 131, 140, 143, 177, 223, 227, 229, 231, 233, 235, 236, 243, 245, 246, 248, 249, 281, 283, 285, 286, 289, 290, 292, 295, 1716, 1718, 1760, 1761, 1762, 1763, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 2026, 2108, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2136, 2138, 2139, 2194, 2226, 2301, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 132, 141, 142, 180, 221, 225, 230, 234, 244, 250, 282, 284, 287, 288, 291, 293, 294, 296, 1717, 1838, 1992, 2030, 2131, 2135, 2137, 2222, 2223, 2225, 2300, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 132, 143, 180, 221, 223, 229, 230, 233, 234, 235, 236, 243, 245, 246, 248, 249, 281, 282, 283, 284, 286, 288, 289, 290, 292, 293, 295, 1717, 1718, 1760, 1840, 1863, 1864, 1865, 1866, 1867, 1991, 1992, 2026, 2030, 2109, 2128, 2129, 2130, 2131, 2133, 2134, 2136, 2137, 2222, 2223, 2225, 2300, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(140, 141, 142, 177, 225, 227, 231, 244, 250, 285, 287, 291, 294, 296, 1716, 1761, 1762, 1763, 1838, 1839, 1852, 1990, 2108, 2132, 2135, 2138, 2139, 2194, 2226, 2301, 2313)</t>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 35, 148, 149, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1755, 1757, 1771, 1772, 1826, 1827, 1898, 2056, 2179, 2227, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 34, 150, 151, 152, 1653, 1753, 1754, 1756, 1773, 1774, 1824, 1825, 1897, 1900, 2054, 2058, 2177, 2229, 2281)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 31, 32, 33, 35, 148, 149, 150, 151, 1653, 1655, 1691, 1692, 1693, 1750, 1752, 1754, 1772, 1773, 1774, 1824, 1827, 1897, 1900, 2054, 2056, 2058, 2179, 2227, 2231, 2281, 2282, 2283, 2288, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 34, 152, 1652, 1654, 1751, 1753, 1755, 1756, 1757, 1771, 1825, 1826, 1898, 2177, 2229, 2279, 2289, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 31, 32, 33, 35, 148, 150, 151, 152, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1826, 1827, 1897, 1900, 2054, 2056, 2058, 2227, 2231, 2279, 2289, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 34, 149, 1652, 1653, 1654, 1655, 1692, 1772, 1825, 1898, 2177, 2179, 2229, 2281, 2282, 2283, 2288, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 226, 276, 277, 278, 1720, 1727, 1776, 1777, 1778, 1779, 1868, 1869, 2027, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 222, 224, 228, 275, 279, 280, 1719, 1721, 1722, 1775, 1870, 2119)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 224, 275, 277, 280, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1779, 1868, 1869, 1870, 2027, 2119, 2124, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 226, 228, 276, 278, 279, 1719, 1778, 2120, 2121, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 222, 224, 226, 276, 277, 279, 280, 1719, 1721, 1722, 1775, 1776, 1778, 1779, 1870, 2027, 2119, 2120, 2121, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 228, 275, 278, 1720, 1727, 1777, 1868, 1869, 2124, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 208, 209, 210, 212, 213, 214, 215, 216, 217, 218, 265, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 206, 207, 211, 219, 220, 266, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 211, 213, 217, 219, 220, 265, 266, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 208, 212, 214, 215, 216, 218, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 207, 208, 209, 210, 213, 214, 215, 217, 218, 219, 265, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 206, 211, 212, 216, 220, 266, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 71, 72, 73, 130, 131, 132, 140, 143, 175, 180, 223, 225, 227, 229, 230, 235, 236, 244, 245, 246, 248, 250, 271, 272, 273, 274, 281, 283, 284, 285, 286, 287, 288, 290, 292, 296, 1717, 1718, 1760, 1761, 1763, 1764, 1766, 1838, 1852, 1863, 1864, 1866, 1867, 1935, 1991, 2108, 2128, 2129, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2194, 2225, 2226, 2257, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 141, 142, 177, 221, 231, 233, 234, 243, 247, 249, 282, 289, 291, 293, 294, 295, 1716, 1762, 1765, 1839, 1840, 1865, 1990, 1992, 2026, 2030, 2109, 2134, 2138, 2139, 2222, 2223, 2300, 2301, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
+2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 72, 130, 140, 141, 143, 177, 180, 223, 227, 229, 231, 233, 234, 235, 243, 244, 247, 248, 249, 271, 272, 273, 281, 283, 284, 285, 286, 287, 290, 291, 292, 294, 295, 296, 1716, 1717, 1760, 1762, 1764, 1765, 1839, 1840, 1863, 1866, 1935, 1991, 1992, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2133, 2134, 2136, 2138, 2139, 2194, 2222, 2223, 2226, 2300, 2301, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 73, 131, 132, 142, 175, 221, 225, 230, 236, 245, 246, 250, 274, 282, 288, 289, 293, 1718, 1761, 1763, 1766, 1838, 1852, 1864, 1865, 1867, 1990, 2026, 2132, 2135, 2137, 2225, 2257, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 72, 132, 141, 142, 143, 175, 177, 180, 227, 229, 231, 233, 234, 235, 236, 243, 246, 247, 248, 249, 250, 271, 272, 273, 281, 284, 286, 289, 290, 292, 293, 294, 1716, 1718, 1760, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1990, 1991, 1992, 2026, 2108, 2109, 2128, 2130, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2226, 2257, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 130, 131, 140, 221, 223, 225, 230, 244, 245, 274, 282, 283, 285, 287, 288, 291, 295, 296, 1717, 1761, 1762, 1865, 1866, 1867, 1935, 2030, 2129, 2131, 2223, 2225, 2300, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 23, 33, 34, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1691, 1693, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1826, 1827, 1897, 1898, 2054, 2056, 2058, 2231, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 31, 32, 35, 1655, 1692, 1750, 1824, 1825, 1900, 2177, 2179, 2227, 2229, 2279, 2281, 2283, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 148, 149, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1752, 1753, 1755, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 2058, 2177, 2179, 2229, 2279, 2283, 2288, 2289, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 32, 34, 35, 150, 151, 1750, 1751, 1754, 1756, 1757, 1900, 2054, 2056, 2227, 2231, 2281, 2282, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 149, 151, 152, 1652, 1655, 1692, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1772, 1773, 1774, 1824, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2279, 2281, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 35, 148, 150, 1653, 1654, 1691, 1753, 1771, 1825, 2177, 2179, 2229, 2231, 2282, 2283, 2288, 2289, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 222, 226, 228, 275, 279, 1721, 1722, 1727, 1776, 1777, 1778, 1779, 1868, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 224, 276, 277, 278, 280, 1719, 1720, 1775, 1869, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 224, 226, 228, 278, 280, 1719, 1720, 1721, 1722, 1775, 1776, 1778, 1779, 1869, 2027, 2119, 2120, 2121, 2125, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 275, 276, 277, 279, 1727, 1777, 1868, 1870, 2124, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 224, 228, 277, 278, 279, 280, 1719, 1721, 1722, 1727, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 226, 275, 276, 1720, 1777, 2120, 2121, 2124, 2125, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 206, 209, 210, 213, 214, 216, 218, 219, 220, 265, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 207, 208, 211, 212, 215, 217, 266, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 209, 210, 211, 213, 214, 215, 216, 219, 267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(208, 212, 217, 218, 220, 265, 266, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 205, 207, 208, 210, 211, 212, 214, 215, 217, 219, 220, 265, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 204, 206, 209, 213, 216, 218, 266, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 73, 130, 131, 141, 143, 177, 221, 223, 229, 230, 231, 235, 236, 243, 244, 246, 247, 248, 249, 250, 273, 283, 285, 286, 287, 288, 290, 291, 292, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2030, 2108, 2128, 2130, 2132, 2133, 2137, 2138, 2194, 2223, 2226, 2300, 2301, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 132, 140, 142, 175, 180, 225, 227, 233, 234, 245, 271, 272, 274, 281, 282, 284, 289, 293, 1765, 1766, 1840, 1935, 2026, 2109, 2129, 2131, 2134, 2135, 2136, 2139, 2222, 2225, 2257, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 71, 73, 141, 142, 143, 221, 225, 229, 230, 233, 235, 236, 243, 247, 249, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 295, 296, 1716, 1717, 1718, 1761, 1762, 1764, 1766, 1838, 1839, 1840, 1863, 1864, 1865, 1867, 1935, 1991, 1992, 2026, 2030, 2108, 2109, 2130, 2131, 2132, 2133, 2136, 2139, 2222, 2223, 2226, 2257, 2301, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 72, 130, 131, 132, 140, 175, 177, 180, 223, 227, 231, 234, 244, 245, 246, 248, 250, 294, 1760, 1763, 1765, 1852, 1866, 1990, 2128, 2129, 2134, 2135, 2137, 2138, 2194, 2225, 2300, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 140, 143, 175, 177, 180, 221, 223, 225, 227, 230, 233, 234, 235, 246, 247, 248, 249, 250, 271, 274, 281, 283, 284, 285, 286, 287, 288, 290, 291, 293, 295, 1760, 1761, 1762, 1763, 1764, 1838, 1839, 1840, 1852, 1865, 1990, 2026, 2030, 2109, 2130, 2131, 2133, 2134, 2136, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2257, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(132, 141, 142, 229, 231, 236, 243, 244, 245, 272, 273, 282, 289, 292, 294, 296, 1716, 1717, 1718, 1765, 1766, 1863, 1864, 1866, 1867, 1935, 1991, 1992, 2108, 2128, 2129, 2132, 2135, 2222, 2302, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(19, 20, 149, 150, 151, 152, 1691, 1692, 1693, 1752, 1753, 1754, 1755, 1897, 1900, 2054, 2056, 2058, 2227, 2231, 2279, 2281, 2282, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 23, 148, 1750, 1751, 1756, 1757, 1898, 2229, 2283, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 149, 150, 151, 1691, 1692, 1693, 1751, 1755, 1756, 1757, 1897, 1898, 1900, 2056, 2058, 2231, 2279, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 148, 152, 1750, 1752, 1753, 1754, 2054, 2227, 2229, 2281)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 149, 150, 1692, 1693, 1750, 1752, 1753, 1754, 1757, 1900, 2056, 2058, 2227, 2231, 2281, 2282, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(148, 151, 152, 1691, 1751, 1755, 1756, 1897, 1898, 2054, 2229, 2279)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 1720, 1721, 1722, 1778, 1868, 1869, 1870, 2027, 2119, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(228, 1719, 1727, 1775, 1776, 1777, 1779, 2120, 2121, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1775, 1777, 1778, 1779, 1868, 1869, 2027, 2119, 2120, 2121, 2124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1722, 1727, 1776, 1870, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 224, 226, 228, 1722, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2027, 2119, 2120, 2121, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 1719, 1720, 1721, 1727, 1868, 2124, 2126, 2224)</t>
+    <t xml:space="preserve">c(19, 20, 23, 34, 148, 149, 152, 1691, 1692, 1752, 1753, 1754, 1755, 1756, 1757, 1898, 1900, 2056, 2058, 2227, 2229, 2279, 2281, 2283, 2288, 2289, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 31, 32, 33, 35, 150, 151, 1693, 1750, 1751, 1897, 2054, 2231, 2282, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 34, 152, 1691, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1900, 2056, 2058, 2227, 2229, 2279, 2281, 2282, 2288, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 35, 148, 149, 150, 151, 1692, 1693, 1750, 1897, 1898, 2054, 2231, 2283, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 33, 34, 149, 150, 151, 152, 1693, 1753, 1754, 1755, 1756, 1757, 1898, 1900, 2054, 2056, 2058, 2231, 2282, 2288, 2289, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 35, 148, 1691, 1692, 1750, 1751, 1752, 1897, 2227, 2229, 2279, 2281, 2283, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 224, 228, 276, 277, 278, 280, 1719, 1721, 1727, 1775, 1777, 1778, 1868, 1869, 2027, 2119, 2120, 2121, 2125, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 222, 226, 275, 279, 1720, 1722, 1776, 1779, 1870, 2124, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 224, 226, 275, 276, 278, 280, 1719, 1721, 1775, 1776, 1779, 1869, 1870, 2027, 2119, 2121, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 228, 277, 279, 1720, 1722, 1727, 1777, 1778, 1868, 2120, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 1719, 1720, 1727, 1776, 1778, 1779, 1868, 2119, 2120, 2124, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 280, 1721, 1722, 1775, 1777, 1869, 1870, 2027, 2121, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 266, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 266, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 71, 72, 73, 130, 131, 132, 140, 141, 142, 177, 223, 229, 230, 233, 235, 236, 243, 244, 245, 247, 248, 249, 250, 271, 272, 273, 274, 281, 283, 284, 285, 286, 288, 291, 292, 293, 295, 1717, 1760, 1761, 1764, 1838, 1840, 1852, 1863, 1865, 1866, 1935, 1990, 1991, 2026, 2030, 2129, 2131, 2132, 2134, 2136, 2137, 2138, 2194, 2222, 2223, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 143, 221, 225, 227, 231, 234, 246, 282, 287, 289, 290, 294, 296, 1716, 1718, 1762, 1763, 1765, 1766, 1839, 1864, 1867, 1992, 2128, 2130, 2133, 2135, 2139, 2225, 2226, 2257, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
+2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 131, 132, 140, 142, 177, 223, 225, 227, 230, 233, 234, 235, 236, 245, 247, 248, 249, 250, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 292, 294, 295, 296, 1716, 1760, 1761, 1766, 1839, 1840, 1852, 1863, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2222, 2226, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 130, 141, 143, 221, 229, 231, 243, 244, 246, 271, 289, 290, 291, 293, 1717, 1718, 1762, 1763, 1764, 1765, 1838, 1864, 2128, 2129, 2130, 2139, 2194, 2223, 2225, 2257, 2300, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 73, 131, 140, 141, 143, 177, 221, 225, 227, 230, 231, 234, 235, 236, 243, 245, 246, 248, 249, 272, 273, 281, 283, 284, 286, 287, 288, 289, 291, 293, 295, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1765, 1838, 1852, 1863, 1864, 1865, 1867, 1935, 1991, 1992, 2026, 2129, 2130, 2131, 2132, 2134, 2136, 2137, 2138, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 72, 130, 132, 142, 223, 229, 233, 244, 247, 250, 271, 274, 282, 285, 290, 292, 294, 296, 1718, 1766, 1839, 1840, 1866, 1990, 2030, 2128, 2133, 2135, 2139, 2194, 2223, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 35, 148, 150, 151, 1692, 1693, 1751, 1753, 1754, 1755, 1756, 1757, 1898, 2054, 2058, 2227, 2229, 2231, 2279, 2281, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 149, 152, 1691, 1750, 1752, 1897, 1900, 2056, 2282, 2283, 2288, 2289, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 33, 35, 148, 149, 150, 151, 1691, 1692, 1693, 1750, 1751, 1753, 1754, 1755, 1757, 1897, 1898, 2056, 2227, 2229, 2279, 2281, 2282, 2288, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 31, 32, 34, 152, 1752, 1756, 1900, 2054, 2058, 2231, 2283, 2289, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 148, 150, 151, 152, 1692, 1693, 1753, 1754, 1755, 1757, 1897, 1898, 2054, 2056, 2058, 2227, 2231, 2279, 2288, 2289, 2290, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(33, 34, 35, 149, 1691, 1750, 1751, 1752, 1756, 1900, 2229, 2281, 2282, 2283, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 224, 275, 276, 277, 278, 1719, 1722, 1775, 1776, 1779, 1868, 1869, 1870, 2120, 2121, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(222, 226, 228, 279, 280, 1720, 1721, 1727, 1777, 1778, 2027, 2119, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 228, 275, 276, 277, 279, 1721, 1722, 1727, 1775, 1777, 1778, 1779, 1869, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 224, 226, 278, 280, 1719, 1720, 1776, 1868, 1870, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 275, 276, 277, 280, 1719, 1721, 1722, 1775, 1776, 1777, 1778, 1868, 1870, 2027, 2119, 2121, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 278, 279, 1720, 1727, 1779, 1869, 2120, 2124, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 266, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265:268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 73, 130, 132, 140, 141, 177, 223, 225, 227, 229, 230, 233, 234, 235, 236, 243, 246, 249, 250, 271, 273, 283, 284, 285, 287, 288, 289, 291, 292, 293, 296, 1717, 1760, 1761, 1762, 1764, 1766, 1838, 1839, 1840, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 2030, 2128, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2225, 2226, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 131, 142, 143, 221, 231, 244, 245, 247, 248, 272, 274, 281, 282, 286, 290, 294, 295, 1716, 1718, 1763, 1765, 1852, 1863, 1992, 2026, 2129, 2134, 2139, 2194, 2222, 2223, 2257, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 71, 72, 131, 132, 140, 142, 143, 223, 229, 230, 231, 233, 236, 243, 245, 246, 247, 248, 250, 271, 273, 283, 285, 286, 287, 289, 290, 291, 292, 293, 294, 1716, 1717, 1761, 1763, 1764, 1765, 1766, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1992, 2026, 2128, 2129, 2130, 2131, 2132, 2134, 2136, 2137, 2139, 2194, 2222, 2225, 2226, 2257, 2300, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 73, 130, 141, 177, 221, 225, 227, 234, 235, 244, 249, 272, 274, 281, 282, 284, 288, 295, 296, 1718, 1760, 1762, 1838, 1839, 1991, 2030, 2133, 2135, 2138, 2223, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 141, 142, 143, 221, 223, 225, 227, 229, 230, 231, 234, 235, 243, 244, 246, 247, 248, 249, 250, 271, 281, 283, 284, 285, 286, 287, 288, 290, 291, 293, 294, 1716, 1717, 1718, 1760, 1761, 1762, 1764, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1867, 1935, 1990, 1991, 2128, 2129, 2131, 2132, 2135, 2136, 2137, 2138, 2139, 2222, 2257, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 131, 132, 140, 177, 233, 236, 245, 272, 273, 274, 282, 289, 292, 295, 296, 1763, 1838, 1865, 1866, 1992, 2026, 2030, 2130, 2133, 2134, 2194, 2223, 2225, 2226, 2300, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 33, 34, 1691, 1693, 1750, 1751, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1825, 1826, 1827, 2054, 2056, 2058, 2179, 2288, 2289, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 31, 32, 35, 1692, 1752, 1754, 1774, 1824, 2177, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 31, 33, 34, 35, 1691, 1692, 1693, 1750, 1752, 1755, 1756, 1757, 1772, 1824, 1825, 1827, 2056, 2058, 2177, 2179, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 32, 1751, 1753, 1754, 1771, 1773, 1774, 1826, 2054, 2288, 2289, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 31, 32, 1691, 1692, 1752, 1754, 1755, 1756, 1757, 1772, 1773, 1774, 1824, 1825, 1826, 2054, 2056, 2058, 2179, 2288, 2289, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 33, 34, 35, 1693, 1750, 1751, 1753, 1771, 1827, 2177, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">NA</t>
   </si>
   <si>
-    <t xml:space="preserve">c(15, 132, 140, 142, 143, 177, 221, 223, 225, 230, 231, 233, 234, 235, 236, 248, 249, 250, 281, 283, 284, 285, 286, 289, 291, 293, 294, 295, 1761, 1762, 1838, 1840, 1852, 1863, 1864, 1865, 1867, 1990, 1991, 1992, 2026, 2030, 2129, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2139, 2222, 2225, 2226, 2300, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 130, 131, 141, 227, 229, 243, 244, 245, 246, 282, 287, 288, 290, 292, 296, 1716, 1717, 1718, 1760, 1763, 1839, 1866, 2128, 2134, 2138, 2194, 2223, 2301, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 132, 140, 141, 143, 177, 221, 223, 225, 229, 230, 231, 233, 234, 236, 243, 248, 249, 282, 283, 284, 285, 286, 288, 290, 291, 292, 294, 1716, 1717, 1761, 1762, 1763, 1838, 1839, 1840, 1863, 1864, 1867, 1991, 2026, 2030, 2128, 2130, 2132, 2134, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2300, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 131, 142, 227, 235, 244, 245, 246, 250, 281, 287, 289, 293, 295, 296, 1718, 1760, 1852, 1865, 1866, 1990, 1992, 2129, 2131, 2133, 2136, 2225, 2301, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 132, 143, 177, 221, 223, 225, 227, 229, 230, 231, 235, 243, 246, 248, 250, 285, 289, 290, 291, 292, 293, 294, 295, 1717, 1718, 1760, 1763, 1838, 1839, 1852, 1864, 1865, 1867, 1990, 1992, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2223, 2225, 2300, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(140, 141, 142, 233, 234, 236, 244, 245, 249, 281, 282, 283, 284, 286, 287, 288, 296, 1716, 1761, 1762, 1840, 1863, 1866, 1991, 2026, 2134, 2194, 2222, 2226, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 148, 149, 150, 1691, 1692, 1693, 1751, 1752, 1754, 1755, 1897, 1898, 1900, 2054, 2056, 2229, 2231, 2279, 2281, 2283)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 151, 152, 1750, 1753, 1756, 1757, 2058, 2227, 2282, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 148, 149, 151, 152, 1693, 1751, 1752, 1753, 1754, 1756, 1757, 1897, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 150, 1691, 1692, 1750, 1755, 1898, 1900, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 148, 149, 150, 152, 1691, 1692, 1751, 1752, 1754, 1755, 1757, 1897, 1898, 1900, 2054, 2227, 2229, 2231, 2279, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 151, 1693, 1750, 1753, 1756, 2056, 2058, 2281, 2282, 2283, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 222, 226, 1720, 1721, 1727, 1776, 1777, 1778, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 224, 228, 1719, 1722, 1775, 1779, 2124, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 222, 224, 226, 228, 1719, 1721, 1722, 1727, 1775, 1779, 1868, 2027, 2119, 2121, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 1720, 1776, 1777, 1778, 1869, 1870, 2120, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 222, 228, 1719, 1720, 1721, 1727, 1775, 1778, 1779, 1869, 1870, 2120, 2121, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 224, 226, 1722, 1776, 1777, 1868, 2027, 2119, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 130, 140, 141, 142, 143, 177, 223, 225, 227, 229, 230, 231, 234, 235, 236, 243, 244, 249, 250, 284, 286, 288, 289, 290, 292, 293, 294, 295, 1760, 1762, 1763, 1838, 1839, 1852, 1866, 1990, 1991, 1992, 2030, 2128, 2130, 2131, 2132, 2133, 2135, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 132, 221, 233, 245, 246, 248, 281, 282, 283, 285, 287, 291, 296, 1716, 1717, 1718, 1761, 1840, 1863, 1864, 1865, 1867, 2026, 2129, 2134, 2136, 2137, 2138, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 141, 142, 143, 177, 221, 225, 227, 229, 230, 231, 234, 235, 243, 244, 245, 248, 250, 285, 286, 287, 288, 289, 291, 292, 293, 294, 295, 296, 1716, 1718, 1760, 1761, 1763, 1839, 1863, 1865, 1866, 1867, 1990, 1991, 2030, 2128, 2132, 2133, 2134, 2135, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 131, 132, 140, 223, 233, 236, 246, 249, 281, 282, 283, 284, 290, 1717, 1762, 1838, 1840, 1852, 1864, 1992, 2026, 2129, 2130, 2131, 2138, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 140, 142, 143, 177, 225, 227, 229, 231, 233, 235, 236, 243, 245, 248, 249, 250, 282, 283, 289, 291, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1852, 1863, 1864, 1865, 1866, 1990, 1991, 1992, 2026, 2128, 2132, 2134, 2135, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 141, 221, 223, 230, 234, 244, 246, 281, 284, 285, 286, 287, 288, 290, 292, 293, 1763, 1838, 1839, 1840, 1867, 2030, 2129, 2130, 2131, 2133, 2138, 2226, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 1692, 1693, 1751, 1752, 1753, 1757, 1773, 1824, 2054, 2056, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 1691, 1750, 1754, 1755, 1756, 2058, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 2054, 2056, 2058, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1757, 1773, 2056, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 1753, 1755, 1756, 1824, 2054, 2058, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 1691, 1692, 1693, 1750, 1753, 1755, 1756, 1773, 2054, 2058, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 1751, 1752, 1754, 1757, 1824, 2056, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(229, 230, 231, 233, 234, 235)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 180, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 180, 229, 230, 231, 233, 234, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 229, 230, 233, 234, 235)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 231, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 229, 231, 233, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 230, 234)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 1691, 1750, 1752, 1755, 1756, 1757, 1824, 2054, 2058, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 1692, 1693, 1751, 1753, 1754, 1773, 2056)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1755, 1756, 1824, 2054, 2058, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 1753, 1754, 1757, 1773, 2056, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 1691, 1692, 1751, 1754, 1755, 1756, 1773, 1824, 2054, 2056, 2058)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 1693, 1750, 1752, 1753, 1757, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 229, 233, 234, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 230, 231)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 229, 230, 231, 234, 235)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 233, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 180, 229, 230, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(231, 233, 234)</t>
+    <t xml:space="preserve">c(70, 72, 177, 180, 229, 230, 231, 235, 236, 272, 273, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 175, 233, 234, 271, 274, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 175, 177, 180, 229, 234, 235, 271, 272, 273, 274, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 230, 231, 233, 236, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 175, 180, 229, 231, 234, 235, 236, 271, 273, 1764, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 177, 230, 233, 272, 274, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 32, 33, 35, 1692, 1751, 1752, 1753, 1754, 1756, 1757, 1771, 1772, 1773, 1774, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 34, 1691, 1693, 1750, 1755, 1824, 1825, 1826, 2289, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 34, 35, 1693, 1751, 1752, 1754, 1756, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 31, 32, 33, 1691, 1692, 1750, 1753, 1755, 1757, 2056, 2058, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 32, 33, 34, 1692, 1693, 1750, 1751, 1754, 1755, 1756, 1772, 1773, 1774, 1824, 1826, 1827, 2054, 2056, 2058, 2179, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 31, 35, 1691, 1752, 1753, 1757, 1771, 1825, 2177, 2288, 2289, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 175, 180, 229, 231, 233, 235, 236, 271, 272, 273, 274, 1764, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 177, 230, 234, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 175, 180, 230, 231, 234, 235, 271, 272, 273, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 177, 229, 233, 236, 274, 1764, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 175, 177, 180, 229, 233, 236, 271, 273, 274, 1764, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 230, 231, 234, 235, 272, 1765)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1751, 1752, 1753, 1754, 1755, 1757, 1773, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1693, 1750, 1756, 1824, 2054, 2056, 2058, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 1691, 1692, 1693, 1751, 1752, 1753, 1754, 1773, 2054, 2058, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 1750, 1755, 1756, 1757, 1824, 2056)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 1691, 1692, 1693, 1751, 1753, 1773, 1824, 2056, 2058, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 1750, 1752, 1754, 1755, 1756, 1757, 2054)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 229, 230, 231, 233, 234)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 180, 230, 231, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(229, 233, 234)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 230, 231, 233, 234, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 229, 235)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 1693, 1750, 1752, 1755, 1757, 1773, 1824, 2054, 2056, 2058, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 1691, 1692, 1751, 1753, 1754, 1756)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 1691, 1693, 1751, 1752, 1757, 1773, 1824, 2054, 2056, 2058, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 1692, 1750, 1753, 1754, 1755, 1756)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 1692, 1693, 1750, 1754, 1755, 1757, 1773, 1824, 2054, 2056, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 1691, 1751, 1752, 1753, 1756, 2058, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 180, 233, 234, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229:231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 230, 231, 233, 234, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 229, 235)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(229, 230, 233, 234, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 180, 231)</t>
+    <t xml:space="preserve">c(17, 18, 19, 23, 31, 33, 1691, 1693, 1752, 1753, 1754, 1756, 1757, 1771, 1773, 1774, 1825, 1826, 1827, 2054, 2056, 2177, 2179, 2288, 2290, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 32, 34, 35, 1692, 1750, 1751, 1755, 1772, 1824, 2058, 2289, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 31, 32, 35, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 1757, 1772, 1774, 1824, 1825, 1827, 2054, 2058, 2177, 2179, 2288, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 33, 34, 1691, 1751, 1755, 1771, 1773, 1826, 2056, 2289, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 35, 1691, 1693, 1750, 1753, 1755, 1772, 1774, 1824, 1826, 1827, 2054, 2058, 2179, 2288, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 1692, 1751, 1752, 1754, 1756, 1757, 1771, 1773, 1825, 2056, 2177, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 175, 177, 180, 229, 230, 233, 235, 271, 272, 274, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 231, 234, 236, 273, 1764, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 175, 177, 180, 230, 231, 233, 235, 271, 272, 274, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 229, 234, 236, 273, 1764, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 175, 177, 180, 229, 231, 234, 236, 271, 274, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 230, 233, 235, 272, 273, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 32, 33, 34, 35, 1691, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1774, 1825, 2054, 2058, 2177, 2179, 2288, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 31, 1692, 1693, 1750, 1757, 1772, 1773, 1824, 1826, 1827, 2056, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 33, 34, 35, 1691, 1693, 1753, 1754, 1755, 1771, 1773, 1774, 1824, 1825, 1826, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 31, 32, 1692, 1750, 1751, 1752, 1756, 1757, 1772, 1827, 2054, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 31, 34, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2177, 2179, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 32, 33, 35, 1691, 1693, 1753, 1757, 2056, 2058, 2288, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 175, 177, 180, 229, 231, 233, 234, 235, 272, 1764, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 230, 236, 271, 273, 274, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 175, 177, 180, 230, 233, 235, 236, 271, 272, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 229, 231, 234, 273, 274)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 175, 177, 231, 234, 236, 271, 272, 273, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 180, 229, 230, 233, 235, 274, 1766)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 1691, 1692, 1693, 1751, 1753, 1754, 1755, 1756, 2058, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 1750, 1752, 1757, 2054, 2056, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 1691, 1750, 1752, 1753, 1754, 1755, 1757, 2054, 2056, 2058, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 1692, 1693, 1751, 1756, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 1692, 1750, 1751, 1752, 1753, 1754, 1757, 2054, 2056, 2058)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 1691, 1693, 1755, 1756, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 180, 231, 233, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(229, 230, 234)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 229, 231, 233, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 230, 234)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 180, 229, 231, 233, 234)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(230, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1751, 1754, 1755, 1756, 1757, 2054, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1693, 1750, 1752, 1753, 2056, 2058, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 2054, 2058, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 1691, 1751, 1755, 1757, 2056, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 1691, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 2056, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 1692, 1752, 1757, 2054, 2058, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 229, 230, 231, 233, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 234, 235)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(177, 229, 230, 233, 235, 236)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(180, 231, 234)</t>
+    <t xml:space="preserve">c(17, 18, 20, 31, 32, 34, 35, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 2056, 2288, 2289, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 23, 33, 1692, 1757, 2054, 2058, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 32, 33, 1691, 1693, 1751, 1752, 1753, 1754, 1757, 2054, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 31, 34, 35, 1692, 1750, 1755, 1756, 2056, 2058, 2288)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1693, 1750, 1753, 1756, 2054, 2056, 2058, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 1692, 1751, 1752, 1754, 1755, 1757, 2288, 2289, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 177, 180, 231, 233, 234, 271, 273, 274, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(175, 229, 230, 235, 236, 272, 1764, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 175, 180, 229, 230, 231, 271, 272, 273, 274, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 177, 233, 234, 235, 236, 1764, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 175, 177, 230, 231, 233, 234, 236, 272, 274, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 180, 229, 235, 271, 273, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 33, 34, 35, 1750, 1751, 1753, 1754, 1755, 1756, 1757, 2056, 2058, 2289, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 31, 32, 1691, 1692, 1693, 1752, 2054, 2288, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 35, 1692, 1693, 1751, 1754, 1756, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 33, 34, 1691, 1750, 1752, 1753, 1755, 1757, 2054, 2056)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 35, 1691, 1692, 1693, 1753, 1754, 1755, 1756, 2054, 2056, 2288, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 33, 34, 1750, 1751, 1752, 1757, 2058, 2289, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 175, 177, 229, 230, 234, 235, 236, 271, 272, 273, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 180, 231, 233, 274, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 231, 233, 234, 236, 271, 272, 273, 274, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 175, 177, 180, 229, 230, 235, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 175, 177, 180, 229, 230, 235, 273, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 231, 233, 234, 236, 271, 272, 274)</t>
   </si>
 </sst>
 </file>
@@ -1644,13 +1691,13 @@
         <v>22</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O2" t="s">
         <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="s">
         <v>24</v>
@@ -1700,13 +1747,13 @@
         <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="s">
         <v>24</v>
@@ -1756,13 +1803,13 @@
         <v>27</v>
       </c>
       <c r="N4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q4" t="s">
         <v>24</v>
@@ -1812,13 +1859,13 @@
         <v>31</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O5" t="s">
         <v>32</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="s">
         <v>33</v>
@@ -1868,13 +1915,13 @@
         <v>34</v>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O6" t="s">
         <v>35</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="s">
         <v>33</v>
@@ -1924,13 +1971,13 @@
         <v>36</v>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O7" t="s">
         <v>37</v>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="s">
         <v>33</v>
@@ -1980,7 +2027,7 @@
         <v>39</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
         <v>40</v>
@@ -2036,7 +2083,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
         <v>43</v>
@@ -2092,7 +2139,7 @@
         <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
         <v>45</v>
@@ -2148,13 +2195,13 @@
         <v>47</v>
       </c>
       <c r="N11" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O11" t="s">
         <v>48</v>
       </c>
       <c r="P11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q11" t="s">
         <v>49</v>
@@ -2204,13 +2251,13 @@
         <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O12" t="s">
         <v>51</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q12" t="s">
         <v>49</v>
@@ -2260,13 +2307,13 @@
         <v>52</v>
       </c>
       <c r="N13" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O13" t="s">
         <v>53</v>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q13" t="s">
         <v>49</v>
@@ -2316,13 +2363,13 @@
         <v>55</v>
       </c>
       <c r="N14" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O14" t="s">
         <v>56</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q14" t="s">
         <v>24</v>
@@ -2372,13 +2419,13 @@
         <v>57</v>
       </c>
       <c r="N15" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O15" t="s">
         <v>58</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q15" t="s">
         <v>24</v>
@@ -2428,13 +2475,13 @@
         <v>59</v>
       </c>
       <c r="N16" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O16" t="s">
         <v>60</v>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q16" t="s">
         <v>24</v>
@@ -2484,13 +2531,13 @@
         <v>62</v>
       </c>
       <c r="N17" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O17" t="s">
         <v>63</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="s">
         <v>33</v>
@@ -2540,13 +2587,13 @@
         <v>64</v>
       </c>
       <c r="N18" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O18" t="s">
         <v>65</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="s">
         <v>33</v>
@@ -2596,13 +2643,13 @@
         <v>66</v>
       </c>
       <c r="N19" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O19" t="s">
         <v>67</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="s">
         <v>33</v>
@@ -2652,7 +2699,7 @@
         <v>69</v>
       </c>
       <c r="N20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
@@ -2708,7 +2755,7 @@
         <v>71</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O21" t="s">
         <v>72</v>
@@ -2764,7 +2811,7 @@
         <v>73</v>
       </c>
       <c r="N22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O22" t="s">
         <v>74</v>
@@ -2820,13 +2867,13 @@
         <v>76</v>
       </c>
       <c r="N23" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O23" t="s">
         <v>77</v>
       </c>
       <c r="P23" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q23" t="s">
         <v>49</v>
@@ -2876,13 +2923,13 @@
         <v>78</v>
       </c>
       <c r="N24" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O24" t="s">
         <v>79</v>
       </c>
       <c r="P24" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q24" t="s">
         <v>49</v>
@@ -2932,13 +2979,13 @@
         <v>80</v>
       </c>
       <c r="N25" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O25" t="s">
         <v>81</v>
       </c>
       <c r="P25" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q25" t="s">
         <v>49</v>
@@ -2988,13 +3035,13 @@
         <v>82</v>
       </c>
       <c r="N26" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O26" t="s">
         <v>83</v>
       </c>
       <c r="P26" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q26" t="s">
         <v>24</v>
@@ -3044,13 +3091,13 @@
         <v>84</v>
       </c>
       <c r="N27" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O27" t="s">
         <v>85</v>
       </c>
       <c r="P27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q27" t="s">
         <v>24</v>
@@ -3100,13 +3147,13 @@
         <v>86</v>
       </c>
       <c r="N28" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O28" t="s">
         <v>87</v>
       </c>
       <c r="P28" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q28" t="s">
         <v>24</v>
@@ -3156,13 +3203,13 @@
         <v>88</v>
       </c>
       <c r="N29" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O29" t="s">
         <v>89</v>
       </c>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q29" t="s">
         <v>33</v>
@@ -3212,13 +3259,13 @@
         <v>90</v>
       </c>
       <c r="N30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O30" t="s">
         <v>91</v>
       </c>
       <c r="P30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q30" t="s">
         <v>33</v>
@@ -3268,13 +3315,13 @@
         <v>92</v>
       </c>
       <c r="N31" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O31" t="s">
         <v>93</v>
       </c>
       <c r="P31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q31" t="s">
         <v>33</v>
@@ -3324,7 +3371,7 @@
         <v>94</v>
       </c>
       <c r="N32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O32" t="s">
         <v>95</v>
@@ -3380,7 +3427,7 @@
         <v>96</v>
       </c>
       <c r="N33" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O33" t="s">
         <v>97</v>
@@ -3436,7 +3483,7 @@
         <v>98</v>
       </c>
       <c r="N34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O34" t="s">
         <v>99</v>
@@ -3492,13 +3539,13 @@
         <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O35" t="s">
         <v>101</v>
       </c>
       <c r="P35" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q35" t="s">
         <v>49</v>
@@ -3548,13 +3595,13 @@
         <v>102</v>
       </c>
       <c r="N36" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O36" t="s">
         <v>103</v>
       </c>
       <c r="P36" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q36" t="s">
         <v>49</v>
@@ -3604,13 +3651,13 @@
         <v>104</v>
       </c>
       <c r="N37" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O37" t="s">
         <v>105</v>
       </c>
       <c r="P37" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q37" t="s">
         <v>49</v>
@@ -3660,13 +3707,13 @@
         <v>106</v>
       </c>
       <c r="N38" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O38" t="s">
         <v>107</v>
       </c>
       <c r="P38" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q38" t="s">
         <v>24</v>
@@ -3716,13 +3763,13 @@
         <v>108</v>
       </c>
       <c r="N39" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O39" t="s">
         <v>109</v>
       </c>
       <c r="P39" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q39" t="s">
         <v>24</v>
@@ -3772,13 +3819,13 @@
         <v>110</v>
       </c>
       <c r="N40" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O40" t="s">
         <v>111</v>
       </c>
       <c r="P40" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q40" t="s">
         <v>24</v>
@@ -3828,13 +3875,13 @@
         <v>112</v>
       </c>
       <c r="N41" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O41" t="s">
         <v>113</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q41" t="s">
         <v>33</v>
@@ -3884,13 +3931,13 @@
         <v>114</v>
       </c>
       <c r="N42" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O42" t="s">
         <v>115</v>
       </c>
       <c r="P42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q42" t="s">
         <v>33</v>
@@ -3940,13 +3987,13 @@
         <v>116</v>
       </c>
       <c r="N43" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O43" t="s">
         <v>117</v>
       </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q43" t="s">
         <v>33</v>
@@ -3996,7 +4043,7 @@
         <v>118</v>
       </c>
       <c r="N44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O44" t="s">
         <v>119</v>
@@ -4052,7 +4099,7 @@
         <v>120</v>
       </c>
       <c r="N45" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O45" t="s">
         <v>121</v>
@@ -4108,7 +4155,7 @@
         <v>122</v>
       </c>
       <c r="N46" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O46" t="s">
         <v>123</v>
@@ -4164,13 +4211,13 @@
         <v>124</v>
       </c>
       <c r="N47" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O47" t="s">
         <v>125</v>
       </c>
       <c r="P47" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q47" t="s">
         <v>49</v>
@@ -4220,13 +4267,13 @@
         <v>126</v>
       </c>
       <c r="N48" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O48" t="s">
         <v>127</v>
       </c>
       <c r="P48" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q48" t="s">
         <v>49</v>
@@ -4276,13 +4323,13 @@
         <v>128</v>
       </c>
       <c r="N49" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O49" t="s">
         <v>129</v>
       </c>
       <c r="P49" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q49" t="s">
         <v>49</v>
@@ -4332,13 +4379,13 @@
         <v>131</v>
       </c>
       <c r="N50" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O50" t="s">
         <v>132</v>
       </c>
       <c r="P50" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q50" t="s">
         <v>24</v>
@@ -4388,13 +4435,13 @@
         <v>133</v>
       </c>
       <c r="N51" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O51" t="s">
         <v>134</v>
       </c>
       <c r="P51" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q51" t="s">
         <v>24</v>
@@ -4444,13 +4491,13 @@
         <v>135</v>
       </c>
       <c r="N52" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O52" t="s">
         <v>136</v>
       </c>
       <c r="P52" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q52" t="s">
         <v>24</v>
@@ -4500,13 +4547,13 @@
         <v>138</v>
       </c>
       <c r="N53" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O53" t="s">
         <v>139</v>
       </c>
       <c r="P53" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q53" t="s">
         <v>33</v>
@@ -4556,13 +4603,13 @@
         <v>140</v>
       </c>
       <c r="N54" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O54" t="s">
         <v>141</v>
       </c>
       <c r="P54" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q54" t="s">
         <v>33</v>
@@ -4612,13 +4659,13 @@
         <v>142</v>
       </c>
       <c r="N55" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O55" t="s">
         <v>143</v>
       </c>
       <c r="P55" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q55" t="s">
         <v>33</v>
@@ -4668,7 +4715,7 @@
         <v>144</v>
       </c>
       <c r="N56" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O56" t="s">
         <v>145</v>
@@ -4724,7 +4771,7 @@
         <v>146</v>
       </c>
       <c r="N57" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O57" t="s">
         <v>147</v>
@@ -4780,7 +4827,7 @@
         <v>148</v>
       </c>
       <c r="N58" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O58" t="s">
         <v>149</v>
@@ -4836,13 +4883,13 @@
         <v>150</v>
       </c>
       <c r="N59" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O59" t="s">
         <v>151</v>
       </c>
       <c r="P59" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q59" t="s">
         <v>49</v>
@@ -4892,13 +4939,13 @@
         <v>152</v>
       </c>
       <c r="N60" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O60" t="s">
         <v>153</v>
       </c>
       <c r="P60" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q60" t="s">
         <v>49</v>
@@ -4948,13 +4995,13 @@
         <v>154</v>
       </c>
       <c r="N61" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O61" t="s">
         <v>155</v>
       </c>
       <c r="P61" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q61" t="s">
         <v>49</v>
@@ -5004,13 +5051,13 @@
         <v>156</v>
       </c>
       <c r="N62" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O62" t="s">
         <v>157</v>
       </c>
       <c r="P62" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q62" t="s">
         <v>24</v>
@@ -5060,13 +5107,13 @@
         <v>158</v>
       </c>
       <c r="N63" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O63" t="s">
         <v>159</v>
       </c>
       <c r="P63" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q63" t="s">
         <v>24</v>
@@ -5116,13 +5163,13 @@
         <v>160</v>
       </c>
       <c r="N64" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O64" t="s">
         <v>161</v>
       </c>
       <c r="P64" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q64" t="s">
         <v>24</v>
@@ -5172,13 +5219,13 @@
         <v>162</v>
       </c>
       <c r="N65" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O65" t="s">
         <v>163</v>
       </c>
       <c r="P65" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q65" t="s">
         <v>33</v>
@@ -5228,13 +5275,13 @@
         <v>164</v>
       </c>
       <c r="N66" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O66" t="s">
         <v>165</v>
       </c>
       <c r="P66" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q66" t="s">
         <v>33</v>
@@ -5284,13 +5331,13 @@
         <v>166</v>
       </c>
       <c r="N67" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O67" t="s">
         <v>167</v>
       </c>
       <c r="P67" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q67" t="s">
         <v>33</v>
@@ -5340,7 +5387,7 @@
         <v>168</v>
       </c>
       <c r="N68" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O68" t="s">
         <v>169</v>
@@ -5396,7 +5443,7 @@
         <v>170</v>
       </c>
       <c r="N69" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O69" t="s">
         <v>171</v>
@@ -5452,7 +5499,7 @@
         <v>172</v>
       </c>
       <c r="N70" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O70" t="s">
         <v>173</v>
@@ -5508,13 +5555,13 @@
         <v>174</v>
       </c>
       <c r="N71" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O71" t="s">
         <v>175</v>
       </c>
       <c r="P71" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q71" t="s">
         <v>49</v>
@@ -5564,13 +5611,13 @@
         <v>176</v>
       </c>
       <c r="N72" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O72" t="s">
         <v>177</v>
       </c>
       <c r="P72" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q72" t="s">
         <v>49</v>
@@ -5620,13 +5667,13 @@
         <v>178</v>
       </c>
       <c r="N73" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="O73" t="s">
         <v>179</v>
       </c>
       <c r="P73" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q73" t="s">
         <v>49</v>
@@ -5676,13 +5723,13 @@
         <v>181</v>
       </c>
       <c r="N74" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O74" t="s">
         <v>182</v>
       </c>
       <c r="P74" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q74" t="s">
         <v>24</v>
@@ -5732,13 +5779,13 @@
         <v>183</v>
       </c>
       <c r="N75" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O75" t="s">
         <v>184</v>
       </c>
       <c r="P75" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q75" t="s">
         <v>24</v>
@@ -5788,13 +5835,13 @@
         <v>185</v>
       </c>
       <c r="N76" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O76" t="s">
         <v>186</v>
       </c>
       <c r="P76" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q76" t="s">
         <v>24</v>
@@ -5844,7 +5891,7 @@
         <v>188</v>
       </c>
       <c r="N77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O77" t="s">
         <v>189</v>
@@ -5900,7 +5947,7 @@
         <v>191</v>
       </c>
       <c r="N78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O78" t="s">
         <v>192</v>
@@ -5956,7 +6003,7 @@
         <v>193</v>
       </c>
       <c r="N79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O79" t="s">
         <v>194</v>
@@ -6012,7 +6059,7 @@
         <v>195</v>
       </c>
       <c r="N80" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O80" t="s">
         <v>196</v>
@@ -6068,7 +6115,7 @@
         <v>197</v>
       </c>
       <c r="N81" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O81" t="s">
         <v>198</v>
@@ -6124,7 +6171,7 @@
         <v>199</v>
       </c>
       <c r="N82" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O82" t="s">
         <v>200</v>
@@ -6180,13 +6227,13 @@
         <v>201</v>
       </c>
       <c r="N83" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="O83" t="s">
         <v>202</v>
       </c>
       <c r="P83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q83" t="s">
         <v>203</v>
@@ -6236,13 +6283,13 @@
         <v>204</v>
       </c>
       <c r="N84" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="O84" t="s">
         <v>205</v>
       </c>
       <c r="P84" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q84" t="s">
         <v>203</v>
@@ -6292,13 +6339,13 @@
         <v>206</v>
       </c>
       <c r="N85" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="O85" t="s">
         <v>207</v>
       </c>
       <c r="P85" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q85" t="s">
         <v>203</v>
@@ -6348,13 +6395,13 @@
         <v>208</v>
       </c>
       <c r="N86" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O86" t="s">
         <v>209</v>
       </c>
       <c r="P86" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q86" t="s">
         <v>24</v>
@@ -6404,13 +6451,13 @@
         <v>210</v>
       </c>
       <c r="N87" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O87" t="s">
         <v>211</v>
       </c>
       <c r="P87" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q87" t="s">
         <v>24</v>
@@ -6460,13 +6507,13 @@
         <v>212</v>
       </c>
       <c r="N88" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O88" t="s">
         <v>213</v>
       </c>
       <c r="P88" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q88" t="s">
         <v>24</v>
@@ -6516,7 +6563,7 @@
         <v>214</v>
       </c>
       <c r="N89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O89" t="s">
         <v>215</v>
@@ -6572,7 +6619,7 @@
         <v>216</v>
       </c>
       <c r="N90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O90" t="s">
         <v>217</v>
@@ -6628,7 +6675,7 @@
         <v>218</v>
       </c>
       <c r="N91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O91" t="s">
         <v>219</v>
@@ -6684,7 +6731,7 @@
         <v>220</v>
       </c>
       <c r="N92" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O92" t="s">
         <v>221</v>
@@ -6740,7 +6787,7 @@
         <v>222</v>
       </c>
       <c r="N93" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O93" t="s">
         <v>223</v>
@@ -6796,7 +6843,7 @@
         <v>224</v>
       </c>
       <c r="N94" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O94" t="s">
         <v>225</v>
@@ -6852,13 +6899,13 @@
         <v>226</v>
       </c>
       <c r="N95" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="O95" t="s">
         <v>227</v>
       </c>
       <c r="P95" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q95" t="s">
         <v>203</v>
@@ -6908,13 +6955,13 @@
         <v>228</v>
       </c>
       <c r="N96" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="O96" t="s">
         <v>229</v>
       </c>
       <c r="P96" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q96" t="s">
         <v>203</v>
@@ -6964,13 +7011,13 @@
         <v>230</v>
       </c>
       <c r="N97" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="O97" t="s">
         <v>231</v>
       </c>
       <c r="P97" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q97" t="s">
         <v>203</v>
@@ -7020,13 +7067,13 @@
         <v>233</v>
       </c>
       <c r="N98" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O98" t="s">
         <v>234</v>
       </c>
       <c r="P98" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q98" t="s">
         <v>24</v>
@@ -7076,13 +7123,13 @@
         <v>235</v>
       </c>
       <c r="N99" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O99" t="s">
         <v>236</v>
       </c>
       <c r="P99" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q99" t="s">
         <v>24</v>
@@ -7132,13 +7179,13 @@
         <v>237</v>
       </c>
       <c r="N100" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O100" t="s">
         <v>238</v>
       </c>
       <c r="P100" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q100" t="s">
         <v>24</v>
@@ -7188,13 +7235,13 @@
         <v>240</v>
       </c>
       <c r="N101" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O101" t="s">
         <v>241</v>
       </c>
       <c r="P101" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q101" t="s">
         <v>242</v>
@@ -7244,13 +7291,13 @@
         <v>243</v>
       </c>
       <c r="N102" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O102" t="s">
         <v>244</v>
       </c>
       <c r="P102" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q102" t="s">
         <v>242</v>
@@ -7300,13 +7347,13 @@
         <v>245</v>
       </c>
       <c r="N103" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O103" t="s">
         <v>246</v>
       </c>
       <c r="P103" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q103" t="s">
         <v>242</v>
@@ -7356,7 +7403,7 @@
         <v>247</v>
       </c>
       <c r="N104" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O104" t="s">
         <v>248</v>
@@ -7412,7 +7459,7 @@
         <v>249</v>
       </c>
       <c r="N105" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O105" t="s">
         <v>250</v>
@@ -7468,7 +7515,7 @@
         <v>251</v>
       </c>
       <c r="N106" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O106" t="s">
         <v>252</v>
@@ -7524,13 +7571,13 @@
         <v>253</v>
       </c>
       <c r="N107" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O107" t="s">
         <v>254</v>
       </c>
       <c r="P107" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q107" t="s">
         <v>255</v>
@@ -7580,13 +7627,13 @@
         <v>256</v>
       </c>
       <c r="N108" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O108" t="s">
         <v>257</v>
       </c>
       <c r="P108" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q108" t="s">
         <v>255</v>
@@ -7636,13 +7683,13 @@
         <v>258</v>
       </c>
       <c r="N109" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O109" t="s">
         <v>259</v>
       </c>
       <c r="P109" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q109" t="s">
         <v>255</v>
@@ -7692,13 +7739,13 @@
         <v>260</v>
       </c>
       <c r="N110" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O110" t="s">
         <v>261</v>
       </c>
       <c r="P110" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q110" t="s">
         <v>24</v>
@@ -7748,13 +7795,13 @@
         <v>262</v>
       </c>
       <c r="N111" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O111" t="s">
         <v>263</v>
       </c>
       <c r="P111" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q111" t="s">
         <v>24</v>
@@ -7804,13 +7851,13 @@
         <v>264</v>
       </c>
       <c r="N112" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O112" t="s">
         <v>265</v>
       </c>
       <c r="P112" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q112" t="s">
         <v>24</v>
@@ -7860,13 +7907,13 @@
         <v>266</v>
       </c>
       <c r="N113" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O113" t="s">
         <v>267</v>
       </c>
       <c r="P113" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q113" t="s">
         <v>242</v>
@@ -7916,13 +7963,13 @@
         <v>268</v>
       </c>
       <c r="N114" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O114" t="s">
         <v>269</v>
       </c>
       <c r="P114" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q114" t="s">
         <v>242</v>
@@ -7972,13 +8019,13 @@
         <v>270</v>
       </c>
       <c r="N115" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O115" t="s">
         <v>271</v>
       </c>
       <c r="P115" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q115" t="s">
         <v>242</v>
@@ -8028,7 +8075,7 @@
         <v>272</v>
       </c>
       <c r="N116" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O116" t="s">
         <v>273</v>
@@ -8084,7 +8131,7 @@
         <v>274</v>
       </c>
       <c r="N117" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O117" t="s">
         <v>275</v>
@@ -8140,7 +8187,7 @@
         <v>276</v>
       </c>
       <c r="N118" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O118" t="s">
         <v>277</v>
@@ -8196,13 +8243,13 @@
         <v>278</v>
       </c>
       <c r="N119" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O119" t="s">
         <v>279</v>
       </c>
       <c r="P119" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q119" t="s">
         <v>255</v>
@@ -8252,13 +8299,13 @@
         <v>280</v>
       </c>
       <c r="N120" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O120" t="s">
         <v>281</v>
       </c>
       <c r="P120" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q120" t="s">
         <v>255</v>
@@ -8308,13 +8355,13 @@
         <v>282</v>
       </c>
       <c r="N121" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O121" t="s">
         <v>283</v>
       </c>
       <c r="P121" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q121" t="s">
         <v>255</v>
@@ -8364,13 +8411,13 @@
         <v>285</v>
       </c>
       <c r="N122" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O122" t="s">
         <v>286</v>
       </c>
       <c r="P122" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q122" t="s">
         <v>287</v>
@@ -8420,13 +8467,13 @@
         <v>288</v>
       </c>
       <c r="N123" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O123" t="s">
         <v>289</v>
       </c>
       <c r="P123" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q123" t="s">
         <v>287</v>
@@ -8476,13 +8523,13 @@
         <v>290</v>
       </c>
       <c r="N124" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O124" t="s">
         <v>291</v>
       </c>
       <c r="P124" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q124" t="s">
         <v>287</v>
@@ -8532,13 +8579,13 @@
         <v>293</v>
       </c>
       <c r="N125" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O125" t="s">
         <v>294</v>
       </c>
       <c r="P125" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q125" t="s">
         <v>242</v>
@@ -8588,13 +8635,13 @@
         <v>295</v>
       </c>
       <c r="N126" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O126" t="s">
         <v>296</v>
       </c>
       <c r="P126" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q126" t="s">
         <v>242</v>
@@ -8644,13 +8691,13 @@
         <v>297</v>
       </c>
       <c r="N127" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O127" t="s">
         <v>298</v>
       </c>
       <c r="P127" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q127" t="s">
         <v>242</v>
@@ -8664,7 +8711,7 @@
         <v>256</v>
       </c>
       <c r="B128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -8699,16 +8746,20 @@
       <c r="M128" t="s">
         <v>299</v>
       </c>
-      <c r="N128"/>
+      <c r="N128" t="n">
+        <v>4</v>
+      </c>
       <c r="O128" t="s">
-        <v>299</v>
-      </c>
-      <c r="P128"/>
+        <v>300</v>
+      </c>
+      <c r="P128" t="n">
+        <v>3</v>
+      </c>
       <c r="Q128" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R128" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="129">
@@ -8716,7 +8767,7 @@
         <v>257</v>
       </c>
       <c r="B129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -8749,18 +8800,22 @@
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>299</v>
-      </c>
-      <c r="N129"/>
+        <v>302</v>
+      </c>
+      <c r="N129" t="n">
+        <v>4</v>
+      </c>
       <c r="O129" t="s">
-        <v>299</v>
-      </c>
-      <c r="P129"/>
+        <v>303</v>
+      </c>
+      <c r="P129" t="n">
+        <v>3</v>
+      </c>
       <c r="Q129" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R129" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="130">
@@ -8768,7 +8823,7 @@
         <v>258</v>
       </c>
       <c r="B130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -8801,18 +8856,22 @@
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>299</v>
-      </c>
-      <c r="N130"/>
+        <v>304</v>
+      </c>
+      <c r="N130" t="n">
+        <v>4</v>
+      </c>
       <c r="O130" t="s">
-        <v>299</v>
-      </c>
-      <c r="P130"/>
+        <v>305</v>
+      </c>
+      <c r="P130" t="n">
+        <v>3</v>
+      </c>
       <c r="Q130" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R130" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="131">
@@ -8853,22 +8912,22 @@
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="N131" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="O131" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P131" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q131" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="R131" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="132">
@@ -8909,22 +8968,22 @@
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="N132" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="O132" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="P132" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q132" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="R132" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="133">
@@ -8965,22 +9024,22 @@
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="N133" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="O133" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="P133" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q133" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="R133" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="134">
@@ -9021,16 +9080,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="N134" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O134" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="P134" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q134" t="s">
         <v>287</v>
@@ -9077,16 +9136,16 @@
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="N135" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O135" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="P135" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q135" t="s">
         <v>287</v>
@@ -9133,16 +9192,16 @@
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="N136" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O136" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="P136" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q136" t="s">
         <v>287</v>
@@ -9189,16 +9248,16 @@
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="N137" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O137" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="P137" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q137" t="s">
         <v>242</v>
@@ -9245,16 +9304,16 @@
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N138" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O138" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="P138" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q138" t="s">
         <v>242</v>
@@ -9301,16 +9360,16 @@
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N139" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O139" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="P139" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q139" t="s">
         <v>242</v>
@@ -9357,18 +9416,22 @@
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>299</v>
-      </c>
-      <c r="N140"/>
+        <v>325</v>
+      </c>
+      <c r="N140" t="n">
+        <v>4</v>
+      </c>
       <c r="O140" t="s">
-        <v>299</v>
-      </c>
-      <c r="P140"/>
+        <v>326</v>
+      </c>
+      <c r="P140" t="n">
+        <v>3</v>
+      </c>
       <c r="Q140" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R140" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="141">
@@ -9409,18 +9472,22 @@
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>299</v>
-      </c>
-      <c r="N141"/>
+        <v>327</v>
+      </c>
+      <c r="N141" t="n">
+        <v>4</v>
+      </c>
       <c r="O141" t="s">
-        <v>299</v>
-      </c>
-      <c r="P141"/>
+        <v>328</v>
+      </c>
+      <c r="P141" t="n">
+        <v>3</v>
+      </c>
       <c r="Q141" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R141" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="142">
@@ -9461,18 +9528,22 @@
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>299</v>
-      </c>
-      <c r="N142"/>
+        <v>329</v>
+      </c>
+      <c r="N142" t="n">
+        <v>4</v>
+      </c>
       <c r="O142" t="s">
-        <v>299</v>
-      </c>
-      <c r="P142"/>
+        <v>330</v>
+      </c>
+      <c r="P142" t="n">
+        <v>3</v>
+      </c>
       <c r="Q142" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R142" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="143">
@@ -9513,22 +9584,22 @@
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="N143" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="O143" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="P143" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q143" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="R143" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="144">
@@ -9569,22 +9640,22 @@
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="N144" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="O144" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="P144" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q144" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="R144" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="145">
@@ -9625,22 +9696,22 @@
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="N145" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="O145" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="P145" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Q145" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="R145" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="146">
@@ -9675,28 +9746,28 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="N146" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O146" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="P146" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q146" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R146" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147">
@@ -9731,28 +9802,28 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="N147" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O147" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="P147" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q147" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R147" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148">
@@ -9787,28 +9858,28 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="N148" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O148" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="P148" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q148" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R148" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="149">
@@ -9843,24 +9914,24 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N149"/>
       <c r="O149" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P149"/>
       <c r="Q149" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R149" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="150">
@@ -9895,24 +9966,24 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
       </c>
       <c r="M150" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N150"/>
       <c r="O150" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P150"/>
       <c r="Q150" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R150" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="151">
@@ -9947,24 +10018,24 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
       </c>
       <c r="M151" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N151"/>
       <c r="O151" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P151"/>
       <c r="Q151" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R151" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="152">
@@ -9999,24 +10070,24 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N152"/>
       <c r="O152" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P152"/>
       <c r="Q152" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R152" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153">
@@ -10051,24 +10122,24 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
       </c>
       <c r="M153" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N153"/>
       <c r="O153" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P153"/>
       <c r="Q153" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R153" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="154">
@@ -10103,24 +10174,24 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
       </c>
       <c r="M154" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N154"/>
       <c r="O154" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P154"/>
       <c r="Q154" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R154" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="155">
@@ -10155,28 +10226,28 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="N155" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O155" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="P155" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q155" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R155" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="156">
@@ -10211,28 +10282,28 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="N156" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O156" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="P156" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q156" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R156" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="157">
@@ -10267,28 +10338,28 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="N157" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O157" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="P157" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q157" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R157" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="158">
@@ -10323,28 +10394,28 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="N158" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O158" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="P158" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q158" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R158" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="159">
@@ -10379,28 +10450,28 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="N159" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O159" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="P159" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q159" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R159" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="160">
@@ -10435,28 +10506,28 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="N160" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O160" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="P160" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q160" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R160" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="161">
@@ -10491,24 +10562,24 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N161"/>
       <c r="O161" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P161"/>
       <c r="Q161" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R161" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="162">
@@ -10543,24 +10614,24 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
       </c>
       <c r="M162" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N162"/>
       <c r="O162" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P162"/>
       <c r="Q162" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R162" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="163">
@@ -10595,24 +10666,24 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
       </c>
       <c r="M163" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N163"/>
       <c r="O163" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P163"/>
       <c r="Q163" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R163" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="164">
@@ -10647,24 +10718,24 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
       </c>
       <c r="M164" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N164"/>
       <c r="O164" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P164"/>
       <c r="Q164" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R164" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="165">
@@ -10699,24 +10770,24 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
       </c>
       <c r="M165" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N165"/>
       <c r="O165" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P165"/>
       <c r="Q165" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R165" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="166">
@@ -10751,24 +10822,24 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
       </c>
       <c r="M166" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N166"/>
       <c r="O166" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P166"/>
       <c r="Q166" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R166" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="167">
@@ -10803,28 +10874,28 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="N167" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O167" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="P167" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q167" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R167" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="168">
@@ -10859,28 +10930,28 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
+        <v>362</v>
+      </c>
+      <c r="N168" t="n">
+        <v>14</v>
+      </c>
+      <c r="O168" t="s">
+        <v>363</v>
+      </c>
+      <c r="P168" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q168" t="s">
         <v>349</v>
       </c>
-      <c r="N168" t="n">
-        <v>6</v>
-      </c>
-      <c r="O168" t="s">
-        <v>350</v>
-      </c>
-      <c r="P168" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q168" t="s">
-        <v>336</v>
-      </c>
       <c r="R168" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="169">
@@ -10915,28 +10986,28 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="N169" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O169" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="P169" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q169" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R169" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="170">
@@ -10971,28 +11042,28 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="N170" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O170" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="P170" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q170" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R170" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="171">
@@ -11027,28 +11098,28 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="N171" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O171" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="P171" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q171" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R171" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="172">
@@ -11083,28 +11154,28 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="N172" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O172" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="P172" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q172" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R172" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="173">
@@ -11139,24 +11210,24 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N173"/>
       <c r="O173" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P173"/>
       <c r="Q173" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R173" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="174">
@@ -11191,24 +11262,24 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
       </c>
       <c r="M174" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N174"/>
       <c r="O174" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P174"/>
       <c r="Q174" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R174" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="175">
@@ -11243,24 +11314,24 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
       </c>
       <c r="M175" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N175"/>
       <c r="O175" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P175"/>
       <c r="Q175" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R175" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="176">
@@ -11295,24 +11366,24 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
       </c>
       <c r="M176" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N176"/>
       <c r="O176" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P176"/>
       <c r="Q176" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R176" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="177">
@@ -11347,24 +11418,24 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
       </c>
       <c r="M177" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N177"/>
       <c r="O177" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P177"/>
       <c r="Q177" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R177" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="178">
@@ -11399,24 +11470,24 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
       </c>
       <c r="M178" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N178"/>
       <c r="O178" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P178"/>
       <c r="Q178" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R178" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="179">
@@ -11451,28 +11522,28 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="N179" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O179" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="P179" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q179" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R179" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180">
@@ -11507,28 +11578,28 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="N180" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O180" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="P180" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q180" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R180" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="181">
@@ -11563,28 +11634,28 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="N181" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O181" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="P181" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q181" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R181" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="182">
@@ -11619,28 +11690,28 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="N182" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O182" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="P182" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q182" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R182" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="183">
@@ -11675,28 +11746,28 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="N183" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O183" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="P183" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q183" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R183" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="184">
@@ -11731,28 +11802,28 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="N184" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O184" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="P184" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q184" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="R184" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
     </row>
     <row r="185">
@@ -11787,24 +11858,24 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
       </c>
       <c r="M185" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N185"/>
       <c r="O185" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P185"/>
       <c r="Q185" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R185" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="186">
@@ -11839,24 +11910,24 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
       </c>
       <c r="M186" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N186"/>
       <c r="O186" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P186"/>
       <c r="Q186" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R186" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="187">
@@ -11891,24 +11962,24 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
       </c>
       <c r="M187" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N187"/>
       <c r="O187" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P187"/>
       <c r="Q187" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R187" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="188">
@@ -11943,24 +12014,24 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
       </c>
       <c r="M188" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N188"/>
       <c r="O188" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P188"/>
       <c r="Q188" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R188" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="189">
@@ -11995,24 +12066,24 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
       </c>
       <c r="M189" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N189"/>
       <c r="O189" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P189"/>
       <c r="Q189" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R189" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="190">
@@ -12047,24 +12118,24 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
       </c>
       <c r="M190" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N190"/>
       <c r="O190" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P190"/>
       <c r="Q190" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R190" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="191">
@@ -12099,28 +12170,28 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="N191" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O191" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="P191" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q191" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R191" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="192">
@@ -12155,28 +12226,28 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="N192" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O192" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="P192" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q192" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R192" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="193">
@@ -12211,28 +12282,28 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="N193" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O193" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="P193" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q193" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R193" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="194">
@@ -12267,28 +12338,28 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="N194" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O194" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="P194" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q194" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="R194" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="195">
@@ -12323,28 +12394,28 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="N195" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O195" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="P195" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q195" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="R195" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="196">
@@ -12379,28 +12450,28 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="N196" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O196" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="P196" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q196" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="R196" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="197">
@@ -12435,24 +12506,24 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
       </c>
       <c r="M197" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N197"/>
       <c r="O197" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P197"/>
       <c r="Q197" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R197" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="198">
@@ -12487,24 +12558,24 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
       </c>
       <c r="M198" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N198"/>
       <c r="O198" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P198"/>
       <c r="Q198" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R198" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="199">
@@ -12539,24 +12610,24 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
       </c>
       <c r="M199" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N199"/>
       <c r="O199" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P199"/>
       <c r="Q199" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R199" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="200">
@@ -12591,24 +12662,24 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
       </c>
       <c r="M200" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N200"/>
       <c r="O200" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P200"/>
       <c r="Q200" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R200" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="201">
@@ -12643,24 +12714,24 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
       </c>
       <c r="M201" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N201"/>
       <c r="O201" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P201"/>
       <c r="Q201" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R201" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="202">
@@ -12695,24 +12766,24 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
       </c>
       <c r="M202" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N202"/>
       <c r="O202" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P202"/>
       <c r="Q202" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R202" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="203">
@@ -12747,28 +12818,28 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="N203" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O203" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="P203" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q203" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R203" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="204">
@@ -12803,28 +12874,28 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="N204" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O204" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="P204" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q204" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R204" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="205">
@@ -12859,28 +12930,28 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="N205" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O205" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="P205" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q205" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R205" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="206">
@@ -12915,28 +12986,28 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="N206" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O206" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="P206" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q206" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="R206" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="207">
@@ -12971,28 +13042,28 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
+        <v>407</v>
+      </c>
+      <c r="N207" t="n">
+        <v>20</v>
+      </c>
+      <c r="O207" t="s">
+        <v>408</v>
+      </c>
+      <c r="P207" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q207" t="s">
         <v>394</v>
       </c>
-      <c r="N207" t="n">
-        <v>14</v>
-      </c>
-      <c r="O207" t="s">
-        <v>395</v>
-      </c>
-      <c r="P207" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q207" t="s">
-        <v>381</v>
-      </c>
       <c r="R207" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="208">
@@ -13027,28 +13098,28 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="N208" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O208" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="P208" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q208" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="R208" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="209">
@@ -13083,24 +13154,24 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
       </c>
       <c r="M209" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N209"/>
       <c r="O209" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P209"/>
       <c r="Q209" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R209" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="210">
@@ -13135,24 +13206,24 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
       </c>
       <c r="M210" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N210"/>
       <c r="O210" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P210"/>
       <c r="Q210" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R210" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="211">
@@ -13187,24 +13258,24 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
       </c>
       <c r="M211" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N211"/>
       <c r="O211" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P211"/>
       <c r="Q211" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R211" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="212">
@@ -13239,24 +13310,24 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
       </c>
       <c r="M212" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N212"/>
       <c r="O212" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P212"/>
       <c r="Q212" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R212" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="213">
@@ -13291,24 +13362,24 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
       </c>
       <c r="M213" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N213"/>
       <c r="O213" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P213"/>
       <c r="Q213" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R213" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="214">
@@ -13343,24 +13414,24 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
       </c>
       <c r="M214" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="N214"/>
       <c r="O214" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="P214"/>
       <c r="Q214" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="R214" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
     </row>
     <row r="215">
@@ -13395,28 +13466,28 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="N215" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O215" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="P215" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q215" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R215" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="216">
@@ -13451,28 +13522,28 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="N216" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O216" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="P216" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q216" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R216" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="217">
@@ -13507,28 +13578,28 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="N217" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O217" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="P217" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q217" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="R217" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
@@ -80,25 +80,25 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 33, 34, 35, 151, 152, 1652, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1773, 1774, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2179, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 32, 148, 149, 150, 1653, 1654, 1655, 1691, 1755, 1757, 1772, 1824, 2177, 2229, 2283, 2290, 2293, 2295)</t>
+    <t xml:space="preserve">c(17, 20, 23, 33, 34, 35, 148, 150, 152, 1653, 1751, 1752, 1753, 1754, 1755, 1757, 1771, 1772, 1773, 1774, 1825, 1827, 1897, 1898, 1900, 2054, 2056, 2177, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 31, 32, 149, 151, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1756, 1824, 1826, 2058, 2179, 2289, 2294)</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 19, 20, 34, 35, 149, 150, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1756, 1772, 1773, 1774, 1826, 1827, 1897, 1898, 1900, 2058, 2179, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 31, 32, 33, 148, 152, 1753, 1754, 1755, 1757, 1771, 1824, 1825, 2054, 2056, 2177, 2229, 2283, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 33, 34, 148, 149, 150, 152, 1655, 1691, 1693, 1751, 1757, 1771, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 1900, 2054, 2056, 2058, 2179, 2227, 2229, 2231, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 35, 151, 1652, 1653, 1654, 1692, 1750, 1752, 1753, 1754, 1755, 1756, 1772, 1827, 2177, 2279, 2281, 2292, 2295)</t>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 34, 35, 149, 150, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1752, 1754, 1755, 1757, 1771, 1773, 1774, 1825, 1826, 1898, 2056, 2177, 2179, 2227, 2229, 2231, 2279, 2283, 2288, 2289, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 32, 148, 151, 1693, 1751, 1753, 1756, 1772, 1824, 1827, 1897, 1900, 2054, 2058, 2281, 2282, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 31, 32, 33, 35, 148, 151, 152, 1653, 1654, 1691, 1693, 1751, 1753, 1755, 1757, 1771, 1772, 1773, 1824, 1826, 1827, 1897, 1898, 2056, 2058, 2177, 2227, 2229, 2231, 2279, 2282, 2283, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 34, 149, 150, 1652, 1655, 1692, 1750, 1752, 1754, 1756, 1774, 1825, 1900, 2054, 2179, 2281, 2288, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
@@ -107,949 +107,949 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 226, 275, 276, 277, 278, 279, 280, 1719, 1720, 1722, 1775, 1777, 1778, 1779, 1868, 1869, 2027, 2035, 2037, 2120, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 224, 228, 1721, 1727, 1776, 1870, 2029, 2033, 2119, 2121, 2124, 2125, 2221)</t>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 276, 277, 278, 279, 1719, 1720, 1722, 1776, 1778, 1779, 1868, 1869, 1870, 2033, 2037, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 275, 280, 1721, 1727, 1775, 1777, 2027, 2029, 2035, 2119, 2120, 2121, 2125)</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 44, 224, 228, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1777, 1778, 1868, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2124, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 226, 275, 276, 277, 1776, 1779, 1869, 2120, 2121, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 228, 275, 276, 277, 278, 280, 1719, 1722, 1777, 1778, 1779, 1869, 1870, 2027, 2029, 2033, 2035, 2119, 2120, 2121, 2124, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 224, 226, 279, 1720, 1721, 1727, 1775, 1776, 1868, 2037, 2125, 2221)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 228, 275, 276, 277, 1721, 1722, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2033, 2119, 2120, 2121, 2124, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(226, 278, 279, 280, 1719, 1720, 1727, 1777, 2027, 2029, 2035, 2037, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 280, 1719, 1720, 1721, 1776, 1777, 1778, 1868, 1869, 2027, 2033, 2119, 2120, 2124, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(277, 278, 279, 1722, 1727, 1775, 1779, 1870, 2029, 2035, 2037, 2121, 2221, 2224)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 208, 211, 212, 215, 216, 217, 218, 219, 265, 266, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 209, 210, 213, 214, 220, 1899, 2230, 2232)</t>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 208, 209, 210, 213, 214, 215, 216, 217, 218, 219, 265, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 207, 211, 212, 220, 266, 268, 1899, 2232)</t>
   </si>
   <si>
     <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 208, 210, 211, 212, 213, 214, 215, 216, 217, 219, 265, 266, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 207, 209, 218, 220, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 205, 206, 209, 210, 211, 212, 214, 216, 218, 219, 220, 266, 267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 207, 208, 213, 215, 217, 265, 2230)</t>
+    <t xml:space="preserve">c(201, 202, 203, 205, 207, 210, 211, 212, 213, 214, 216, 217, 219, 265, 266, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 206, 208, 209, 215, 218, 220, 267, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 207, 208, 209, 211, 212, 213, 214, 216, 217, 219, 220, 266, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 206, 210, 215, 218, 265, 267, 268, 1899)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(15, 70, 72, 73, 141, 142, 176, 177, 178, 179, 180, 221, 225, 227, 229, 230, 231, 233, 234, 236, 243, 244, 245, 246, 247, 248, 249, 271, 273, 281, 282, 283, 286, 287, 290, 292, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1839, 1840, 1863, 1864, 1865, 1867, 1874, 1875, 1935, 1990, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2131, 2134, 2138, 2194, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 71, 130, 131, 132, 140, 143, 175, 181, 182, 223, 235, 250, 272, 274, 284, 285, 288, 289, 291, 293, 1717, 1766, 1838, 1852, 1866, 1876, 1991, 1992, 2129, 2130, 2132, 2133, 2135, 2136, 2137, 2139, 2222, 2313)</t>
+    <t xml:space="preserve">c(14, 15, 71, 72, 73, 130, 132, 140, 141, 142, 143, 175, 176, 179, 181, 182, 221, 225, 227, 229, 231, 233, 234, 244, 246, 248, 250, 271, 273, 281, 282, 283, 284, 286, 289, 290, 291, 292, 293, 295, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1765, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1874, 1875, 1876, 1935, 1990, 2026, 2028, 2032, 2034, 2036, 2108, 2109, 2131, 2132, 2133, 2134, 2138, 2194, 2222, 2226, 2257, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 131, 177, 178, 180, 223, 230, 235, 236, 243, 245, 247, 249, 272, 274, 285, 287, 288, 294, 1761, 1764, 1766, 1865, 1867, 1991, 1992, 2030, 2128, 2129, 2130, 2135, 2136, 2137, 2139, 2223, 2225, 2300, 2303, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 
 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 73, 130, 131, 132, 142, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 230, 234, 235, 236, 244, 245, 246, 248, 249, 250, 271, 272, 281, 282, 283, 286, 287, 288, 290, 291, 292, 296, 1760, 1762, 1763, 1764, 1765, 1766, 1839, 1840, 1852, 1864, 1875, 1876, 1935, 1990, 1991, 1992, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2132, 2134, 2136, 2138, 2194, 2222, 2223, 2257, 2300, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 140, 141, 143, 175, 229, 231, 233, 243, 247, 273, 274, 284, 285, 289, 293, 294, 295, 1716, 1717, 1718, 1761, 1838, 1863, 1865, 1866, 1867, 1874, 2026, 2028, 2130, 2131, 2133, 2135, 2137, 2139, 2225, 2226, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 132, 141, 142, 143, 175, 176, 180, 182, 221, 223, 225, 227, 230, 233, 234, 235, 236, 243, 244, 245, 246, 247, 249, 271, 272, 273, 274, 281, 283, 286, 292, 293, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1766, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 2026, 2028, 2030, 2034, 2036, 2108, 2109, 2128, 2132, 2135, 2136, 2137, 2139, 2223, 2226, 2257, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 130, 131, 140, 177, 178, 179, 181, 229, 231, 248, 250, 282, 284, 285, 287, 288, 289, 290, 291, 294, 295, 1717, 1764, 1765, 1840, 1875, 1992, 2032, 2129, 2130, 2131, 2133, 2134, 2138, 2194, 2222, 2225, 2302, 2313)</t>
+    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 131, 132, 141, 142, 143, 179, 180, 181, 221, 227, 229, 230, 234, 236, 244, 245, 246, 247, 248, 249, 274, 282, 283, 284, 286, 287, 289, 290, 291, 292, 293, 294, 295, 296, 1717, 1760, 1762, 1763, 1765, 1838, 1840, 1852, 1863, 1867, 1874, 1875, 1876, 1935, 1990, 2028, 2032, 2034, 2036, 2109, 2128, 2129, 2131, 2132, 2133, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2257, 2300, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 71, 140, 175, 176, 177, 178, 182, 223, 225, 231, 233, 235, 243, 250, 271, 272, 273, 281, 285, 288, 1716, 1718, 1761, 1764, 1766, 1839, 1864, 1865, 1866, 1991, 1992, 2026, 2030, 2108, 2130, 2134, 2136, 2226, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 73, 130, 132, 140, 142, 175, 177, 179, 181, 225, 227, 230, 231, 233, 234, 235, 236, 246, 247, 248, 249, 272, 274, 281, 282, 283, 284, 285, 286, 288, 289, 290, 291, 293, 294, 295, 1716, 1760, 1761, 1762, 1765, 1838, 1839, 1840, 1863, 1864, 1865, 1874, 1875, 1876, 1935, 1990, 2026, 2030, 2034, 2108, 2109, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2222, 2223, 2226, 2257, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 72, 131, 141, 143, 176, 178, 180, 182, 221, 223, 229, 243, 244, 245, 250, 271, 273, 287, 292, 296, 1717, 1718, 1763, 1764, 1766, 1852, 1866, 1867, 1991, 1992, 2028, 2032, 2036, 2128, 2129, 2130, 2194, 2225, 2300)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 35, 152, 1653, 1654, 1655, 1692, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1774, 1825, 1898, 2054, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 148, 149, 150, 151, 1652, 1691, 1753, 1771, 1772, 1773, 1824, 1826, 1827, 1897, 1900, 2056, 2281, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 148, 149, 1652, 1654, 1655, 1691, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1824, 1825, 1827, 1897, 1898, 1900, 2058, 2179, 2227, 2229, 2231, 2281, 2282, 2289, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 33, 34, 35, 150, 151, 152, 1653, 1693, 1772, 1773, 1826, 2054, 2056, 2177, 2279, 2283, 2288, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 31, 32, 33, 34, 35, 151, 152, 1652, 1653, 1655, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1771, 1772, 1774, 1824, 1826, 1827, 1897, 2054, 2056, 2058, 2177, 2179, 2227, 2231, 2281, 2282, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 148, 149, 150, 1654, 1691, 1693, 1753, 1757, 1773, 1825, 1898, 1900, 2229, 2279, 2283, 2288, 2292)</t>
+    <t xml:space="preserve">c(32, 33, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1692, 1693, 1750, 1752, 1753, 1754, 1755, 1756, 1773, 1826, 1827, 1898, 1900, 2054, 2056, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 34, 1655, 1691, 1751, 1757, 1771, 1772, 1774, 1824, 1825, 1897, 2058, 2229, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 34, 35, 148, 152, 1652, 1654, 1691, 1692, 1693, 1750, 1752, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1826, 1827, 2054, 2056, 2177, 2179, 2227, 2229, 2282, 2283, 2288, 2289, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 32, 149, 150, 151, 1653, 1655, 1751, 1753, 1772, 1825, 1897, 1898, 1900, 2058, 2231, 2279, 2281, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 23, 31, 32, 34, 35, 148, 149, 150, 151, 1653, 1654, 1691, 1692, 1693, 1750, 1752, 1755, 1771, 1772, 1773, 1774, 1824, 1825, 1827, 1897, 1898, 2054, 2058, 2177, 2179, 2227, 2231, 2281, 2282, 2288, 2290, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 33, 152, 1652, 1655, 1751, 1753, 1754, 1756, 1757, 1826, 1900, 2056, 2229, 2279, 2283, 2289, 2293, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 222, 224, 226, 228, 275, 278, 279, 1719, 1720, 1721, 1727, 1775, 1776, 1868, 1869, 1870, 2027, 2029, 2033, 2119, 2120, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 276, 277, 280, 1722, 1777, 1778, 1779, 2035, 2037, 2121, 2124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 226, 228, 275, 276, 277, 279, 1719, 1721, 1722, 1727, 1775, 1777, 1779, 1868, 1869, 1870, 2035, 2037, 2119, 2120, 2121, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(222, 224, 278, 280, 1720, 1776, 1778, 2027, 2029, 2033, 2124, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 222, 224, 277, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1778, 1868, 1869, 2027, 2029, 2033, 2119, 2120, 2121, 2124, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 226, 228, 275, 276, 278, 1777, 1779, 1870, 2035, 2037, 2126, 2221)</t>
+    <t xml:space="preserve">c(42, 43, 44, 224, 226, 228, 275, 279, 1719, 1721, 1722, 1727, 1776, 1777, 1779, 1869, 1870, 2027, 2029, 2033, 2119, 2120, 2121, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 222, 276, 277, 278, 280, 1720, 1775, 1778, 1868, 2035, 2037, 2124, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 275, 277, 278, 1719, 1720, 1721, 1727, 1776, 1777, 1778, 1869, 1870, 2027, 2033, 2035, 2037, 2119, 2120, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 226, 228, 276, 279, 280, 1722, 1775, 1779, 1868, 2029, 2121, 2124, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 222, 224, 228, 275, 276, 278, 279, 1719, 1720, 1722, 1776, 1777, 1779, 1868, 1869, 2027, 2029, 2033, 2035, 2119, 2120, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 226, 277, 280, 1721, 1727, 1775, 1778, 1870, 2037, 2121, 2124, 2126, 2221)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 208, 209, 212, 215, 217, 220, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(207, 210, 211, 213, 214, 216, 218, 219, 265)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 205, 207, 208, 209, 210, 211, 212, 214, 215, 216, 219, 266, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 206, 213, 217, 218, 220, 265, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 205, 206, 207, 208, 209, 211, 214, 215, 216, 218, 219, 220, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 210, 212, 213, 217, 265, 266, 2232)</t>
+    <t xml:space="preserve">c(201, 202, 203, 209, 210, 212, 213, 214, 215, 216, 217, 219, 220, 265, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 206, 207, 208, 211, 218, 266, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 212, 213, 214, 217, 218, 219, 265, 266, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 208, 211, 215, 216, 220, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 210, 211, 214, 215, 216, 218, 220, 265, 267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(208, 209, 212, 213, 217, 219, 266, 268, 2230)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 132, 140, 141, 142, 175, 176, 177, 178, 179, 180, 181, 182, 223, 227, 230, 231, 233, 235, 236, 244, 246, 248, 249, 271, 272, 274, 281, 282, 284, 287, 291, 292, 295, 296, 1717, 1718, 1760, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1852, 1863, 1867, 1874, 1875, 1991, 2026, 2034, 2109, 2129, 2130, 2131, 2132, 2134, 2136, 2137, 2139, 2194, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(131, 143, 221, 225, 229, 234, 243, 245, 247, 250, 273, 283, 285, 286, 288, 289, 290, 293, 294, 1716, 1762, 1840, 1864, 1865, 1866, 1876, 1935, 1990, 1992, 2028, 2030, 2032, 2036, 2108, 2128, 2133, 2135, 2138, 2222, 2223)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 71, 72, 130, 143, 175, 176, 177, 178, 179, 180, 181, 223, 225, 227, 229, 231, 234, 235, 243, 244, 246, 248, 250, 271, 272, 273, 274, 281, 283, 284, 285, 286, 289, 290, 291, 292, 293, 296, 1716, 1717, 1761, 1762, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1874, 1875, 1876, 1935, 1992, 2026, 2028, 2030, 2036, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2138, 2139, 2194, 2225, 2226, 2257, 2300, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 70, 73, 131, 132, 140, 141, 142, 182, 221, 230, 233, 236, 245, 247, 249, 282, 287, 288, 294, 295, 1718, 1760, 1763, 1764, 1765, 1867, 1990, 1991, 2032, 2034, 2108, 2109, 2136, 2137, 2222, 2223, 2301, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 72, 131, 140, 141, 142, 175, 177, 178, 179, 181, 182, 221, 223, 229, 233, 234, 235, 236, 243, 244, 246, 247, 248, 250, 271, 272, 273, 274, 281, 282, 283, 284, 288, 289, 291, 293, 294, 296, 1717, 1718, 1760, 1761, 1764, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1875, 1876, 1935, 1991, 2026, 2028, 2032, 2034, 2036, 2108, 2109, 2129, 2130, 2132, 2133, 2134, 2138, 2139, 2194, 2223, 2225, 2226, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 71, 73, 130, 132, 143, 176, 180, 225, 227, 230, 231, 245, 249, 285, 286, 287, 290, 292, 295, 1716, 1762, 1763, 1765, 1865, 1867, 1874, 1990, 1992, 2030, 2128, 2131, 2135, 2136, 2137, 2222, 2257, 2300, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 33, 150, 151, 1653, 1654, 1655, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1772, 1773, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2229, 2231, 2279, 2282, 2283, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 32, 34, 35, 148, 149, 152, 1652, 1691, 1692, 1755, 1757, 1774, 1898, 2227, 2281, 2288, 2289, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 34, 148, 150, 151, 1654, 1655, 1691, 1692, 1693, 1751, 1754, 1771, 1772, 1773, 1774, 1825, 1826, 1900, 2054, 2056, 2058, 2177, 2227, 2229, 2231, 2279, 2282, 2283, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(33, 35, 149, 152, 1652, 1653, 1750, 1752, 1753, 1755, 1756, 1757, 1824, 1827, 1897, 1898, 2179, 2281, 2288, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 34, 148, 149, 150, 1653, 1654, 1691, 1750, 1752, 1754, 1755, 1756, 1771, 1772, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2058, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 33, 35, 151, 152, 1652, 1655, 1692, 1693, 1751, 1753, 1757, 1773, 1774, 1898, 2056, 2177, 2179, 2227, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 228, 275, 277, 279, 280, 1720, 1721, 1722, 1775, 1777, 1778, 1779, 1868, 1869, 2027, 2035, 2037, 2120, 2121, 2124, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 226, 276, 278, 1719, 1727, 1776, 1870, 2029, 2033, 2119, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 224, 226, 228, 275, 276, 278, 279, 280, 1719, 1720, 1721, 1775, 1776, 1778, 1868, 2027, 2029, 2033, 2037, 2120, 2125, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 277, 1722, 1727, 1777, 1779, 1869, 1870, 2035, 2119, 2121, 2124, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 275, 278, 280, 1720, 1722, 1776, 1778, 1779, 1868, 1870, 2033, 2035, 2037, 2119, 2120, 2121, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 276, 277, 279, 1719, 1721, 1727, 1775, 1777, 1869, 2027, 2029, 2124, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 207, 208, 210, 211, 214, 215, 217, 218, 219, 266, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 206, 209, 212, 213, 216, 220, 265, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 205, 206, 207, 211, 212, 214, 215, 216, 217, 218, 219, 220, 266, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 208, 209, 210, 213, 265, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 208, 211, 212, 215, 216, 217, 218, 265, 266, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 209, 210, 213, 214, 219, 220, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 70, 72, 73, 130, 131, 132, 140, 142, 143, 176, 177, 178, 179, 180, 181, 182, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 244, 245, 247, 249, 250, 271, 272, 274, 283, 284, 285, 287, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1765, 1766, 1838, 1839, 1852, 1863, 1864, 1867, 1874, 1875, 1876, 1991, 2028, 2034, 2109, 2128, 2129, 2131, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2226, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 71, 141, 175, 221, 243, 246, 248, 273, 281, 282, 286, 288, 289, 1760, 1761, 1762, 1763, 1764, 1840, 1865, 1866, 1935, 1990, 1992, 2026, 2030, 2032, 2036, 2108, 2130, 2132, 2225, 2257, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 70, 72, 130, 141, 143, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 233, 234, 235, 236, 244, 245, 246, 247, 249, 271, 272, 274, 281, 282, 283, 285, 286, 289, 290, 293, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1839, 1863, 1864, 1866, 1867, 1874, 1875, 1935, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2139, 2194, 2222, 2223, 2225, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 71, 73, 131, 132, 140, 142, 175, 227, 229, 230, 231, 243, 248, 250, 273, 284, 287, 288, 291, 292, 294, 295, 1718, 1765, 1766, 1838, 1840, 1852, 1865, 1876, 1990, 2108, 2109, 2128, 2129, 2138, 2226, 2257, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 72, 130, 131, 132, 141, 142, 176, 177, 178, 179, 180, 181, 225, 227, 231, 234, 235, 245, 246, 247, 248, 250, 271, 273, 281, 282, 283, 287, 288, 290, 291, 292, 294, 296, 1760, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1865, 1866, 1867, 1874, 1875, 1990, 1991, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2129, 2130, 2131, 2132, 2134, 2135, 2137, 2139, 2194, 2222, 2223, 2225, 2257, 2300, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 140, 143, 175, 182, 221, 223, 229, 230, 233, 236, 243, 244, 249, 272, 274, 284, 285, 286, 289, 293, 295, 1716, 1717, 1718, 1762, 1864, 1876, 1935, 1992, 2026, 2128, 2133, 2136, 2138, 2226, 2301, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 148, 149, 151, 152, 1652, 1654, 1655, 1692, 1693, 1750, 1751, 1752, 1753, 1756, 1757, 1771, 1772, 1824, 1825, 1826, 1897, 1898, 2058, 2179, 2229, 2231, 2281, 2282, 2288, 2289, 2290, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 34, 35, 150, 1653, 1691, 1754, 1755, 1773, 1774, 1827, 1900, 2054, 2056, 2177, 2227, 2279, 2283, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 148, 149, 151, 1652, 1653, 1655, 1691, 1692, 1752, 1753, 1754, 1756, 1771, 1773, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 31, 32, 33, 34, 35, 150, 152, 1654, 1693, 1750, 1751, 1755, 1757, 1772, 1774, 1897, 2281, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 150, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1824, 1825, 1827, 1898, 1900, 2054, 2056, 2058, 2177, 2279, 2283, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(35, 148, 149, 151, 152, 1654, 1693, 1753, 1774, 1826, 1897, 2179, 2227, 2229, 2231, 2281, 2282, 2288, 2289, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 224, 226, 228, 275, 276, 279, 280, 1719, 1721, 1722, 1775, 1778, 1779, 1869, 2027, 2029, 2035, 2037, 2119, 2120, 2124, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 277, 278, 1720, 1727, 1776, 1777, 1868, 1870, 2033, 2121, 2125, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 224, 228, 275, 276, 277, 278, 279, 280, 1719, 1721, 1722, 1776, 1777, 1778, 1870, 2027, 2029, 2033, 2120, 2121, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 226, 1720, 1727, 1775, 1779, 1868, 1869, 2035, 2037, 2119, 2124, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 222, 224, 226, 275, 277, 279, 1720, 1721, 1722, 1727, 1775, 1776, 1778, 1869, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 228, 276, 278, 280, 1719, 1777, 1779, 1868, 1870, 2124, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 209, 212, 213, 215, 216, 219, 220, 265, 266, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 207, 208, 210, 211, 214, 217, 218, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 206, 208, 209, 212, 213, 215, 217, 218, 265, 266, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 207, 210, 211, 214, 216, 219, 220, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 207, 208, 209, 210, 212, 213, 214, 215, 216, 219, 265, 266, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 205, 206, 211, 217, 218, 220, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 71, 72, 73, 130, 140, 141, 142, 176, 177, 179, 181, 182, 223, 225, 227, 229, 233, 234, 235, 236, 244, 246, 247, 248, 271, 272, 273, 274, 282, 284, 287, 289, 291, 293, 294, 295, 296, 1718, 1760, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1935, 1990, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2109, 2128, 2129, 2130, 2132, 2133, 2135, 2137, 2138, 2139, 2223, 2225, 2226, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 131, 132, 143, 175, 178, 180, 221, 230, 231, 243, 245, 249, 250, 281, 283, 285, 286, 288, 290, 292, 1716, 1717, 1761, 1865, 1867, 1874, 1875, 1876, 2030, 2108, 2131, 2134, 2136, 2194, 2222, 2257, 2300, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 70, 71, 72, 73, 130, 132, 140, 141, 142, 143, 177, 178, 179, 180, 181, 182, 221, 225, 227, 230, 231, 234, 235, 236, 245, 247, 249, 250, 271, 272, 273, 274, 281, 282, 284, 286, 287, 288, 289, 290, 291, 293, 294, 295, 1716, 1760, 1762, 1763, 1764, 1840, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1992, 2028, 2032, 2036, 2109, 2129, 2130, 2132, 2138, 2139, 2222, 2223, 2225, 2257, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 131, 175, 176, 223, 229, 233, 243, 244, 246, 248, 283, 285, 292, 296, 1717, 1718, 1761, 1765, 1766, 1838, 1839, 1852, 1863, 1935, 1991, 2026, 2030, 2034, 2108, 2128, 2131, 2133, 2134, 2135, 2136, 2137, 2194, 2226, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 71, 72, 131, 132, 140, 141, 142, 176, 177, 178, 179, 180, 181, 182, 225, 229, 230, 231, 233, 234, 235, 236, 245, 249, 250, 271, 272, 273, 282, 283, 285, 287, 291, 292, 293, 295, 296, 1718, 1760, 1762, 1764, 1765, 1838, 1840, 1863, 1864, 1865, 1867, 1874, 1875, 1876, 1935, 1991, 1992, 2028, 2032, 2034, 2036, 2108, 2109, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2194, 2222, 2223, 2226, 2257, 2300, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 130, 143, 175, 221, 223, 227, 243, 244, 246, 247, 248, 274, 281, 284, 286, 288, 289, 290, 294, 1716, 1717, 1761, 1763, 1766, 1839, 1852, 1866, 1990, 2026, 2030, 2128, 2129, 2134, 2139, 2225, 2302, 2312, 2313)</t>
+    <t xml:space="preserve">c(14, 15, 70, 72, 73, 140, 177, 178, 179, 180, 221, 225, 229, 230, 231, 233, 234, 236, 243, 244, 245, 247, 248, 250, 271, 272, 274, 281, 282, 284, 285, 286, 287, 288, 289, 291, 292, 1716, 1717, 1718, 1760, 1761, 1763, 1765, 1766, 1838, 1840, 1852, 1863, 1865, 1867, 1874, 1875, 1876, 1935, 1990, 2026, 2028, 2034, 2036, 2109, 2128, 2130, 2131, 2132, 2135, 2136, 2138, 2194, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 71, 130, 131, 132, 141, 142, 143, 175, 176, 181, 182, 223, 227, 235, 246, 249, 273, 283, 290, 293, 294, 295, 296, 1762, 1764, 1839, 1864, 1866, 1991, 1992, 2030, 2032, 2108, 2129, 2133, 2134, 2137, 2139, 2222)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 70, 71, 131, 132, 140, 141, 142, 143, 175, 176, 177, 179, 180, 181, 182, 221, 223, 227, 229, 230, 233, 236, 243, 244, 245, 246, 247, 248, 249, 271, 273, 282, 283, 286, 287, 288, 289, 290, 293, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1765, 1766, 1839, 1852, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2034, 2109, 2128, 2130, 2132, 2134, 2135, 2137, 2139, 2194, 2222, 2225, 2226, 2257, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 72, 73, 130, 178, 225, 231, 234, 235, 250, 272, 274, 281, 284, 285, 291, 292, 294, 295, 296, 1762, 1838, 1840, 1863, 1864, 1865, 1866, 2028, 2030, 2032, 2036, 2108, 2129, 2131, 2133, 2136, 2138, 2223, 2300, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 71, 73, 130, 140, 142, 143, 175, 176, 177, 178, 179, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 243, 244, 247, 249, 250, 273, 274, 281, 283, 284, 285, 286, 287, 288, 290, 291, 292, 293, 294, 296, 1717, 1760, 1761, 1762, 1763, 1764, 1766, 1838, 1839, 1840, 1852, 1863, 1867, 1874, 1876, 1935, 2026, 2036, 2128, 2129, 2131, 2132, 2133, 2134, 2136, 2139, 2194, 2225, 2226, 2257, 2300, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 131, 132, 141, 180, 234, 235, 236, 245, 246, 248, 271, 272, 282, 289, 295, 1716, 1718, 1765, 1864, 1865, 1866, 1875, 1990, 1991, 1992, 2028, 2030, 2032, 2034, 2108, 2109, 2130, 2135, 2137, 2138, 2222, 2223, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 31, 32, 33, 34, 35, 148, 151, 152, 1653, 1654, 1655, 1691, 1692, 1752, 1757, 1772, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 2056, 2058, 2177, 2179, 2227, 2231, 2281, 2282, 2288, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 149, 150, 1652, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 1771, 1827, 1900, 2054, 2229, 2279, 2283, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 31, 33, 34, 149, 150, 151, 152, 1652, 1653, 1691, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1771, 1774, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2279, 2281, 2282, 2288, 2289, 2290, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 23, 32, 35, 148, 1654, 1655, 1693, 1753, 1757, 1772, 1773, 1824, 1898, 2231, 2283, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 33, 34, 35, 149, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1751, 1752, 1753, 1755, 1756, 1824, 1825, 1826, 1898, 1900, 2056, 2179, 2227, 2229, 2231, 2279, 2283, 2288, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 148, 150, 152, 1750, 1754, 1757, 1771, 1772, 1773, 1774, 1827, 1897, 2054, 2058, 2177, 2281, 2282, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1722, 1775, 1776, 1777, 1779, 1868, 2037, 2119, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 1719, 1720, 1721, 1727, 1778, 1869, 1870, 2027, 2029, 2033, 2035, 2120)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 228, 275, 276, 278, 1720, 1721, 1722, 1727, 1775, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2033, 2124, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(226, 277, 279, 280, 1719, 1776, 2029, 2035, 2037, 2119, 2120, 2121, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 226, 228, 275, 276, 278, 280, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1870, 2027, 2029, 2033, 2035, 2119, 2120, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 222, 224, 277, 279, 1719, 1720, 1721, 1722, 1869, 2037, 2121, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 204, 205, 208, 210, 211, 213, 216, 217, 218, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 206, 207, 209, 212, 214, 215, 265)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 208, 210, 211, 212, 216, 220, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 209, 213, 214, 215, 217, 218, 219, 265)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 208, 210, 214, 215, 216, 219, 220, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 209, 211, 212, 213, 217, 218, 265, 266)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 73, 130, 140, 141, 142, 143, 176, 177, 178, 179, 181, 182, 221, 223, 227, 229, 230, 231, 234, 235, 236, 243, 244, 245, 246, 248, 249, 271, 274, 282, 283, 284, 285, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1763, 1764, 1765, 1766, 1838, 1840, 1852, 1864, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 1992, 2030, 2034, 2129, 2131, 2133, 2135, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 72, 131, 132, 175, 180, 225, 233, 247, 250, 272, 273, 281, 286, 1718, 1761, 1762, 1839, 1863, 1865, 1875, 2026, 2028, 2032, 2036, 2108, 2109, 2128, 2130, 2132, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 72, 130, 141, 142, 176, 178, 179, 181, 182, 223, 225, 229, 230, 231, 233, 235, 236, 244, 246, 247, 248, 249, 271, 272, 273, 282, 283, 284, 285, 286, 287, 288, 289, 290, 292, 293, 294, 295, 296, 1716, 1761, 1762, 1763, 1765, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1875, 1935, 1990, 2028, 2032, 2034, 2036, 2109, 2128, 2130, 2131, 2132, 2133, 2135, 2137, 2194, 2222, 2223, 2225, 2257, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 131, 132, 140, 143, 175, 177, 180, 221, 227, 234, 243, 245, 250, 274, 281, 291, 1717, 1718, 1760, 1764, 1766, 1840, 1867, 1874, 1876, 1991, 1992, 2026, 2030, 2108, 2129, 2134, 2136, 2138, 2139, 2226, 2300, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 71, 132, 140, 141, 142, 143, 175, 177, 178, 179, 182, 223, 225, 229, 230, 231, 234, 235, 236, 243, 245, 246, 247, 248, 250, 272, 273, 274, 281, 282, 283, 284, 285, 286, 288, 289, 290, 291, 292, 294, 295, 1716, 1717, 1718, 1761, 1763, 1764, 1765, 1838, 1839, 1840, 1863, 1865, 1867, 1874, 1875, 1876, 1935, 1991, 1992, 2028, 2036, 2108, 2109, 2129, 2132, 2135, 2136, 2137, 2138, 2194, 2223, 2257, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 131, 176, 180, 181, 221, 227, 233, 244, 249, 271, 287, 293, 296, 1760, 1762, 1766, 1852, 1864, 1866, 1990, 2026, 2030, 2032, 2034, 2128, 2130, 2131, 2133, 2134, 2139, 2222, 2225, 2226, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 32, 33, 34, 35, 148, 149, 150, 152, 1653, 1654, 1691, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1772, 1774, 1826, 1827, 1897, 1898, 1900, 2056, 2058, 2179, 2227, 2229, 2282, 2288, 2289, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 31, 151, 1652, 1655, 1693, 1757, 1773, 1824, 1825, 2054, 2177, 2231, 2279, 2281, 2283, 2290, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 34, 35, 148, 150, 151, 152, 1652, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1774, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2056, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 31, 32, 33, 149, 1653, 1654, 1655, 1691, 1755, 1757, 1772, 1773, 1897, 2058, 2177, 2179, 2229, 2283, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1752, 1757, 1771, 1824, 1826, 1897, 1898, 1900, 2056, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 23, 1693, 1751, 1753, 1754, 1755, 1756, 1772, 1773, 1774, 1825, 1827, 2054, 2058, 2177, 2229, 2289, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 275, 277, 278, 279, 1721, 1722, 1776, 1778, 1779, 1869, 1870, 2027, 2033, 2035, 2119, 2120, 2121, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 276, 280, 1719, 1720, 1727, 1775, 1777, 1868, 2029, 2037, 2124, 2125, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 224, 228, 275, 276, 278, 279, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1778, 1869, 1870, 2037, 2119, 2121, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 222, 226, 277, 1722, 1777, 1779, 1868, 2027, 2029, 2033, 2035, 2120, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 228, 276, 277, 278, 280, 1719, 1720, 1721, 1722, 1775, 1776, 1777, 1779, 1868, 1869, 1870, 2027, 2029, 2035, 2037, 2119, 2120, 2124, 2125, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 275, 279, 1727, 1778, 2033, 2121, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 205, 208, 209, 210, 211, 213, 215, 216, 217, 219, 220, 265, 266, 267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 206, 207, 212, 214, 218, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 208, 209, 211, 213, 215, 216, 219, 220, 266, 267, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(205, 210, 212, 214, 217, 218, 265, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 206, 207, 208, 209, 210, 211, 214, 215, 216, 217, 219, 220, 265, 266, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 212, 213, 218, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 70, 71, 72, 130, 132, 140, 141, 142, 175, 176, 177, 178, 179, 180, 181, 182, 221, 227, 229, 230, 243, 244, 246, 247, 248, 249, 250, 271, 272, 273, 274, 282, 283, 284, 285, 286, 288, 289, 290, 291, 292, 294, 296, 1716, 1717, 1718, 1761, 1762, 1763, 1764, 1765, 1839, 1852, 1863, 1865, 1866, 1875, 1876, 1935, 1992, 2026, 2028, 2030, 2032, 2034, 2130, 2131, 2132, 2134, 2135, 2139, 2194, 2225, 2226, 2257, 2300, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 73, 131, 143, 223, 225, 231, 233, 234, 235, 236, 245, 281, 287, 293, 295, 1760, 1766, 1838, 1840, 1864, 1867, 1874, 1990, 1991, 2036, 2108, 2109, 2128, 2129, 2133, 2136, 2137, 2138, 2222, 2223, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 71, 73, 140, 142, 143, 175, 176, 178, 179, 180, 182, 221, 225, 227, 231, 234, 236, 244, 245, 246, 249, 250, 271, 272, 281, 282, 283, 286, 287, 289, 290, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1765, 1766, 1838, 1839, 1840, 1864, 1865, 1866, 1867, 1874, 1876, 1935, 1992, 2026, 2028, 2030, 2034, 2036, 2108, 2128, 2129, 2130, 2131, 2133, 2134, 2135, 2136, 2138, 2139, 2194, 2223, 2226, 2257, 2300, 2301, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 72, 130, 131, 132, 141, 177, 181, 223, 229, 230, 233, 235, 243, 247, 248, 273, 274, 284, 285, 288, 291, 292, 293, 1717, 1764, 1852, 1863, 1875, 1990, 1991, 2032, 2109, 2132, 2137, 2222, 2225, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 73, 130, 131, 132, 143, 175, 179, 181, 182, 221, 223, 225, 227, 230, 231, 234, 235, 243, 245, 246, 247, 248, 249, 250, 271, 273, 274, 283, 285, 286, 290, 292, 293, 294, 296, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1766, 1838, 1839, 1840, 1852, 1863, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1992, 2028, 2030, 2034, 2128, 2131, 2132, 2133, 2134, 2138, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 70, 72, 140, 141, 142, 176, 177, 178, 180, 229, 233, 236, 244, 272, 281, 282, 284, 287, 288, 289, 291, 295, 1762, 1765, 1864, 1935, 1991, 2026, 2032, 2036, 2108, 2109, 2129, 2130, 2135, 2136, 2137, 2139, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(19, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1655, 1691, 1692, 1752, 1753, 1756, 1757, 1771, 1772, 1774, 1824, 1897, 1898, 1900, 2054, 2056, 2177, 2179, 2227, 2231, 2279, 2281, 2288, 2289, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 1653, 1654, 1693, 1750, 1751, 1754, 1755, 1773, 1825, 1826, 1827, 2058, 2229, 2282, 2283, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 32, 33, 34, 148, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1751, 1752, 1753, 1754, 1755, 1772, 1773, 1824, 1826, 1827, 1897, 1900, 2177, 2179, 2229, 2279, 2281, 2282, 2283, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 31, 35, 149, 1750, 1756, 1757, 1771, 1774, 1825, 1898, 2054, 2056, 2058, 2227, 2231, 2288, 2289, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 148, 149, 150, 151, 1652, 1654, 1655, 1692, 1693, 1751, 1752, 1754, 1755, 1771, 1773, 1774, 1900, 2056, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(35, 152, 1653, 1691, 1750, 1753, 1756, 1757, 1772, 1824, 1825, 1826, 1827, 1897, 1898, 2054, 2058, 2229, 2283, 2295)</t>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 1652, 1653, 1691, 1692, 1693, 1752, 1754, 1755, 1757, 1771, 1773, 1774, 1827, 1898, 2058, 2177, 2179, 2227, 2229, 2231, 2281, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 151, 152, 1654, 1655, 1750, 1751, 1753, 1756, 1772, 1824, 1825, 1826, 1897, 1900, 2054, 2056, 2279, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 150, 151, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1772, 1826, 1827, 1897, 1900, 2058, 2177, 2229, 2279, 2282, 2283, 2288, 2289, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(149, 152, 1652, 1654, 1693, 1753, 1771, 1773, 1774, 1824, 1825, 1898, 2054, 2056, 2179, 2227, 2231, 2281, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 34, 148, 149, 150, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1757, 1774, 1824, 1825, 1826, 1897, 1898, 2056, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(33, 35, 151, 152, 1653, 1753, 1755, 1756, 1771, 1772, 1773, 1827, 1900, 2054, 2058, 2229, 2289, 2290, 2293, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 44, 222, 224, 226, 275, 277, 279, 280, 1720, 1722, 1727, 1779, 1868, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 228, 276, 278, 1719, 1721, 1775, 1776, 1777, 1778, 1869, 2120, 2121)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 222, 224, 228, 277, 279, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1869, 1870, 2029, 2033, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 226, 275, 276, 278, 280, 1719, 1720, 1722, 1868, 2027, 2035, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 222, 224, 277, 279, 280, 1720, 1722, 1727, 1775, 1776, 1777, 1779, 1869, 1870, 2027, 2029, 2035, 2037, 2119, 2120, 2121, 2124, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 226, 228, 275, 276, 278, 1719, 1721, 1778, 1868, 2033, 2125, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 206, 207, 208, 209, 211, 212, 213, 216, 217, 219, 220, 265, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 210, 214, 215, 218, 266, 267, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 205, 206, 208, 209, 210, 211, 214, 215, 216, 217, 218, 265, 266, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 207, 212, 213, 219, 220, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 208, 209, 210, 211, 212, 214, 215, 218, 220, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 213, 216, 217, 219, 265, 266, 267, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 71, 73, 130, 131, 132, 141, 176, 177, 179, 181, 182, 221, 223, 225, 227, 229, 231, 233, 234, 235, 236, 243, 246, 247, 248, 250, 271, 273, 281, 284, 286, 287, 288, 289, 290, 292, 293, 294, 295, 296, 1760, 1761, 1763, 1764, 1765, 1766, 1863, 1865, 1866, 1874, 1875, 1876, 1991, 1992, 2026, 2032, 2034, 2036, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2194, 2226, 2257, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 72, 140, 142, 143, 175, 178, 180, 230, 244, 245, 249, 272, 274, 282, 283, 285, 291, 1716, 1717, 1718, 1762, 1838, 1839, 1840, 1852, 1864, 1867, 1935, 1990, 2028, 2030, 2108, 2131, 2136, 2222, 2223, 2225, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 71, 73, 130, 131, 132, 140, 141, 143, 175, 176, 177, 179, 180, 181, 182, 225, 229, 230, 231, 236, 243, 245, 246, 247, 248, 249, 250, 271, 272, 273, 281, 282, 283, 284, 286, 287, 288, 289, 290, 291, 295, 296, 1718, 1761, 1762, 1763, 1765, 1766, 1838, 1852, 1863, 1864, 1866, 1867, 1874, 1875, 1935, 1990, 2028, 2030, 2032, 2034, 2129, 2131, 2133, 2134, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 72, 142, 178, 221, 223, 227, 233, 234, 235, 244, 274, 285, 292, 293, 294, 1716, 1717, 1760, 1764, 1839, 1840, 1865, 1876, 1991, 1992, 2026, 2036, 2108, 2109, 2128, 2130, 2132, 2135, 2136, 2222, 2257, 2300, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 131, 132, 140, 141, 143, 177, 181, 182, 223, 225, 229, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 273, 274, 281, 283, 284, 286, 287, 288, 290, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1763, 1764, 1765, 1838, 1852, 1864, 1866, 1867, 1874, 1875, 1990, 1992, 2026, 2028, 2032, 2034, 2036, 2109, 2131, 2132, 2133, 2137, 2138, 2139, 2222, 2223, 2225, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 130, 142, 175, 176, 178, 179, 180, 221, 227, 230, 231, 233, 234, 272, 282, 285, 289, 291, 292, 1716, 1762, 1766, 1839, 1840, 1863, 1865, 1876, 1935, 1991, 2030, 2108, 2128, 2129, 2130, 2134, 2135, 2136, 2194, 2226)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 31, 32, 33, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1692, 1693, 1750, 1751, 1753, 1755, 1756, 1771, 1773, 1824, 1825, 1897, 1900, 2054, 2058, 2177, 2179, 2227, 2229, 2279, 2281, 2282, 2288, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 34, 35, 1653, 1691, 1752, 1754, 1757, 1772, 1774, 1826, 1827, 1898, 2056, 2231, 2283, 2289, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 34, 149, 150, 151, 1654, 1655, 1691, 1750, 1751, 1753, 1754, 1755, 1772, 1773, 1824, 1826, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 33, 35, 148, 152, 1652, 1653, 1692, 1693, 1752, 1756, 1757, 1771, 1774, 1825, 1827, 2179, 2229, 2283, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 31, 33, 34, 35, 148, 150, 151, 152, 1654, 1655, 1692, 1693, 1751, 1752, 1753, 1754, 1755, 1757, 1772, 1824, 1825, 1827, 1897, 1898, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 23, 32, 149, 1652, 1653, 1691, 1750, 1756, 1771, 1773, 1774, 1826, 1900, 2054, 2056, 2058, 2281, 2289, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 226, 228, 275, 277, 278, 280, 1719, 1720, 1722, 1776, 1777, 1778, 1870, 2029, 2033, 2035, 2037, 2121, 2124, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 276, 279, 1721, 1727, 1775, 1779, 1868, 1869, 2027, 2119, 2120, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 222, 224, 275, 276, 277, 278, 279, 280, 1719, 1721, 1722, 1727, 1775, 1777, 1778, 1779, 1869, 1870, 2037, 2119, 2120, 2121, 2124, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 226, 228, 1720, 1776, 1868, 2027, 2029, 2033, 2035, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 226, 275, 277, 280, 1719, 1720, 1721, 1775, 1778, 1779, 1868, 1869, 1870, 2029, 2033, 2037, 2119, 2120, 2124, 2125, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(224, 228, 276, 278, 279, 1722, 1727, 1776, 1777, 2027, 2035, 2121, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 207, 210, 211, 212, 213, 214, 215, 217, 218, 219, 220, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 206, 208, 209, 216, 265, 266, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 205, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 219, 220, 266, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 206, 218, 265, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 209, 212, 213, 215, 216, 217, 220, 266, 267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 208, 210, 211, 214, 218, 219, 265, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 140, 141, 143, 175, 176, 177, 178, 180, 181, 182, 221, 223, 227, 230, 231, 233, 236, 243, 246, 247, 248, 249, 271, 272, 273, 281, 284, 286, 287, 290, 293, 294, 296, 1717, 1718, 1761, 1762, 1763, 1765, 1766, 1839, 1864, 1874, 1876, 1935, 1991, 1992, 2026, 2028, 2030, 2034, 2036, 2108, 2109, 2128, 2130, 2131, 2132, 2133, 2134, 2135, 2137, 2138, 2139, 2222, 2223, 2225, 2257, 2301, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 142, 179, 225, 229, 234, 235, 244, 245, 250, 274, 282, 283, 285, 288, 289, 291, 292, 295, 1716, 1760, 1764, 1838, 1840, 1852, 1863, 1865, 1866, 1867, 1875, 1990, 2032, 2129, 2136, 2194, 2226, 2300, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 71, 73, 132, 140, 142, 143, 175, 176, 182, 221, 223, 225, 227, 229, 231, 233, 236, 243, 246, 247, 248, 249, 250, 271, 273, 274, 281, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 293, 295, 1716, 1718, 1761, 1762, 1763, 1765, 1766, 1840, 1852, 1864, 1865, 1867, 1875, 1876, 1935, 1990, 2026, 2028, 2030, 2034, 2108, 2109, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2226, 2257, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 72, 130, 131, 141, 177, 178, 179, 180, 181, 230, 234, 235, 244, 245, 272, 285, 294, 296, 1717, 1760, 1764, 1838, 1839, 1863, 1866, 1874, 1991, 1992, 2032, 2036, 2128, 2223, 2225, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 131, 132, 140, 142, 175, 178, 179, 182, 223, 225, 229, 231, 233, 234, 235, 236, 244, 245, 246, 247, 248, 249, 271, 281, 284, 285, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1761, 1763, 1764, 1765, 1766, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 2026, 2028, 2030, 2036, 2128, 2129, 2131, 2133, 2135, 2136, 2137, 2138, 2194, 2223, 2225, 2300, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 141, 143, 176, 177, 180, 181, 221, 227, 230, 243, 250, 272, 273, 274, 282, 283, 286, 287, 1718, 1762, 1838, 1839, 1875, 1992, 2032, 2034, 2108, 2109, 2130, 2132, 2134, 2139, 2222, 2226, 2257, 2301, 2302, 2303, 2313)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 226, 228, 275, 276, 277, 278, 279, 280, 1721, 1722, 1727, 1775, 1869, 1870, 2029, 2035, 2037, 2121, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(222, 224, 1719, 1720, 1776, 1777, 1778, 1779, 1868, 2027, 2033, 2119, 2120, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 228, 275, 276, 277, 279, 1719, 1727, 1776, 1777, 1778, 1779, 1869, 1870, 2027, 2029, 2035, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 224, 226, 278, 280, 1720, 1721, 1722, 1775, 1868, 2033, 2037, 2119, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 226, 228, 275, 276, 279, 280, 1719, 1720, 1721, 1722, 1775, 1777, 1778, 1779, 1868, 1869, 2027, 2029, 2033, 2035, 2037, 2119, 2124, 2125, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 277, 278, 1727, 1776, 1870, 2120, 2121, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 207, 208, 209, 210, 211, 212, 213, 214, 216, 217, 218, 219, 220, 265, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 205, 206, 215, 266, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 210, 213, 214, 215, 216, 218, 219, 220, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 208, 209, 211, 212, 217, 265, 266, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 205, 206, 207, 209, 210, 211, 212, 215, 217, 219, 220, 265, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 208, 213, 214, 216, 218, 266, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 71, 72, 130, 140, 141, 143, 175, 177, 178, 179, 180, 181, 182, 221, 223, 227, 229, 230, 231, 234, 236, 243, 245, 246, 247, 249, 250, 271, 272, 273, 281, 283, 284, 285, 286, 288, 290, 292, 293, 294, 295, 296, 1717, 1760, 1763, 1766, 1839, 1840, 1863, 1864, 1866, 1874, 1990, 1991, 1992, 2026, 2028, 2034, 2036, 2108, 2128, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2138, 2139, 2194, 2226, 2257, 2300, 2301, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 73, 131, 132, 142, 176, 225, 233, 235, 244, 248, 274, 282, 287, 289, 291, 1716, 1718, 1761, 1762, 1764, 1765, 1838, 1852, 1865, 1867, 1875, 1876, 1935, 2030, 2032, 2109, 2129, 2137, 2222, 2223, 2225, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 72, 130, 131, 132, 140, 176, 177, 179, 180, 182, 223, 227, 230, 234, 236, 243, 244, 247, 248, 249, 272, 273, 281, 282, 283, 285, 286, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1764, 1766, 1838, 1840, 1852, 1864, 1865, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2130, 2131, 2133, 2134, 2135, 2137, 2139, 2194, 2222, 2257, 2300, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 141, 142, 143, 175, 178, 181, 221, 225, 229, 231, 233, 235, 245, 246, 250, 271, 274, 284, 287, 1761, 1765, 1839, 1863, 1875, 2034, 2036, 2108, 2109, 2128, 2129, 2132, 2136, 2138, 2223, 2225, 2226, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 72, 73, 130, 132, 141, 142, 175, 177, 178, 182, 221, 223, 225, 229, 230, 231, 233, 234, 235, 243, 244, 245, 249, 274, 281, 283, 285, 286, 287, 288, 289, 292, 293, 294, 295, 296, 1716, 1760, 1761, 1764, 1766, 1838, 1839, 1852, 1863, 1865, 1867, 1935, 1990, 1992, 2028, 2030, 2032, 2036, 2108, 2109, 2128, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2138, 2194, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 131, 140, 143, 176, 179, 180, 181, 227, 236, 246, 247, 248, 250, 271, 272, 273, 282, 284, 290, 291, 1717, 1718, 1762, 1763, 1765, 1840, 1864, 1866, 1874, 1875, 1876, 1991, 2026, 2034, 2129, 2137, 2139, 2223, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 31, 32, 33, 34, 35, 148, 149, 152, 1652, 1654, 1693, 1752, 1753, 1754, 1755, 1756, 1771, 1772, 1774, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 23, 150, 151, 1653, 1655, 1691, 1692, 1750, 1751, 1757, 1773, 1898, 2056, 2058, 2177, 2281, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 32, 33, 34, 35, 150, 1652, 1653, 1654, 1655, 1691, 1751, 1752, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 1827, 1897, 1900, 2058, 2177, 2179, 2227, 2279, 2281, 2282, 2288, 2289, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 31, 148, 149, 151, 152, 1692, 1693, 1750, 1754, 1825, 1898, 2054, 2056, 2229, 2231, 2283, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 33, 34, 148, 149, 150, 151, 1652, 1654, 1691, 1692, 1693, 1751, 1752, 1753, 1757, 1771, 1773, 1774, 1825, 1827, 1897, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 31, 32, 35, 152, 1653, 1655, 1750, 1754, 1755, 1756, 1772, 1824, 1826, 2054, 2179, 2281, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 222, 224, 226, 275, 276, 277, 278, 279, 280, 1721, 1722, 1727, 1777, 1778, 1779, 1870, 2033, 2035, 2037, 2119, 2121, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 228, 1719, 1720, 1775, 1776, 1868, 1869, 2027, 2029, 2120, 2124, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 222, 226, 276, 277, 278, 1719, 1727, 1776, 1777, 1778, 1868, 1869, 2027, 2029, 2033, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 224, 228, 275, 279, 280, 1720, 1721, 1722, 1775, 1779, 1870, 2035, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 276, 277, 278, 279, 280, 1720, 1721, 1722, 1775, 1776, 1868, 2029, 2033, 2035, 2119, 2120, 2121, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 228, 275, 1719, 1727, 1777, 1778, 1779, 1869, 1870, 2027, 2037, 2124, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 208, 209, 211, 213, 217, 218, 220, 266, 267, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(207, 210, 212, 214, 215, 216, 219, 265, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 206, 208, 212, 213, 215, 216, 217, 218, 219, 220, 266, 267, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 207, 209, 210, 211, 214, 265, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 205, 206, 208, 209, 210, 211, 214, 215, 219, 265, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 207, 212, 213, 216, 217, 218, 220)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 130, 131, 132, 140, 142, 176, 177, 178, 179, 181, 182, 221, 230, 231, 233, 235, 236, 243, 244, 245, 246, 247, 248, 249, 271, 273, 274, 281, 283, 286, 289, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1765, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1875, 1876, 1935, 1990, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2129, 2131, 2132, 2133, 2135, 2136, 2194, 2223, 2225, 2300, 2301, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 72, 73, 141, 143, 175, 180, 223, 225, 227, 229, 234, 250, 272, 282, 284, 285, 287, 288, 290, 291, 1764, 1766, 1838, 1840, 1874, 1991, 1992, 2128, 2130, 2134, 2137, 2138, 2139, 2222, 2226, 2257, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 71, 72, 73, 131, 132, 140, 141, 142, 176, 177, 178, 179, 180, 182, 221, 225, 227, 229, 231, 235, 236, 243, 244, 245, 246, 248, 271, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 292, 293, 294, 296, 1717, 1718, 1761, 1762, 1763, 1764, 1765, 1840, 1852, 1865, 1874, 1875, 1876, 1990, 1991, 1992, 2028, 2030, 2032, 2034, 2108, 2131, 2132, 2133, 2135, 2137, 2138, 2222, 2223, 2226, 2257, 2300, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 130, 143, 175, 181, 223, 230, 233, 234, 247, 249, 250, 272, 290, 291, 295, 1716, 1760, 1766, 1838, 1839, 1863, 1864, 1866, 1867, 1935, 2026, 2036, 2109, 2128, 2129, 2130, 2134, 2136, 2139, 2194, 2225, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 72, 130, 131, 132, 140, 141, 175, 176, 177, 179, 180, 182, 223, 229, 230, 234, 236, 243, 244, 245, 247, 248, 250, 271, 273, 274, 281, 282, 285, 286, 288, 289, 291, 294, 296, 1716, 1717, 1718, 1760, 1762, 1764, 1766, 1839, 1852, 1863, 1865, 1866, 1867, 1875, 1876, 2026, 2030, 2032, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2194, 2222, 2223, 2225, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 142, 143, 178, 181, 221, 225, 227, 231, 233, 235, 246, 249, 272, 283, 284, 287, 290, 292, 293, 295, 1761, 1763, 1765, 1838, 1840, 1864, 1874, 1935, 1990, 1991, 1992, 2028, 2034, 2036, 2137, 2138, 2139, 2226)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 34, 35, 149, 151, 152, 1652, 1653, 1693, 1750, 1751, 1752, 1753, 1756, 1757, 1774, 1824, 1825, 1827, 1897, 1898, 2054, 2058, 2177, 2179, 2227, 2229, 2281, 2283, 2288, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(31, 148, 150, 1654, 1655, 1691, 1692, 1754, 1755, 1771, 1772, 1773, 1826, 1900, 2056, 2231, 2279, 2282, 2289, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 34, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1691, 1692, 1752, 1757, 1771, 1773, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2177, 2179, 2227, 2229, 2281, 2282, 2283, 2289, 2290, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 33, 35, 1653, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 1772, 1774, 1824, 2058, 2231, 2279, 2288, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 32, 34, 35, 148, 149, 151, 152, 1652, 1653, 1655, 1691, 1693, 1750, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1898, 2054, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 33, 150, 1654, 1692, 1751, 1752, 1772, 1825, 1826, 1827, 1897, 1900, 2056, 2282, 2283)</t>
+    <t xml:space="preserve">c(18, 20, 32, 33, 148, 149, 150, 151, 152, 1653, 1654, 1692, 1750, 1751, 1754, 1755, 1756, 1757, 1771, 1772, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2179, 2227, 2229, 2231, 2279, 2288, 2289, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 31, 34, 35, 1652, 1655, 1691, 1693, 1752, 1753, 1773, 1774, 2177, 2281, 2282, 2283, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 1653, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1825, 2054, 2056, 2179, 2227, 2229, 2231, 2288, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(152, 1652, 1692, 1772, 1826, 1827, 1897, 1898, 1900, 2058, 2177, 2279, 2281, 2282, 2283, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 33, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1754, 1757, 1771, 1772, 1824, 1826, 1827, 1900, 2056, 2058, 2177, 2179, 2227, 2231, 2279, 2281, 2283, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 34, 35, 1751, 1752, 1753, 1755, 1756, 1773, 1774, 1825, 1897, 1898, 2054, 2229, 2282, 2288, 2289, 2292, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 43, 44, 1720, 1722, 1775, 1776, 1779, 1869, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 1719, 1721, 1727, 1777, 1778, 1868)</t>
+    <t xml:space="preserve">c(43, 1719, 1721, 1722, 1727, 1775, 1776, 1777, 1779, 1869, 1870, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 1720, 1778, 1868, 2027)</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(43, 1719, 1721, 1722, 1727, 1775, 1777, 1779, 1868, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 1720, 1776, 1778, 1869)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 1719, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1720, 1721, 1868, 1869, 1870, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 210, 212, 213, 214, 216, 217, 218, 220, 266, 267, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 207, 211, 215, 219, 265, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 208, 209, 210, 212, 213, 214, 215, 217, 220, 266, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 206, 207, 211, 216, 218, 219, 265, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 209, 210, 211, 213, 217, 218, 219, 220, 265, 266, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 208, 212, 214, 215, 216, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 131, 132, 140, 141, 177, 230, 231, 233, 234, 235, 281, 283, 284, 285, 286, 290, 291, 293, 294, 295, 296, 1716, 1717, 1718, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1992, 2026, 2030, 2108, 2137, 2138, 2139, 2194, 2223, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 130, 142, 143, 229, 236, 282, 287, 288, 289, 292, 1764, 1865, 1935, 1990, 1991, 2109, 2222, 2225, 2226, 2300, 2301, 2302, 2312)</t>
+    <t xml:space="preserve">c(43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1779, 1868, 1869, 2027, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 1776, 1777, 1778, 1870, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 1719, 1720, 1721, 1776, 1778, 1868, 1869, 1870, 2027, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 1722, 1727, 1775, 1777, 1779, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 207, 208, 210, 211, 214, 215, 218, 219, 220, 265, 266, 267, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 206, 209, 212, 213, 216, 217, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 206, 207, 208, 209, 210, 216, 217, 220, 265, 266, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 211, 212, 213, 214, 215, 218, 219, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 207, 209, 212, 214, 215, 216, 217, 218, 219, 220, 265, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 205, 206, 208, 210, 211, 213, 266)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 130, 140, 141, 143, 231, 233, 234, 235, 236, 282, 283, 284, 285, 287, 290, 293, 294, 295, 296, 1717, 1718, 1764, 1766, 1838, 1852, 1863, 1864, 1990, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2222, 2223, 2225, 2226, 2300, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 131, 132, 142, 177, 229, 230, 281, 286, 288, 289, 291, 292, 1716, 1765, 1839, 1840, 1865, 1935, 1991, 2194, 2302, 2303)</t>
   </si>
   <si>
     <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 141, 143, 177, 229, 230, 231, 233, 234, 235, 236, 282, 283, 284, 286, 288, 291, 292, 295, 296, 1716, 1717, 1718, 1765, 1838, 1840, 1863, 1935, 1990, 1992, 2109, 2137, 2138, 2139, 2222, 2223, 2225, 2226, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 140, 142, 281, 285, 287, 289, 290, 293, 294, 1764, 1766, 1839, 1852, 1864, 1865, 1991, 2026, 2030, 2108, 2194, 2300, 2301, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 131, 132, 140, 142, 229, 231, 233, 234, 236, 281, 283, 285, 286, 288, 289, 291, 292, 295, 296, 1716, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1865, 1990, 1991, 2026, 2030, 2108, 2109, 2137, 2139, 2194, 2222, 2225, 2226, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 130, 141, 143, 177, 230, 235, 282, 284, 287, 290, 293, 294, 1717, 1718, 1852, 1864, 1935, 1992, 2138, 2223, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 149, 150, 152, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1772, 1773, 1774, 1825, 1827, 1897, 2054, 2056, 2177, 2179, 2227, 2229, 2231, 2283, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 34, 35, 148, 151, 1654, 1693, 1757, 1824, 1826, 1898, 1900, 2058, 2279, 2281, 2282, 2288, 2289, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 34, 148, 149, 150, 152, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 1757, 1773, 1774, 1824, 1827, 1897, 2056, 2058, 2177, 2179, 2227, 2229, 2281, 2282, 2283, 2288, 2289, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 32, 33, 35, 151, 1652, 1751, 1755, 1771, 1772, 1825, 1826, 1898, 1900, 2054, 2231, 2279, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 150, 152, 1652, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1774, 1824, 1827, 1898, 1900, 2054, 2058, 2179, 2227, 2231, 2279, 2281, 2282, 2288, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 33, 34, 35, 148, 149, 151, 1654, 1693, 1773, 1825, 1826, 1897, 2056, 2177, 2229, 2283, 2289, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 1720, 1721, 1722, 1727, 1776, 1868, 1869, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 1719, 1775, 1777, 1778, 1779)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 1721, 1722, 1727, 1776, 1777, 1778, 1779, 1870, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 1719, 1720, 1775, 1868, 1869, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 1719, 1721, 1727, 1775, 1776, 1777, 1779, 1868, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 1720, 1722, 1778, 1869, 1870)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 205, 206, 207, 208, 210, 211, 214, 216, 217, 218, 219, 265, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 209, 212, 213, 215, 220, 266, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 208, 209, 210, 213, 214, 215, 216, 218, 219, 265, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 207, 211, 212, 217, 220, 266, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 209, 210, 212, 213, 214, 215, 216, 220, 265, 266, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 207, 208, 211, 217, 218, 219, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 130, 132, 140, 141, 142, 177, 230, 231, 233, 234, 286, 288, 289, 290, 291, 292, 293, 294, 295, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1852, 1863, 1864, 1935, 1990, 1991, 2026, 2030, 2108, 2109, 2138, 2139, 2194, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 131, 143, 229, 235, 236, 281, 282, 283, 284, 285, 287, 296, 1840, 1865, 1992, 2137, 2222, 2223, 2225, 2226, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 130, 131, 132, 142, 177, 229, 230, 236, 281, 283, 284, 286, 287, 288, 289, 290, 292, 293, 295, 296, 1717, 1718, 1766, 1838, 1839, 1840, 1852, 1863, 1865, 1935, 1990, 1992, 2026, 2030, 2108, 2138, 2194, 2225, 2226, 2300, 2301, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 140, 141, 143, 231, 233, 234, 235, 282, 285, 291, 294, 1716, 1764, 1765, 1864, 1991, 2109, 2137, 2139, 2222, 2223, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 131, 132, 140, 141, 142, 177, 229, 233, 234, 236, 281, 282, 283, 284, 285, 286, 287, 290, 291, 292, 295, 296, 1716, 1717, 1765, 1838, 1839, 1840, 1865, 1935, 1991, 1992, 2030, 2108, 2109, 2138, 2139, 2223, 2225, 2226, 2300, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 130, 143, 230, 231, 235, 288, 289, 293, 294, 1718, 1764, 1766, 1852, 1863, 1864, 1990, 2026, 2137, 2194, 2222, 2301, 2312)</t>
+    <t xml:space="preserve">c(70, 72, 73, 130, 131, 140, 141, 229, 233, 236, 281, 282, 283, 284, 285, 286, 288, 291, 293, 294, 296, 1717, 1718, 1764, 1765, 1766, 1838, 1840, 1852, 1863, 1864, 1935, 1991, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2226, 2300, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 132, 142, 143, 177, 230, 231, 234, 235, 287, 289, 290, 292, 295, 1716, 1839, 1865, 1990, 1992, 2223, 2225, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 130, 131, 140, 230, 231, 233, 234, 235, 236, 282, 286, 289, 290, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1840, 1852, 1864, 1865, 1990, 1991, 1992, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2226, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 132, 141, 142, 143, 177, 229, 281, 283, 284, 285, 287, 288, 291, 292, 293, 1839, 1863, 1935, 2026, 2223, 2225, 2300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 31, 33, 34, 35, 149, 151, 152, 1652, 1653, 1654, 1655, 1692, 1693, 1752, 1753, 1754, 1755, 1757, 1771, 1772, 1773, 1824, 1825, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2279, 2282, 2283, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 32, 148, 150, 1691, 1750, 1751, 1756, 1774, 1826, 1898, 2229, 2231, 2281, 2288, 2289, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 149, 150, 151, 1654, 1655, 1691, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1774, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2058, 2179, 2227, 2229, 2279, 2281, 2289, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 35, 148, 152, 1652, 1653, 1692, 1693, 1750, 1773, 1897, 2056, 2177, 2231, 2282, 2283, 2288, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 23, 31, 33, 34, 35, 148, 149, 151, 152, 1652, 1653, 1654, 1655, 1692, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1824, 1826, 1827, 2054, 2177, 2227, 2229, 2231, 2281, 2282, 2288, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 32, 150, 1691, 1752, 1772, 1774, 1825, 1897, 1898, 1900, 2056, 2058, 2179, 2279, 2283, 2289, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 1721, 1727, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 1719, 1720, 1722, 1775, 1776, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 1719, 1720, 1721, 1722, 1727, 1777, 1778, 1779, 1869, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 1775, 1776, 1868, 1870, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 1719, 1720, 1721, 1722, 1777, 1779, 1869, 1870, 2027, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 1727, 1775, 1776, 1778, 1868)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 218, 220, 266, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 216, 217, 219, 265, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 210, 212, 214, 215, 218, 219, 220, 265, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 208, 209, 211, 213, 216, 217, 266, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 205, 206, 207, 211, 213, 214, 215, 216, 217, 218, 219, 220, 265, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 208, 209, 210, 212, 266, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 142, 143, 177, 229, 230, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 290, 291, 294, 295, 1716, 1717, 1718, 1764, 1766, 1852, 1865, 1990, 1992, 2108, 2138, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(132, 140, 141, 231, 288, 289, 292, 293, 296, 1765, 1838, 1839, 1840, 1863, 1864, 1935, 1991, 2026, 2030, 2109, 2137, 2139, 2194, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 130, 131, 132, 140, 141, 177, 229, 230, 231, 233, 234, 281, 284, 287, 288, 290, 292, 294, 296, 1716, 1764, 1766, 1839, 1840, 1935, 1990, 1992, 2030, 2108, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 142, 143, 235, 236, 282, 283, 285, 286, 289, 291, 293, 295, 1717, 1718, 1765, 1838, 1852, 1863, 1864, 1865, 1991, 2026, 2109)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 130, 132, 141, 142, 143, 229, 231, 233, 234, 235, 281, 282, 283, 284, 286, 287, 288, 290, 291, 292, 293, 294, 296, 1716, 1717, 1718, 1838, 1839, 1840, 1864, 1935, 1990, 1991, 1992, 2108, 2137, 2138, 2139, 2225, 2226, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 131, 140, 177, 230, 236, 285, 289, 295, 1764, 1765, 1766, 1852, 1863, 1865, 2026, 2030, 2109, 2194, 2222, 2223, 2300, 2302, 2303)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 35, 148, 149, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1755, 1757, 1771, 1772, 1826, 1827, 1898, 2056, 2179, 2227, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 34, 150, 151, 152, 1653, 1753, 1754, 1756, 1773, 1774, 1824, 1825, 1897, 1900, 2054, 2058, 2177, 2229, 2281)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 32, 33, 35, 148, 149, 150, 151, 1653, 1655, 1691, 1692, 1693, 1750, 1752, 1754, 1772, 1773, 1774, 1824, 1827, 1897, 1900, 2054, 2056, 2058, 2179, 2227, 2231, 2281, 2282, 2283, 2288, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 34, 152, 1652, 1654, 1751, 1753, 1755, 1756, 1757, 1771, 1825, 1826, 1898, 2177, 2229, 2279, 2289, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 31, 32, 33, 35, 148, 150, 151, 152, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1826, 1827, 1897, 1900, 2054, 2056, 2058, 2227, 2231, 2279, 2289, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 34, 149, 1652, 1653, 1654, 1655, 1692, 1772, 1825, 1898, 2177, 2179, 2229, 2281, 2282, 2283, 2288, 2294)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 33, 35, 148, 149, 150, 151, 1652, 1653, 1655, 1691, 1692, 1693, 1750, 1751, 1753, 1755, 1756, 1757, 1774, 1824, 1827, 1897, 1900, 2054, 2056, 2058, 2179, 2227, 2231, 2279, 2288, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(32, 34, 152, 1654, 1752, 1754, 1771, 1772, 1773, 1825, 1826, 1898, 2177, 2229, 2281, 2282, 2283, 2289, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 148, 150, 152, 1653, 1654, 1655, 1691, 1692, 1693, 1753, 1754, 1755, 1772, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 2054, 2056, 2177, 2179, 2229, 2231, 2282, 2283, 2289, 2290, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 149, 151, 1652, 1750, 1751, 1752, 1756, 1757, 1771, 1827, 1900, 2058, 2227, 2279, 2281, 2288, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 31, 33, 34, 148, 149, 150, 152, 1654, 1655, 1691, 1692, 1750, 1751, 1754, 1755, 1771, 1773, 1774, 1824, 1825, 1827, 1898, 1900, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 32, 35, 151, 1652, 1653, 1693, 1752, 1753, 1756, 1757, 1772, 1826, 1897, 2054, 2281, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 43, 44, 226, 276, 277, 278, 1720, 1727, 1776, 1777, 1778, 1779, 1868, 1869, 2027, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 222, 224, 228, 275, 279, 280, 1719, 1721, 1722, 1775, 1870, 2119)</t>
+    <t xml:space="preserve">c(41, 43, 224, 226, 228, 276, 277, 279, 280, 1720, 1722, 1775, 1776, 1778, 1779, 1868, 1869, 2027, 2119, 2121, 2124, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 275, 278, 1719, 1721, 1727, 1777, 1870, 2120, 2126, 2221)</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 44, 222, 224, 275, 277, 280, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1779, 1868, 1869, 1870, 2027, 2119, 2124, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 226, 228, 276, 278, 279, 1719, 1778, 2120, 2121, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 222, 224, 226, 276, 277, 279, 280, 1719, 1721, 1722, 1775, 1776, 1778, 1779, 1870, 2027, 2119, 2120, 2121, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 228, 275, 278, 1720, 1727, 1777, 1868, 1869, 2124, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 208, 209, 210, 212, 213, 214, 215, 216, 217, 218, 265, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 206, 207, 211, 219, 220, 266, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 211, 213, 217, 219, 220, 265, 266, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 208, 212, 214, 215, 216, 218, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 207, 208, 209, 210, 213, 214, 215, 217, 218, 219, 265, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 206, 211, 212, 216, 220, 266, 267, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 71, 72, 73, 130, 131, 132, 140, 143, 175, 180, 223, 225, 227, 229, 230, 235, 236, 244, 245, 246, 248, 250, 271, 272, 273, 274, 281, 283, 284, 285, 286, 287, 288, 290, 292, 296, 1717, 1718, 1760, 1761, 1763, 1764, 1766, 1838, 1852, 1863, 1864, 1866, 1867, 1935, 1991, 2108, 2128, 2129, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2194, 2225, 2226, 2257, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 141, 142, 177, 221, 231, 233, 234, 243, 247, 249, 282, 289, 291, 293, 294, 295, 1716, 1762, 1765, 1839, 1840, 1865, 1990, 1992, 2026, 2030, 2109, 2134, 2138, 2139, 2222, 2223, 2300, 2301, 2302)</t>
+    <t xml:space="preserve">c(41, 222, 224, 226, 228, 275, 278, 279, 1720, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2119, 2120, 2121, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 276, 277, 280, 1719, 1721, 2027, 2124, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 226, 228, 275, 276, 277, 278, 279, 1720, 1721, 1722, 1775, 1776, 1779, 1870, 2027, 2119, 2121, 2124, 2125, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 224, 280, 1719, 1727, 1777, 1778, 1868, 1869, 2120, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 207, 209, 210, 211, 212, 215, 217, 218, 219, 220, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 206, 208, 213, 214, 216, 265, 266, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 204, 205, 206, 207, 208, 212, 213, 214, 215, 216, 219, 265, 266, 267, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 209, 210, 211, 217, 218, 220, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 205, 206, 207, 208, 209, 211, 212, 213, 214, 216, 217, 219, 220, 265, 266, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 210, 215, 218, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 73, 130, 131, 132, 140, 141, 142, 143, 177, 180, 221, 223, 229, 231, 233, 234, 236, 243, 249, 271, 273, 274, 281, 282, 284, 286, 287, 288, 289, 290, 291, 292, 294, 295, 296, 1716, 1717, 1760, 1762, 1765, 1838, 1839, 1852, 1864, 1865, 1990, 1992, 2030, 2108, 2109, 2128, 2129, 2132, 2133, 2134, 2136, 2137, 2138, 2194, 2222, 2223, 2257, 2300, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 72, 175, 225, 227, 230, 235, 244, 245, 246, 247, 248, 250, 272, 283, 285, 293, 1718, 1761, 1763, 1764, 1766, 1840, 1863, 1866, 1867, 1935, 1991, 2026, 2130, 2131, 2135, 2139, 2225, 2226, 2312)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 130, 140, 141, 143, 177, 180, 223, 227, 229, 231, 233, 234, 235, 243, 244, 247, 248, 249, 271, 272, 273, 281, 283, 284, 285, 286, 287, 290, 291, 292, 294, 295, 296, 1716, 1717, 1760, 1762, 1764, 1765, 1839, 1840, 1863, 1866, 1935, 1991, 1992, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2133, 2134, 2136, 2138, 2139, 2194, 2222, 2223, 2226, 2300, 2301, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 73, 131, 132, 142, 175, 221, 225, 230, 236, 245, 246, 250, 274, 282, 288, 289, 293, 1718, 1761, 1763, 1766, 1838, 1852, 1864, 1865, 1867, 1990, 2026, 2132, 2135, 2137, 2225, 2257, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 71, 72, 132, 141, 142, 143, 175, 177, 180, 227, 229, 231, 233, 234, 235, 236, 243, 246, 247, 248, 249, 250, 271, 272, 273, 281, 284, 286, 289, 290, 292, 293, 294, 1716, 1718, 1760, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1990, 1991, 1992, 2026, 2108, 2109, 2128, 2130, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2226, 2257, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 130, 131, 140, 221, 223, 225, 230, 244, 245, 274, 282, 283, 285, 287, 288, 291, 295, 296, 1717, 1761, 1762, 1865, 1866, 1867, 1935, 2030, 2129, 2131, 2223, 2225, 2300, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 23, 33, 34, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1691, 1693, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1826, 1827, 1897, 1898, 2054, 2056, 2058, 2231, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 31, 32, 35, 1655, 1692, 1750, 1824, 1825, 1900, 2177, 2179, 2227, 2229, 2279, 2281, 2283, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 148, 149, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1752, 1753, 1755, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 2058, 2177, 2179, 2229, 2279, 2283, 2288, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 32, 34, 35, 150, 151, 1750, 1751, 1754, 1756, 1757, 1900, 2054, 2056, 2227, 2231, 2281, 2282, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 149, 151, 152, 1652, 1655, 1692, 1693, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1772, 1773, 1774, 1824, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2279, 2281, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 35, 148, 150, 1653, 1654, 1691, 1753, 1771, 1825, 2177, 2179, 2229, 2231, 2282, 2283, 2288, 2289, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 222, 226, 228, 275, 279, 1721, 1722, 1727, 1776, 1777, 1778, 1779, 1868, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 224, 276, 277, 278, 280, 1719, 1720, 1775, 1869, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 224, 226, 228, 278, 280, 1719, 1720, 1721, 1722, 1775, 1776, 1778, 1779, 1869, 2027, 2119, 2120, 2121, 2125, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 275, 276, 277, 279, 1727, 1777, 1868, 1870, 2124, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 224, 228, 277, 278, 279, 280, 1719, 1721, 1722, 1727, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 222, 226, 275, 276, 1720, 1777, 2120, 2121, 2124, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 205, 206, 209, 210, 213, 214, 216, 218, 219, 220, 265, 267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 207, 208, 211, 212, 215, 217, 266, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 209, 210, 211, 213, 214, 215, 216, 219, 267, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(208, 212, 217, 218, 220, 265, 266, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 205, 207, 208, 210, 211, 212, 214, 215, 217, 219, 220, 265, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 206, 209, 213, 216, 218, 266, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 73, 130, 131, 141, 143, 177, 221, 223, 229, 230, 231, 235, 236, 243, 244, 246, 247, 248, 249, 250, 273, 283, 285, 286, 287, 288, 290, 291, 292, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2030, 2108, 2128, 2130, 2132, 2133, 2137, 2138, 2194, 2223, 2226, 2300, 2301, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 132, 140, 142, 175, 180, 225, 227, 233, 234, 245, 271, 272, 274, 281, 282, 284, 289, 293, 1765, 1766, 1840, 1935, 2026, 2109, 2129, 2131, 2134, 2135, 2136, 2139, 2222, 2225, 2257, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 71, 73, 141, 142, 143, 221, 225, 229, 230, 233, 235, 236, 243, 247, 249, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 295, 296, 1716, 1717, 1718, 1761, 1762, 1764, 1766, 1838, 1839, 1840, 1863, 1864, 1865, 1867, 1935, 1991, 1992, 2026, 2030, 2108, 2109, 2130, 2131, 2132, 2133, 2136, 2139, 2222, 2223, 2226, 2257, 2301, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 72, 130, 131, 132, 140, 175, 177, 180, 223, 227, 231, 234, 244, 245, 246, 248, 250, 294, 1760, 1763, 1765, 1852, 1866, 1990, 2128, 2129, 2134, 2135, 2137, 2138, 2194, 2225, 2300, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 140, 143, 175, 177, 180, 221, 223, 225, 227, 230, 233, 234, 235, 246, 247, 248, 249, 250, 271, 274, 281, 283, 284, 285, 286, 287, 288, 290, 291, 293, 295, 1760, 1761, 1762, 1763, 1764, 1838, 1839, 1840, 1852, 1865, 1990, 2026, 2030, 2109, 2130, 2131, 2133, 2134, 2136, 2137, 2138, 2139, 2194, 2223, 2225, 2226, 2257, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 141, 142, 229, 231, 236, 243, 244, 245, 272, 273, 282, 289, 292, 294, 296, 1716, 1717, 1718, 1765, 1766, 1863, 1864, 1866, 1867, 1935, 1991, 1992, 2108, 2128, 2129, 2132, 2135, 2222, 2302, 2313)</t>
+    <t xml:space="preserve">c(15, 70, 71, 72, 73, 130, 132, 140, 177, 180, 221, 225, 227, 229, 230, 233, 234, 235, 236, 243, 244, 246, 247, 248, 250, 271, 272, 273, 274, 281, 282, 284, 287, 288, 290, 292, 293, 294, 296, 1716, 1718, 1761, 1763, 1765, 1766, 1838, 1840, 1864, 1865, 1990, 1991, 1992, 2030, 2108, 2109, 2131, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2225, 2257, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 131, 141, 142, 143, 175, 223, 231, 245, 249, 283, 285, 286, 289, 291, 295, 1717, 1760, 1762, 1764, 1839, 1852, 1863, 1866, 1867, 1935, 2026, 2128, 2129, 2130, 2132, 2134, 2223, 2226, 2300, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 131, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 231, 234, 244, 247, 273, 274, 282, 283, 285, 286, 287, 288, 289, 295, 296, 1716, 1717, 1760, 1761, 1762, 1764, 1765, 1838, 1839, 1840, 1852, 1863, 1864, 1867, 1935, 1990, 1991, 1992, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2137, 2138, 2223, 2225, 2226, 2257, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 132, 140, 230, 233, 235, 236, 243, 245, 246, 248, 249, 250, 271, 272, 281, 284, 290, 291, 292, 293, 294, 1718, 1763, 1766, 1865, 1866, 2026, 2134, 2135, 2136, 2139, 2194, 2222, 2300, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 32, 35, 148, 149, 150, 151, 1653, 1654, 1655, 1691, 1692, 1693, 1752, 1753, 1757, 1771, 1772, 1824, 1826, 1827, 1898, 1900, 2054, 2058, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 31, 33, 34, 152, 1652, 1750, 1751, 1754, 1755, 1756, 1773, 1774, 1825, 1897, 2056, 2229, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 33, 35, 148, 149, 150, 152, 1652, 1654, 1655, 1691, 1750, 1751, 1752, 1753, 1756, 1771, 1772, 1773, 1774, 1825, 1897, 2054, 2058, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 31, 32, 34, 151, 1653, 1692, 1693, 1754, 1755, 1757, 1824, 1826, 1827, 1898, 1900, 2056, 2177, 2289, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 34, 35, 148, 150, 151, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 1773, 1825, 1826, 1897, 1898, 1900, 2054, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2283, 2289, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 31, 32, 33, 149, 152, 1653, 1751, 1755, 1757, 1771, 1772, 1774, 1824, 1827, 2056, 2282, 2288, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 276, 280, 1719, 1720, 1776, 1778, 1868, 1869, 1870, 2027, 2119, 2120, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 275, 277, 278, 279, 1721, 1722, 1727, 1775, 1777, 1779, 2121, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 224, 275, 280, 1719, 1721, 1727, 1775, 1776, 1777, 1779, 1868, 1869, 2027, 2119, 2120, 2121, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 226, 228, 276, 277, 278, 279, 1720, 1722, 1778, 1870, 2124, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 226, 228, 275, 276, 277, 278, 1719, 1721, 1722, 1775, 1777, 1779, 1869, 1870, 2027, 2120, 2121, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 224, 279, 280, 1720, 1727, 1776, 1778, 1868, 2119, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 206, 210, 211, 212, 214, 218, 219, 220, 265, 266, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 207, 208, 209, 213, 215, 216, 217, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 209, 210, 212, 213, 216, 218, 219, 266, 267, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(208, 211, 214, 215, 217, 220, 265, 268, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 212, 213, 215, 216, 217, 219, 265, 266, 267, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 210, 211, 214, 218, 220, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 72, 73, 130, 131, 140, 141, 143, 175, 177, 180, 223, 225, 230, 231, 233, 234, 235, 243, 244, 246, 247, 248, 249, 250, 271, 272, 273, 274, 282, 283, 286, 287, 289, 291, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1764, 1839, 1863, 1864, 1935, 1990, 1992, 2030, 2109, 2129, 2131, 2133, 2135, 2137, 2139, 2222, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 132, 142, 221, 227, 229, 236, 245, 281, 284, 285, 288, 290, 1716, 1762, 1763, 1765, 1766, 1838, 1840, 1852, 1865, 1866, 1867, 1991, 2026, 2108, 2128, 2130, 2132, 2134, 2136, 2138, 2194, 2223, 2257)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 141, 142, 143, 175, 180, 225, 227, 229, 230, 231, 234, 235, 236, 243, 244, 245, 247, 248, 250, 273, 282, 283, 285, 287, 288, 289, 290, 291, 295, 296, 1716, 1717, 1760, 1761, 1763, 1764, 1838, 1840, 1863, 1864, 1866, 1935, 1990, 1991, 1992, 2030, 2109, 2128, 2129, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2222, 2223, 2225, 2226, 2300, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 131, 132, 140, 177, 221, 223, 233, 246, 249, 271, 272, 274, 281, 284, 286, 292, 293, 294, 1718, 1762, 1765, 1766, 1839, 1852, 1865, 1867, 2026, 2108, 2130, 2134, 2194, 2257, 2301, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 73, 141, 142, 143, 175, 177, 225, 227, 229, 230, 231, 234, 236, 246, 249, 271, 272, 273, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1864, 1865, 1935, 1990, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2257, 2300, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 130, 131, 132, 140, 180, 221, 223, 233, 235, 243, 244, 245, 247, 248, 250, 274, 281, 285, 1718, 1852, 1866, 1867, 1991, 2132, 2133, 2135, 2223, 2225, 2226, 2301, 2303, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(19, 20, 23, 34, 148, 149, 152, 1691, 1692, 1752, 1753, 1754, 1755, 1756, 1757, 1898, 1900, 2056, 2058, 2227, 2229, 2279, 2281, 2283, 2288, 2289, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 31, 32, 33, 35, 150, 151, 1693, 1750, 1751, 1897, 2054, 2231, 2282, 2290)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 33, 35, 148, 149, 150, 152, 1693, 1750, 1752, 1755, 1756, 1757, 1897, 2054, 2058, 2227, 2279, 2281, 2282, 2288, 2289, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(32, 34, 151, 1691, 1692, 1751, 1753, 1754, 1898, 1900, 2056, 2229, 2231, 2283, 2292, 2294)</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 34, 152, 1691, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1900, 2056, 2058, 2227, 2229, 2279, 2281, 2282, 2288, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(31, 35, 148, 149, 150, 151, 1692, 1693, 1750, 1897, 1898, 2054, 2231, 2283, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 33, 34, 149, 150, 151, 152, 1693, 1753, 1754, 1755, 1756, 1757, 1898, 1900, 2054, 2056, 2058, 2231, 2282, 2288, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 35, 148, 1691, 1692, 1750, 1751, 1752, 1897, 2227, 2229, 2279, 2281, 2283, 2292, 2294)</t>
+    <t xml:space="preserve">c(19, 20, 23, 31, 32, 33, 34, 148, 150, 151, 1692, 1693, 1750, 1752, 1753, 1754, 1755, 1757, 1897, 2054, 2056, 2231, 2282, 2283, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 35, 149, 152, 1691, 1751, 1756, 1898, 1900, 2058, 2227, 2229, 2279, 2281, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 31, 32, 34, 35, 148, 149, 150, 151, 1691, 1692, 1750, 1751, 1754, 1756, 1900, 2058, 2229, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 33, 152, 1693, 1752, 1753, 1755, 1757, 1897, 1898, 2054, 2056, 2227, 2283, 2292)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 43, 44, 224, 228, 276, 277, 278, 280, 1719, 1721, 1727, 1775, 1777, 1778, 1868, 1869, 2027, 2119, 2120, 2121, 2125, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 222, 226, 275, 279, 1720, 1722, 1776, 1779, 1870, 2124, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 226, 275, 276, 278, 280, 1719, 1721, 1775, 1776, 1779, 1869, 1870, 2027, 2119, 2121, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 228, 277, 279, 1720, 1722, 1727, 1777, 1778, 1868, 2120, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 1719, 1720, 1727, 1776, 1778, 1779, 1868, 2119, 2120, 2124, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 280, 1721, 1722, 1775, 1777, 1869, 1870, 2027, 2121, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 267, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 268, 1899)</t>
+    <t xml:space="preserve">c(41, 43, 44, 222, 226, 275, 276, 277, 278, 279, 280, 1719, 1720, 1722, 1777, 1778, 1779, 1868, 1869, 2119, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 224, 228, 1721, 1727, 1775, 1776, 1870, 2027, 2120, 2121, 2124, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 222, 226, 228, 275, 277, 278, 279, 280, 1719, 1720, 1722, 1727, 1779, 1868, 1869, 2027, 2119, 2121, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 224, 276, 1721, 1775, 1776, 1777, 1778, 1870, 2120, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 275, 276, 279, 280, 1722, 1727, 1775, 1778, 1779, 1868, 1870, 2027, 2121, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 228, 277, 278, 1719, 1720, 1721, 1776, 1777, 1869, 2119, 2120, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 267, 268)</t>
   </si>
   <si>
     <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(265, 266, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(267, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(267, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 71, 72, 73, 130, 131, 132, 140, 141, 142, 177, 223, 229, 230, 233, 235, 236, 243, 244, 245, 247, 248, 249, 250, 271, 272, 273, 274, 281, 283, 284, 285, 286, 288, 291, 292, 293, 295, 1717, 1760, 1761, 1764, 1838, 1840, 1852, 1863, 1865, 1866, 1935, 1990, 1991, 2026, 2030, 2129, 2131, 2132, 2134, 2136, 2137, 2138, 2194, 2222, 2223, 2300, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 143, 221, 225, 227, 231, 234, 246, 282, 287, 289, 290, 294, 296, 1716, 1718, 1762, 1763, 1765, 1766, 1839, 1864, 1867, 1992, 2128, 2130, 2133, 2135, 2139, 2225, 2226, 2257, 2303)</t>
+    <t xml:space="preserve">c(265, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 72, 73, 130, 132, 140, 177, 221, 223, 227, 229, 230, 231, 235, 236, 245, 246, 247, 248, 249, 271, 272, 273, 284, 285, 286, 287, 288, 289, 290, 295, 1716, 1718, 1760, 1762, 1763, 1764, 1766, 1838, 1839, 1840, 1852, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2129, 2130, 2132, 2133, 2134, 2135, 2136, 2139, 2194, 2222, 2223, 2225, 2300, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 71, 131, 141, 142, 143, 225, 233, 234, 243, 244, 250, 274, 281, 282, 283, 291, 292, 293, 294, 296, 1717, 1761, 1765, 1863, 1864, 1865, 2128, 2131, 2137, 2138, 2226, 2257, 2302)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 131, 132, 140, 142, 177, 223, 225, 227, 230, 233, 234, 235, 236, 245, 247, 248, 249, 250, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 292, 294, 295, 296, 1716, 1760, 1761, 1766, 1839, 1840, 1852, 1863, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2222, 2226, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 130, 141, 143, 221, 229, 231, 243, 244, 246, 271, 289, 290, 291, 293, 1717, 1718, 1762, 1763, 1764, 1765, 1838, 1864, 2128, 2129, 2130, 2139, 2194, 2223, 2225, 2257, 2300, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 73, 131, 140, 141, 143, 177, 221, 225, 227, 230, 231, 234, 235, 236, 243, 245, 246, 248, 249, 272, 273, 281, 283, 284, 286, 287, 288, 289, 291, 293, 295, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1765, 1838, 1852, 1863, 1864, 1865, 1867, 1935, 1991, 1992, 2026, 2129, 2130, 2131, 2132, 2134, 2136, 2137, 2138, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 72, 130, 132, 142, 223, 229, 233, 244, 247, 250, 271, 274, 282, 285, 290, 292, 294, 296, 1718, 1766, 1839, 1840, 1866, 1990, 2030, 2128, 2133, 2135, 2139, 2194, 2223, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 35, 148, 150, 151, 1692, 1693, 1751, 1753, 1754, 1755, 1756, 1757, 1898, 2054, 2058, 2227, 2229, 2231, 2279, 2281, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 31, 149, 152, 1691, 1750, 1752, 1897, 1900, 2056, 2282, 2283, 2288, 2289, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 33, 35, 148, 149, 150, 151, 1691, 1692, 1693, 1750, 1751, 1753, 1754, 1755, 1757, 1897, 1898, 2056, 2227, 2229, 2279, 2281, 2282, 2288, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 31, 32, 34, 152, 1752, 1756, 1900, 2054, 2058, 2231, 2283, 2289, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 148, 150, 151, 152, 1692, 1693, 1753, 1754, 1755, 1757, 1897, 1898, 2054, 2056, 2058, 2227, 2231, 2279, 2288, 2289, 2290, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(33, 34, 35, 149, 1691, 1750, 1751, 1752, 1756, 1900, 2229, 2281, 2282, 2283, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 224, 275, 276, 277, 278, 1719, 1722, 1775, 1776, 1779, 1868, 1869, 1870, 2120, 2121, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(222, 226, 228, 279, 280, 1720, 1721, 1727, 1777, 1778, 2027, 2119, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 44, 228, 275, 276, 277, 279, 1721, 1722, 1727, 1775, 1777, 1778, 1779, 1869, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 222, 224, 226, 278, 280, 1719, 1720, 1776, 1868, 1870, 2027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 275, 276, 277, 280, 1719, 1721, 1722, 1775, 1776, 1777, 1778, 1868, 1870, 2027, 2119, 2121, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 278, 279, 1720, 1727, 1779, 1869, 2120, 2124, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265:268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 73, 130, 132, 140, 141, 177, 223, 225, 227, 229, 230, 233, 234, 235, 236, 243, 246, 249, 250, 271, 273, 283, 284, 285, 287, 288, 289, 291, 292, 293, 296, 1717, 1760, 1761, 1762, 1764, 1766, 1838, 1839, 1840, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 2030, 2128, 2130, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2225, 2226, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 131, 142, 143, 221, 231, 244, 245, 247, 248, 272, 274, 281, 282, 286, 290, 294, 295, 1716, 1718, 1763, 1765, 1852, 1863, 1992, 2026, 2129, 2134, 2139, 2194, 2222, 2223, 2257, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 71, 72, 131, 132, 140, 142, 143, 223, 229, 230, 231, 233, 236, 243, 245, 246, 247, 248, 250, 271, 273, 283, 285, 286, 287, 289, 290, 291, 292, 293, 294, 1716, 1717, 1761, 1763, 1764, 1765, 1766, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1992, 2026, 2128, 2129, 2130, 2131, 2132, 2134, 2136, 2137, 2139, 2194, 2222, 2225, 2226, 2257, 2300, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 73, 130, 141, 177, 221, 225, 227, 234, 235, 244, 249, 272, 274, 281, 282, 284, 288, 295, 296, 1718, 1760, 1762, 1838, 1839, 1991, 2030, 2133, 2135, 2138, 2223, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 141, 142, 143, 221, 223, 225, 227, 229, 230, 231, 234, 235, 243, 244, 246, 247, 248, 249, 250, 271, 281, 283, 284, 285, 286, 287, 288, 290, 291, 293, 294, 1716, 1717, 1718, 1760, 1761, 1762, 1764, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1867, 1935, 1990, 1991, 2128, 2129, 2131, 2132, 2135, 2136, 2137, 2138, 2139, 2222, 2257, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 131, 132, 140, 177, 233, 236, 245, 272, 273, 274, 282, 289, 292, 295, 296, 1763, 1838, 1865, 1866, 1992, 2026, 2030, 2130, 2133, 2134, 2194, 2223, 2225, 2226, 2300, 2301, 2302, 2312)</t>
+    <t xml:space="preserve">c(13, 70, 71, 72, 73, 130, 131, 132, 140, 142, 143, 177, 221, 225, 229, 230, 231, 234, 236, 245, 246, 247, 248, 249, 250, 272, 273, 274, 284, 286, 287, 289, 291, 292, 293, 294, 295, 296, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1852, 1863, 1864, 1865, 1866, 1935, 1991, 2026, 2128, 2129, 2134, 2136, 2137, 2139, 2194, 2222, 2223, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 141, 223, 227, 233, 235, 243, 244, 271, 281, 282, 283, 285, 288, 290, 1716, 1717, 1839, 1840, 1867, 1990, 1992, 2030, 2130, 2131, 2132, 2133, 2135, 2138, 2225, 2226, 2257, 2300, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 72, 131, 140, 141, 142, 143, 223, 225, 227, 229, 230, 233, 234, 235, 236, 243, 244, 245, 247, 248, 249, 250, 271, 274, 282, 283, 285, 287, 289, 291, 292, 293, 295, 1716, 1717, 1760, 1762, 1763, 1764, 1765, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2130, 2131, 2132, 2134, 2136, 2137, 2225, 2226, 2257, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 130, 132, 177, 221, 231, 246, 272, 273, 281, 284, 286, 288, 290, 294, 296, 1718, 1761, 1766, 1838, 1867, 2129, 2133, 2135, 2138, 2139, 2194, 2222, 2223, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 32, 33, 34, 35, 149, 150, 152, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1897, 1900, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2289, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 23, 31, 148, 151, 1691, 1755, 1757, 1898, 2054, 2282, 2283, 2288, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 32, 33, 148, 150, 151, 152, 1691, 1693, 1750, 1751, 1753, 1754, 1755, 1757, 1897, 1898, 1900, 2058, 2229, 2231, 2279, 2282, 2283, 2289, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 31, 34, 35, 149, 1692, 1752, 1756, 2054, 2056, 2227, 2281, 2288, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 23, 31, 32, 33, 34, 35, 148, 150, 151, 152, 1691, 1692, 1750, 1751, 1752, 1755, 1756, 1897, 1898, 1900, 2058, 2227, 2282, 2288, 2289, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 149, 1693, 1753, 1754, 1757, 2054, 2056, 2229, 2231, 2279, 2281, 2283, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 224, 226, 228, 276, 280, 1720, 1722, 1727, 1776, 1777, 1779, 1868, 1869, 2119, 2120, 2121, 2124, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 222, 275, 277, 278, 279, 1719, 1721, 1775, 1778, 1870, 2027, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 228, 276, 277, 278, 279, 280, 1720, 1721, 1775, 1777, 1779, 1868, 1870, 2119, 2120, 2121, 2125, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(226, 275, 1719, 1722, 1727, 1776, 1778, 1869, 2027, 2124, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 275, 278, 279, 280, 1721, 1722, 1776, 1777, 1778, 1869, 1870, 2027, 2119, 2120, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 276, 277, 1719, 1720, 1727, 1775, 1779, 1868, 2121, 2124, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 266, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(265, 267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(266, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 130, 131, 132, 140, 141, 142, 177, 221, 223, 225, 231, 234, 235, 236, 244, 245, 246, 248, 249, 271, 272, 281, 282, 283, 284, 287, 289, 290, 292, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1765, 1766, 1838, 1852, 1864, 1865, 1866, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2301, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 72, 73, 143, 227, 229, 230, 233, 243, 247, 250, 273, 274, 285, 286, 288, 291, 293, 1717, 1763, 1764, 1839, 1840, 1863, 1867, 1935, 1990, 1991, 2226, 2257, 2300, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 130, 131, 140, 142, 143, 177, 223, 225, 229, 230, 233, 234, 236, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 286, 288, 289, 290, 293, 294, 295, 296, 1716, 1717, 1718, 1761, 1762, 1764, 1765, 1766, 1852, 1863, 1864, 1865, 1866, 1990, 1992, 2128, 2129, 2130, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2226, 2257, 2301, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 132, 141, 221, 227, 231, 235, 243, 244, 245, 284, 285, 287, 291, 292, 1760, 1763, 1838, 1839, 1840, 1867, 1935, 1991, 2026, 2030, 2131, 2135, 2194, 2222, 2223, 2225, 2300, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 73, 131, 140, 141, 142, 143, 221, 223, 227, 229, 231, 233, 234, 235, 236, 243, 245, 246, 247, 248, 250, 271, 273, 274, 281, 282, 283, 284, 285, 287, 288, 290, 292, 293, 295, 296, 1717, 1718, 1760, 1762, 1763, 1764, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1992, 2030, 2128, 2129, 2133, 2134, 2137, 2138, 2139, 2223, 2225, 2257, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 72, 130, 132, 177, 225, 230, 244, 249, 272, 286, 289, 291, 294, 1716, 1761, 1765, 1766, 1838, 1839, 1935, 1991, 2026, 2130, 2131, 2132, 2135, 2136, 2194, 2222, 2226, 2303)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 20, 23, 33, 34, 1691, 1693, 1750, 1751, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1825, 1826, 1827, 2054, 2056, 2058, 2179, 2288, 2289, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 31, 32, 35, 1692, 1752, 1754, 1774, 1824, 2177, 2292, 2293, 2294)</t>
+    <t xml:space="preserve">c(19, 20, 23, 31, 32, 33, 1691, 1692, 1693, 1752, 1753, 1754, 1755, 1756, 1771, 1774, 1824, 1827, 2054, 2058, 2179, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 34, 35, 1750, 1751, 1757, 1772, 1773, 1825, 1826, 2056, 2177, 2292)</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 33, 34, 35, 1691, 1692, 1693, 1750, 1752, 1755, 1756, 1757, 1772, 1824, 1825, 1827, 2056, 2058, 2177, 2179, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 32, 1751, 1753, 1754, 1771, 1773, 1774, 1826, 2054, 2288, 2289, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 31, 32, 1691, 1692, 1752, 1754, 1755, 1756, 1757, 1772, 1773, 1774, 1824, 1825, 1826, 2054, 2056, 2058, 2179, 2288, 2289, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 33, 34, 35, 1693, 1750, 1751, 1753, 1771, 1827, 2177, 2290, 2294)</t>
+    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1752, 1753, 1755, 1757, 1771, 1773, 1774, 1827, 2056, 2058, 2288, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 1751, 1754, 1756, 1772, 1824, 1825, 1826, 2054, 2177, 2179, 2289, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 33, 35, 1691, 1692, 1693, 1752, 1753, 1756, 1771, 1772, 1773, 1824, 1825, 1826, 2054, 2177, 2179, 2288, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 34, 1750, 1751, 1754, 1755, 1757, 1774, 1827, 2056, 2058, 2289, 2290, 2292)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
@@ -1058,214 +1058,214 @@
     <t xml:space="preserve">NA</t>
   </si>
   <si>
-    <t xml:space="preserve">c(70, 72, 177, 180, 229, 230, 231, 235, 236, 272, 273, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 175, 233, 234, 271, 274, 1764)</t>
+    <t xml:space="preserve">c(70, 71, 73, 175, 177, 231, 233, 234, 236, 271, 273, 274, 1764, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 180, 229, 230, 235, 272, 1766, 1935)</t>
   </si>
   <si>
     <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(70, 71, 73, 175, 177, 180, 229, 234, 235, 271, 272, 273, 274, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 230, 231, 233, 236, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 175, 180, 229, 231, 234, 235, 236, 271, 273, 1764, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 177, 230, 233, 272, 274, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 32, 33, 35, 1692, 1751, 1752, 1753, 1754, 1756, 1757, 1771, 1772, 1773, 1774, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 34, 1691, 1693, 1750, 1755, 1824, 1825, 1826, 2289, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 34, 35, 1693, 1751, 1752, 1754, 1756, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 31, 32, 33, 1691, 1692, 1750, 1753, 1755, 1757, 2056, 2058, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 32, 33, 34, 1692, 1693, 1750, 1751, 1754, 1755, 1756, 1772, 1773, 1774, 1824, 1826, 1827, 2054, 2056, 2058, 2179, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 31, 35, 1691, 1752, 1753, 1757, 1771, 1825, 2177, 2288, 2289, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 175, 180, 229, 231, 233, 235, 236, 271, 272, 273, 274, 1764, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 177, 230, 234, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 175, 180, 230, 231, 234, 235, 271, 272, 273, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 177, 229, 233, 236, 274, 1764, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 175, 177, 180, 229, 233, 236, 271, 273, 274, 1764, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 230, 231, 234, 235, 272, 1765)</t>
+    <t xml:space="preserve">c(71, 72, 73, 177, 180, 229, 230, 233, 234, 235, 236, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 175, 231, 271, 272, 273, 274, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 175, 177, 230, 233, 234, 235, 236, 271, 272, 273, 274, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 180, 229, 231, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 33, 35, 1692, 1750, 1752, 1755, 1756, 1771, 1772, 1773, 1774, 1825, 1826, 2054, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 34, 1691, 1693, 1751, 1753, 1754, 1757, 1824, 1827, 2056, 2058, 2177, 2179)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1773, 1824, 1827, 2056, 2058, 2177, 2288, 2289, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 1692, 1693, 1757, 1771, 1772, 1774, 1825, 1826, 2054, 2179, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 31, 35, 1692, 1693, 1750, 1751, 1754, 1756, 1757, 1771, 1774, 1824, 1825, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 32, 33, 34, 1691, 1752, 1753, 1755, 1772, 1773, 1826, 2289, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 177, 180, 229, 230, 231, 234, 235, 271, 273, 274, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 175, 233, 236, 272, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 175, 229, 230, 231, 233, 236, 271, 274, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 177, 180, 234, 235, 272, 273, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 229, 234, 235, 236, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 175, 177, 180, 230, 231, 233, 271)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 31, 33, 1691, 1693, 1752, 1753, 1754, 1756, 1757, 1771, 1773, 1774, 1825, 1826, 1827, 2054, 2056, 2177, 2179, 2288, 2290, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 32, 34, 35, 1692, 1750, 1751, 1755, 1772, 1824, 2058, 2289, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 32, 35, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 1757, 1772, 1774, 1824, 1825, 1827, 2054, 2058, 2177, 2179, 2288, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 33, 34, 1691, 1751, 1755, 1771, 1773, 1826, 2056, 2289, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 35, 1691, 1693, 1750, 1753, 1755, 1772, 1774, 1824, 1826, 1827, 2054, 2058, 2179, 2288, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 1692, 1751, 1752, 1754, 1756, 1757, 1771, 1773, 1825, 2056, 2177, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 175, 177, 180, 229, 230, 233, 235, 271, 272, 274, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 231, 234, 236, 273, 1764, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 175, 177, 180, 230, 231, 233, 235, 271, 272, 274, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 229, 234, 236, 273, 1764, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 175, 177, 180, 229, 231, 234, 236, 271, 274, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 230, 233, 235, 272, 273, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 32, 33, 34, 35, 1691, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1774, 1825, 2054, 2058, 2177, 2179, 2288, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 31, 1692, 1693, 1750, 1757, 1772, 1773, 1824, 1826, 1827, 2056, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 33, 34, 35, 1691, 1693, 1753, 1754, 1755, 1771, 1773, 1774, 1824, 1825, 1826, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 31, 32, 1692, 1750, 1751, 1752, 1756, 1757, 1772, 1827, 2054, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 31, 34, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2177, 2179, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 23, 32, 33, 35, 1691, 1693, 1753, 1757, 2056, 2058, 2288, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 175, 177, 180, 229, 231, 233, 234, 235, 272, 1764, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 230, 236, 271, 273, 274, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 175, 177, 180, 230, 233, 235, 236, 271, 272, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 229, 231, 234, 273, 274)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 175, 177, 231, 234, 236, 271, 272, 273, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 180, 229, 230, 233, 235, 274, 1766)</t>
+    <t xml:space="preserve">c(17, 18, 19, 31, 32, 34, 35, 1691, 1750, 1751, 1752, 1755, 1756, 1757, 1771, 1772, 1824, 1825, 1827, 2056, 2058, 2179, 2288, 2289, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 33, 1692, 1693, 1753, 1754, 1773, 1774, 1826, 2054, 2177, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 33, 35, 1751, 1753, 1754, 1755, 1757, 1771, 1772, 1773, 1825, 1826, 1827, 2054, 2056, 2058, 2179, 2289, 2290, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 34, 1691, 1692, 1693, 1750, 1752, 1756, 1774, 1824, 2177, 2288, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 1692, 1693, 1751, 1754, 1755, 1756, 1772, 1824, 1825, 1826, 1827, 2054, 2058, 2177, 2288, 2289, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 1691, 1750, 1752, 1753, 1757, 1771, 1773, 1774, 2056, 2179, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 177, 180, 229, 230, 231, 233, 234, 271, 273, 274, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 175, 235, 236, 272, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 175, 180, 229, 230, 233, 234, 236, 271, 272, 273, 274, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 177, 231, 235, 1764, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 175, 229, 231, 233, 234, 236, 271, 272, 274, 1764, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 177, 180, 230, 235, 273, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 33, 1691, 1750, 1752, 1753, 1754, 1757, 1771, 1773, 1774, 1824, 1825, 1826, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 31, 32, 34, 35, 1692, 1693, 1751, 1755, 1756, 1772, 1827)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 32, 34, 35, 1691, 1692, 1693, 1750, 1751, 1754, 1756, 1771, 1772, 1774, 1824, 1826, 1827, 2056, 2177, 2179, 2289, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 31, 33, 1752, 1753, 1755, 1757, 1773, 1825, 2054, 2058, 2288, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 32, 33, 35, 1692, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 31, 34, 1691, 1693, 1750, 1751, 1752, 1754, 1825, 1827, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 175, 177, 229, 230, 233, 234, 272, 274, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 180, 231, 235, 236, 271, 273)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 175, 180, 229, 230, 233, 234, 235, 271, 272, 273, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 177, 231, 236, 274, 1764, 1765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 175, 177, 180, 229, 231, 234, 236, 274, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 230, 233, 235, 271, 272, 273, 1766)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 20, 31, 32, 34, 35, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 2056, 2288, 2289, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 23, 33, 1692, 1757, 2054, 2058, 2290, 2292, 2293, 2295)</t>
+    <t xml:space="preserve">c(18, 19, 31, 32, 33, 34, 35, 1691, 1692, 1750, 1751, 1753, 1754, 1756, 1757, 2058, 2289, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 1693, 1752, 1755, 2054, 2056, 2288, 2292, 2294)</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 32, 33, 1691, 1693, 1751, 1752, 1753, 1754, 1757, 2054, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 31, 34, 35, 1692, 1750, 1755, 1756, 2056, 2058, 2288)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1693, 1750, 1753, 1756, 2054, 2056, 2058, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 1692, 1751, 1752, 1754, 1755, 1757, 2288, 2289, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 177, 180, 231, 233, 234, 271, 273, 274, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(175, 229, 230, 235, 236, 272, 1764, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 175, 180, 229, 230, 231, 271, 272, 273, 274, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 177, 233, 234, 235, 236, 1764, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 175, 177, 230, 231, 233, 234, 236, 272, 274, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 180, 229, 235, 271, 273, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 33, 34, 35, 1750, 1751, 1753, 1754, 1755, 1756, 1757, 2056, 2058, 2289, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 31, 32, 1691, 1692, 1693, 1752, 2054, 2288, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 35, 1692, 1693, 1751, 1754, 1756, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 33, 34, 1691, 1750, 1752, 1753, 1755, 1757, 2054, 2056)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 35, 1691, 1692, 1693, 1753, 1754, 1755, 1756, 2054, 2056, 2288, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 33, 34, 1750, 1751, 1752, 1757, 2058, 2289, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 175, 177, 229, 230, 234, 235, 236, 271, 272, 273, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 180, 231, 233, 274, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 231, 233, 234, 236, 271, 272, 273, 274, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 175, 177, 180, 229, 230, 235, 1764)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 175, 177, 180, 229, 230, 235, 273, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 231, 233, 234, 236, 271, 272, 274)</t>
+    <t xml:space="preserve">c(18, 19, 23, 31, 34, 35, 1691, 1692, 1693, 1750, 1754, 1756, 2054, 2058, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 32, 33, 1751, 1752, 1753, 1755, 1757, 2056, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 32, 33, 34, 1692, 1693, 1751, 1752, 1755, 1756, 1757, 2056, 2058, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 31, 35, 1691, 1750, 1753, 1754, 2054, 2288, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 175, 177, 229, 231, 233, 235, 271, 272, 273, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 180, 230, 234, 236, 274, 1764)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 177, 180, 229, 230, 233, 236, 271, 272, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 175, 231, 234, 235, 273, 274, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 175, 177, 180, 231, 233, 235, 236, 271, 1764, 1765, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 229, 230, 234, 272, 273, 274, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 31, 34, 35, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 23, 32, 33, 1692, 1693, 2056, 2058, 2288, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 34, 1692, 1693, 1750, 1752, 1753, 1754, 1755, 1757, 2056, 2058, 2288, 2289, 2290, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 31, 32, 33, 35, 1691, 1751, 1756, 2054, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 32, 35, 1691, 1693, 1750, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 31, 33, 34, 1692, 1751, 2288, 2289, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 175, 229, 234, 235, 236, 271, 272, 274, 1764, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 177, 180, 230, 231, 233, 273, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 175, 229, 231, 233, 234, 235, 272, 273, 274, 1764, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 177, 180, 230, 236, 271, 1765, 1766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 73, 177, 180, 229, 231, 233, 234, 235, 236, 271, 272, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 175, 230, 273, 274, 1764, 1765, 1766)</t>
   </si>
 </sst>
 </file>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="326">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -77,1195 +77,922 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 33, 34, 35, 148, 150, 152, 1653, 1751, 1752, 1753, 1754, 1755, 1757, 1771, 1772, 1773, 1774, 1825, 1827, 1897, 1898, 1900, 2054, 2056, 2177, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 31, 32, 149, 151, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1756, 1824, 1826, 2058, 2179, 2289, 2294)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 32, 34, 35, 148, 149, 150, 151, 152, 1653, 1654, 1655, 1693, 1752, 1754, 1756, 1771, 1772, 1774, 1825, 1827, 1898, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 23, 31, 33, 1652, 1691, 1692, 1750, 1751, 1753, 1755, 1757, 1773, 1824, 1826, 1897, 1900, 2281, 2290, 2292)</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 34, 35, 149, 150, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1752, 1754, 1755, 1757, 1771, 1773, 1774, 1825, 1826, 1898, 2056, 2177, 2179, 2227, 2229, 2231, 2279, 2283, 2288, 2289, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 32, 148, 151, 1693, 1751, 1753, 1756, 1772, 1824, 1827, 1897, 1900, 2054, 2058, 2281, 2282, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 32, 33, 35, 148, 151, 152, 1653, 1654, 1691, 1693, 1751, 1753, 1755, 1757, 1771, 1772, 1773, 1824, 1826, 1827, 1897, 1898, 2056, 2058, 2177, 2227, 2229, 2231, 2279, 2282, 2283, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 34, 149, 150, 1652, 1655, 1692, 1750, 1752, 1754, 1756, 1774, 1825, 1900, 2054, 2179, 2281, 2288, 2295)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 34, 35, 149, 150, 152, 1652, 1653, 1654, 1655, 1693, 1751, 1752, 1753, 1756, 1771, 1774, 1824, 1825, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2227, 2279, 2283, 2288, 2289, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 148, 151, 1691, 1692, 1750, 1754, 1755, 1757, 1772, 1773, 1826, 2179, 2229, 2231, 2281, 2282, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 34, 148, 149, 150, 151, 152, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1757, 1772, 1774, 1825, 1826, 1827, 1897, 1898, 1900, 2058, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 32, 33, 35, 1653, 1755, 1771, 1773, 1824, 2054, 2056, 2177, 2179, 2281, 2289, 2290, 2292, 2293, 2294)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 276, 277, 278, 279, 1719, 1720, 1722, 1776, 1778, 1779, 1868, 1869, 1870, 2033, 2037, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 275, 280, 1721, 1727, 1775, 1777, 2027, 2029, 2035, 2119, 2120, 2121, 2125)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 222, 224, 275, 276, 277, 278, 279, 1719, 1721, 1722, 1727, 1775, 1777, 1778, 1868, 1869, 1870, 2033, 2035, 2037, 2119, 2121, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 226, 228, 280, 1720, 1776, 1779, 2027, 2029, 2120, 2124, 2125, 2224)</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 228, 275, 276, 277, 1721, 1722, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2033, 2119, 2120, 2121, 2124, 2125, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(226, 278, 279, 280, 1719, 1720, 1727, 1777, 2027, 2029, 2035, 2037, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 280, 1719, 1720, 1721, 1776, 1777, 1778, 1868, 1869, 2027, 2033, 2119, 2120, 2124, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(277, 278, 279, 1722, 1727, 1775, 1779, 1870, 2029, 2035, 2037, 2121, 2221, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 44, 222, 226, 228, 275, 276, 278, 279, 280, 1719, 1720, 1721, 1722, 1777, 1868, 1869, 1870, 2033, 2035, 2121, 2124, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 224, 277, 1727, 1775, 1776, 1778, 1779, 2027, 2029, 2037, 2119, 2120, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 226, 228, 275, 277, 278, 279, 280, 1719, 1721, 1722, 1727, 1775, 1776, 1777, 1779, 1868, 1869, 1870, 2027, 2033, 2037, 2119, 2120, 2125, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 224, 276, 1720, 1778, 2029, 2035, 2121, 2124, 2126, 2127, 2221)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 208, 209, 210, 213, 214, 215, 216, 217, 218, 219, 265, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 207, 211, 212, 220, 266, 268, 1899, 2232)</t>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 211, 212, 213, 216, 217, 219, 266, 267, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 208, 214, 215, 218, 220, 265, 2230, 2232)</t>
   </si>
   <si>
     <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 207, 210, 211, 212, 213, 214, 216, 217, 219, 265, 266, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 206, 208, 209, 215, 218, 220, 267, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 207, 208, 209, 211, 212, 213, 214, 216, 217, 219, 220, 266, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 206, 210, 215, 218, 265, 267, 268, 1899)</t>
+    <t xml:space="preserve">c(201, 202, 203, 205, 208, 210, 212, 213, 215, 216, 217, 218, 219, 220, 265, 267, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 206, 207, 209, 211, 214, 266, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 211, 212, 213, 215, 216, 217, 219, 220, 265, 266, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 210, 214, 218, 268, 1899, 2230, 2232)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(14, 15, 71, 72, 73, 130, 132, 140, 141, 142, 143, 175, 176, 179, 181, 182, 221, 225, 227, 229, 231, 233, 234, 244, 246, 248, 250, 271, 273, 281, 282, 283, 284, 286, 289, 290, 291, 292, 293, 295, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1765, 1838, 1839, 1840, 1852, 1863, 1864, 1866, 1874, 1875, 1876, 1935, 1990, 2026, 2028, 2032, 2034, 2036, 2108, 2109, 2131, 2132, 2133, 2134, 2138, 2194, 2222, 2226, 2257, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 131, 177, 178, 180, 223, 230, 235, 236, 243, 245, 247, 249, 272, 274, 285, 287, 288, 294, 1761, 1764, 1766, 1865, 1867, 1991, 1992, 2030, 2128, 2129, 2130, 2135, 2136, 2137, 2139, 2223, 2225, 2300, 2303, 2313)</t>
+    <t xml:space="preserve">c(13, 14, 71, 73, 130, 131, 140, 141, 142, 143, 175, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 233, 235, 236, 244, 245, 247, 249, 272, 274, 281, 285, 287, 290, 291, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1764, 1765, 1839, 1863, 1864, 1865, 1866, 1874, 1875, 1990, 1991, 1992, 2028, 2030, 2032, 2036, 2109, 2128, 2129, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2226, 2257, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 72, 132, 176, 231, 234, 243, 246, 248, 250, 271, 273, 282, 283, 284, 286, 288, 289, 1716, 1762, 1763, 1766, 1838, 1840, 1852, 1867, 1876, 1935, 2026, 2034, 2108, 2130, 2131, 2134, 2222, 2223, 2225, 2300, 2312)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 
 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 131, 132, 141, 142, 143, 179, 180, 181, 221, 227, 229, 230, 234, 236, 244, 245, 246, 247, 248, 249, 274, 282, 283, 284, 286, 287, 289, 290, 291, 292, 293, 294, 295, 296, 1717, 1760, 1762, 1763, 1765, 1838, 1840, 1852, 1863, 1867, 1874, 1875, 1876, 1935, 1990, 2028, 2032, 2034, 2036, 2109, 2128, 2129, 2131, 2132, 2133, 2135, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2257, 2300, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 71, 140, 175, 176, 177, 178, 182, 223, 225, 231, 233, 235, 243, 250, 271, 272, 273, 281, 285, 288, 1716, 1718, 1761, 1764, 1766, 1839, 1864, 1865, 1866, 1991, 1992, 2026, 2030, 2108, 2130, 2134, 2136, 2226, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 73, 130, 132, 140, 142, 175, 177, 179, 181, 225, 227, 230, 231, 233, 234, 235, 236, 246, 247, 248, 249, 272, 274, 281, 282, 283, 284, 285, 286, 288, 289, 290, 291, 293, 294, 295, 1716, 1760, 1761, 1762, 1765, 1838, 1839, 1840, 1863, 1864, 1865, 1874, 1875, 1876, 1935, 1990, 2026, 2030, 2034, 2108, 2109, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2222, 2223, 2226, 2257, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 72, 131, 141, 143, 176, 178, 180, 182, 221, 223, 229, 243, 244, 245, 250, 271, 273, 287, 292, 296, 1717, 1718, 1763, 1764, 1766, 1852, 1866, 1867, 1991, 1992, 2028, 2032, 2036, 2128, 2129, 2130, 2194, 2225, 2300)</t>
+    <t xml:space="preserve">c(14, 15, 70, 71, 72, 73, 131, 132, 140, 141, 142, 175, 176, 177, 178, 181, 223, 229, 230, 231, 235, 236, 243, 244, 248, 249, 271, 272, 273, 274, 283, 284, 285, 286, 288, 291, 292, 293, 294, 295, 1716, 1717, 1718, 1761, 1763, 1764, 1766, 1840, 1852, 1863, 1864, 1874, 1991, 1992, 2028, 2030, 2032, 2034, 2036, 2108, 2129, 2130, 2131, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 130, 143, 179, 180, 182, 221, 225, 227, 233, 234, 245, 246, 247, 250, 281, 282, 287, 289, 290, 296, 1760, 1762, 1765, 1838, 1839, 1865, 1866, 1867, 1875, 1876, 1935, 1990, 2026, 2109, 2128, 2132, 2134, 2300, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 141, 142, 143, 175, 177, 178, 179, 180, 181, 223, 227, 230, 233, 234, 235, 236, 243, 244, 245, 246, 247, 249, 250, 271, 272, 273, 274, 281, 283, 284, 287, 288, 290, 294, 295, 1716, 1717, 1718, 1760, 1763, 1765, 1838, 1865, 1874, 1876, 1935, 1990, 1991, 1992, 2028, 2034, 2036, 2108, 2109, 2129, 2131, 2136, 2137, 2138, 2194, 2222, 2223, 2225, 2226, 2257, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(140, 176, 182, 221, 225, 229, 231, 248, 282, 285, 286, 289, 291, 292, 293, 296, 1761, 1762, 1764, 1766, 1839, 1840, 1852, 1863, 1864, 1866, 1867, 1875, 2026, 2030, 2032, 2128, 2130, 2132, 2133, 2134, 2135, 2139, 2300, 2312)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(32, 33, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1692, 1693, 1750, 1752, 1753, 1754, 1755, 1756, 1773, 1826, 1827, 1898, 1900, 2054, 2056, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 34, 1655, 1691, 1751, 1757, 1771, 1772, 1774, 1824, 1825, 1897, 2058, 2229, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 33, 34, 35, 148, 152, 1652, 1654, 1691, 1692, 1693, 1750, 1752, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1826, 1827, 2054, 2056, 2177, 2179, 2227, 2229, 2282, 2283, 2288, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 32, 149, 150, 151, 1653, 1655, 1751, 1753, 1772, 1825, 1897, 1898, 1900, 2058, 2231, 2279, 2281, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 23, 31, 32, 34, 35, 148, 149, 150, 151, 1653, 1654, 1691, 1692, 1693, 1750, 1752, 1755, 1771, 1772, 1773, 1774, 1824, 1825, 1827, 1897, 1898, 2054, 2058, 2177, 2179, 2227, 2231, 2281, 2282, 2288, 2290, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 33, 152, 1652, 1655, 1751, 1753, 1754, 1756, 1757, 1826, 1900, 2056, 2229, 2279, 2283, 2289, 2293, 2295)</t>
+    <t xml:space="preserve">c(18, 23, 31, 34, 35, 148, 150, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1752, 1754, 1755, 1756, 1757, 1772, 1773, 1824, 1825, 1826, 1827, 1897, 2054, 2058, 2179, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 32, 33, 149, 152, 1751, 1753, 1771, 1774, 1898, 1900, 2056, 2177, 2227, 2229, 2231, 2279, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 33, 34, 35, 148, 150, 151, 152, 1653, 1654, 1691, 1692, 1751, 1752, 1755, 1757, 1771, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2179, 2227, 2231, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 31, 32, 149, 1652, 1655, 1693, 1750, 1753, 1754, 1756, 1772, 1773, 1774, 2056, 2058, 2177, 2229, 2279, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 23, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1754, 1755, 1757, 1771, 1772, 1826, 1827, 1898, 2054, 2056, 2058, 2177, 2179, 2227, 2231, 2281, 2282, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 31, 32, 33, 34, 1751, 1752, 1753, 1756, 1773, 1774, 1824, 1825, 1897, 1900, 2229, 2279, 2283)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(42, 43, 44, 224, 226, 228, 275, 279, 1719, 1721, 1722, 1727, 1776, 1777, 1779, 1869, 1870, 2027, 2029, 2033, 2119, 2120, 2121, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 222, 276, 277, 278, 280, 1720, 1775, 1778, 1868, 2035, 2037, 2124, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 275, 277, 278, 1719, 1720, 1721, 1727, 1776, 1777, 1778, 1869, 1870, 2027, 2033, 2035, 2037, 2119, 2120, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 226, 228, 276, 279, 280, 1722, 1775, 1779, 1868, 2029, 2121, 2124, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 222, 224, 228, 275, 276, 278, 279, 1719, 1720, 1722, 1776, 1777, 1779, 1868, 1869, 2027, 2029, 2033, 2035, 2119, 2120, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 226, 277, 280, 1721, 1727, 1775, 1778, 1870, 2037, 2121, 2124, 2126, 2221)</t>
+    <t xml:space="preserve">c(44, 222, 228, 275, 277, 278, 280, 1719, 1721, 1722, 1727, 1775, 1777, 1778, 1779, 1869, 1870, 2027, 2033, 2035, 2119, 2120, 2121, 2124, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 224, 226, 276, 279, 1720, 1776, 1868, 2029, 2037, 2125, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 275, 277, 1719, 1720, 1727, 1775, 1777, 1779, 1868, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 224, 226, 228, 276, 278, 279, 280, 1721, 1722, 1776, 1778, 1869)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 228, 275, 276, 277, 1719, 1721, 1722, 1775, 1778, 1779, 1868, 1869, 2027, 2035, 2037, 2119, 2120, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 224, 226, 278, 279, 280, 1720, 1727, 1776, 1777, 1870, 2029, 2033, 2121)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 209, 210, 212, 213, 214, 215, 216, 217, 219, 220, 265, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 205, 206, 207, 208, 211, 218, 266, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 212, 213, 214, 217, 218, 219, 265, 266, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 208, 211, 215, 216, 220, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 210, 211, 214, 215, 216, 218, 220, 265, 267, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(208, 209, 212, 213, 217, 219, 266, 268, 2230)</t>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 210, 211, 212, 213, 214, 215, 217, 265, 266, 267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 208, 209, 216, 218, 219, 220, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 206, 208, 209, 210, 211, 212, 213, 215, 216, 217, 218, 219, 265, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 207, 214, 220, 266, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 205, 206, 207, 208, 209, 212, 213, 214, 215, 217, 218, 219, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 210, 211, 216, 220, 265, 266)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(14, 15, 70, 72, 73, 140, 177, 178, 179, 180, 221, 225, 229, 230, 231, 233, 234, 236, 243, 244, 245, 247, 248, 250, 271, 272, 274, 281, 282, 284, 285, 286, 287, 288, 289, 291, 292, 1716, 1717, 1718, 1760, 1761, 1763, 1765, 1766, 1838, 1840, 1852, 1863, 1865, 1867, 1874, 1875, 1876, 1935, 1990, 2026, 2028, 2034, 2036, 2109, 2128, 2130, 2131, 2132, 2135, 2136, 2138, 2194, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 71, 130, 131, 132, 141, 142, 143, 175, 176, 181, 182, 223, 227, 235, 246, 249, 273, 283, 290, 293, 294, 295, 296, 1762, 1764, 1839, 1864, 1866, 1991, 1992, 2030, 2032, 2108, 2129, 2133, 2134, 2137, 2139, 2222)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 70, 71, 131, 132, 140, 141, 142, 143, 175, 176, 177, 179, 180, 181, 182, 221, 223, 227, 229, 230, 233, 236, 243, 244, 245, 246, 247, 248, 249, 271, 273, 282, 283, 286, 287, 288, 289, 290, 293, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1765, 1766, 1839, 1852, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2034, 2109, 2128, 2130, 2132, 2134, 2135, 2137, 2139, 2194, 2222, 2225, 2226, 2257, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 72, 73, 130, 178, 225, 231, 234, 235, 250, 272, 274, 281, 284, 285, 291, 292, 294, 295, 296, 1762, 1838, 1840, 1863, 1864, 1865, 1866, 2028, 2030, 2032, 2036, 2108, 2129, 2131, 2133, 2136, 2138, 2223, 2300, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 71, 73, 130, 140, 142, 143, 175, 176, 177, 178, 179, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 243, 244, 247, 249, 250, 273, 274, 281, 283, 284, 285, 286, 287, 288, 290, 291, 292, 293, 294, 296, 1717, 1760, 1761, 1762, 1763, 1764, 1766, 1838, 1839, 1840, 1852, 1863, 1867, 1874, 1876, 1935, 2026, 2036, 2128, 2129, 2131, 2132, 2133, 2134, 2136, 2139, 2194, 2225, 2226, 2257, 2300, 2301, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 131, 132, 141, 180, 234, 235, 236, 245, 246, 248, 271, 272, 282, 289, 295, 1716, 1718, 1765, 1864, 1865, 1866, 1875, 1990, 1991, 1992, 2028, 2030, 2032, 2034, 2108, 2109, 2130, 2135, 2137, 2138, 2222, 2223, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 31, 32, 33, 34, 35, 148, 151, 152, 1653, 1654, 1655, 1691, 1692, 1752, 1757, 1772, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 2056, 2058, 2177, 2179, 2227, 2231, 2281, 2282, 2288, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 149, 150, 1652, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 1771, 1827, 1900, 2054, 2229, 2279, 2283, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 31, 33, 34, 149, 150, 151, 152, 1652, 1653, 1691, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1771, 1774, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2279, 2281, 2282, 2288, 2289, 2290, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 23, 32, 35, 148, 1654, 1655, 1693, 1753, 1757, 1772, 1773, 1824, 1898, 2231, 2283, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 33, 34, 35, 149, 151, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1751, 1752, 1753, 1755, 1756, 1824, 1825, 1826, 1898, 1900, 2056, 2179, 2227, 2229, 2231, 2279, 2283, 2288, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 148, 150, 152, 1750, 1754, 1757, 1771, 1772, 1773, 1774, 1827, 1897, 2054, 2058, 2177, 2281, 2282, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1722, 1775, 1776, 1777, 1779, 1868, 2037, 2119, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 1719, 1720, 1721, 1727, 1778, 1869, 1870, 2027, 2029, 2033, 2035, 2120)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 228, 275, 276, 278, 1720, 1721, 1722, 1727, 1775, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2033, 2124, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(226, 277, 279, 280, 1719, 1776, 2029, 2035, 2037, 2119, 2120, 2121, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 226, 228, 275, 276, 278, 280, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1870, 2027, 2029, 2033, 2035, 2119, 2120, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 222, 224, 277, 279, 1719, 1720, 1721, 1722, 1869, 2037, 2121, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 205, 208, 210, 211, 213, 216, 217, 218, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 206, 207, 209, 212, 214, 215, 265)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 208, 210, 211, 212, 216, 220, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 209, 213, 214, 215, 217, 218, 219, 265)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 208, 210, 214, 215, 216, 219, 220, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 209, 211, 212, 213, 217, 218, 265, 266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 73, 130, 140, 141, 142, 143, 176, 177, 178, 179, 181, 182, 221, 223, 227, 229, 230, 231, 234, 235, 236, 243, 244, 245, 246, 248, 249, 271, 274, 282, 283, 284, 285, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1763, 1764, 1765, 1766, 1838, 1840, 1852, 1864, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 1992, 2030, 2034, 2129, 2131, 2133, 2135, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 72, 131, 132, 175, 180, 225, 233, 247, 250, 272, 273, 281, 286, 1718, 1761, 1762, 1839, 1863, 1865, 1875, 2026, 2028, 2032, 2036, 2108, 2109, 2128, 2130, 2132, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 72, 130, 141, 142, 176, 178, 179, 181, 182, 223, 225, 229, 230, 231, 233, 235, 236, 244, 246, 247, 248, 249, 271, 272, 273, 282, 283, 284, 285, 286, 287, 288, 289, 290, 292, 293, 294, 295, 296, 1716, 1761, 1762, 1763, 1765, 1838, 1839, 1852, 1863, 1864, 1865, 1866, 1875, 1935, 1990, 2028, 2032, 2034, 2036, 2109, 2128, 2130, 2131, 2132, 2133, 2135, 2137, 2194, 2222, 2223, 2225, 2257, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 131, 132, 140, 143, 175, 177, 180, 221, 227, 234, 243, 245, 250, 274, 281, 291, 1717, 1718, 1760, 1764, 1766, 1840, 1867, 1874, 1876, 1991, 1992, 2026, 2030, 2108, 2129, 2134, 2136, 2138, 2139, 2226, 2300, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 71, 132, 140, 141, 142, 143, 175, 177, 178, 179, 182, 223, 225, 229, 230, 231, 234, 235, 236, 243, 245, 246, 247, 248, 250, 272, 273, 274, 281, 282, 283, 284, 285, 286, 288, 289, 290, 291, 292, 294, 295, 1716, 1717, 1718, 1761, 1763, 1764, 1765, 1838, 1839, 1840, 1863, 1865, 1867, 1874, 1875, 1876, 1935, 1991, 1992, 2028, 2036, 2108, 2109, 2129, 2132, 2135, 2136, 2137, 2138, 2194, 2223, 2257, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 131, 176, 180, 181, 221, 227, 233, 244, 249, 271, 287, 293, 296, 1760, 1762, 1766, 1852, 1864, 1866, 1990, 2026, 2030, 2032, 2034, 2128, 2130, 2131, 2133, 2134, 2139, 2222, 2225, 2226, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 32, 33, 34, 35, 148, 149, 150, 152, 1653, 1654, 1691, 1692, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1772, 1774, 1826, 1827, 1897, 1898, 1900, 2056, 2058, 2179, 2227, 2229, 2282, 2288, 2289, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 31, 151, 1652, 1655, 1693, 1757, 1773, 1824, 1825, 2054, 2177, 2231, 2279, 2281, 2283, 2290, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 34, 35, 148, 150, 151, 152, 1652, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1774, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2056, 2227, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 31, 32, 33, 149, 1653, 1654, 1655, 1691, 1755, 1757, 1772, 1773, 1897, 2058, 2177, 2179, 2229, 2283, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1750, 1752, 1757, 1771, 1824, 1826, 1897, 1898, 1900, 2056, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 23, 1693, 1751, 1753, 1754, 1755, 1756, 1772, 1773, 1774, 1825, 1827, 2054, 2058, 2177, 2229, 2289, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 275, 277, 278, 279, 1721, 1722, 1776, 1778, 1779, 1869, 1870, 2027, 2033, 2035, 2119, 2120, 2121, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 276, 280, 1719, 1720, 1727, 1775, 1777, 1868, 2029, 2037, 2124, 2125, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 224, 228, 275, 276, 278, 279, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1778, 1869, 1870, 2037, 2119, 2121, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 222, 226, 277, 1722, 1777, 1779, 1868, 2027, 2029, 2033, 2035, 2120, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 228, 276, 277, 278, 280, 1719, 1720, 1721, 1722, 1775, 1776, 1777, 1779, 1868, 1869, 1870, 2027, 2029, 2035, 2037, 2119, 2120, 2124, 2125, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 275, 279, 1727, 1778, 2033, 2121, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 205, 208, 209, 210, 211, 213, 215, 216, 217, 219, 220, 265, 266, 267, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 206, 207, 212, 214, 218, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 206, 207, 208, 209, 211, 213, 215, 216, 219, 220, 266, 267, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(205, 210, 212, 214, 217, 218, 265, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 206, 207, 208, 209, 210, 211, 214, 215, 216, 217, 219, 220, 265, 266, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 212, 213, 218, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 70, 71, 72, 130, 132, 140, 141, 142, 175, 176, 177, 178, 179, 180, 181, 182, 221, 227, 229, 230, 243, 244, 246, 247, 248, 249, 250, 271, 272, 273, 274, 282, 283, 284, 285, 286, 288, 289, 290, 291, 292, 294, 296, 1716, 1717, 1718, 1761, 1762, 1763, 1764, 1765, 1839, 1852, 1863, 1865, 1866, 1875, 1876, 1935, 1992, 2026, 2028, 2030, 2032, 2034, 2130, 2131, 2132, 2134, 2135, 2139, 2194, 2225, 2226, 2257, 2300, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 73, 131, 143, 223, 225, 231, 233, 234, 235, 236, 245, 281, 287, 293, 295, 1760, 1766, 1838, 1840, 1864, 1867, 1874, 1990, 1991, 2036, 2108, 2109, 2128, 2129, 2133, 2136, 2137, 2138, 2222, 2223, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 71, 73, 140, 142, 143, 175, 176, 178, 179, 180, 182, 221, 225, 227, 231, 234, 236, 244, 245, 246, 249, 250, 271, 272, 281, 282, 283, 286, 287, 289, 290, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1763, 1765, 1766, 1838, 1839, 1840, 1864, 1865, 1866, 1867, 1874, 1876, 1935, 1992, 2026, 2028, 2030, 2034, 2036, 2108, 2128, 2129, 2130, 2131, 2133, 2134, 2135, 2136, 2138, 2139, 2194, 2223, 2226, 2257, 2300, 2301, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 72, 130, 131, 132, 141, 177, 181, 223, 229, 230, 233, 235, 243, 247, 248, 273, 274, 284, 285, 288, 291, 292, 293, 1717, 1764, 1852, 1863, 1875, 1990, 1991, 2032, 2109, 2132, 2137, 2222, 2225, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 71, 73, 130, 131, 132, 143, 175, 179, 181, 182, 221, 223, 225, 227, 230, 231, 234, 235, 243, 245, 246, 247, 248, 249, 250, 271, 273, 274, 283, 285, 286, 290, 292, 293, 294, 296, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1766, 1838, 1839, 1840, 1852, 1863, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1992, 2028, 2030, 2034, 2128, 2131, 2132, 2133, 2134, 2138, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 70, 72, 140, 141, 142, 176, 177, 178, 180, 229, 233, 236, 244, 272, 281, 282, 284, 287, 288, 289, 291, 295, 1762, 1765, 1864, 1935, 1991, 2026, 2032, 2036, 2108, 2109, 2129, 2130, 2135, 2136, 2137, 2139, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 1652, 1653, 1691, 1692, 1693, 1752, 1754, 1755, 1757, 1771, 1773, 1774, 1827, 1898, 2058, 2177, 2179, 2227, 2229, 2231, 2281, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 151, 152, 1654, 1655, 1750, 1751, 1753, 1756, 1772, 1824, 1825, 1826, 1897, 1900, 2054, 2056, 2279, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 150, 151, 1653, 1655, 1691, 1692, 1750, 1751, 1752, 1754, 1755, 1756, 1757, 1772, 1826, 1827, 1897, 1900, 2058, 2177, 2229, 2279, 2282, 2283, 2288, 2289, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(149, 152, 1652, 1654, 1693, 1753, 1771, 1773, 1774, 1824, 1825, 1898, 2054, 2056, 2179, 2227, 2231, 2281, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 34, 148, 149, 150, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1757, 1774, 1824, 1825, 1826, 1897, 1898, 2056, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(33, 35, 151, 152, 1653, 1753, 1755, 1756, 1771, 1772, 1773, 1827, 1900, 2054, 2058, 2229, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 226, 228, 275, 276, 277, 278, 279, 280, 1721, 1722, 1727, 1775, 1869, 1870, 2029, 2035, 2037, 2121, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(222, 224, 1719, 1720, 1776, 1777, 1778, 1779, 1868, 2027, 2033, 2119, 2120, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 228, 275, 276, 277, 279, 1719, 1727, 1776, 1777, 1778, 1779, 1869, 1870, 2027, 2029, 2035, 2120, 2121, 2124, 2125, 2126, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 224, 226, 278, 280, 1720, 1721, 1722, 1775, 1868, 2033, 2037, 2119, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 226, 228, 275, 276, 279, 280, 1719, 1720, 1721, 1722, 1775, 1777, 1778, 1779, 1868, 1869, 2027, 2029, 2033, 2035, 2037, 2119, 2124, 2125, 2126, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 277, 278, 1727, 1776, 1870, 2120, 2121, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 207, 208, 209, 210, 211, 212, 213, 214, 216, 217, 218, 219, 220, 265, 267, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 205, 206, 215, 266, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 210, 213, 214, 215, 216, 218, 219, 220, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 208, 209, 211, 212, 217, 265, 266, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 205, 206, 207, 209, 210, 211, 212, 215, 217, 219, 220, 265, 267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 208, 213, 214, 216, 218, 266, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 71, 72, 130, 140, 141, 143, 175, 177, 178, 179, 180, 181, 182, 221, 223, 227, 229, 230, 231, 234, 236, 243, 245, 246, 247, 249, 250, 271, 272, 273, 281, 283, 284, 285, 286, 288, 290, 292, 293, 294, 295, 296, 1717, 1760, 1763, 1766, 1839, 1840, 1863, 1864, 1866, 1874, 1990, 1991, 1992, 2026, 2028, 2034, 2036, 2108, 2128, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2138, 2139, 2194, 2226, 2257, 2300, 2301, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 73, 131, 132, 142, 176, 225, 233, 235, 244, 248, 274, 282, 287, 289, 291, 1716, 1718, 1761, 1762, 1764, 1765, 1838, 1852, 1865, 1867, 1875, 1876, 1935, 2030, 2032, 2109, 2129, 2137, 2222, 2223, 2225, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 72, 130, 131, 132, 140, 176, 177, 179, 180, 182, 223, 227, 230, 234, 236, 243, 244, 247, 248, 249, 272, 273, 281, 282, 283, 285, 286, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1764, 1766, 1838, 1840, 1852, 1864, 1865, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2130, 2131, 2133, 2134, 2135, 2137, 2139, 2194, 2222, 2257, 2300, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 141, 142, 143, 175, 178, 181, 221, 225, 229, 231, 233, 235, 245, 246, 250, 271, 274, 284, 287, 1761, 1765, 1839, 1863, 1875, 2034, 2036, 2108, 2109, 2128, 2129, 2132, 2136, 2138, 2223, 2225, 2226, 2301, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 72, 73, 130, 132, 141, 142, 175, 177, 178, 182, 221, 223, 225, 229, 230, 231, 233, 234, 235, 243, 244, 245, 249, 274, 281, 283, 285, 286, 287, 288, 289, 292, 293, 294, 295, 296, 1716, 1760, 1761, 1764, 1766, 1838, 1839, 1852, 1863, 1865, 1867, 1935, 1990, 1992, 2028, 2030, 2032, 2036, 2108, 2109, 2128, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2138, 2194, 2222, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 131, 140, 143, 176, 179, 180, 181, 227, 236, 246, 247, 248, 250, 271, 272, 273, 282, 284, 290, 291, 1717, 1718, 1762, 1763, 1765, 1840, 1864, 1866, 1874, 1875, 1876, 1991, 2026, 2034, 2129, 2137, 2139, 2223, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 31, 32, 33, 34, 35, 148, 149, 152, 1652, 1654, 1693, 1752, 1753, 1754, 1755, 1756, 1771, 1772, 1774, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 23, 150, 151, 1653, 1655, 1691, 1692, 1750, 1751, 1757, 1773, 1898, 2056, 2058, 2177, 2281, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 32, 33, 34, 35, 150, 1652, 1653, 1654, 1655, 1691, 1751, 1752, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 1827, 1897, 1900, 2058, 2177, 2179, 2227, 2279, 2281, 2282, 2288, 2289, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 31, 148, 149, 151, 152, 1692, 1693, 1750, 1754, 1825, 1898, 2054, 2056, 2229, 2231, 2283, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 33, 34, 148, 149, 150, 151, 1652, 1654, 1691, 1692, 1693, 1751, 1752, 1753, 1757, 1771, 1773, 1774, 1825, 1827, 1897, 1898, 1900, 2056, 2058, 2177, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 31, 32, 35, 152, 1653, 1655, 1750, 1754, 1755, 1756, 1772, 1824, 1826, 2054, 2179, 2281, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 222, 224, 226, 275, 276, 277, 278, 279, 280, 1721, 1722, 1727, 1777, 1778, 1779, 1870, 2033, 2035, 2037, 2119, 2121, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 228, 1719, 1720, 1775, 1776, 1868, 1869, 2027, 2029, 2120, 2124, 2126, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 222, 226, 276, 277, 278, 1719, 1727, 1776, 1777, 1778, 1868, 1869, 2027, 2029, 2033, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 224, 228, 275, 279, 280, 1720, 1721, 1722, 1775, 1779, 1870, 2035, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 276, 277, 278, 279, 280, 1720, 1721, 1722, 1775, 1776, 1868, 2029, 2033, 2035, 2119, 2120, 2121, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 228, 275, 1719, 1727, 1777, 1778, 1779, 1869, 1870, 2027, 2037, 2124, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 208, 209, 211, 213, 217, 218, 220, 266, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(207, 210, 212, 214, 215, 216, 219, 265, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 206, 208, 212, 213, 215, 216, 217, 218, 219, 220, 266, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 207, 209, 210, 211, 214, 265, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 205, 206, 208, 209, 210, 211, 214, 215, 219, 265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 207, 212, 213, 216, 217, 218, 220)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 130, 131, 132, 140, 142, 176, 177, 178, 179, 181, 182, 221, 230, 231, 233, 235, 236, 243, 244, 245, 246, 247, 248, 249, 271, 273, 274, 281, 283, 286, 289, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1765, 1839, 1852, 1863, 1864, 1865, 1866, 1867, 1875, 1876, 1935, 1990, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2129, 2131, 2132, 2133, 2135, 2136, 2194, 2223, 2225, 2300, 2301, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(14, 15, 72, 73, 141, 143, 175, 180, 223, 225, 227, 229, 234, 250, 272, 282, 284, 285, 287, 288, 290, 291, 1764, 1766, 1838, 1840, 1874, 1991, 1992, 2128, 2130, 2134, 2137, 2138, 2139, 2222, 2226, 2257, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 71, 72, 73, 131, 132, 140, 141, 142, 176, 177, 178, 179, 180, 182, 221, 225, 227, 229, 231, 235, 236, 243, 244, 245, 246, 248, 271, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 292, 293, 294, 296, 1717, 1718, 1761, 1762, 1763, 1764, 1765, 1840, 1852, 1865, 1874, 1875, 1876, 1990, 1991, 1992, 2028, 2030, 2032, 2034, 2108, 2131, 2132, 2133, 2135, 2137, 2138, 2222, 2223, 2226, 2257, 2300, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 130, 143, 175, 181, 223, 230, 233, 234, 247, 249, 250, 272, 290, 291, 295, 1716, 1760, 1766, 1838, 1839, 1863, 1864, 1866, 1867, 1935, 2026, 2036, 2109, 2128, 2129, 2130, 2134, 2136, 2139, 2194, 2225, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 72, 130, 131, 132, 140, 141, 175, 176, 177, 179, 180, 182, 223, 229, 230, 234, 236, 243, 244, 245, 247, 248, 250, 271, 273, 274, 281, 282, 285, 286, 288, 289, 291, 294, 296, 1716, 1717, 1718, 1760, 1762, 1764, 1766, 1839, 1852, 1863, 1865, 1866, 1867, 1875, 1876, 2026, 2030, 2032, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2194, 2222, 2223, 2225, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 142, 143, 178, 181, 221, 225, 227, 231, 233, 235, 246, 249, 272, 283, 284, 287, 290, 292, 293, 295, 1761, 1763, 1765, 1838, 1840, 1864, 1874, 1935, 1990, 1991, 1992, 2028, 2034, 2036, 2137, 2138, 2139, 2226)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 32, 33, 148, 149, 150, 151, 152, 1653, 1654, 1692, 1750, 1751, 1754, 1755, 1756, 1757, 1771, 1772, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2179, 2227, 2229, 2231, 2279, 2288, 2289, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 31, 34, 35, 1652, 1655, 1691, 1693, 1752, 1753, 1773, 1774, 2177, 2281, 2282, 2283, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 1653, 1654, 1655, 1691, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1774, 1824, 1825, 2054, 2056, 2179, 2227, 2229, 2231, 2288, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(152, 1652, 1692, 1772, 1826, 1827, 1897, 1898, 1900, 2058, 2177, 2279, 2281, 2282, 2283, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 31, 32, 33, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1754, 1757, 1771, 1772, 1824, 1826, 1827, 1900, 2056, 2058, 2177, 2179, 2227, 2231, 2279, 2281, 2283, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 34, 35, 1751, 1752, 1753, 1755, 1756, 1773, 1774, 1825, 1897, 1898, 2054, 2229, 2282, 2288, 2289, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 1719, 1721, 1722, 1727, 1775, 1776, 1777, 1779, 1869, 1870, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 1720, 1778, 1868, 2027)</t>
+    <t xml:space="preserve">c(13, 14, 15, 70, 72, 73, 130, 131, 141, 142, 143, 175, 176, 177, 179, 180, 182, 221, 223, 225, 227, 229, 230, 234, 236, 245, 247, 250, 271, 272, 274, 282, 283, 284, 285, 286, 288, 289, 292, 296, 1716, 1717, 1718, 1760, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 2026, 2028, 2032, 2036, 2108, 2109, 2131, 2132, 2134, 2137, 2138, 2139, 2194, 2225, 2226, 2257, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 132, 140, 178, 181, 231, 233, 235, 243, 244, 246, 248, 249, 273, 281, 287, 290, 291, 293, 294, 295, 1761, 1840, 1852, 1863, 1864, 1865, 1992, 2030, 2034, 2128, 2129, 2130, 2133, 2135, 2136, 2222, 2223, 2300, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 72, 73, 130, 131, 132, 140, 142, 175, 176, 177, 178, 180, 181, 182, 221, 225, 229, 230, 234, 235, 236, 244, 245, 247, 248, 249, 250, 273, 283, 284, 286, 287, 288, 290, 291, 293, 296, 1716, 1717, 1718, 1761, 1762, 1763, 1764, 1766, 1838, 1839, 1852, 1863, 1865, 1866, 1874, 1875, 1991, 2026, 2028, 2030, 2032, 2108, 2109, 2128, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2222, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 141, 143, 179, 223, 227, 231, 233, 243, 246, 271, 272, 274, 281, 282, 285, 289, 292, 294, 295, 1760, 1765, 1840, 1864, 1867, 1876, 1935, 1990, 1992, 2034, 2036, 2129, 2130, 2194, 2223, 2225, 2226, 2257, 2300, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 72, 130, 132, 141, 142, 176, 177, 178, 179, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 244, 245, 246, 247, 249, 250, 271, 272, 273, 282, 283, 285, 286, 287, 288, 289, 291, 292, 293, 294, 296, 1717, 1718, 1763, 1765, 1838, 1840, 1863, 1866, 1867, 1874, 1876, 1935, 1991, 1992, 2030, 2034, 2036, 2108, 2130, 2131, 2132, 2133, 2134, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 73, 131, 140, 143, 175, 180, 181, 243, 248, 274, 281, 284, 290, 295, 1716, 1760, 1761, 1762, 1764, 1766, 1839, 1852, 1864, 1865, 1875, 1990, 2026, 2028, 2032, 2109, 2128, 2129, 2135, 2136, 2137, 2257, 2301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 34, 35, 148, 149, 1652, 1653, 1654, 1691, 1692, 1693, 1752, 1753, 1756, 1772, 1774, 1824, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(32, 33, 150, 151, 152, 1655, 1750, 1751, 1754, 1755, 1757, 1771, 1773, 1825, 1826, 1898, 2283, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 31, 33, 34, 35, 148, 149, 1652, 1653, 1655, 1692, 1693, 1750, 1753, 1754, 1755, 1756, 1771, 1772, 1773, 1825, 1826, 1827, 1898, 1900, 2058, 2177, 2179, 2227, 2231, 2279, 2282, 2283, 2288, 2289, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 32, 150, 151, 152, 1654, 1691, 1751, 1752, 1757, 1774, 1824, 1897, 2054, 2056, 2229, 2281, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 34, 148, 149, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1752, 1753, 1754, 1755, 1756, 1824, 1825, 1827, 1897, 1900, 2058, 2177, 2179, 2229, 2231, 2281, 2282, 2283, 2288, 2289, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 35, 150, 1693, 1750, 1751, 1757, 1771, 1772, 1773, 1774, 1826, 1898, 2054, 2056, 2227, 2279, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 222, 226, 277, 278, 279, 1719, 1721, 1722, 1727, 1775, 1779, 1868, 1869, 1870, 2029, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 224, 228, 275, 276, 280, 1720, 1776, 1777, 1778, 2027, 2033, 2035, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 222, 224, 228, 275, 276, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1868, 1869, 1870, 2027, 2033, 2035, 2037, 2119, 2120, 2124, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 226, 277, 1775, 1776, 1777, 1778, 1779, 2029, 2121, 2125, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1727, 1775, 1776, 1777, 1779, 1869, 2027, 2029, 2037, 2119, 2120, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 228, 275, 1722, 1778, 1868, 1870, 2033, 2035, 2121, 2124, 2125, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 207, 208, 211, 212, 214, 215, 216, 217, 218, 220, 265, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 206, 209, 210, 213, 219, 266, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 206, 207, 208, 209, 210, 214, 215, 218, 220, 265, 266, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 211, 212, 213, 216, 217, 219, 267, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 208, 210, 211, 212, 213, 214, 215, 216, 219, 220, 265, 266, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(206, 207, 209, 217, 218, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 71, 72, 73, 131, 132, 141, 142, 175, 176, 177, 178, 179, 180, 182, 221, 227, 230, 231, 233, 234, 236, 244, 245, 246, 249, 250, 271, 272, 274, 281, 282, 284, 285, 287, 288, 293, 294, 295, 1716, 1718, 1762, 1763, 1765, 1838, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2108, 2109, 2129, 2130, 2131, 2132, 2135, 2136, 2137, 2139, 2222, 2223, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 130, 140, 143, 181, 223, 225, 229, 235, 243, 247, 248, 273, 283, 286, 289, 290, 291, 292, 296, 1717, 1760, 1761, 1764, 1766, 1839, 1840, 1935, 2036, 2128, 2133, 2134, 2138, 2194, 2225, 2226, 2257, 2300, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 180, 182, 223, 225, 229, 231, 235, 236, 243, 244, 246, 247, 249, 272, 281, 282, 283, 284, 285, 286, 288, 290, 291, 292, 293, 294, 1716, 1717, 1762, 1764, 1838, 1863, 1866, 1867, 1874, 1875, 1876, 1991, 1992, 2026, 2028, 2032, 2034, 2036, 2108, 2109, 2129, 2130, 2131, 2133, 2134, 2135, 2136, 2137, 2139, 2222, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 72, 178, 179, 181, 221, 227, 230, 233, 234, 245, 248, 250, 271, 273, 274, 287, 289, 295, 296, 1718, 1760, 1761, 1763, 1765, 1766, 1839, 1840, 1852, 1864, 1865, 1935, 1990, 2030, 2128, 2132, 2138, 2194, 2223, 2257)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 73, 131, 132, 140, 141, 142, 143, 175, 176, 177, 179, 180, 181, 182, 221, 227, 230, 234, 235, 243, 244, 245, 246, 247, 248, 249, 273, 274, 281, 282, 284, 285, 287, 288, 289, 293, 294, 1716, 1717, 1718, 1761, 1762, 1763, 1764, 1765, 1766, 1840, 1852, 1863, 1865, 1866, 1867, 1874, 1876, 1935, 2026, 2028, 2030, 2032, 2034, 2108, 2130, 2131, 2132, 2133, 2135, 2137, 2138, 2139, 2223, 2257, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 72, 130, 178, 223, 225, 229, 231, 233, 236, 250, 271, 272, 283, 286, 290, 291, 292, 295, 296, 1760, 1838, 1839, 1864, 1875, 1990, 1991, 1992, 2036, 2109, 2128, 2129, 2134, 2136, 2194, 2222, 2225, 2226, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 23, 31, 34, 35, 149, 150, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1771, 1772, 1773, 1824, 1826, 1897, 1898, 2054, 2056, 2177, 2227, 2231, 2282, 2283, 2288, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 32, 33, 148, 151, 152, 1755, 1757, 1774, 1825, 1827, 1900, 2058, 2179, 2229, 2279, 2281, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 32, 33, 35, 149, 150, 151, 1652, 1654, 1655, 1691, 1693, 1750, 1751, 1753, 1755, 1756, 1757, 1771, 1772, 1774, 1824, 1825, 1826, 1827, 1898, 2054, 2056, 2058, 2179, 2229, 2231, 2281, 2283, 2288, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 31, 34, 148, 152, 1653, 1692, 1752, 1754, 1773, 1897, 1900, 2177, 2227, 2279, 2282, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 33, 148, 150, 151, 1653, 1654, 1655, 1691, 1693, 1750, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1827, 1898, 1900, 2054, 2058, 2177, 2227, 2229, 2231, 2281, 2282, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 34, 35, 149, 152, 1652, 1692, 1751, 1752, 1754, 1825, 1826, 1897, 2056, 2179, 2279, 2283, 2288, 2289, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 222, 224, 226, 276, 278, 279, 280, 1719, 1720, 1722, 1727, 1776, 1777, 1779, 1869, 2029, 2033, 2035, 2119, 2120, 2121, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 228, 275, 277, 1721, 1775, 1778, 1868, 1870, 2027, 2037, 2124, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 222, 224, 226, 228, 275, 280, 1719, 1720, 1721, 1722, 1775, 1777, 1778, 1779, 1869, 1870, 2029, 2033, 2037, 2119, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 276, 277, 278, 279, 1727, 1776, 1868, 2027, 2035, 2120, 2121, 2124, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 224, 228, 275, 276, 278, 279, 280, 1722, 1775, 1776, 1778, 1869, 1870, 2033, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 222, 226, 277, 1719, 1720, 1721, 1727, 1777, 1779, 1868, 2027, 2029, 2035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 208, 210, 211, 212, 213, 217, 218, 219, 220, 265, 266, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 206, 207, 209, 214, 215, 216, 267, 268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 208, 209, 210, 211, 212, 214, 215, 218, 219, 220, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 207, 213, 216, 217, 265, 266, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 207, 208, 209, 212, 215, 216, 218, 219, 265, 266, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 210, 211, 213, 214, 217, 220, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 71, 72, 130, 131, 142, 143, 175, 176, 177, 179, 180, 181, 221, 223, 227, 235, 236, 243, 244, 248, 249, 271, 272, 274, 281, 282, 283, 284, 285, 286, 288, 289, 290, 291, 294, 295, 1717, 1760, 1761, 1762, 1764, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1866, 1867, 1874, 1876, 1991, 1992, 2030, 2034, 2036, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2138, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 73, 132, 140, 141, 178, 182, 225, 229, 230, 231, 233, 234, 245, 246, 247, 250, 273, 287, 292, 293, 296, 1716, 1718, 1763, 1838, 1865, 1875, 1935, 1990, 2026, 2028, 2032, 2108, 2136, 2137, 2139, 2194, 2222)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 130, 140, 141, 142, 175, 177, 178, 179, 181, 182, 223, 225, 227, 230, 231, 233, 234, 235, 236, 244, 246, 248, 249, 250, 273, 274, 281, 282, 285, 286, 287, 288, 289, 290, 291, 293, 1717, 1760, 1762, 1763, 1764, 1765, 1766, 1839, 1852, 1865, 1866, 1867, 1874, 1876, 1935, 1990, 1991, 1992, 2026, 2030, 2036, 2108, 2128, 2132, 2133, 2136, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 131, 132, 143, 176, 180, 221, 229, 243, 245, 247, 271, 272, 283, 284, 292, 294, 295, 296, 1716, 1718, 1761, 1838, 1840, 1863, 1864, 1875, 2028, 2032, 2034, 2109, 2129, 2130, 2131, 2134, 2135, 2137, 2138, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 71, 130, 131, 142, 143, 177, 179, 181, 182, 225, 227, 229, 230, 231, 233, 243, 244, 246, 247, 248, 271, 272, 273, 274, 281, 282, 283, 284, 285, 287, 288, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1864, 1866, 1867, 1874, 1990, 1991, 1992, 2026, 2032, 2036, 2109, 2128, 2130, 2133, 2134, 2135, 2137, 2139, 2194, 2222, 2223, 2225, 2257, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 70, 72, 73, 132, 140, 141, 175, 176, 178, 180, 221, 223, 234, 235, 236, 245, 249, 250, 286, 289, 1762, 1852, 1865, 1875, 1876, 1935, 2028, 2030, 2034, 2108, 2129, 2131, 2132, 2136, 2138, 2226, 2300, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 31, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1693, 1753, 1754, 1755, 1756, 1757, 1771, 1774, 1825, 1826, 1897, 1898, 1900, 2056, 2058, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 32, 33, 34, 35, 1691, 1692, 1750, 1751, 1752, 1772, 1773, 1824, 1827, 2054, 2229, 2283, 2288, 2289, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 34, 149, 150, 151, 152, 1653, 1655, 1693, 1750, 1755, 1756, 1757, 1771, 1774, 1824, 1825, 1826, 1827, 1897, 1900, 2054, 2056, 2177, 2179, 2229, 2279, 2282, 2283, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 33, 35, 148, 1652, 1654, 1691, 1692, 1751, 1752, 1753, 1754, 1772, 1773, 1898, 2058, 2227, 2231, 2281, 2288)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 23, 31, 32, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1691, 1692, 1693, 1750, 1751, 1752, 1754, 1756, 1757, 1772, 1773, 1824, 1826, 1827, 1897, 2054, 2058, 2177, 2227, 2229, 2279, 2283, 2288, 2289, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 33, 34, 1655, 1753, 1755, 1771, 1774, 1825, 1898, 1900, 2056, 2179, 2231, 2281, 2282, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 44, 222, 275, 276, 279, 280, 1720, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1870, 2027, 2029, 2033, 2035, 2121, 2124, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 224, 226, 228, 277, 278, 1719, 1721, 1722, 1869, 2037, 2119, 2120, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 224, 226, 228, 275, 276, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1868, 1870, 2029, 2035, 2037, 2120, 2124, 2125, 2126, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 277, 278, 1776, 1777, 1778, 1779, 1869, 2027, 2033, 2119, 2121, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 222, 224, 226, 228, 275, 276, 278, 279, 280, 1721, 1727, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2035, 2037, 2119, 2120, 2121, 2124, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 277, 1719, 1720, 1722, 1777, 2027, 2029, 2033, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 206, 207, 208, 210, 211, 212, 213, 215, 216, 218, 219, 220, 265, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 209, 214, 217, 266, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 205, 206, 207, 208, 210, 211, 212, 214, 215, 216, 218, 219, 220, 267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 209, 213, 217, 265, 266, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 204, 206, 207, 208, 209, 210, 211, 212, 216, 217, 218, 220, 265, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 205, 213, 214, 215, 219, 266, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 70, 71, 72, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 180, 181, 225, 229, 230, 231, 234, 235, 243, 244, 245, 247, 249, 250, 273, 281, 282, 283, 284, 286, 289, 292, 293, 294, 295, 296, 1716, 1718, 1760, 1762, 1763, 1764, 1765, 1838, 1839, 1840, 1863, 1864, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2108, 2109, 2128, 2130, 2131, 2132, 2133, 2134, 2137, 2138, 2139, 2226, 2301, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 73, 130, 179, 182, 221, 223, 227, 233, 236, 246, 248, 271, 272, 274, 285, 287, 288, 290, 291, 1717, 1761, 1766, 1852, 1865, 1866, 1867, 1935, 2036, 2129, 2135, 2136, 2194, 2222, 2223, 2225, 2257, 2300, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 131, 132, 175, 176, 178, 179, 181, 223, 225, 227, 230, 231, 234, 235, 236, 243, 244, 245, 246, 247, 249, 250, 272, 274, 281, 282, 284, 285, 286, 288, 290, 291, 292, 294, 295, 1716, 1760, 1763, 1765, 1766, 1864, 1865, 1866, 1875, 1876, 1990, 1991, 1992, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2132, 2133, 2134, 2137, 2139, 2194, 2222, 2223, 2226, 2257, 2300, 2301, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 140, 141, 142, 143, 177, 180, 182, 221, 229, 233, 248, 271, 273, 283, 287, 289, 293, 296, 1717, 1718, 1761, 1762, 1764, 1838, 1839, 1840, 1852, 1863, 1867, 1874, 1935, 2026, 2131, 2135, 2136, 2138, 2225, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 70, 72, 140, 141, 143, 175, 176, 179, 181, 182, 223, 225, 227, 229, 231, 234, 236, 243, 244, 245, 246, 271, 273, 274, 282, 283, 284, 285, 286, 288, 289, 291, 293, 294, 295, 296, 1717, 1718, 1760, 1762, 1764, 1765, 1766, 1840, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1992, 2026, 2028, 2032, 2036, 2108, 2129, 2130, 2132, 2133, 2136, 2137, 2138, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 73, 130, 131, 132, 142, 177, 178, 180, 221, 230, 233, 235, 247, 248, 249, 250, 272, 281, 287, 290, 292, 1716, 1761, 1763, 1838, 1839, 1852, 1935, 1991, 2030, 2034, 2109, 2128, 2131, 2134, 2135, 2139, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 149, 150, 151, 152, 1652, 1691, 1692, 1750, 1751, 1753, 1755, 1757, 1772, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 1900, 2054, 2058, 2177, 2179, 2227, 2231, 2281, 2282, 2283, 2289, 2290, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 33, 34, 35, 148, 1653, 1654, 1655, 1693, 1752, 1754, 1756, 1771, 1827, 2056, 2229, 2279, 2288, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 34, 148, 1652, 1653, 1655, 1692, 1693, 1750, 1751, 1752, 1757, 1773, 1825, 1826, 1827, 1897, 1898, 1900, 2056, 2058, 2177, 2179, 2227, 2229, 2279, 2281, 2282, 2288, 2289, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(33, 35, 149, 150, 151, 152, 1654, 1691, 1753, 1754, 1755, 1756, 1771, 1772, 1774, 1824, 2054, 2231, 2283, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1692, 1693, 1750, 1753, 1754, 1755, 1771, 1772, 1773, 1774, 1824, 1826, 1827, 1897, 1898, 1900, 2054, 2177, 2229, 2279, 2281, 2282, 2288, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 34, 35, 1691, 1751, 1752, 1756, 1757, 1825, 2056, 2058, 2179, 2227, 2231, 2283, 2289, 2290, 2292, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 224, 226, 228, 275, 276, 279, 280, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 2027, 2029, 2037, 2121, 2124, 2125, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 277, 278, 1719, 1720, 1721, 1870, 2033, 2035, 2119, 2120, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 224, 226, 275, 276, 277, 278, 280, 1719, 1722, 1727, 1775, 1776, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2035, 2120, 2124, 2125, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 228, 279, 1720, 1721, 1777, 2033, 2037, 2119, 2121, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 280, 1720, 1722, 1727, 1776, 1777, 1779, 1869, 1870, 2029, 2033, 2037, 2119, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 279, 1719, 1721, 1775, 1778, 1868, 2027, 2035, 2120, 2121, 2124, 2125, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 209, 211, 212, 213, 214, 216, 217, 218, 220, 267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(207, 208, 210, 215, 219, 265, 266, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 206, 207, 208, 210, 211, 214, 218, 220, 265, 266, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 209, 212, 213, 215, 216, 217, 219, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 213, 214, 215, 216, 217, 219, 265, 266, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(207, 208, 209, 210, 211, 212, 218, 220, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 73, 130, 131, 140, 175, 176, 177, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 235, 243, 244, 245, 248, 250, 271, 272, 273, 281, 282, 283, 284, 286, 288, 289, 290, 291, 292, 294, 295, 1717, 1718, 1761, 1762, 1764, 1765, 1766, 1838, 1863, 1864, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 2028, 2030, 2032, 2034, 2036, 2108, 2130, 2131, 2133, 2134, 2135, 2136, 2138, 2194, 2223, 2225, 2257, 2301, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 15, 71, 132, 141, 142, 143, 178, 231, 233, 234, 236, 246, 247, 249, 274, 285, 287, 293, 296, 1716, 1760, 1763, 1839, 1840, 1852, 1865, 1992, 2026, 2109, 2128, 2129, 2132, 2137, 2139, 2222, 2226, 2300, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(14, 15, 71, 72, 130, 140, 141, 142, 175, 176, 179, 180, 229, 230, 233, 234, 235, 236, 243, 244, 247, 248, 249, 250, 271, 272, 273, 274, 281, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 296, 1717, 1718, 1760, 1763, 1765, 1838, 1840, 1852, 1865, 1866, 1867, 1875, 1876, 1935, 1990, 2028, 2032, 2034, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2137, 2138, 2139, 2194, 2222, 2225, 2226, 2257, 2300, 2301, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 73, 131, 132, 143, 177, 178, 181, 182, 221, 223, 225, 227, 231, 245, 246, 282, 283, 295, 1716, 1761, 1762, 1764, 1766, 1839, 1863, 1864, 1874, 1991, 1992, 2026, 2030, 2036, 2135, 2136, 2223, 2302, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 14, 71, 72, 130, 132, 140, 142, 143, 175, 176, 177, 178, 179, 180, 182, 225, 229, 230, 233, 234, 236, 243, 245, 246, 248, 249, 250, 271, 272, 274, 283, 284, 285, 286, 287, 288, 289, 290, 293, 295, 296, 1718, 1760, 1761, 1762, 1763, 1765, 1838, 1840, 1863, 1864, 1866, 1867, 1875, 1935, 1990, 1991, 2026, 2032, 2034, 2036, 2108, 2128, 2129, 2130, 2131, 2133, 2134, 2136, 2137, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 73, 131, 141, 181, 221, 223, 227, 231, 235, 244, 247, 273, 281, 282, 291, 292, 294, 1716, 1717, 1764, 1766, 1839, 1852, 1865, 1874, 1876, 1992, 2028, 2030, 2109, 2132, 2135, 2138, 2139, 2194, 2222, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 20, 31, 32, 148, 149, 150, 152, 1652, 1653, 1654, 1655, 1691, 1693, 1751, 1753, 1754, 1755, 1756, 1771, 1772, 1774, 1824, 1825, 1897, 1898, 1900, 2054, 2056, 2058, 2179, 2227, 2229, 2231, 2279, 2289, 2290, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 23, 33, 34, 35, 151, 1692, 1750, 1752, 1757, 1773, 1826, 1827, 2177, 2281, 2282, 2283, 2288, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 32, 34, 150, 152, 1653, 1654, 1691, 1692, 1693, 1751, 1752, 1753, 1755, 1756, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2290, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 31, 33, 35, 148, 149, 151, 1652, 1655, 1750, 1754, 1757, 1771, 1897, 1898, 2288, 2289, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 32, 33, 148, 149, 150, 151, 1652, 1653, 1654, 1691, 1692, 1750, 1753, 1754, 1755, 1771, 1772, 1774, 1824, 1827, 1897, 1898, 2054, 2056, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2283, 2288, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 31, 34, 35, 152, 1655, 1693, 1751, 1752, 1756, 1757, 1773, 1825, 1826, 1900, 2058, 2282, 2289, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 1719, 1720, 1722, 1727, 1776, 1777, 1778, 1869, 1870, 2027, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 1721, 1775, 1779, 1868, 2224)</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1779, 1868, 1869, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 1776, 1777, 1778, 1870, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 1719, 1720, 1721, 1776, 1778, 1868, 1869, 1870, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 1722, 1727, 1775, 1777, 1779, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 207, 208, 210, 211, 214, 215, 218, 219, 220, 265, 266, 267, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 205, 206, 209, 212, 213, 216, 217, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 205, 206, 207, 208, 209, 210, 216, 217, 220, 265, 266, 267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 211, 212, 213, 214, 215, 218, 219, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 207, 209, 212, 214, 215, 216, 217, 218, 219, 220, 265, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 205, 206, 208, 210, 211, 213, 266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 130, 140, 141, 143, 231, 233, 234, 235, 236, 282, 283, 284, 285, 287, 290, 293, 294, 295, 296, 1717, 1718, 1764, 1766, 1838, 1852, 1863, 1864, 1990, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2222, 2223, 2225, 2226, 2300, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 131, 132, 142, 177, 229, 230, 281, 286, 288, 289, 291, 292, 1716, 1765, 1839, 1840, 1865, 1935, 1991, 2194, 2302, 2303)</t>
+    <t xml:space="preserve">c(41, 42, 44, 1719, 1720, 1721, 1722, 1775, 1776, 1779, 1870, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 1727, 1777, 1778, 1868, 1869, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 1719, 1720, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 2027, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 1721, 1722, 1727, 1870, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 206, 209, 210, 211, 212, 213, 215, 216, 217, 218, 220, 267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 207, 208, 214, 219, 265, 266, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 206, 207, 208, 212, 213, 214, 215, 216, 218, 220, 266, 267, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 209, 210, 211, 217, 219, 265, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 209, 210, 211, 212, 217, 218, 265, 266, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 208, 213, 214, 215, 216, 219, 220, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 72, 130, 132, 141, 142, 177, 231, 233, 234, 281, 282, 284, 285, 286, 289, 291, 295, 296, 1716, 1718, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2223, 2226, 2300, 2301, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 73, 131, 140, 143, 229, 230, 235, 236, 283, 287, 288, 290, 292, 293, 294, 1717, 1764, 1765, 2194, 2222, 2225, 2303, 2312)</t>
   </si>
   <si>
     <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(70, 72, 73, 130, 131, 140, 141, 229, 233, 236, 281, 282, 283, 284, 285, 286, 288, 291, 293, 294, 296, 1717, 1718, 1764, 1765, 1766, 1838, 1840, 1852, 1863, 1864, 1935, 1991, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2226, 2300, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 132, 142, 143, 177, 230, 231, 234, 235, 287, 289, 290, 292, 295, 1716, 1839, 1865, 1990, 1992, 2223, 2225, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 130, 131, 140, 230, 231, 233, 234, 235, 236, 282, 286, 289, 290, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1840, 1852, 1864, 1865, 1990, 1991, 1992, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2226, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 73, 132, 141, 142, 143, 177, 229, 281, 283, 284, 285, 287, 288, 291, 292, 293, 1839, 1863, 1935, 2026, 2223, 2225, 2300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 23, 31, 33, 34, 35, 149, 151, 152, 1652, 1653, 1654, 1655, 1692, 1693, 1752, 1753, 1754, 1755, 1757, 1771, 1772, 1773, 1824, 1825, 1827, 1897, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2279, 2282, 2283, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 32, 148, 150, 1691, 1750, 1751, 1756, 1774, 1826, 1898, 2229, 2231, 2281, 2288, 2289, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 149, 150, 151, 1654, 1655, 1691, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1774, 1824, 1825, 1826, 1827, 1898, 1900, 2054, 2058, 2179, 2227, 2229, 2279, 2281, 2289, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 35, 148, 152, 1652, 1653, 1692, 1693, 1750, 1773, 1897, 2056, 2177, 2231, 2282, 2283, 2288, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 23, 31, 33, 34, 35, 148, 149, 151, 152, 1652, 1653, 1654, 1655, 1692, 1693, 1750, 1751, 1753, 1754, 1755, 1756, 1757, 1771, 1773, 1824, 1826, 1827, 2054, 2177, 2227, 2229, 2231, 2281, 2282, 2288, 2290, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 32, 150, 1691, 1752, 1772, 1774, 1825, 1897, 1898, 1900, 2056, 2058, 2179, 2279, 2283, 2289, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 1721, 1727, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 1719, 1720, 1722, 1775, 1776, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 1719, 1720, 1721, 1722, 1727, 1777, 1778, 1779, 1869, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 1775, 1776, 1868, 1870, 2027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 44, 1719, 1720, 1721, 1722, 1777, 1779, 1869, 1870, 2027, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 1727, 1775, 1776, 1778, 1868)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 218, 220, 266, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 204, 216, 217, 219, 265, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 207, 210, 212, 214, 215, 218, 219, 220, 265, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(206, 208, 209, 211, 213, 216, 217, 266, 267)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 205, 206, 207, 211, 213, 214, 215, 216, 217, 218, 219, 220, 265, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 204, 208, 209, 210, 212, 266, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 142, 143, 177, 229, 230, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 290, 291, 294, 295, 1716, 1717, 1718, 1764, 1766, 1852, 1865, 1990, 1992, 2108, 2138, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(132, 140, 141, 231, 288, 289, 292, 293, 296, 1765, 1838, 1839, 1840, 1863, 1864, 1935, 1991, 2026, 2030, 2109, 2137, 2139, 2194, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 130, 131, 132, 140, 141, 177, 229, 230, 231, 233, 234, 281, 284, 287, 288, 290, 292, 294, 296, 1716, 1764, 1766, 1839, 1840, 1935, 1990, 1992, 2030, 2108, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 142, 143, 235, 236, 282, 283, 285, 286, 289, 291, 293, 295, 1717, 1718, 1765, 1838, 1852, 1863, 1864, 1865, 1991, 2026, 2109)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 130, 132, 141, 142, 143, 229, 231, 233, 234, 235, 281, 282, 283, 284, 286, 287, 288, 290, 291, 292, 293, 294, 296, 1716, 1717, 1718, 1838, 1839, 1840, 1864, 1935, 1990, 1991, 1992, 2108, 2137, 2138, 2139, 2225, 2226, 2301, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 131, 140, 177, 230, 236, 285, 289, 295, 1764, 1765, 1766, 1852, 1863, 1865, 2026, 2030, 2109, 2194, 2222, 2223, 2300, 2302, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 33, 35, 148, 149, 150, 151, 1652, 1653, 1655, 1691, 1692, 1693, 1750, 1751, 1753, 1755, 1756, 1757, 1774, 1824, 1827, 1897, 1900, 2054, 2056, 2058, 2179, 2227, 2231, 2279, 2288, 2290, 2292, 2293)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(32, 34, 152, 1654, 1752, 1754, 1771, 1772, 1773, 1825, 1826, 1898, 2177, 2229, 2281, 2282, 2283, 2289, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 148, 150, 152, 1653, 1654, 1655, 1691, 1692, 1693, 1753, 1754, 1755, 1772, 1773, 1774, 1824, 1825, 1826, 1897, 1898, 2054, 2056, 2177, 2179, 2229, 2231, 2282, 2283, 2289, 2290, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 149, 151, 1652, 1750, 1751, 1752, 1756, 1757, 1771, 1827, 1900, 2058, 2227, 2279, 2281, 2288, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 31, 33, 34, 148, 149, 150, 152, 1654, 1655, 1691, 1692, 1750, 1751, 1754, 1755, 1771, 1773, 1774, 1824, 1825, 1827, 1898, 1900, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2282, 2283, 2288, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 32, 35, 151, 1652, 1653, 1693, 1752, 1753, 1756, 1757, 1772, 1826, 1897, 2054, 2281, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 224, 226, 228, 276, 277, 279, 280, 1720, 1722, 1775, 1776, 1778, 1779, 1868, 1869, 2027, 2119, 2121, 2124, 2125, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 222, 275, 278, 1719, 1721, 1727, 1777, 1870, 2120, 2126, 2221)</t>
+    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 141, 142, 234, 282, 283, 285, 286, 287, 289, 290, 291, 292, 293, 296, 1716, 1718, 1764, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 2030, 2109, 2139, 2222, 2223, 2225, 2226, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(140, 143, 177, 229, 230, 231, 233, 235, 236, 281, 284, 288, 294, 295, 1717, 1838, 1992, 2026, 2108, 2137, 2138, 2194, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 283, 286, 287, 288, 289, 290, 296, 1716, 1718, 1764, 1765, 1766, 1838, 1840, 1863, 1864, 1865, 1935, 1990, 1991, 2108, 2137, 2138, 2139, 2194, 2223, 2225, 2300, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 130, 131, 132, 140, 282, 284, 285, 291, 292, 293, 294, 295, 1717, 1839, 1852, 1992, 2026, 2030, 2109, 2222, 2226, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 31, 32, 33, 34, 150, 152, 1652, 1653, 1654, 1693, 1751, 1752, 1753, 1754, 1755, 1756, 1773, 1774, 1824, 1825, 1827, 1897, 1898, 2054, 2058, 2177, 2179, 2227, 2279, 2281, 2282, 2283, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 35, 148, 149, 151, 1655, 1691, 1692, 1750, 1757, 1771, 1772, 1826, 1900, 2056, 2229, 2231, 2288, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 33, 34, 148, 149, 150, 151, 1652, 1654, 1655, 1691, 1693, 1751, 1753, 1755, 1756, 1757, 1772, 1826, 1827, 1897, 1898, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 35, 152, 1653, 1692, 1750, 1752, 1754, 1771, 1773, 1774, 1824, 1825, 1900, 2054, 2056, 2288, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 32, 33, 35, 149, 151, 152, 1653, 1654, 1692, 1750, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1824, 1825, 1897, 1900, 2054, 2058, 2177, 2179, 2227, 2231, 2282, 2283, 2288, 2289, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(23, 31, 34, 148, 150, 1652, 1655, 1691, 1693, 1751, 1774, 1826, 1827, 1898, 2056, 2229, 2279, 2281, 2290, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 44, 1722, 1727, 1775, 1776, 1777, 1778, 1868, 1870, 2027, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 1719, 1720, 1721, 1779, 1869, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1778, 1869, 2027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 1777, 1779, 1868, 1870, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 1720, 1722, 1727, 1775, 1778, 1779, 1868, 1869, 1870, 2027, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 1719, 1721, 1776, 1777, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 206, 208, 209, 211, 212, 213, 214, 215, 216, 217, 218, 265, 266, 268, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 207, 210, 219, 220, 267, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 205, 206, 207, 210, 212, 213, 214, 217, 218, 219, 220, 265, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 208, 209, 211, 215, 216, 266, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 203, 208, 209, 212, 214, 215, 217, 218, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(204, 205, 206, 207, 210, 211, 213, 216, 219)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73, 130, 132, 140, 141, 177, 231, 233, 234, 235, 284, 285, 287, 288, 289, 290, 291, 293, 294, 1716, 1717, 1764, 1765, 1838, 1839, 1840, 1852, 1864, 1935, 1990, 1991, 2026, 2030, 2108, 2109, 2137, 2138, 2194, 2223, 2225, 2226, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 131, 142, 143, 229, 230, 236, 281, 282, 283, 286, 292, 295, 296, 1718, 1766, 1863, 1865, 1992, 2139, 2222, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 73, 130, 131, 132, 140, 142, 230, 231, 234, 282, 286, 287, 288, 289, 290, 292, 293, 294, 295, 296, 1716, 1718, 1764, 1838, 1852, 1863, 1864, 1935, 1990, 2026, 2030, 2108, 2109, 2137, 2139, 2194, 2222, 2223, 2226, 2300, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 141, 143, 177, 229, 233, 235, 236, 281, 283, 284, 285, 291, 1717, 1765, 1766, 1839, 1840, 1865, 1991, 1992, 2138, 2225, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(130, 132, 140, 142, 143, 229, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 287, 289, 290, 292, 294, 295, 296, 1716, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1865, 2030, 2109, 2138, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 131, 141, 177, 230, 286, 288, 291, 293, 1717, 1852, 1864, 1935, 1990, 1991, 1992, 2026, 2108, 2137, 2139, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 20, 23, 32, 33, 149, 151, 152, 1653, 1654, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1757, 1772, 1773, 1774, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2179, 2227, 2229, 2231, 2281, 2289, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 19, 31, 34, 35, 148, 150, 1652, 1655, 1691, 1755, 1771, 1824, 2058, 2177, 2279, 2282, 2283, 2288, 2290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 34, 35, 149, 150, 151, 152, 1652, 1653, 1691, 1692, 1693, 1750, 1752, 1754, 1756, 1757, 1771, 1772, 1774, 1826, 1897, 1898, 2054, 2056, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 33, 148, 1654, 1655, 1751, 1753, 1755, 1773, 1824, 1825, 1827, 1900, 2058, 2177, 2179, 2288, 2289, 2290, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1753, 1756, 1772, 1773, 1824, 1825, 1826, 1827, 1900, 2054, 2177, 2227, 2231, 2279, 2283, 2288, 2289, 2290, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 23, 1751, 1752, 1754, 1755, 1757, 1771, 1774, 1897, 1898, 2056, 2058, 2179, 2229, 2281, 2282, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 275, 276, 278, 279, 280, 1719, 1720, 1775, 1776, 1777, 1778, 1868, 1869, 2027, 2120, 2121, 2124, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 224, 226, 228, 277, 1721, 1722, 1727, 1779, 1870, 2119, 2126, 2224)</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 222, 224, 226, 228, 275, 278, 279, 1720, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2119, 2120, 2121, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 276, 277, 280, 1719, 1721, 2027, 2124, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 226, 228, 275, 276, 277, 278, 279, 1720, 1721, 1722, 1775, 1776, 1779, 1870, 2027, 2119, 2121, 2124, 2125, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 224, 280, 1719, 1727, 1777, 1778, 1868, 1869, 2120, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 205, 207, 209, 210, 211, 212, 215, 217, 218, 219, 220, 267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(204, 206, 208, 213, 214, 216, 265, 266, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(203, 204, 205, 206, 207, 208, 212, 213, 214, 215, 216, 219, 265, 266, 267, 268, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 209, 210, 211, 217, 218, 220, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 205, 206, 207, 208, 209, 211, 212, 213, 214, 216, 217, 219, 220, 265, 266, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 204, 210, 215, 218, 267, 268, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 73, 130, 131, 132, 140, 141, 142, 143, 177, 180, 221, 223, 229, 231, 233, 234, 236, 243, 249, 271, 273, 274, 281, 282, 284, 286, 287, 288, 289, 290, 291, 292, 294, 295, 296, 1716, 1717, 1760, 1762, 1765, 1838, 1839, 1852, 1864, 1865, 1990, 1992, 2030, 2108, 2109, 2128, 2129, 2132, 2133, 2134, 2136, 2137, 2138, 2194, 2222, 2223, 2257, 2300, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 72, 175, 225, 227, 230, 235, 244, 245, 246, 247, 248, 250, 272, 283, 285, 293, 1718, 1761, 1763, 1764, 1766, 1840, 1863, 1866, 1867, 1935, 1991, 2026, 2130, 2131, 2135, 2139, 2225, 2226, 2312)</t>
+    <t xml:space="preserve">c(41, 44, 222, 226, 228, 277, 278, 279, 280, 1720, 1722, 1775, 1776, 1777, 1778, 1779, 1869, 2027, 2119, 2120, 2121, 2124, 2127, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 224, 275, 276, 1719, 1721, 1727, 1868, 1870, 2125, 2126, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 275, 276, 278, 279, 1719, 1720, 1722, 1727, 1775, 1777, 1778, 1868, 1869, 2121, 2125, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 277, 280, 1721, 1776, 1779, 1870, 2027, 2119, 2120, 2124, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 204, 205, 206, 209, 210, 211, 212, 216, 217, 218, 219, 266, 267, 268, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 207, 208, 213, 214, 215, 220, 265, 1899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 205, 206, 208, 209, 210, 211, 212, 213, 214, 215, 217, 218, 219, 266, 267)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 207, 216, 220, 265, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 202, 204, 205, 206, 208, 211, 212, 213, 214, 216, 219, 220, 265, 267, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(203, 207, 209, 210, 215, 217, 218, 266, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 71, 72, 130, 132, 140, 142, 143, 175, 180, 221, 223, 225, 229, 231, 233, 235, 236, 243, 247, 248, 249, 271, 273, 281, 283, 284, 286, 287, 288, 289, 290, 291, 292, 295, 296, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1839, 1852, 1863, 1865, 1867, 1935, 1992, 2030, 2108, 2109, 2129, 2131, 2132, 2133, 2134, 2135, 2136, 2139, 2222, 2223, 2226, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 73, 131, 141, 177, 227, 230, 234, 244, 245, 246, 250, 272, 274, 282, 285, 293, 294, 1716, 1717, 1838, 1840, 1864, 1866, 1990, 1991, 2026, 2128, 2130, 2137, 2138, 2194, 2225, 2257, 2300)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(15, 70, 71, 72, 73, 130, 132, 140, 177, 180, 221, 225, 227, 229, 230, 233, 234, 235, 236, 243, 244, 246, 247, 248, 250, 271, 272, 273, 274, 281, 282, 284, 287, 288, 290, 292, 293, 294, 296, 1716, 1718, 1761, 1763, 1765, 1766, 1838, 1840, 1864, 1865, 1990, 1991, 1992, 2030, 2108, 2109, 2131, 2133, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2225, 2257, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 131, 141, 142, 143, 175, 223, 231, 245, 249, 283, 285, 286, 289, 291, 295, 1717, 1760, 1762, 1764, 1839, 1852, 1863, 1866, 1867, 1935, 2026, 2128, 2129, 2130, 2132, 2134, 2223, 2226, 2300, 2301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 131, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 231, 234, 244, 247, 273, 274, 282, 283, 285, 286, 287, 288, 289, 295, 296, 1716, 1717, 1760, 1761, 1762, 1764, 1765, 1838, 1839, 1840, 1852, 1863, 1864, 1867, 1935, 1990, 1991, 1992, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2137, 2138, 2223, 2225, 2226, 2257, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(130, 132, 140, 230, 233, 235, 236, 243, 245, 246, 248, 249, 250, 271, 272, 281, 284, 290, 291, 292, 293, 294, 1718, 1763, 1766, 1865, 1866, 2026, 2134, 2135, 2136, 2139, 2194, 2222, 2300, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 32, 35, 148, 149, 150, 151, 1653, 1654, 1655, 1691, 1692, 1693, 1752, 1753, 1757, 1771, 1772, 1824, 1826, 1827, 1898, 1900, 2054, 2058, 2177, 2179, 2227, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 31, 33, 34, 152, 1652, 1750, 1751, 1754, 1755, 1756, 1773, 1774, 1825, 1897, 2056, 2229, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 33, 35, 148, 149, 150, 152, 1652, 1654, 1655, 1691, 1750, 1751, 1752, 1753, 1756, 1771, 1772, 1773, 1774, 1825, 1897, 2054, 2058, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 31, 32, 34, 151, 1653, 1692, 1693, 1754, 1755, 1757, 1824, 1826, 1827, 1898, 1900, 2056, 2177, 2289, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 34, 35, 148, 150, 151, 1652, 1654, 1655, 1691, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 1773, 1825, 1826, 1897, 1898, 1900, 2054, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2283, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 31, 32, 33, 149, 152, 1653, 1751, 1755, 1757, 1771, 1772, 1774, 1824, 1827, 2056, 2282, 2288, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 276, 280, 1719, 1720, 1776, 1778, 1868, 1869, 1870, 2027, 2119, 2120, 2124, 2125, 2126, 2127, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 275, 277, 278, 279, 1721, 1722, 1727, 1775, 1777, 1779, 2121, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 44, 222, 224, 275, 280, 1719, 1721, 1727, 1775, 1776, 1777, 1779, 1868, 1869, 2027, 2119, 2120, 2121, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(43, 226, 228, 276, 277, 278, 279, 1720, 1722, 1778, 1870, 2124, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 226, 228, 275, 276, 277, 278, 1719, 1721, 1722, 1775, 1777, 1779, 1869, 1870, 2027, 2120, 2121, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 44, 222, 224, 279, 280, 1720, 1727, 1776, 1778, 1868, 2119, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 203, 204, 205, 206, 210, 211, 212, 214, 218, 219, 220, 265, 266, 267, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 207, 208, 209, 213, 215, 216, 217, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 209, 210, 212, 213, 216, 218, 219, 266, 267, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(208, 211, 214, 215, 217, 220, 265, 268, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(201, 203, 204, 205, 206, 208, 209, 212, 213, 215, 216, 217, 219, 265, 266, 267, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(202, 207, 210, 211, 214, 218, 220, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 73, 130, 131, 140, 141, 143, 175, 177, 180, 223, 225, 230, 231, 233, 234, 235, 243, 244, 246, 247, 248, 249, 250, 271, 272, 273, 274, 282, 283, 286, 287, 289, 291, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1764, 1839, 1863, 1864, 1935, 1990, 1992, 2030, 2109, 2129, 2131, 2133, 2135, 2137, 2139, 2222, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 132, 142, 221, 227, 229, 236, 245, 281, 284, 285, 288, 290, 1716, 1762, 1763, 1765, 1766, 1838, 1840, 1852, 1865, 1866, 1867, 1991, 2026, 2108, 2128, 2130, 2132, 2134, 2136, 2138, 2194, 2223, 2257)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 73, 130, 141, 142, 143, 175, 180, 225, 227, 229, 230, 231, 234, 235, 236, 243, 244, 245, 247, 248, 250, 273, 282, 283, 285, 287, 288, 289, 290, 291, 295, 296, 1716, 1717, 1760, 1761, 1763, 1764, 1838, 1840, 1863, 1864, 1866, 1935, 1990, 1991, 1992, 2030, 2109, 2128, 2129, 2131, 2132, 2133, 2135, 2136, 2137, 2138, 2139, 2222, 2223, 2225, 2226, 2300, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 131, 132, 140, 177, 221, 223, 233, 246, 249, 271, 272, 274, 281, 284, 286, 292, 293, 294, 1718, 1762, 1765, 1766, 1839, 1852, 1865, 1867, 2026, 2108, 2130, 2134, 2194, 2257, 2301, 2302, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 73, 141, 142, 143, 175, 177, 225, 227, 229, 230, 231, 234, 236, 246, 249, 271, 272, 273, 282, 283, 284, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1864, 1865, 1935, 1990, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2134, 2136, 2137, 2138, 2139, 2194, 2222, 2257, 2300, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 130, 131, 132, 140, 180, 221, 223, 233, 235, 243, 244, 245, 247, 248, 250, 274, 281, 285, 1718, 1852, 1866, 1867, 1991, 2132, 2133, 2135, 2223, 2225, 2226, 2301, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 33, 35, 148, 149, 150, 152, 1693, 1750, 1752, 1755, 1756, 1757, 1897, 2054, 2058, 2227, 2279, 2281, 2282, 2288, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(32, 34, 151, 1691, 1692, 1751, 1753, 1754, 1898, 1900, 2056, 2229, 2231, 2283, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 23, 31, 32, 33, 34, 148, 150, 151, 1692, 1693, 1750, 1752, 1753, 1754, 1755, 1757, 1897, 2054, 2056, 2231, 2282, 2283, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 35, 149, 152, 1691, 1751, 1756, 1898, 1900, 2058, 2227, 2229, 2279, 2281, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 32, 34, 35, 148, 149, 150, 151, 1691, 1692, 1750, 1751, 1754, 1756, 1900, 2058, 2229, 2231, 2279, 2281, 2282, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 33, 152, 1693, 1752, 1753, 1755, 1757, 1897, 1898, 2054, 2056, 2227, 2283, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 43, 44, 222, 226, 275, 276, 277, 278, 279, 280, 1719, 1720, 1722, 1777, 1778, 1779, 1868, 1869, 2119, 2125, 2126, 2127, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 224, 228, 1721, 1727, 1775, 1776, 1870, 2027, 2120, 2121, 2124, 2221)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 222, 226, 228, 275, 277, 278, 279, 280, 1719, 1720, 1722, 1727, 1779, 1868, 1869, 2027, 2119, 2121, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 224, 276, 1721, 1775, 1776, 1777, 1778, 1870, 2120, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 275, 276, 279, 280, 1722, 1727, 1775, 1778, 1779, 1868, 1870, 2027, 2121, 2124, 2126, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(44, 228, 277, 278, 1719, 1720, 1721, 1776, 1777, 1869, 2119, 2120, 2125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 267, 268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 267, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 267, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 70, 72, 73, 130, 132, 140, 177, 221, 223, 227, 229, 230, 231, 235, 236, 245, 246, 247, 248, 249, 271, 272, 273, 284, 285, 286, 287, 288, 289, 290, 295, 1716, 1718, 1760, 1762, 1763, 1764, 1766, 1838, 1839, 1840, 1852, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2129, 2130, 2132, 2133, 2134, 2135, 2136, 2139, 2194, 2222, 2223, 2225, 2300, 2301, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 71, 131, 141, 142, 143, 225, 233, 234, 243, 244, 250, 274, 281, 282, 283, 291, 292, 293, 294, 296, 1717, 1761, 1765, 1863, 1864, 1865, 2128, 2131, 2137, 2138, 2226, 2257, 2302)</t>
+    <t xml:space="preserve">c(13, 70, 71, 72, 73, 132, 140, 142, 143, 175, 177, 180, 221, 223, 225, 229, 230, 231, 233, 236, 243, 244, 248, 249, 250, 271, 274, 282, 285, 286, 290, 291, 294, 296, 1716, 1717, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1839, 1840, 1852, 1865, 1866, 1935, 1990, 1991, 1992, 2026, 2109, 2128, 2129, 2130, 2132, 2133, 2136, 2137, 2138, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 130, 131, 141, 227, 234, 235, 245, 246, 247, 272, 273, 281, 283, 284, 287, 288, 289, 292, 293, 295, 1718, 1838, 1863, 1864, 1867, 2030, 2108, 2131, 2134, 2135, 2139, 2194, 2222, 2223, 2225)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 142, 143, 175, 180, 225, 229, 230, 233, 234, 235, 245, 247, 248, 249, 250, 271, 274, 281, 282, 285, 286, 287, 288, 289, 291, 293, 295, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1865, 1866, 1990, 1992, 2026, 2128, 2129, 2136, 2137, 2138, 2139, 2194, 2222, 2226, 2257, 2300, 2301, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(140, 141, 177, 221, 223, 227, 231, 236, 243, 244, 246, 272, 273, 283, 284, 290, 292, 294, 296, 1863, 1864, 1867, 1935, 1991, 2030, 2108, 2109, 2130, 2131, 2132, 2133, 2134, 2135, 2223, 2225, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 32, 35, 149, 150, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1771, 1772, 1773, 1774, 1824, 1827, 1897, 1898, 1900, 2054, 2056, 2177, 2179, 2227, 2281, 2282, 2283, 2288, 2290, 2292, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(31, 33, 34, 148, 151, 152, 1652, 1653, 1654, 1655, 1757, 1825, 1826, 2058, 2229, 2231, 2279, 2289, 2293, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 31, 32, 33, 35, 148, 149, 150, 1652, 1653, 1655, 1691, 1693, 1752, 1753, 1754, 1755, 1756, 1771, 1772, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 2054, 2058, 2231, 2281, 2282, 2283, 2288, 2289, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 34, 151, 152, 1654, 1692, 1750, 1751, 1757, 1773, 1900, 2056, 2177, 2179, 2227, 2229, 2279, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 20, 23, 33, 34, 148, 149, 150, 152, 1654, 1692, 1693, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2056, 2058, 2177, 2179, 2229, 2231, 2282, 2283, 2288, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 31, 32, 35, 151, 1652, 1653, 1655, 1691, 1750, 1771, 1772, 1773, 1774, 2054, 2227, 2279, 2281, 2289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 275, 277, 278, 279, 280, 1720, 1721, 1727, 1776, 1777, 1779, 1868, 1870, 2027, 2119, 2121, 2125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 276, 1719, 1722, 1775, 1778, 1869, 2120, 2124, 2126, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 224, 226, 228, 275, 276, 280, 1719, 1721, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 2027, 2121, 2124, 2125, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 222, 277, 278, 279, 1720, 1722, 1870, 2119, 2120, 2126, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(43, 44, 222, 224, 226, 228, 276, 277, 1719, 1720, 1727, 1775, 1776, 1777, 1779, 1868, 1869, 2027, 2119, 2124, 2125, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 275, 278, 279, 280, 1721, 1722, 1778, 1870, 2120, 2121, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 205, 206, 207, 208, 209, 210, 212, 215, 216, 219, 220, 265, 266, 267, 268, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 211, 213, 214, 217, 218, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 205, 206, 207, 209, 210, 211, 212, 215, 216, 218, 219, 220, 265, 266, 267, 1899, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 203, 204, 208, 213, 214, 217, 268, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(202, 204, 205, 206, 207, 208, 209, 210, 211, 214, 216, 218, 219, 220, 266, 268, 1899, 2230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(201, 203, 212, 213, 215, 217, 265, 267, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 72, 73, 131, 132, 141, 142, 175, 177, 180, 221, 225, 229, 230, 231, 233, 234, 235, 243, 245, 247, 248, 249, 273, 274, 281, 282, 286, 287, 288, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1865, 1867, 1935, 1991, 2026, 2030, 2108, 2109, 2129, 2130, 2135, 2136, 2138, 2194, 2222, 2223, 2257, 2300, 2301, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(71, 130, 140, 143, 223, 227, 236, 244, 246, 250, 271, 272, 283, 284, 285, 289, 290, 291, 1716, 1763, 1864, 1866, 1990, 1992, 2128, 2131, 2132, 2133, 2134, 2137, 2139, 2225, 2226, 2302, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 72, 73, 131, 140, 141, 143, 180, 223, 227, 229, 230, 231, 235, 236, 243, 244, 246, 249, 250, 272, 273, 274, 281, 282, 283, 286, 290, 291, 292, 293, 294, 295, 296, 1717, 1718, 1760, 1761, 1762, 1764, 1765, 1766, 1838, 1864, 1865, 1866, 1867, 1935, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2131, 2134, 2137, 2138, 2139, 2194, 2225, 2226, 2257, 2300, 2301, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 130, 132, 142, 175, 177, 221, 225, 233, 234, 245, 247, 248, 271, 284, 285, 287, 288, 289, 1716, 1763, 1839, 1840, 1852, 1863, 1990, 1991, 2130, 2132, 2133, 2135, 2136, 2222, 2223, 2302, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 73, 131, 140, 142, 143, 175, 177, 180, 223, 225, 230, 231, 234, 235, 236, 244, 247, 248, 249, 250, 273, 281, 283, 285, 287, 288, 290, 291, 292, 293, 295, 296, 1718, 1760, 1761, 1762, 1764, 1765, 1766, 1839, 1840, 1863, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2131, 2133, 2134, 2135, 2136, 2137, 2138, 2194, 2223, 2225, 2226, 2302, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 72, 130, 132, 141, 221, 227, 229, 233, 243, 245, 246, 271, 272, 274, 282, 284, 286, 289, 294, 1716, 1717, 1763, 1838, 1852, 1864, 1866, 1867, 2130, 2132, 2139, 2222, 2257, 2300, 2301, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(18, 19, 20, 31, 34, 1692, 1693, 1750, 1752, 1753, 1754, 1756, 1771, 1773, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2179, 2288, 2289, 2290, 2292, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 23, 32, 33, 35, 1691, 1751, 1755, 1757, 1772, 1774, 2177, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 33, 35, 1691, 1692, 1751, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 2056, 2177, 2179, 2289, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 34, 1693, 1750, 1752, 1754, 1827, 2054, 2058, 2288, 2290, 2292, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 20, 31, 32, 33, 34, 35, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1771, 1772, 1773, 1774, 1824, 1825, 2054, 2056, 2058, 2288, 2289, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 23, 1691, 1756, 1757, 1826, 1827, 2177, 2179, 2290, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 224, 226, 276, 277, 278, 279, 280, 1719, 1720, 1722, 1777, 1778, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 44, 222, 228, 275, 1721, 1727, 1775, 1776, 1779, 1868, 1869, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 222, 224, 228, 276, 277, 278, 280, 1719, 1720, 1721, 1727, 1775, 1777, 1778, 1870, 2119, 2121, 2125, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 226, 275, 279, 1722, 1776, 1779, 1868, 1869, 2027, 2120, 2124, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 226, 275, 277, 278, 280, 1720, 1721, 1722, 1727, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 224, 228, 276, 279, 1719, 1775, 1776, 1777, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 71, 72, 73, 130, 132, 141, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 243, 244, 246, 247, 249, 271, 272, 273, 274, 281, 282, 283, 284, 285, 287, 288, 294, 295, 296, 1718, 1760, 1761, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1863, 1865, 1866, 1935, 1990, 2026, 2030, 2130, 2133, 2134, 2135, 2137, 2138, 2223, 2225, 2226, 2257, 2301, 2303, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 131, 140, 142, 236, 245, 248, 250, 286, 289, 290, 291, 292, 293, 1716, 1717, 1762, 1852, 1864, 1867, 1991, 1992, 2128, 2129, 2131, 2132, 2136, 2139, 2194, 2222, 2300, 2302, 2312)</t>
   </si>
   <si>
     <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 73, 130, 131, 132, 140, 142, 143, 177, 221, 225, 229, 230, 231, 234, 236, 245, 246, 247, 248, 249, 250, 272, 273, 274, 284, 286, 287, 289, 291, 292, 293, 294, 295, 296, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1852, 1863, 1864, 1865, 1866, 1935, 1991, 2026, 2128, 2129, 2134, 2136, 2137, 2139, 2194, 2222, 2223, 2301, 2302, 2303, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 141, 223, 227, 233, 235, 243, 244, 271, 281, 282, 283, 285, 288, 290, 1716, 1717, 1839, 1840, 1867, 1990, 1992, 2030, 2130, 2131, 2132, 2133, 2135, 2138, 2225, 2226, 2257, 2300, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 72, 131, 140, 141, 142, 143, 223, 225, 227, 229, 230, 233, 234, 235, 236, 243, 244, 245, 247, 248, 249, 250, 271, 274, 282, 283, 285, 287, 289, 291, 292, 293, 295, 1716, 1717, 1760, 1762, 1763, 1764, 1765, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2130, 2131, 2132, 2134, 2136, 2137, 2225, 2226, 2257, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 130, 132, 177, 221, 231, 246, 272, 273, 281, 284, 286, 288, 290, 294, 296, 1718, 1761, 1766, 1838, 1867, 2129, 2133, 2135, 2138, 2139, 2194, 2222, 2223, 2300, 2301, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 32, 33, 34, 35, 149, 150, 152, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1756, 1897, 1900, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 23, 31, 148, 151, 1691, 1755, 1757, 1898, 2054, 2282, 2283, 2288, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 32, 33, 148, 150, 151, 152, 1691, 1693, 1750, 1751, 1753, 1754, 1755, 1757, 1897, 1898, 1900, 2058, 2229, 2231, 2279, 2282, 2283, 2289, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 31, 34, 35, 149, 1692, 1752, 1756, 2054, 2056, 2227, 2281, 2288, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 23, 31, 32, 33, 34, 35, 148, 150, 151, 152, 1691, 1692, 1750, 1751, 1752, 1755, 1756, 1897, 1898, 1900, 2058, 2227, 2282, 2288, 2289, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 149, 1693, 1753, 1754, 1757, 2054, 2056, 2229, 2231, 2279, 2281, 2283, 2290)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 224, 226, 228, 276, 280, 1720, 1722, 1727, 1776, 1777, 1779, 1868, 1869, 2119, 2120, 2121, 2124, 2125, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 222, 275, 277, 278, 279, 1719, 1721, 1775, 1778, 1870, 2027, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 228, 276, 277, 278, 279, 280, 1720, 1721, 1775, 1777, 1779, 1868, 1870, 2119, 2120, 2121, 2125, 2126)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(226, 275, 1719, 1722, 1727, 1776, 1778, 1869, 2027, 2124, 2127, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(42, 43, 44, 222, 224, 226, 228, 275, 278, 279, 280, 1721, 1722, 1776, 1777, 1778, 1869, 1870, 2027, 2119, 2120, 2125, 2126, 2127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(41, 276, 277, 1719, 1720, 1727, 1775, 1779, 1868, 2121, 2124, 2221, 2224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 267, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(268, 1899, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 267, 268, 2230)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 1899, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 267, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(266, 268, 1899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 130, 131, 132, 140, 141, 142, 177, 221, 223, 225, 231, 234, 235, 236, 244, 245, 246, 248, 249, 271, 272, 281, 282, 283, 284, 287, 289, 290, 292, 294, 295, 296, 1716, 1718, 1760, 1761, 1762, 1765, 1766, 1838, 1852, 1864, 1865, 1866, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2301, 2302)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 72, 73, 143, 227, 229, 230, 233, 243, 247, 250, 273, 274, 285, 286, 288, 291, 293, 1717, 1763, 1764, 1839, 1840, 1863, 1867, 1935, 1990, 1991, 2226, 2257, 2300, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 130, 131, 140, 142, 143, 177, 223, 225, 229, 230, 233, 234, 236, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 286, 288, 289, 290, 293, 294, 295, 296, 1716, 1717, 1718, 1761, 1762, 1764, 1765, 1766, 1852, 1863, 1864, 1865, 1866, 1990, 1992, 2128, 2129, 2130, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2226, 2257, 2301, 2302, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 132, 141, 221, 227, 231, 235, 243, 244, 245, 284, 285, 287, 291, 292, 1760, 1763, 1838, 1839, 1840, 1867, 1935, 1991, 2026, 2030, 2131, 2135, 2194, 2222, 2223, 2225, 2300, 2303, 2312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(15, 73, 131, 140, 141, 142, 143, 221, 223, 227, 229, 231, 233, 234, 235, 236, 243, 245, 246, 247, 248, 250, 271, 273, 274, 281, 282, 283, 284, 285, 287, 288, 290, 292, 293, 295, 296, 1717, 1718, 1760, 1762, 1763, 1764, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1992, 2030, 2128, 2129, 2133, 2134, 2137, 2138, 2139, 2223, 2225, 2257, 2300, 2301, 2302, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 70, 71, 72, 130, 132, 177, 225, 230, 244, 249, 272, 286, 289, 291, 294, 1716, 1761, 1765, 1766, 1838, 1839, 1935, 1991, 2026, 2130, 2131, 2132, 2135, 2136, 2194, 2222, 2226, 2303)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 20, 23, 31, 32, 33, 1691, 1692, 1693, 1752, 1753, 1754, 1755, 1756, 1771, 1774, 1824, 1827, 2054, 2058, 2179, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 34, 35, 1750, 1751, 1757, 1772, 1773, 1825, 1826, 2056, 2177, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1752, 1753, 1755, 1757, 1771, 1773, 1774, 1827, 2056, 2058, 2288, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 1751, 1754, 1756, 1772, 1824, 1825, 1826, 2054, 2177, 2179, 2289, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 33, 35, 1691, 1692, 1693, 1752, 1753, 1756, 1771, 1772, 1773, 1824, 1825, 1826, 2054, 2177, 2179, 2288, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 34, 1750, 1751, 1754, 1755, 1757, 1774, 1827, 2056, 2058, 2289, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 175, 177, 231, 233, 234, 236, 271, 273, 274, 1764, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 180, 229, 230, 235, 272, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 177, 180, 229, 230, 233, 234, 235, 236, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 175, 231, 271, 272, 273, 274, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 175, 177, 230, 233, 234, 235, 236, 271, 272, 273, 274, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 180, 229, 231, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 23, 31, 32, 33, 35, 1692, 1750, 1752, 1755, 1756, 1771, 1772, 1773, 1774, 1825, 1826, 2054, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 34, 1691, 1693, 1751, 1753, 1754, 1757, 1824, 1827, 2056, 2058, 2177, 2179)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1773, 1824, 1827, 2056, 2058, 2177, 2288, 2289, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 1692, 1693, 1757, 1771, 1772, 1774, 1825, 1826, 2054, 2179, 2290, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 35, 1692, 1693, 1750, 1751, 1754, 1756, 1757, 1771, 1774, 1824, 1825, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2290, 2292, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 32, 33, 34, 1691, 1752, 1753, 1755, 1772, 1773, 1826, 2289, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 177, 180, 229, 230, 231, 234, 235, 271, 273, 274, 1764)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 175, 233, 236, 272, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 175, 229, 230, 231, 233, 236, 271, 274, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 177, 180, 234, 235, 272, 273, 1764)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 229, 234, 235, 236, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 175, 177, 180, 230, 231, 233, 271)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 31, 32, 34, 35, 1691, 1750, 1751, 1752, 1755, 1756, 1757, 1771, 1772, 1824, 1825, 1827, 2056, 2058, 2179, 2288, 2289, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 33, 1692, 1693, 1753, 1754, 1773, 1774, 1826, 2054, 2177, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 20, 23, 31, 32, 33, 35, 1751, 1753, 1754, 1755, 1757, 1771, 1772, 1773, 1825, 1826, 1827, 2054, 2056, 2058, 2179, 2289, 2290, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 34, 1691, 1692, 1693, 1750, 1752, 1756, 1774, 1824, 2177, 2288, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 1692, 1693, 1751, 1754, 1755, 1756, 1772, 1824, 1825, 1826, 1827, 2054, 2058, 2177, 2288, 2289, 2290, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(19, 31, 1691, 1750, 1752, 1753, 1757, 1771, 1773, 1774, 2056, 2179, 2292, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 72, 177, 180, 229, 230, 231, 233, 234, 271, 273, 274, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(73, 175, 235, 236, 272, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 73, 175, 180, 229, 230, 233, 234, 236, 271, 272, 273, 274, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 177, 231, 235, 1764, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 175, 229, 231, 233, 234, 236, 271, 272, 274, 1764, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 177, 180, 230, 235, 273, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 33, 1691, 1750, 1752, 1753, 1754, 1757, 1771, 1773, 1774, 1824, 1825, 1826, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 31, 32, 34, 35, 1692, 1693, 1751, 1755, 1756, 1772, 1827)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 23, 32, 34, 35, 1691, 1692, 1693, 1750, 1751, 1754, 1756, 1771, 1772, 1774, 1824, 1826, 1827, 2056, 2177, 2179, 2289, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 31, 33, 1752, 1753, 1755, 1757, 1773, 1825, 2054, 2058, 2288, 2290, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 20, 32, 33, 35, 1692, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1826, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 23, 31, 34, 1691, 1693, 1750, 1751, 1752, 1754, 1825, 1827, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 175, 177, 229, 230, 233, 234, 272, 274, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 180, 231, 235, 236, 271, 273)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 175, 180, 229, 230, 233, 234, 235, 271, 272, 273, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 177, 231, 236, 274, 1764, 1765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 71, 73, 175, 177, 180, 229, 231, 234, 236, 274, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(72, 230, 233, 235, 271, 272, 273, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 31, 32, 33, 34, 35, 1691, 1692, 1750, 1751, 1753, 1754, 1756, 1757, 2058, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 23, 1693, 1752, 1755, 2054, 2056, 2288, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 31, 34, 35, 1691, 1692, 1693, 1750, 1754, 1756, 2054, 2058, 2288, 2289, 2290, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 32, 33, 1751, 1752, 1753, 1755, 1757, 2056, 2292)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 32, 33, 34, 1692, 1693, 1751, 1752, 1755, 1756, 1757, 2056, 2058, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(20, 23, 31, 35, 1691, 1750, 1753, 1754, 2054, 2288, 2289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 73, 175, 177, 229, 231, 233, 235, 271, 272, 273, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 180, 230, 234, 236, 274, 1764)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 177, 180, 229, 230, 233, 236, 271, 272, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 175, 231, 234, 235, 273, 274, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 175, 177, 180, 231, 233, 235, 236, 271, 1764, 1765, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 229, 230, 234, 272, 273, 274, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 20, 31, 34, 35, 1691, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2289, 2290, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 19, 23, 32, 33, 1692, 1693, 2056, 2058, 2288, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 34, 1692, 1693, 1750, 1752, 1753, 1754, 1755, 1757, 2056, 2058, 2288, 2289, 2290, 2293, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(23, 31, 32, 33, 35, 1691, 1751, 1756, 2054, 2292, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(18, 19, 23, 32, 35, 1691, 1693, 1750, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2292, 2293, 2294)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 20, 31, 33, 34, 1692, 1751, 2288, 2289, 2290, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 72, 73, 175, 229, 234, 235, 236, 271, 272, 274, 1764, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 177, 180, 230, 231, 233, 273, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 175, 229, 231, 233, 234, 235, 272, 273, 274, 1764, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 177, 180, 230, 236, 271, 1765, 1766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(71, 72, 73, 177, 180, 229, 231, 233, 234, 235, 236, 271, 272, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(70, 175, 230, 273, 274, 1764, 1765, 1766)</t>
+    <t xml:space="preserve">c(72, 73, 131, 141, 142, 143, 177, 221, 225, 231, 233, 243, 244, 245, 248, 249, 250, 271, 272, 273, 281, 283, 284, 286, 288, 289, 292, 293, 295, 296, 1716, 1717, 1718, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1852, 1863, 1864, 1865, 1866, 1935, 2026, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2194, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 130, 132, 140, 223, 227, 229, 230, 234, 235, 236, 246, 247, 274, 282, 285, 287, 290, 291, 294, 1760, 1839, 1840, 1867, 1990, 1991, 1992, 2030, 2135, 2222, 2223)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 72, 130, 132, 140, 141, 142, 143, 177, 223, 225, 227, 229, 230, 231, 233, 235, 236, 245, 246, 248, 249, 250, 272, 273, 274, 281, 282, 283, 285, 286, 287, 289, 290, 291, 293, 294, 295, 1716, 1760, 1761, 1762, 1839, 1852, 1863, 1864, 1865, 1867, 1935, 2030, 2128, 2131, 2133, 2134, 2135, 2136, 2138, 2194, 2225, 2226, 2257, 2301, 2302, 2303, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 73, 131, 221, 234, 243, 244, 247, 271, 284, 288, 292, 296, 1717, 1718, 1763, 1764, 1765, 1766, 1838, 1840, 1866, 1990, 1991, 1992, 2026, 2129, 2130, 2132, 2137, 2139, 2222, 2223, 2300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 23, 32, 33, 34, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1774, 1824, 2054, 2056, 2058, 2177, 2288, 2289, 2290, 2294)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(20, 31, 35, 1691, 1692, 1693, 1773, 1825, 1826, 1827, 2179, 2292, 2293, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 32, 33, 34, 35, 1692, 1693, 1752, 1753, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1827, 2054, 2056, 2177, 2288, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 31, 1691, 1750, 1751, 1754, 1825, 1826, 2058, 2179, 2289, 2290, 2292, 2293)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 20, 23, 31, 32, 35, 1750, 1754, 1755, 1756, 1757, 1771, 1772, 1774, 1824, 1825, 1827, 2054, 2056, 2179, 2288, 2289, 2290, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(19, 33, 34, 1691, 1692, 1693, 1751, 1752, 1753, 1773, 1826, 2058, 2177, 2292)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 43, 222, 226, 275, 278, 279, 280, 1719, 1720, 1722, 1775, 1776, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 44, 224, 228, 276, 277, 1721, 1727, 1777, 1778, 2127, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 42, 43, 224, 226, 275, 277, 279, 280, 1719, 1721, 1722, 1727, 1775, 1776, 1779, 1869, 1870, 2027, 2119, 2121, 2125, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(44, 222, 228, 276, 278, 1720, 1777, 1778, 1868, 2120, 2124, 2126, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(41, 222, 224, 226, 228, 275, 276, 278, 279, 280, 1720, 1727, 1775, 1776, 1777, 1870, 2027, 2119, 2120, 2121, 2124, 2126, 2221, 2224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(42, 43, 44, 277, 1719, 1721, 1722, 1778, 1779, 1868, 1869, 2125, 2127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 72, 73, 132, 140, 142, 177, 221, 225, 227, 230, 231, 234, 235, 236, 243, 244, 245, 247, 248, 249, 250, 271, 273, 274, 282, 283, 284, 285, 286, 287, 289, 290, 291, 296, 1717, 1718, 1760, 1761, 1763, 1765, 1838, 1839, 1852, 1863, 1864, 1865, 1867, 1990, 1992, 2026, 2030, 2129, 2130, 2131, 2132, 2133, 2134, 2136, 2137, 2138, 2194, 2222, 2226, 2300, 2301, 2303, 2312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 70, 71, 130, 131, 141, 143, 223, 229, 233, 246, 272, 281, 288, 292, 293, 294, 295, 1716, 1762, 1764, 1766, 1840, 1866, 1935, 1991, 2128, 2135, 2139, 2223, 2225, 2257, 2302, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 71, 72, 73, 131, 132, 140, 141, 142, 177, 221, 223, 225, 227, 230, 231, 233, 234, 243, 244, 245, 246, 247, 248, 271, 274, 283, 284, 285, 286, 289, 294, 295, 1716, 1717, 1761, 1762, 1763, 1764, 1765, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1990, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2134, 2135, 2136, 2137, 2139, 2225, 2226, 2257, 2300, 2301, 2312, 2313)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 130, 143, 229, 235, 236, 249, 250, 272, 273, 281, 282, 287, 288, 290, 291, 292, 293, 296, 1718, 1760, 1766, 1866, 1867, 1935, 1991, 2132, 2133, 2138, 2194, 2222, 2223, 2302, 2303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 71, 130, 131, 132, 141, 142, 143, 221, 223, 225, 227, 230, 231, 233, 234, 235, 243, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 284, 285, 288, 289, 290, 294, 1717, 1718, 1760, 1763, 1764, 1765, 1766, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2128, 2132, 2133, 2134, 2136, 2137, 2138, 2139, 2222, 2223, 2257, 2301, 2302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(15, 70, 72, 73, 140, 177, 229, 236, 244, 245, 283, 286, 287, 291, 292, 293, 295, 296, 1716, 1761, 1762, 1838, 2030, 2129, 2130, 2131, 2135, 2194, 2225, 2226, 2300, 2303, 2312, 2313)</t>
   </si>
 </sst>
 </file>
@@ -3026,19 +2753,19 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N26" t="n">
         <v>40</v>
       </c>
       <c r="O26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P26" t="n">
         <v>20</v>
@@ -3082,19 +2809,19 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
       </c>
       <c r="M27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P27" t="n">
         <v>20</v>
@@ -3138,19 +2865,19 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N28" t="n">
         <v>40</v>
       </c>
       <c r="O28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P28" t="n">
         <v>20</v>
@@ -3200,13 +2927,13 @@
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N29" t="n">
         <v>27</v>
       </c>
       <c r="O29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P29" t="n">
         <v>14</v>
@@ -3256,13 +2983,13 @@
         <v>2</v>
       </c>
       <c r="M30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N30" t="n">
         <v>27</v>
       </c>
       <c r="O30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P30" t="n">
         <v>14</v>
@@ -3312,13 +3039,13 @@
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N31" t="n">
         <v>27</v>
       </c>
       <c r="O31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P31" t="n">
         <v>14</v>
@@ -3362,19 +3089,19 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N32" t="n">
         <v>18</v>
       </c>
       <c r="O32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P32" t="n">
         <v>9</v>
@@ -3418,19 +3145,19 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N33" t="n">
         <v>18</v>
       </c>
       <c r="O33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P33" t="n">
         <v>9</v>
@@ -3474,19 +3201,19 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N34" t="n">
         <v>18</v>
       </c>
       <c r="O34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P34" t="n">
         <v>9</v>
@@ -3536,13 +3263,13 @@
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N35" t="n">
         <v>79</v>
       </c>
       <c r="O35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P35" t="n">
         <v>40</v>
@@ -3592,13 +3319,13 @@
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N36" t="n">
         <v>79</v>
       </c>
       <c r="O36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P36" t="n">
         <v>40</v>
@@ -3648,13 +3375,13 @@
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N37" t="n">
         <v>79</v>
       </c>
       <c r="O37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P37" t="n">
         <v>40</v>
@@ -3698,19 +3425,19 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N38" t="n">
         <v>40</v>
       </c>
       <c r="O38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P38" t="n">
         <v>20</v>
@@ -3754,19 +3481,19 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N39" t="n">
         <v>40</v>
       </c>
       <c r="O39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P39" t="n">
         <v>20</v>
@@ -3810,19 +3537,19 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
       </c>
       <c r="M40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N40" t="n">
         <v>40</v>
       </c>
       <c r="O40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P40" t="n">
         <v>20</v>
@@ -3872,13 +3599,13 @@
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N41" t="n">
         <v>27</v>
       </c>
       <c r="O41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P41" t="n">
         <v>14</v>
@@ -3928,13 +3655,13 @@
         <v>2</v>
       </c>
       <c r="M42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N42" t="n">
         <v>27</v>
       </c>
       <c r="O42" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P42" t="n">
         <v>14</v>
@@ -3984,13 +3711,13 @@
         <v>3</v>
       </c>
       <c r="M43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N43" t="n">
         <v>27</v>
       </c>
       <c r="O43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P43" t="n">
         <v>14</v>
@@ -4034,19 +3761,19 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N44" t="n">
         <v>18</v>
       </c>
       <c r="O44" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P44" t="n">
         <v>9</v>
@@ -4090,19 +3817,19 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N45" t="n">
         <v>18</v>
       </c>
       <c r="O45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P45" t="n">
         <v>9</v>
@@ -4146,19 +3873,19 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
       </c>
       <c r="M46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N46" t="n">
         <v>18</v>
       </c>
       <c r="O46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P46" t="n">
         <v>9</v>
@@ -4208,13 +3935,13 @@
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N47" t="n">
         <v>79</v>
       </c>
       <c r="O47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P47" t="n">
         <v>40</v>
@@ -4264,13 +3991,13 @@
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N48" t="n">
         <v>79</v>
       </c>
       <c r="O48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P48" t="n">
         <v>40</v>
@@ -4320,13 +4047,13 @@
         <v>3</v>
       </c>
       <c r="M49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N49" t="n">
         <v>79</v>
       </c>
       <c r="O49" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P49" t="n">
         <v>40</v>
@@ -4370,19 +4097,19 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N50" t="n">
         <v>40</v>
       </c>
       <c r="O50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P50" t="n">
         <v>20</v>
@@ -4426,19 +4153,19 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N51" t="n">
         <v>40</v>
       </c>
       <c r="O51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P51" t="n">
         <v>20</v>
@@ -4482,19 +4209,19 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
       </c>
       <c r="M52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N52" t="n">
         <v>40</v>
       </c>
       <c r="O52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P52" t="n">
         <v>20</v>
@@ -4538,19 +4265,19 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N53" t="n">
         <v>27</v>
       </c>
       <c r="O53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P53" t="n">
         <v>14</v>
@@ -4594,19 +4321,19 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N54" t="n">
         <v>27</v>
       </c>
       <c r="O54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P54" t="n">
         <v>14</v>
@@ -4650,19 +4377,19 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
       </c>
       <c r="M55" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N55" t="n">
         <v>27</v>
       </c>
       <c r="O55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P55" t="n">
         <v>14</v>
@@ -4706,19 +4433,19 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N56" t="n">
         <v>18</v>
       </c>
       <c r="O56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P56" t="n">
         <v>9</v>
@@ -4762,19 +4489,19 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N57" t="n">
         <v>18</v>
       </c>
       <c r="O57" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P57" t="n">
         <v>9</v>
@@ -4818,19 +4545,19 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
       </c>
       <c r="M58" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N58" t="n">
         <v>18</v>
       </c>
       <c r="O58" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P58" t="n">
         <v>9</v>
@@ -4874,19 +4601,19 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N59" t="n">
         <v>79</v>
       </c>
       <c r="O59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P59" t="n">
         <v>40</v>
@@ -4930,19 +4657,19 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N60" t="n">
         <v>79</v>
       </c>
       <c r="O60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P60" t="n">
         <v>40</v>
@@ -4986,19 +4713,19 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N61" t="n">
         <v>79</v>
       </c>
       <c r="O61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P61" t="n">
         <v>40</v>
@@ -5042,19 +4769,19 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N62" t="n">
         <v>40</v>
       </c>
       <c r="O62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P62" t="n">
         <v>20</v>
@@ -5098,19 +4825,19 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
       </c>
       <c r="M63" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N63" t="n">
         <v>40</v>
       </c>
       <c r="O63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P63" t="n">
         <v>20</v>
@@ -5154,19 +4881,19 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
       </c>
       <c r="M64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N64" t="n">
         <v>40</v>
       </c>
       <c r="O64" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P64" t="n">
         <v>20</v>
@@ -5210,19 +4937,19 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N65" t="n">
         <v>27</v>
       </c>
       <c r="O65" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P65" t="n">
         <v>14</v>
@@ -5266,19 +4993,19 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
       </c>
       <c r="M66" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N66" t="n">
         <v>27</v>
       </c>
       <c r="O66" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P66" t="n">
         <v>14</v>
@@ -5322,19 +5049,19 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
       </c>
       <c r="M67" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N67" t="n">
         <v>27</v>
       </c>
       <c r="O67" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P67" t="n">
         <v>14</v>
@@ -5378,19 +5105,19 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N68" t="n">
         <v>18</v>
       </c>
       <c r="O68" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P68" t="n">
         <v>9</v>
@@ -5434,19 +5161,19 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N69" t="n">
         <v>18</v>
       </c>
       <c r="O69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P69" t="n">
         <v>9</v>
@@ -5490,19 +5217,19 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
       </c>
       <c r="M70" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N70" t="n">
         <v>18</v>
       </c>
       <c r="O70" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P70" t="n">
         <v>9</v>
@@ -5546,19 +5273,19 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N71" t="n">
         <v>79</v>
       </c>
       <c r="O71" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P71" t="n">
         <v>40</v>
@@ -5602,19 +5329,19 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
       </c>
       <c r="M72" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N72" t="n">
         <v>79</v>
       </c>
       <c r="O72" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P72" t="n">
         <v>40</v>
@@ -5658,19 +5385,19 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
       </c>
       <c r="M73" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N73" t="n">
         <v>79</v>
       </c>
       <c r="O73" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P73" t="n">
         <v>40</v>
@@ -5714,19 +5441,19 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N74" t="n">
         <v>40</v>
       </c>
       <c r="O74" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P74" t="n">
         <v>20</v>
@@ -5770,19 +5497,19 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
       </c>
       <c r="M75" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N75" t="n">
         <v>40</v>
       </c>
       <c r="O75" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P75" t="n">
         <v>20</v>
@@ -5826,19 +5553,19 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
       </c>
       <c r="M76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N76" t="n">
         <v>40</v>
       </c>
       <c r="O76" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P76" t="n">
         <v>20</v>
@@ -5882,28 +5609,28 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N77" t="n">
         <v>13</v>
       </c>
       <c r="O77" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P77" t="n">
         <v>7</v>
       </c>
       <c r="Q77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78">
@@ -5938,28 +5665,28 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N78" t="n">
         <v>13</v>
       </c>
       <c r="O78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P78" t="n">
         <v>7</v>
       </c>
       <c r="Q78" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R78" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="79">
@@ -5994,28 +5721,28 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N79" t="n">
         <v>13</v>
       </c>
       <c r="O79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P79" t="n">
         <v>7</v>
       </c>
       <c r="Q79" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R79" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80">
@@ -6050,19 +5777,19 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N80" t="n">
         <v>18</v>
       </c>
       <c r="O80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P80" t="n">
         <v>9</v>
@@ -6106,19 +5833,19 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
       </c>
       <c r="M81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N81" t="n">
         <v>18</v>
       </c>
       <c r="O81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P81" t="n">
         <v>9</v>
@@ -6162,19 +5889,19 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
       </c>
       <c r="M82" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N82" t="n">
         <v>18</v>
       </c>
       <c r="O82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P82" t="n">
         <v>9</v>
@@ -6218,28 +5945,28 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N83" t="n">
         <v>46</v>
       </c>
       <c r="O83" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P83" t="n">
         <v>24</v>
       </c>
       <c r="Q83" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R83" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="84">
@@ -6274,28 +6001,28 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N84" t="n">
         <v>46</v>
       </c>
       <c r="O84" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P84" t="n">
         <v>24</v>
       </c>
       <c r="Q84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85">
@@ -6330,28 +6057,28 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N85" t="n">
         <v>46</v>
       </c>
       <c r="O85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P85" t="n">
         <v>24</v>
       </c>
       <c r="Q85" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R85" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86">
@@ -6386,19 +6113,19 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N86" t="n">
         <v>40</v>
       </c>
       <c r="O86" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P86" t="n">
         <v>20</v>
@@ -6442,19 +6169,19 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
       </c>
       <c r="M87" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N87" t="n">
         <v>40</v>
       </c>
       <c r="O87" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P87" t="n">
         <v>20</v>
@@ -6498,19 +6225,19 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
       </c>
       <c r="M88" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N88" t="n">
         <v>40</v>
       </c>
       <c r="O88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P88" t="n">
         <v>20</v>
@@ -6554,28 +6281,28 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N89" t="n">
         <v>13</v>
       </c>
       <c r="O89" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P89" t="n">
         <v>7</v>
       </c>
       <c r="Q89" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R89" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="90">
@@ -6610,28 +6337,28 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N90" t="n">
         <v>13</v>
       </c>
       <c r="O90" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P90" t="n">
         <v>7</v>
       </c>
       <c r="Q90" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R90" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91">
@@ -6666,28 +6393,28 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N91" t="n">
         <v>13</v>
       </c>
       <c r="O91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P91" t="n">
         <v>7</v>
       </c>
       <c r="Q91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92">
@@ -6722,19 +6449,19 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N92" t="n">
         <v>18</v>
       </c>
       <c r="O92" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P92" t="n">
         <v>9</v>
@@ -6778,19 +6505,19 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N93" t="n">
         <v>18</v>
       </c>
       <c r="O93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P93" t="n">
         <v>9</v>
@@ -6834,19 +6561,19 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
       </c>
       <c r="M94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N94" t="n">
         <v>18</v>
       </c>
       <c r="O94" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P94" t="n">
         <v>9</v>
@@ -6890,28 +6617,28 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N95" t="n">
         <v>46</v>
       </c>
       <c r="O95" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P95" t="n">
         <v>24</v>
       </c>
       <c r="Q95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96">
@@ -6946,28 +6673,28 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N96" t="n">
         <v>46</v>
       </c>
       <c r="O96" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P96" t="n">
         <v>24</v>
       </c>
       <c r="Q96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97">
@@ -7002,28 +6729,28 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N97" t="n">
         <v>46</v>
       </c>
       <c r="O97" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P97" t="n">
         <v>24</v>
       </c>
       <c r="Q97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98">
@@ -7058,19 +6785,19 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N98" t="n">
         <v>40</v>
       </c>
       <c r="O98" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P98" t="n">
         <v>20</v>
@@ -7114,19 +6841,19 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N99" t="n">
         <v>40</v>
       </c>
       <c r="O99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P99" t="n">
         <v>20</v>
@@ -7170,19 +6897,19 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N100" t="n">
         <v>40</v>
       </c>
       <c r="O100" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P100" t="n">
         <v>20</v>
@@ -7226,28 +6953,28 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N101" t="n">
         <v>24</v>
       </c>
       <c r="O101" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P101" t="n">
         <v>13</v>
       </c>
       <c r="Q101" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R101" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="102">
@@ -7282,28 +7009,28 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N102" t="n">
         <v>24</v>
       </c>
       <c r="O102" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P102" t="n">
         <v>13</v>
       </c>
       <c r="Q102" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R102" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="103">
@@ -7338,28 +7065,28 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N103" t="n">
         <v>24</v>
       </c>
       <c r="O103" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P103" t="n">
         <v>13</v>
       </c>
       <c r="Q103" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R103" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="104">
@@ -7394,19 +7121,19 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N104" t="n">
         <v>18</v>
       </c>
       <c r="O104" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P104" t="n">
         <v>9</v>
@@ -7450,19 +7177,19 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
       </c>
       <c r="M105" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N105" t="n">
         <v>18</v>
       </c>
       <c r="O105" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P105" t="n">
         <v>9</v>
@@ -7506,19 +7233,19 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
       </c>
       <c r="M106" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N106" t="n">
         <v>18</v>
       </c>
       <c r="O106" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P106" t="n">
         <v>9</v>
@@ -7562,28 +7289,28 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N107" t="n">
         <v>70</v>
       </c>
       <c r="O107" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P107" t="n">
         <v>36</v>
       </c>
       <c r="Q107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108">
@@ -7618,28 +7345,28 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N108" t="n">
         <v>70</v>
       </c>
       <c r="O108" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P108" t="n">
         <v>36</v>
       </c>
       <c r="Q108" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R108" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="109">
@@ -7674,28 +7401,28 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N109" t="n">
         <v>70</v>
       </c>
       <c r="O109" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P109" t="n">
         <v>36</v>
       </c>
       <c r="Q109" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R109" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="110">
@@ -7730,19 +7457,19 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N110" t="n">
         <v>40</v>
       </c>
       <c r="O110" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P110" t="n">
         <v>20</v>
@@ -7786,19 +7513,19 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N111" t="n">
         <v>40</v>
       </c>
       <c r="O111" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P111" t="n">
         <v>20</v>
@@ -7842,19 +7569,19 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N112" t="n">
         <v>40</v>
       </c>
       <c r="O112" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P112" t="n">
         <v>20</v>
@@ -7898,28 +7625,28 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N113" t="n">
         <v>24</v>
       </c>
       <c r="O113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P113" t="n">
         <v>13</v>
       </c>
       <c r="Q113" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R113" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="114">
@@ -7954,28 +7681,28 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N114" t="n">
         <v>24</v>
       </c>
       <c r="O114" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P114" t="n">
         <v>13</v>
       </c>
       <c r="Q114" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R114" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="115">
@@ -8010,28 +7737,28 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N115" t="n">
         <v>24</v>
       </c>
       <c r="O115" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P115" t="n">
         <v>13</v>
       </c>
       <c r="Q115" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R115" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="116">
@@ -8066,19 +7793,19 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N116" t="n">
         <v>18</v>
       </c>
       <c r="O116" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P116" t="n">
         <v>9</v>
@@ -8122,19 +7849,19 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
       </c>
       <c r="M117" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N117" t="n">
         <v>18</v>
       </c>
       <c r="O117" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P117" t="n">
         <v>9</v>
@@ -8178,19 +7905,19 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
       </c>
       <c r="M118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N118" t="n">
         <v>18</v>
       </c>
       <c r="O118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P118" t="n">
         <v>9</v>
@@ -8234,28 +7961,28 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N119" t="n">
         <v>70</v>
       </c>
       <c r="O119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P119" t="n">
         <v>36</v>
       </c>
       <c r="Q119" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R119" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="120">
@@ -8290,28 +8017,28 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N120" t="n">
         <v>70</v>
       </c>
       <c r="O120" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P120" t="n">
         <v>36</v>
       </c>
       <c r="Q120" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R120" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="121">
@@ -8346,28 +8073,28 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N121" t="n">
         <v>70</v>
       </c>
       <c r="O121" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P121" t="n">
         <v>36</v>
       </c>
       <c r="Q121" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R121" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="122">
@@ -8402,28 +8129,28 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N122" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O122" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P122" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q122" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R122" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="123">
@@ -8458,28 +8185,28 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
+        <v>289</v>
+      </c>
+      <c r="N123" t="n">
+        <v>27</v>
+      </c>
+      <c r="O123" t="s">
+        <v>290</v>
+      </c>
+      <c r="P123" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q123" t="s">
         <v>288</v>
       </c>
-      <c r="N123" t="n">
-        <v>30</v>
-      </c>
-      <c r="O123" t="s">
-        <v>289</v>
-      </c>
-      <c r="P123" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>287</v>
-      </c>
       <c r="R123" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="124">
@@ -8514,28 +8241,28 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N124" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O124" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P124" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q124" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R124" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="125">
@@ -8570,28 +8297,28 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N125" t="n">
         <v>24</v>
       </c>
       <c r="O125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P125" t="n">
         <v>13</v>
       </c>
       <c r="Q125" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R125" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="126">
@@ -8626,28 +8353,28 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N126" t="n">
         <v>24</v>
       </c>
       <c r="O126" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P126" t="n">
         <v>13</v>
       </c>
       <c r="Q126" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R126" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="127">
@@ -8682,28 +8409,28 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N127" t="n">
         <v>24</v>
       </c>
       <c r="O127" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P127" t="n">
         <v>13</v>
       </c>
       <c r="Q127" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R127" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="128">
@@ -8711,7 +8438,7 @@
         <v>256</v>
       </c>
       <c r="B128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -8738,28 +8465,24 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>299</v>
-      </c>
-      <c r="N128" t="n">
-        <v>4</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N128"/>
       <c r="O128" t="s">
         <v>300</v>
       </c>
-      <c r="P128" t="n">
-        <v>3</v>
-      </c>
+      <c r="P128"/>
       <c r="Q128" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R128" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="129">
@@ -8767,7 +8490,7 @@
         <v>257</v>
       </c>
       <c r="B129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="s">
         <v>18</v>
@@ -8794,28 +8517,24 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>302</v>
-      </c>
-      <c r="N129" t="n">
-        <v>4</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N129"/>
       <c r="O129" t="s">
-        <v>303</v>
-      </c>
-      <c r="P129" t="n">
-        <v>3</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="P129"/>
       <c r="Q129" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R129" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="130">
@@ -8823,7 +8542,7 @@
         <v>258</v>
       </c>
       <c r="B130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="s">
         <v>18</v>
@@ -8850,28 +8569,24 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>304</v>
-      </c>
-      <c r="N130" t="n">
-        <v>4</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N130"/>
       <c r="O130" t="s">
-        <v>305</v>
-      </c>
-      <c r="P130" t="n">
-        <v>3</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="P130"/>
       <c r="Q130" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R130" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="131">
@@ -8906,28 +8621,28 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="N131" t="n">
         <v>68</v>
       </c>
       <c r="O131" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="P131" t="n">
         <v>34</v>
       </c>
       <c r="Q131" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="R131" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="132">
@@ -8962,28 +8677,28 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="N132" t="n">
         <v>68</v>
       </c>
       <c r="O132" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="P132" t="n">
         <v>34</v>
       </c>
       <c r="Q132" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="R132" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="133">
@@ -9018,28 +8733,28 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N133" t="n">
         <v>68</v>
       </c>
       <c r="O133" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="P133" t="n">
         <v>34</v>
       </c>
       <c r="Q133" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="R133" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="134">
@@ -9074,28 +8789,28 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="N134" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O134" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="P134" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q134" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R134" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="135">
@@ -9130,28 +8845,28 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N135" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O135" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="P135" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q135" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R135" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="136">
@@ -9186,28 +8901,28 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N136" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O136" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="P136" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q136" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R136" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="137">
@@ -9242,28 +8957,28 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="N137" t="n">
         <v>24</v>
       </c>
       <c r="O137" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="P137" t="n">
         <v>13</v>
       </c>
       <c r="Q137" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R137" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="138">
@@ -9298,28 +9013,28 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="N138" t="n">
         <v>24</v>
       </c>
       <c r="O138" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="P138" t="n">
         <v>13</v>
       </c>
       <c r="Q138" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R138" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="139">
@@ -9354,28 +9069,28 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="N139" t="n">
         <v>24</v>
       </c>
       <c r="O139" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P139" t="n">
         <v>13</v>
       </c>
       <c r="Q139" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R139" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="140">
@@ -9410,28 +9125,24 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>325</v>
-      </c>
-      <c r="N140" t="n">
-        <v>4</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N140"/>
       <c r="O140" t="s">
-        <v>326</v>
-      </c>
-      <c r="P140" t="n">
-        <v>3</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="P140"/>
       <c r="Q140" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R140" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="141">
@@ -9466,28 +9177,24 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>327</v>
-      </c>
-      <c r="N141" t="n">
-        <v>4</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N141"/>
       <c r="O141" t="s">
-        <v>328</v>
-      </c>
-      <c r="P141" t="n">
-        <v>3</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="P141"/>
       <c r="Q141" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R141" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="142">
@@ -9522,28 +9229,24 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>329</v>
-      </c>
-      <c r="N142" t="n">
-        <v>4</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N142"/>
       <c r="O142" t="s">
-        <v>330</v>
-      </c>
-      <c r="P142" t="n">
-        <v>3</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="P142"/>
       <c r="Q142" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R142" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143">
@@ -9578,28 +9281,28 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="N143" t="n">
         <v>68</v>
       </c>
       <c r="O143" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="P143" t="n">
         <v>34</v>
       </c>
       <c r="Q143" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="R143" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="144">
@@ -9634,28 +9337,28 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="N144" t="n">
         <v>68</v>
       </c>
       <c r="O144" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="P144" t="n">
         <v>34</v>
       </c>
       <c r="Q144" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="R144" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="145">
@@ -9690,3916 +9393,28 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="N145" t="n">
         <v>68</v>
       </c>
       <c r="O145" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="P145" t="n">
         <v>34</v>
       </c>
       <c r="Q145" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="R145" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>292</v>
-      </c>
-      <c r="B146" t="b">
-        <v>0</v>
-      </c>
-      <c r="C146" t="s">
-        <v>18</v>
-      </c>
-      <c r="D146" t="s">
-        <v>19</v>
-      </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" t="s">
-        <v>20</v>
-      </c>
-      <c r="I146" t="n">
-        <v>7</v>
-      </c>
-      <c r="J146" t="n">
-        <v>3</v>
-      </c>
-      <c r="K146" t="s">
-        <v>337</v>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="s">
-        <v>338</v>
-      </c>
-      <c r="N146" t="n">
-        <v>27</v>
-      </c>
-      <c r="O146" t="s">
-        <v>339</v>
-      </c>
-      <c r="P146" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q146" t="s">
-        <v>340</v>
-      </c>
-      <c r="R146" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>293</v>
-      </c>
-      <c r="B147" t="b">
-        <v>0</v>
-      </c>
-      <c r="C147" t="s">
-        <v>18</v>
-      </c>
-      <c r="D147" t="s">
-        <v>19</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" t="s">
-        <v>20</v>
-      </c>
-      <c r="I147" t="n">
-        <v>7</v>
-      </c>
-      <c r="J147" t="n">
-        <v>3</v>
-      </c>
-      <c r="K147" t="s">
-        <v>337</v>
-      </c>
-      <c r="L147" t="n">
-        <v>2</v>
-      </c>
-      <c r="M147" t="s">
-        <v>341</v>
-      </c>
-      <c r="N147" t="n">
-        <v>27</v>
-      </c>
-      <c r="O147" t="s">
-        <v>342</v>
-      </c>
-      <c r="P147" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q147" t="s">
-        <v>340</v>
-      </c>
-      <c r="R147" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>294</v>
-      </c>
-      <c r="B148" t="b">
-        <v>0</v>
-      </c>
-      <c r="C148" t="s">
-        <v>18</v>
-      </c>
-      <c r="D148" t="s">
-        <v>19</v>
-      </c>
-      <c r="E148" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" t="s">
-        <v>20</v>
-      </c>
-      <c r="I148" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" t="n">
-        <v>3</v>
-      </c>
-      <c r="K148" t="s">
-        <v>337</v>
-      </c>
-      <c r="L148" t="n">
-        <v>3</v>
-      </c>
-      <c r="M148" t="s">
-        <v>343</v>
-      </c>
-      <c r="N148" t="n">
-        <v>27</v>
-      </c>
-      <c r="O148" t="s">
-        <v>344</v>
-      </c>
-      <c r="P148" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q148" t="s">
-        <v>340</v>
-      </c>
-      <c r="R148" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>298</v>
-      </c>
-      <c r="B149" t="b">
-        <v>1</v>
-      </c>
-      <c r="C149" t="s">
-        <v>18</v>
-      </c>
-      <c r="D149" t="s">
-        <v>19</v>
-      </c>
-      <c r="E149" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" t="n">
-        <v>2</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1</v>
-      </c>
-      <c r="H149" t="s">
-        <v>29</v>
-      </c>
-      <c r="I149" t="n">
-        <v>7</v>
-      </c>
-      <c r="J149" t="n">
-        <v>3</v>
-      </c>
-      <c r="K149" t="s">
-        <v>345</v>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="s">
-        <v>346</v>
-      </c>
-      <c r="N149"/>
-      <c r="O149" t="s">
-        <v>346</v>
-      </c>
-      <c r="P149"/>
-      <c r="Q149" t="s">
-        <v>346</v>
-      </c>
-      <c r="R149" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>299</v>
-      </c>
-      <c r="B150" t="b">
-        <v>1</v>
-      </c>
-      <c r="C150" t="s">
-        <v>18</v>
-      </c>
-      <c r="D150" t="s">
-        <v>19</v>
-      </c>
-      <c r="E150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" t="n">
-        <v>2</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1</v>
-      </c>
-      <c r="H150" t="s">
-        <v>29</v>
-      </c>
-      <c r="I150" t="n">
-        <v>7</v>
-      </c>
-      <c r="J150" t="n">
-        <v>3</v>
-      </c>
-      <c r="K150" t="s">
-        <v>345</v>
-      </c>
-      <c r="L150" t="n">
-        <v>2</v>
-      </c>
-      <c r="M150" t="s">
-        <v>346</v>
-      </c>
-      <c r="N150"/>
-      <c r="O150" t="s">
-        <v>346</v>
-      </c>
-      <c r="P150"/>
-      <c r="Q150" t="s">
-        <v>346</v>
-      </c>
-      <c r="R150" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>300</v>
-      </c>
-      <c r="B151" t="b">
-        <v>1</v>
-      </c>
-      <c r="C151" t="s">
-        <v>18</v>
-      </c>
-      <c r="D151" t="s">
-        <v>19</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" t="n">
-        <v>2</v>
-      </c>
-      <c r="G151" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" t="s">
-        <v>29</v>
-      </c>
-      <c r="I151" t="n">
-        <v>7</v>
-      </c>
-      <c r="J151" t="n">
-        <v>3</v>
-      </c>
-      <c r="K151" t="s">
-        <v>345</v>
-      </c>
-      <c r="L151" t="n">
-        <v>3</v>
-      </c>
-      <c r="M151" t="s">
-        <v>346</v>
-      </c>
-      <c r="N151"/>
-      <c r="O151" t="s">
-        <v>346</v>
-      </c>
-      <c r="P151"/>
-      <c r="Q151" t="s">
-        <v>346</v>
-      </c>
-      <c r="R151" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>304</v>
-      </c>
-      <c r="B152" t="b">
-        <v>1</v>
-      </c>
-      <c r="C152" t="s">
-        <v>18</v>
-      </c>
-      <c r="D152" t="s">
-        <v>19</v>
-      </c>
-      <c r="E152" t="n">
-        <v>2</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" t="s">
-        <v>38</v>
-      </c>
-      <c r="I152" t="n">
-        <v>7</v>
-      </c>
-      <c r="J152" t="n">
-        <v>3</v>
-      </c>
-      <c r="K152" t="s">
-        <v>337</v>
-      </c>
-      <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="s">
-        <v>346</v>
-      </c>
-      <c r="N152"/>
-      <c r="O152" t="s">
-        <v>346</v>
-      </c>
-      <c r="P152"/>
-      <c r="Q152" t="s">
-        <v>346</v>
-      </c>
-      <c r="R152" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>305</v>
-      </c>
-      <c r="B153" t="b">
-        <v>1</v>
-      </c>
-      <c r="C153" t="s">
-        <v>18</v>
-      </c>
-      <c r="D153" t="s">
-        <v>19</v>
-      </c>
-      <c r="E153" t="n">
-        <v>2</v>
-      </c>
-      <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" t="s">
-        <v>38</v>
-      </c>
-      <c r="I153" t="n">
-        <v>7</v>
-      </c>
-      <c r="J153" t="n">
-        <v>3</v>
-      </c>
-      <c r="K153" t="s">
-        <v>337</v>
-      </c>
-      <c r="L153" t="n">
-        <v>2</v>
-      </c>
-      <c r="M153" t="s">
-        <v>346</v>
-      </c>
-      <c r="N153"/>
-      <c r="O153" t="s">
-        <v>346</v>
-      </c>
-      <c r="P153"/>
-      <c r="Q153" t="s">
-        <v>346</v>
-      </c>
-      <c r="R153" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>306</v>
-      </c>
-      <c r="B154" t="b">
-        <v>1</v>
-      </c>
-      <c r="C154" t="s">
-        <v>18</v>
-      </c>
-      <c r="D154" t="s">
-        <v>19</v>
-      </c>
-      <c r="E154" t="n">
-        <v>2</v>
-      </c>
-      <c r="F154" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" t="s">
-        <v>38</v>
-      </c>
-      <c r="I154" t="n">
-        <v>7</v>
-      </c>
-      <c r="J154" t="n">
-        <v>3</v>
-      </c>
-      <c r="K154" t="s">
-        <v>337</v>
-      </c>
-      <c r="L154" t="n">
-        <v>3</v>
-      </c>
-      <c r="M154" t="s">
-        <v>346</v>
-      </c>
-      <c r="N154"/>
-      <c r="O154" t="s">
-        <v>346</v>
-      </c>
-      <c r="P154"/>
-      <c r="Q154" t="s">
-        <v>346</v>
-      </c>
-      <c r="R154" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>310</v>
-      </c>
-      <c r="B155" t="b">
-        <v>0</v>
-      </c>
-      <c r="C155" t="s">
-        <v>18</v>
-      </c>
-      <c r="D155" t="s">
-        <v>19</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2</v>
-      </c>
-      <c r="F155" t="n">
-        <v>2</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H155" t="s">
-        <v>46</v>
-      </c>
-      <c r="I155" t="n">
-        <v>7</v>
-      </c>
-      <c r="J155" t="n">
-        <v>3</v>
-      </c>
-      <c r="K155" t="s">
-        <v>345</v>
-      </c>
-      <c r="L155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M155" t="s">
-        <v>347</v>
-      </c>
-      <c r="N155" t="n">
-        <v>14</v>
-      </c>
-      <c r="O155" t="s">
-        <v>348</v>
-      </c>
-      <c r="P155" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q155" t="s">
-        <v>349</v>
-      </c>
-      <c r="R155" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>311</v>
-      </c>
-      <c r="B156" t="b">
-        <v>0</v>
-      </c>
-      <c r="C156" t="s">
-        <v>18</v>
-      </c>
-      <c r="D156" t="s">
-        <v>19</v>
-      </c>
-      <c r="E156" t="n">
-        <v>2</v>
-      </c>
-      <c r="F156" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
-      <c r="H156" t="s">
-        <v>46</v>
-      </c>
-      <c r="I156" t="n">
-        <v>7</v>
-      </c>
-      <c r="J156" t="n">
-        <v>3</v>
-      </c>
-      <c r="K156" t="s">
-        <v>345</v>
-      </c>
-      <c r="L156" t="n">
-        <v>2</v>
-      </c>
-      <c r="M156" t="s">
-        <v>350</v>
-      </c>
-      <c r="N156" t="n">
-        <v>14</v>
-      </c>
-      <c r="O156" t="s">
-        <v>351</v>
-      </c>
-      <c r="P156" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q156" t="s">
-        <v>349</v>
-      </c>
-      <c r="R156" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>312</v>
-      </c>
-      <c r="B157" t="b">
-        <v>0</v>
-      </c>
-      <c r="C157" t="s">
-        <v>18</v>
-      </c>
-      <c r="D157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E157" t="n">
-        <v>2</v>
-      </c>
-      <c r="F157" t="n">
-        <v>2</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" t="s">
-        <v>46</v>
-      </c>
-      <c r="I157" t="n">
-        <v>7</v>
-      </c>
-      <c r="J157" t="n">
-        <v>3</v>
-      </c>
-      <c r="K157" t="s">
-        <v>345</v>
-      </c>
-      <c r="L157" t="n">
-        <v>3</v>
-      </c>
-      <c r="M157" t="s">
-        <v>352</v>
-      </c>
-      <c r="N157" t="n">
-        <v>14</v>
-      </c>
-      <c r="O157" t="s">
-        <v>353</v>
-      </c>
-      <c r="P157" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>349</v>
-      </c>
-      <c r="R157" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>316</v>
-      </c>
-      <c r="B158" t="b">
-        <v>0</v>
-      </c>
-      <c r="C158" t="s">
-        <v>18</v>
-      </c>
-      <c r="D158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" t="n">
-        <v>2</v>
-      </c>
-      <c r="H158" t="s">
-        <v>54</v>
-      </c>
-      <c r="I158" t="n">
-        <v>7</v>
-      </c>
-      <c r="J158" t="n">
-        <v>3</v>
-      </c>
-      <c r="K158" t="s">
-        <v>337</v>
-      </c>
-      <c r="L158" t="n">
-        <v>1</v>
-      </c>
-      <c r="M158" t="s">
-        <v>354</v>
-      </c>
-      <c r="N158" t="n">
-        <v>27</v>
-      </c>
-      <c r="O158" t="s">
-        <v>355</v>
-      </c>
-      <c r="P158" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q158" t="s">
-        <v>340</v>
-      </c>
-      <c r="R158" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>317</v>
-      </c>
-      <c r="B159" t="b">
-        <v>0</v>
-      </c>
-      <c r="C159" t="s">
-        <v>18</v>
-      </c>
-      <c r="D159" t="s">
-        <v>19</v>
-      </c>
-      <c r="E159" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" t="n">
-        <v>2</v>
-      </c>
-      <c r="H159" t="s">
-        <v>54</v>
-      </c>
-      <c r="I159" t="n">
-        <v>7</v>
-      </c>
-      <c r="J159" t="n">
-        <v>3</v>
-      </c>
-      <c r="K159" t="s">
-        <v>337</v>
-      </c>
-      <c r="L159" t="n">
-        <v>2</v>
-      </c>
-      <c r="M159" t="s">
-        <v>356</v>
-      </c>
-      <c r="N159" t="n">
-        <v>27</v>
-      </c>
-      <c r="O159" t="s">
-        <v>357</v>
-      </c>
-      <c r="P159" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q159" t="s">
-        <v>340</v>
-      </c>
-      <c r="R159" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>318</v>
-      </c>
-      <c r="B160" t="b">
-        <v>0</v>
-      </c>
-      <c r="C160" t="s">
-        <v>18</v>
-      </c>
-      <c r="D160" t="s">
-        <v>19</v>
-      </c>
-      <c r="E160" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" t="n">
-        <v>2</v>
-      </c>
-      <c r="H160" t="s">
-        <v>54</v>
-      </c>
-      <c r="I160" t="n">
-        <v>7</v>
-      </c>
-      <c r="J160" t="n">
-        <v>3</v>
-      </c>
-      <c r="K160" t="s">
-        <v>337</v>
-      </c>
-      <c r="L160" t="n">
-        <v>3</v>
-      </c>
-      <c r="M160" t="s">
-        <v>358</v>
-      </c>
-      <c r="N160" t="n">
-        <v>27</v>
-      </c>
-      <c r="O160" t="s">
-        <v>359</v>
-      </c>
-      <c r="P160" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q160" t="s">
-        <v>340</v>
-      </c>
-      <c r="R160" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>322</v>
-      </c>
-      <c r="B161" t="b">
-        <v>1</v>
-      </c>
-      <c r="C161" t="s">
-        <v>18</v>
-      </c>
-      <c r="D161" t="s">
-        <v>19</v>
-      </c>
-      <c r="E161" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" t="n">
-        <v>2</v>
-      </c>
-      <c r="G161" t="n">
-        <v>2</v>
-      </c>
-      <c r="H161" t="s">
-        <v>61</v>
-      </c>
-      <c r="I161" t="n">
-        <v>7</v>
-      </c>
-      <c r="J161" t="n">
-        <v>3</v>
-      </c>
-      <c r="K161" t="s">
-        <v>345</v>
-      </c>
-      <c r="L161" t="n">
-        <v>1</v>
-      </c>
-      <c r="M161" t="s">
-        <v>346</v>
-      </c>
-      <c r="N161"/>
-      <c r="O161" t="s">
-        <v>346</v>
-      </c>
-      <c r="P161"/>
-      <c r="Q161" t="s">
-        <v>346</v>
-      </c>
-      <c r="R161" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>323</v>
-      </c>
-      <c r="B162" t="b">
-        <v>1</v>
-      </c>
-      <c r="C162" t="s">
-        <v>18</v>
-      </c>
-      <c r="D162" t="s">
-        <v>19</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" t="n">
-        <v>2</v>
-      </c>
-      <c r="G162" t="n">
-        <v>2</v>
-      </c>
-      <c r="H162" t="s">
-        <v>61</v>
-      </c>
-      <c r="I162" t="n">
-        <v>7</v>
-      </c>
-      <c r="J162" t="n">
-        <v>3</v>
-      </c>
-      <c r="K162" t="s">
-        <v>345</v>
-      </c>
-      <c r="L162" t="n">
-        <v>2</v>
-      </c>
-      <c r="M162" t="s">
-        <v>346</v>
-      </c>
-      <c r="N162"/>
-      <c r="O162" t="s">
-        <v>346</v>
-      </c>
-      <c r="P162"/>
-      <c r="Q162" t="s">
-        <v>346</v>
-      </c>
-      <c r="R162" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>324</v>
-      </c>
-      <c r="B163" t="b">
-        <v>1</v>
-      </c>
-      <c r="C163" t="s">
-        <v>18</v>
-      </c>
-      <c r="D163" t="s">
-        <v>19</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="n">
-        <v>2</v>
-      </c>
-      <c r="G163" t="n">
-        <v>2</v>
-      </c>
-      <c r="H163" t="s">
-        <v>61</v>
-      </c>
-      <c r="I163" t="n">
-        <v>7</v>
-      </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
-      <c r="K163" t="s">
-        <v>345</v>
-      </c>
-      <c r="L163" t="n">
-        <v>3</v>
-      </c>
-      <c r="M163" t="s">
-        <v>346</v>
-      </c>
-      <c r="N163"/>
-      <c r="O163" t="s">
-        <v>346</v>
-      </c>
-      <c r="P163"/>
-      <c r="Q163" t="s">
-        <v>346</v>
-      </c>
-      <c r="R163" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>328</v>
-      </c>
-      <c r="B164" t="b">
-        <v>1</v>
-      </c>
-      <c r="C164" t="s">
-        <v>18</v>
-      </c>
-      <c r="D164" t="s">
-        <v>19</v>
-      </c>
-      <c r="E164" t="n">
-        <v>2</v>
-      </c>
-      <c r="F164" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" t="n">
-        <v>2</v>
-      </c>
-      <c r="H164" t="s">
-        <v>68</v>
-      </c>
-      <c r="I164" t="n">
-        <v>7</v>
-      </c>
-      <c r="J164" t="n">
-        <v>3</v>
-      </c>
-      <c r="K164" t="s">
-        <v>337</v>
-      </c>
-      <c r="L164" t="n">
-        <v>1</v>
-      </c>
-      <c r="M164" t="s">
-        <v>346</v>
-      </c>
-      <c r="N164"/>
-      <c r="O164" t="s">
-        <v>346</v>
-      </c>
-      <c r="P164"/>
-      <c r="Q164" t="s">
-        <v>346</v>
-      </c>
-      <c r="R164" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>329</v>
-      </c>
-      <c r="B165" t="b">
-        <v>1</v>
-      </c>
-      <c r="C165" t="s">
-        <v>18</v>
-      </c>
-      <c r="D165" t="s">
-        <v>19</v>
-      </c>
-      <c r="E165" t="n">
-        <v>2</v>
-      </c>
-      <c r="F165" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" t="n">
-        <v>2</v>
-      </c>
-      <c r="H165" t="s">
-        <v>68</v>
-      </c>
-      <c r="I165" t="n">
-        <v>7</v>
-      </c>
-      <c r="J165" t="n">
-        <v>3</v>
-      </c>
-      <c r="K165" t="s">
-        <v>337</v>
-      </c>
-      <c r="L165" t="n">
-        <v>2</v>
-      </c>
-      <c r="M165" t="s">
-        <v>346</v>
-      </c>
-      <c r="N165"/>
-      <c r="O165" t="s">
-        <v>346</v>
-      </c>
-      <c r="P165"/>
-      <c r="Q165" t="s">
-        <v>346</v>
-      </c>
-      <c r="R165" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>330</v>
-      </c>
-      <c r="B166" t="b">
-        <v>1</v>
-      </c>
-      <c r="C166" t="s">
-        <v>18</v>
-      </c>
-      <c r="D166" t="s">
-        <v>19</v>
-      </c>
-      <c r="E166" t="n">
-        <v>2</v>
-      </c>
-      <c r="F166" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" t="n">
-        <v>2</v>
-      </c>
-      <c r="H166" t="s">
-        <v>68</v>
-      </c>
-      <c r="I166" t="n">
-        <v>7</v>
-      </c>
-      <c r="J166" t="n">
-        <v>3</v>
-      </c>
-      <c r="K166" t="s">
-        <v>337</v>
-      </c>
-      <c r="L166" t="n">
-        <v>3</v>
-      </c>
-      <c r="M166" t="s">
-        <v>346</v>
-      </c>
-      <c r="N166"/>
-      <c r="O166" t="s">
-        <v>346</v>
-      </c>
-      <c r="P166"/>
-      <c r="Q166" t="s">
-        <v>346</v>
-      </c>
-      <c r="R166" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>334</v>
-      </c>
-      <c r="B167" t="b">
-        <v>0</v>
-      </c>
-      <c r="C167" t="s">
-        <v>18</v>
-      </c>
-      <c r="D167" t="s">
-        <v>19</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2</v>
-      </c>
-      <c r="F167" t="n">
-        <v>2</v>
-      </c>
-      <c r="G167" t="n">
-        <v>2</v>
-      </c>
-      <c r="H167" t="s">
-        <v>75</v>
-      </c>
-      <c r="I167" t="n">
-        <v>7</v>
-      </c>
-      <c r="J167" t="n">
-        <v>3</v>
-      </c>
-      <c r="K167" t="s">
-        <v>345</v>
-      </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="s">
-        <v>360</v>
-      </c>
-      <c r="N167" t="n">
-        <v>14</v>
-      </c>
-      <c r="O167" t="s">
-        <v>361</v>
-      </c>
-      <c r="P167" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q167" t="s">
-        <v>349</v>
-      </c>
-      <c r="R167" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>335</v>
-      </c>
-      <c r="B168" t="b">
-        <v>0</v>
-      </c>
-      <c r="C168" t="s">
-        <v>18</v>
-      </c>
-      <c r="D168" t="s">
-        <v>19</v>
-      </c>
-      <c r="E168" t="n">
-        <v>2</v>
-      </c>
-      <c r="F168" t="n">
-        <v>2</v>
-      </c>
-      <c r="G168" t="n">
-        <v>2</v>
-      </c>
-      <c r="H168" t="s">
-        <v>75</v>
-      </c>
-      <c r="I168" t="n">
-        <v>7</v>
-      </c>
-      <c r="J168" t="n">
-        <v>3</v>
-      </c>
-      <c r="K168" t="s">
-        <v>345</v>
-      </c>
-      <c r="L168" t="n">
-        <v>2</v>
-      </c>
-      <c r="M168" t="s">
-        <v>362</v>
-      </c>
-      <c r="N168" t="n">
-        <v>14</v>
-      </c>
-      <c r="O168" t="s">
-        <v>363</v>
-      </c>
-      <c r="P168" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q168" t="s">
-        <v>349</v>
-      </c>
-      <c r="R168" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>336</v>
-      </c>
-      <c r="B169" t="b">
-        <v>0</v>
-      </c>
-      <c r="C169" t="s">
-        <v>18</v>
-      </c>
-      <c r="D169" t="s">
-        <v>19</v>
-      </c>
-      <c r="E169" t="n">
-        <v>2</v>
-      </c>
-      <c r="F169" t="n">
-        <v>2</v>
-      </c>
-      <c r="G169" t="n">
-        <v>2</v>
-      </c>
-      <c r="H169" t="s">
-        <v>75</v>
-      </c>
-      <c r="I169" t="n">
-        <v>7</v>
-      </c>
-      <c r="J169" t="n">
-        <v>3</v>
-      </c>
-      <c r="K169" t="s">
-        <v>345</v>
-      </c>
-      <c r="L169" t="n">
-        <v>3</v>
-      </c>
-      <c r="M169" t="s">
-        <v>364</v>
-      </c>
-      <c r="N169" t="n">
-        <v>14</v>
-      </c>
-      <c r="O169" t="s">
-        <v>365</v>
-      </c>
-      <c r="P169" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q169" t="s">
-        <v>349</v>
-      </c>
-      <c r="R169" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>340</v>
-      </c>
-      <c r="B170" t="b">
-        <v>0</v>
-      </c>
-      <c r="C170" t="s">
-        <v>18</v>
-      </c>
-      <c r="D170" t="s">
-        <v>19</v>
-      </c>
-      <c r="E170" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" t="n">
-        <v>1</v>
-      </c>
-      <c r="H170" t="s">
-        <v>20</v>
-      </c>
-      <c r="I170" t="n">
-        <v>8</v>
-      </c>
-      <c r="J170" t="n">
-        <v>3</v>
-      </c>
-      <c r="K170" t="s">
-        <v>366</v>
-      </c>
-      <c r="L170" t="n">
-        <v>1</v>
-      </c>
-      <c r="M170" t="s">
-        <v>367</v>
-      </c>
-      <c r="N170" t="n">
-        <v>27</v>
-      </c>
-      <c r="O170" t="s">
-        <v>368</v>
-      </c>
-      <c r="P170" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q170" t="s">
-        <v>340</v>
-      </c>
-      <c r="R170" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>341</v>
-      </c>
-      <c r="B171" t="b">
-        <v>0</v>
-      </c>
-      <c r="C171" t="s">
-        <v>18</v>
-      </c>
-      <c r="D171" t="s">
-        <v>19</v>
-      </c>
-      <c r="E171" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" t="s">
-        <v>20</v>
-      </c>
-      <c r="I171" t="n">
-        <v>8</v>
-      </c>
-      <c r="J171" t="n">
-        <v>3</v>
-      </c>
-      <c r="K171" t="s">
-        <v>366</v>
-      </c>
-      <c r="L171" t="n">
-        <v>2</v>
-      </c>
-      <c r="M171" t="s">
-        <v>369</v>
-      </c>
-      <c r="N171" t="n">
-        <v>27</v>
-      </c>
-      <c r="O171" t="s">
-        <v>370</v>
-      </c>
-      <c r="P171" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q171" t="s">
-        <v>340</v>
-      </c>
-      <c r="R171" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>342</v>
-      </c>
-      <c r="B172" t="b">
-        <v>0</v>
-      </c>
-      <c r="C172" t="s">
-        <v>18</v>
-      </c>
-      <c r="D172" t="s">
-        <v>19</v>
-      </c>
-      <c r="E172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" t="n">
-        <v>1</v>
-      </c>
-      <c r="H172" t="s">
-        <v>20</v>
-      </c>
-      <c r="I172" t="n">
-        <v>8</v>
-      </c>
-      <c r="J172" t="n">
-        <v>3</v>
-      </c>
-      <c r="K172" t="s">
-        <v>366</v>
-      </c>
-      <c r="L172" t="n">
-        <v>3</v>
-      </c>
-      <c r="M172" t="s">
-        <v>371</v>
-      </c>
-      <c r="N172" t="n">
-        <v>27</v>
-      </c>
-      <c r="O172" t="s">
-        <v>372</v>
-      </c>
-      <c r="P172" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>340</v>
-      </c>
-      <c r="R172" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>346</v>
-      </c>
-      <c r="B173" t="b">
-        <v>1</v>
-      </c>
-      <c r="C173" t="s">
-        <v>18</v>
-      </c>
-      <c r="D173" t="s">
-        <v>19</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" t="n">
-        <v>2</v>
-      </c>
-      <c r="G173" t="n">
-        <v>1</v>
-      </c>
-      <c r="H173" t="s">
-        <v>29</v>
-      </c>
-      <c r="I173" t="n">
-        <v>8</v>
-      </c>
-      <c r="J173" t="n">
-        <v>3</v>
-      </c>
-      <c r="K173" t="s">
-        <v>345</v>
-      </c>
-      <c r="L173" t="n">
-        <v>1</v>
-      </c>
-      <c r="M173" t="s">
-        <v>346</v>
-      </c>
-      <c r="N173"/>
-      <c r="O173" t="s">
-        <v>346</v>
-      </c>
-      <c r="P173"/>
-      <c r="Q173" t="s">
-        <v>346</v>
-      </c>
-      <c r="R173" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>347</v>
-      </c>
-      <c r="B174" t="b">
-        <v>1</v>
-      </c>
-      <c r="C174" t="s">
-        <v>18</v>
-      </c>
-      <c r="D174" t="s">
-        <v>19</v>
-      </c>
-      <c r="E174" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" t="n">
-        <v>2</v>
-      </c>
-      <c r="G174" t="n">
-        <v>1</v>
-      </c>
-      <c r="H174" t="s">
-        <v>29</v>
-      </c>
-      <c r="I174" t="n">
-        <v>8</v>
-      </c>
-      <c r="J174" t="n">
-        <v>3</v>
-      </c>
-      <c r="K174" t="s">
-        <v>345</v>
-      </c>
-      <c r="L174" t="n">
-        <v>2</v>
-      </c>
-      <c r="M174" t="s">
-        <v>346</v>
-      </c>
-      <c r="N174"/>
-      <c r="O174" t="s">
-        <v>346</v>
-      </c>
-      <c r="P174"/>
-      <c r="Q174" t="s">
-        <v>346</v>
-      </c>
-      <c r="R174" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>348</v>
-      </c>
-      <c r="B175" t="b">
-        <v>1</v>
-      </c>
-      <c r="C175" t="s">
-        <v>18</v>
-      </c>
-      <c r="D175" t="s">
-        <v>19</v>
-      </c>
-      <c r="E175" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" t="n">
-        <v>2</v>
-      </c>
-      <c r="G175" t="n">
-        <v>1</v>
-      </c>
-      <c r="H175" t="s">
-        <v>29</v>
-      </c>
-      <c r="I175" t="n">
-        <v>8</v>
-      </c>
-      <c r="J175" t="n">
-        <v>3</v>
-      </c>
-      <c r="K175" t="s">
-        <v>345</v>
-      </c>
-      <c r="L175" t="n">
-        <v>3</v>
-      </c>
-      <c r="M175" t="s">
-        <v>346</v>
-      </c>
-      <c r="N175"/>
-      <c r="O175" t="s">
-        <v>346</v>
-      </c>
-      <c r="P175"/>
-      <c r="Q175" t="s">
-        <v>346</v>
-      </c>
-      <c r="R175" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>352</v>
-      </c>
-      <c r="B176" t="b">
-        <v>1</v>
-      </c>
-      <c r="C176" t="s">
-        <v>18</v>
-      </c>
-      <c r="D176" t="s">
-        <v>19</v>
-      </c>
-      <c r="E176" t="n">
-        <v>2</v>
-      </c>
-      <c r="F176" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" t="n">
-        <v>1</v>
-      </c>
-      <c r="H176" t="s">
-        <v>38</v>
-      </c>
-      <c r="I176" t="n">
-        <v>8</v>
-      </c>
-      <c r="J176" t="n">
-        <v>3</v>
-      </c>
-      <c r="K176" t="s">
-        <v>366</v>
-      </c>
-      <c r="L176" t="n">
-        <v>1</v>
-      </c>
-      <c r="M176" t="s">
-        <v>346</v>
-      </c>
-      <c r="N176"/>
-      <c r="O176" t="s">
-        <v>346</v>
-      </c>
-      <c r="P176"/>
-      <c r="Q176" t="s">
-        <v>346</v>
-      </c>
-      <c r="R176" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>353</v>
-      </c>
-      <c r="B177" t="b">
-        <v>1</v>
-      </c>
-      <c r="C177" t="s">
-        <v>18</v>
-      </c>
-      <c r="D177" t="s">
-        <v>19</v>
-      </c>
-      <c r="E177" t="n">
-        <v>2</v>
-      </c>
-      <c r="F177" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H177" t="s">
-        <v>38</v>
-      </c>
-      <c r="I177" t="n">
-        <v>8</v>
-      </c>
-      <c r="J177" t="n">
-        <v>3</v>
-      </c>
-      <c r="K177" t="s">
-        <v>366</v>
-      </c>
-      <c r="L177" t="n">
-        <v>2</v>
-      </c>
-      <c r="M177" t="s">
-        <v>346</v>
-      </c>
-      <c r="N177"/>
-      <c r="O177" t="s">
-        <v>346</v>
-      </c>
-      <c r="P177"/>
-      <c r="Q177" t="s">
-        <v>346</v>
-      </c>
-      <c r="R177" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>354</v>
-      </c>
-      <c r="B178" t="b">
-        <v>1</v>
-      </c>
-      <c r="C178" t="s">
-        <v>18</v>
-      </c>
-      <c r="D178" t="s">
-        <v>19</v>
-      </c>
-      <c r="E178" t="n">
-        <v>2</v>
-      </c>
-      <c r="F178" t="n">
-        <v>1</v>
-      </c>
-      <c r="G178" t="n">
-        <v>1</v>
-      </c>
-      <c r="H178" t="s">
-        <v>38</v>
-      </c>
-      <c r="I178" t="n">
-        <v>8</v>
-      </c>
-      <c r="J178" t="n">
-        <v>3</v>
-      </c>
-      <c r="K178" t="s">
-        <v>366</v>
-      </c>
-      <c r="L178" t="n">
-        <v>3</v>
-      </c>
-      <c r="M178" t="s">
-        <v>346</v>
-      </c>
-      <c r="N178"/>
-      <c r="O178" t="s">
-        <v>346</v>
-      </c>
-      <c r="P178"/>
-      <c r="Q178" t="s">
-        <v>346</v>
-      </c>
-      <c r="R178" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>358</v>
-      </c>
-      <c r="B179" t="b">
-        <v>0</v>
-      </c>
-      <c r="C179" t="s">
-        <v>18</v>
-      </c>
-      <c r="D179" t="s">
-        <v>19</v>
-      </c>
-      <c r="E179" t="n">
-        <v>2</v>
-      </c>
-      <c r="F179" t="n">
-        <v>2</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="s">
-        <v>46</v>
-      </c>
-      <c r="I179" t="n">
-        <v>8</v>
-      </c>
-      <c r="J179" t="n">
-        <v>3</v>
-      </c>
-      <c r="K179" t="s">
-        <v>345</v>
-      </c>
-      <c r="L179" t="n">
-        <v>1</v>
-      </c>
-      <c r="M179" t="s">
-        <v>373</v>
-      </c>
-      <c r="N179" t="n">
-        <v>14</v>
-      </c>
-      <c r="O179" t="s">
-        <v>374</v>
-      </c>
-      <c r="P179" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q179" t="s">
-        <v>349</v>
-      </c>
-      <c r="R179" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>359</v>
-      </c>
-      <c r="B180" t="b">
-        <v>0</v>
-      </c>
-      <c r="C180" t="s">
-        <v>18</v>
-      </c>
-      <c r="D180" t="s">
-        <v>19</v>
-      </c>
-      <c r="E180" t="n">
-        <v>2</v>
-      </c>
-      <c r="F180" t="n">
-        <v>2</v>
-      </c>
-      <c r="G180" t="n">
-        <v>1</v>
-      </c>
-      <c r="H180" t="s">
-        <v>46</v>
-      </c>
-      <c r="I180" t="n">
-        <v>8</v>
-      </c>
-      <c r="J180" t="n">
-        <v>3</v>
-      </c>
-      <c r="K180" t="s">
-        <v>345</v>
-      </c>
-      <c r="L180" t="n">
-        <v>2</v>
-      </c>
-      <c r="M180" t="s">
-        <v>375</v>
-      </c>
-      <c r="N180" t="n">
-        <v>14</v>
-      </c>
-      <c r="O180" t="s">
-        <v>376</v>
-      </c>
-      <c r="P180" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q180" t="s">
-        <v>349</v>
-      </c>
-      <c r="R180" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>360</v>
-      </c>
-      <c r="B181" t="b">
-        <v>0</v>
-      </c>
-      <c r="C181" t="s">
-        <v>18</v>
-      </c>
-      <c r="D181" t="s">
-        <v>19</v>
-      </c>
-      <c r="E181" t="n">
-        <v>2</v>
-      </c>
-      <c r="F181" t="n">
-        <v>2</v>
-      </c>
-      <c r="G181" t="n">
-        <v>1</v>
-      </c>
-      <c r="H181" t="s">
-        <v>46</v>
-      </c>
-      <c r="I181" t="n">
-        <v>8</v>
-      </c>
-      <c r="J181" t="n">
-        <v>3</v>
-      </c>
-      <c r="K181" t="s">
-        <v>345</v>
-      </c>
-      <c r="L181" t="n">
-        <v>3</v>
-      </c>
-      <c r="M181" t="s">
-        <v>377</v>
-      </c>
-      <c r="N181" t="n">
-        <v>14</v>
-      </c>
-      <c r="O181" t="s">
-        <v>378</v>
-      </c>
-      <c r="P181" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q181" t="s">
-        <v>349</v>
-      </c>
-      <c r="R181" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>364</v>
-      </c>
-      <c r="B182" t="b">
-        <v>0</v>
-      </c>
-      <c r="C182" t="s">
-        <v>18</v>
-      </c>
-      <c r="D182" t="s">
-        <v>19</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" t="n">
-        <v>2</v>
-      </c>
-      <c r="H182" t="s">
-        <v>54</v>
-      </c>
-      <c r="I182" t="n">
-        <v>8</v>
-      </c>
-      <c r="J182" t="n">
-        <v>3</v>
-      </c>
-      <c r="K182" t="s">
-        <v>366</v>
-      </c>
-      <c r="L182" t="n">
-        <v>1</v>
-      </c>
-      <c r="M182" t="s">
-        <v>379</v>
-      </c>
-      <c r="N182" t="n">
-        <v>27</v>
-      </c>
-      <c r="O182" t="s">
-        <v>380</v>
-      </c>
-      <c r="P182" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q182" t="s">
-        <v>340</v>
-      </c>
-      <c r="R182" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>365</v>
-      </c>
-      <c r="B183" t="b">
-        <v>0</v>
-      </c>
-      <c r="C183" t="s">
-        <v>18</v>
-      </c>
-      <c r="D183" t="s">
-        <v>19</v>
-      </c>
-      <c r="E183" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" t="n">
-        <v>2</v>
-      </c>
-      <c r="H183" t="s">
-        <v>54</v>
-      </c>
-      <c r="I183" t="n">
-        <v>8</v>
-      </c>
-      <c r="J183" t="n">
-        <v>3</v>
-      </c>
-      <c r="K183" t="s">
-        <v>366</v>
-      </c>
-      <c r="L183" t="n">
-        <v>2</v>
-      </c>
-      <c r="M183" t="s">
-        <v>381</v>
-      </c>
-      <c r="N183" t="n">
-        <v>27</v>
-      </c>
-      <c r="O183" t="s">
-        <v>382</v>
-      </c>
-      <c r="P183" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q183" t="s">
-        <v>340</v>
-      </c>
-      <c r="R183" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>366</v>
-      </c>
-      <c r="B184" t="b">
-        <v>0</v>
-      </c>
-      <c r="C184" t="s">
-        <v>18</v>
-      </c>
-      <c r="D184" t="s">
-        <v>19</v>
-      </c>
-      <c r="E184" t="n">
-        <v>1</v>
-      </c>
-      <c r="F184" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" t="n">
-        <v>2</v>
-      </c>
-      <c r="H184" t="s">
-        <v>54</v>
-      </c>
-      <c r="I184" t="n">
-        <v>8</v>
-      </c>
-      <c r="J184" t="n">
-        <v>3</v>
-      </c>
-      <c r="K184" t="s">
-        <v>366</v>
-      </c>
-      <c r="L184" t="n">
-        <v>3</v>
-      </c>
-      <c r="M184" t="s">
-        <v>383</v>
-      </c>
-      <c r="N184" t="n">
-        <v>27</v>
-      </c>
-      <c r="O184" t="s">
-        <v>384</v>
-      </c>
-      <c r="P184" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q184" t="s">
-        <v>340</v>
-      </c>
-      <c r="R184" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>370</v>
-      </c>
-      <c r="B185" t="b">
-        <v>1</v>
-      </c>
-      <c r="C185" t="s">
-        <v>18</v>
-      </c>
-      <c r="D185" t="s">
-        <v>19</v>
-      </c>
-      <c r="E185" t="n">
-        <v>1</v>
-      </c>
-      <c r="F185" t="n">
-        <v>2</v>
-      </c>
-      <c r="G185" t="n">
-        <v>2</v>
-      </c>
-      <c r="H185" t="s">
-        <v>61</v>
-      </c>
-      <c r="I185" t="n">
-        <v>8</v>
-      </c>
-      <c r="J185" t="n">
-        <v>3</v>
-      </c>
-      <c r="K185" t="s">
-        <v>345</v>
-      </c>
-      <c r="L185" t="n">
-        <v>1</v>
-      </c>
-      <c r="M185" t="s">
-        <v>346</v>
-      </c>
-      <c r="N185"/>
-      <c r="O185" t="s">
-        <v>346</v>
-      </c>
-      <c r="P185"/>
-      <c r="Q185" t="s">
-        <v>346</v>
-      </c>
-      <c r="R185" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>371</v>
-      </c>
-      <c r="B186" t="b">
-        <v>1</v>
-      </c>
-      <c r="C186" t="s">
-        <v>18</v>
-      </c>
-      <c r="D186" t="s">
-        <v>19</v>
-      </c>
-      <c r="E186" t="n">
-        <v>1</v>
-      </c>
-      <c r="F186" t="n">
-        <v>2</v>
-      </c>
-      <c r="G186" t="n">
-        <v>2</v>
-      </c>
-      <c r="H186" t="s">
-        <v>61</v>
-      </c>
-      <c r="I186" t="n">
-        <v>8</v>
-      </c>
-      <c r="J186" t="n">
-        <v>3</v>
-      </c>
-      <c r="K186" t="s">
-        <v>345</v>
-      </c>
-      <c r="L186" t="n">
-        <v>2</v>
-      </c>
-      <c r="M186" t="s">
-        <v>346</v>
-      </c>
-      <c r="N186"/>
-      <c r="O186" t="s">
-        <v>346</v>
-      </c>
-      <c r="P186"/>
-      <c r="Q186" t="s">
-        <v>346</v>
-      </c>
-      <c r="R186" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>372</v>
-      </c>
-      <c r="B187" t="b">
-        <v>1</v>
-      </c>
-      <c r="C187" t="s">
-        <v>18</v>
-      </c>
-      <c r="D187" t="s">
-        <v>19</v>
-      </c>
-      <c r="E187" t="n">
-        <v>1</v>
-      </c>
-      <c r="F187" t="n">
-        <v>2</v>
-      </c>
-      <c r="G187" t="n">
-        <v>2</v>
-      </c>
-      <c r="H187" t="s">
-        <v>61</v>
-      </c>
-      <c r="I187" t="n">
-        <v>8</v>
-      </c>
-      <c r="J187" t="n">
-        <v>3</v>
-      </c>
-      <c r="K187" t="s">
-        <v>345</v>
-      </c>
-      <c r="L187" t="n">
-        <v>3</v>
-      </c>
-      <c r="M187" t="s">
-        <v>346</v>
-      </c>
-      <c r="N187"/>
-      <c r="O187" t="s">
-        <v>346</v>
-      </c>
-      <c r="P187"/>
-      <c r="Q187" t="s">
-        <v>346</v>
-      </c>
-      <c r="R187" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>376</v>
-      </c>
-      <c r="B188" t="b">
-        <v>1</v>
-      </c>
-      <c r="C188" t="s">
-        <v>18</v>
-      </c>
-      <c r="D188" t="s">
-        <v>19</v>
-      </c>
-      <c r="E188" t="n">
-        <v>2</v>
-      </c>
-      <c r="F188" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" t="n">
-        <v>2</v>
-      </c>
-      <c r="H188" t="s">
-        <v>68</v>
-      </c>
-      <c r="I188" t="n">
-        <v>8</v>
-      </c>
-      <c r="J188" t="n">
-        <v>3</v>
-      </c>
-      <c r="K188" t="s">
-        <v>366</v>
-      </c>
-      <c r="L188" t="n">
-        <v>1</v>
-      </c>
-      <c r="M188" t="s">
-        <v>346</v>
-      </c>
-      <c r="N188"/>
-      <c r="O188" t="s">
-        <v>346</v>
-      </c>
-      <c r="P188"/>
-      <c r="Q188" t="s">
-        <v>346</v>
-      </c>
-      <c r="R188" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>377</v>
-      </c>
-      <c r="B189" t="b">
-        <v>1</v>
-      </c>
-      <c r="C189" t="s">
-        <v>18</v>
-      </c>
-      <c r="D189" t="s">
-        <v>19</v>
-      </c>
-      <c r="E189" t="n">
-        <v>2</v>
-      </c>
-      <c r="F189" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" t="n">
-        <v>2</v>
-      </c>
-      <c r="H189" t="s">
-        <v>68</v>
-      </c>
-      <c r="I189" t="n">
-        <v>8</v>
-      </c>
-      <c r="J189" t="n">
-        <v>3</v>
-      </c>
-      <c r="K189" t="s">
-        <v>366</v>
-      </c>
-      <c r="L189" t="n">
-        <v>2</v>
-      </c>
-      <c r="M189" t="s">
-        <v>346</v>
-      </c>
-      <c r="N189"/>
-      <c r="O189" t="s">
-        <v>346</v>
-      </c>
-      <c r="P189"/>
-      <c r="Q189" t="s">
-        <v>346</v>
-      </c>
-      <c r="R189" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>378</v>
-      </c>
-      <c r="B190" t="b">
-        <v>1</v>
-      </c>
-      <c r="C190" t="s">
-        <v>18</v>
-      </c>
-      <c r="D190" t="s">
-        <v>19</v>
-      </c>
-      <c r="E190" t="n">
-        <v>2</v>
-      </c>
-      <c r="F190" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" t="n">
-        <v>2</v>
-      </c>
-      <c r="H190" t="s">
-        <v>68</v>
-      </c>
-      <c r="I190" t="n">
-        <v>8</v>
-      </c>
-      <c r="J190" t="n">
-        <v>3</v>
-      </c>
-      <c r="K190" t="s">
-        <v>366</v>
-      </c>
-      <c r="L190" t="n">
-        <v>3</v>
-      </c>
-      <c r="M190" t="s">
-        <v>346</v>
-      </c>
-      <c r="N190"/>
-      <c r="O190" t="s">
-        <v>346</v>
-      </c>
-      <c r="P190"/>
-      <c r="Q190" t="s">
-        <v>346</v>
-      </c>
-      <c r="R190" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>382</v>
-      </c>
-      <c r="B191" t="b">
-        <v>0</v>
-      </c>
-      <c r="C191" t="s">
-        <v>18</v>
-      </c>
-      <c r="D191" t="s">
-        <v>19</v>
-      </c>
-      <c r="E191" t="n">
-        <v>2</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2</v>
-      </c>
-      <c r="G191" t="n">
-        <v>2</v>
-      </c>
-      <c r="H191" t="s">
-        <v>75</v>
-      </c>
-      <c r="I191" t="n">
-        <v>8</v>
-      </c>
-      <c r="J191" t="n">
-        <v>3</v>
-      </c>
-      <c r="K191" t="s">
-        <v>345</v>
-      </c>
-      <c r="L191" t="n">
-        <v>1</v>
-      </c>
-      <c r="M191" t="s">
-        <v>385</v>
-      </c>
-      <c r="N191" t="n">
-        <v>14</v>
-      </c>
-      <c r="O191" t="s">
-        <v>386</v>
-      </c>
-      <c r="P191" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q191" t="s">
-        <v>349</v>
-      </c>
-      <c r="R191" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>383</v>
-      </c>
-      <c r="B192" t="b">
-        <v>0</v>
-      </c>
-      <c r="C192" t="s">
-        <v>18</v>
-      </c>
-      <c r="D192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E192" t="n">
-        <v>2</v>
-      </c>
-      <c r="F192" t="n">
-        <v>2</v>
-      </c>
-      <c r="G192" t="n">
-        <v>2</v>
-      </c>
-      <c r="H192" t="s">
-        <v>75</v>
-      </c>
-      <c r="I192" t="n">
-        <v>8</v>
-      </c>
-      <c r="J192" t="n">
-        <v>3</v>
-      </c>
-      <c r="K192" t="s">
-        <v>345</v>
-      </c>
-      <c r="L192" t="n">
-        <v>2</v>
-      </c>
-      <c r="M192" t="s">
-        <v>387</v>
-      </c>
-      <c r="N192" t="n">
-        <v>14</v>
-      </c>
-      <c r="O192" t="s">
-        <v>388</v>
-      </c>
-      <c r="P192" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q192" t="s">
-        <v>349</v>
-      </c>
-      <c r="R192" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>384</v>
-      </c>
-      <c r="B193" t="b">
-        <v>0</v>
-      </c>
-      <c r="C193" t="s">
-        <v>18</v>
-      </c>
-      <c r="D193" t="s">
-        <v>19</v>
-      </c>
-      <c r="E193" t="n">
-        <v>2</v>
-      </c>
-      <c r="F193" t="n">
-        <v>2</v>
-      </c>
-      <c r="G193" t="n">
-        <v>2</v>
-      </c>
-      <c r="H193" t="s">
-        <v>75</v>
-      </c>
-      <c r="I193" t="n">
-        <v>8</v>
-      </c>
-      <c r="J193" t="n">
-        <v>3</v>
-      </c>
-      <c r="K193" t="s">
-        <v>345</v>
-      </c>
-      <c r="L193" t="n">
-        <v>3</v>
-      </c>
-      <c r="M193" t="s">
-        <v>389</v>
-      </c>
-      <c r="N193" t="n">
-        <v>14</v>
-      </c>
-      <c r="O193" t="s">
-        <v>390</v>
-      </c>
-      <c r="P193" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q193" t="s">
-        <v>349</v>
-      </c>
-      <c r="R193" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>388</v>
-      </c>
-      <c r="B194" t="b">
-        <v>0</v>
-      </c>
-      <c r="C194" t="s">
-        <v>18</v>
-      </c>
-      <c r="D194" t="s">
-        <v>19</v>
-      </c>
-      <c r="E194" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" t="n">
-        <v>1</v>
-      </c>
-      <c r="H194" t="s">
-        <v>20</v>
-      </c>
-      <c r="I194" t="n">
-        <v>9</v>
-      </c>
-      <c r="J194" t="n">
-        <v>3</v>
-      </c>
-      <c r="K194" t="s">
-        <v>391</v>
-      </c>
-      <c r="L194" t="n">
-        <v>1</v>
-      </c>
-      <c r="M194" t="s">
-        <v>392</v>
-      </c>
-      <c r="N194" t="n">
-        <v>20</v>
-      </c>
-      <c r="O194" t="s">
-        <v>393</v>
-      </c>
-      <c r="P194" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q194" t="s">
-        <v>394</v>
-      </c>
-      <c r="R194" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>389</v>
-      </c>
-      <c r="B195" t="b">
-        <v>0</v>
-      </c>
-      <c r="C195" t="s">
-        <v>18</v>
-      </c>
-      <c r="D195" t="s">
-        <v>19</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" t="n">
-        <v>1</v>
-      </c>
-      <c r="G195" t="n">
-        <v>1</v>
-      </c>
-      <c r="H195" t="s">
-        <v>20</v>
-      </c>
-      <c r="I195" t="n">
-        <v>9</v>
-      </c>
-      <c r="J195" t="n">
-        <v>3</v>
-      </c>
-      <c r="K195" t="s">
-        <v>391</v>
-      </c>
-      <c r="L195" t="n">
-        <v>2</v>
-      </c>
-      <c r="M195" t="s">
-        <v>395</v>
-      </c>
-      <c r="N195" t="n">
-        <v>20</v>
-      </c>
-      <c r="O195" t="s">
-        <v>396</v>
-      </c>
-      <c r="P195" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q195" t="s">
-        <v>394</v>
-      </c>
-      <c r="R195" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>390</v>
-      </c>
-      <c r="B196" t="b">
-        <v>0</v>
-      </c>
-      <c r="C196" t="s">
-        <v>18</v>
-      </c>
-      <c r="D196" t="s">
-        <v>19</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
-      <c r="H196" t="s">
-        <v>20</v>
-      </c>
-      <c r="I196" t="n">
-        <v>9</v>
-      </c>
-      <c r="J196" t="n">
-        <v>3</v>
-      </c>
-      <c r="K196" t="s">
-        <v>391</v>
-      </c>
-      <c r="L196" t="n">
-        <v>3</v>
-      </c>
-      <c r="M196" t="s">
-        <v>397</v>
-      </c>
-      <c r="N196" t="n">
-        <v>20</v>
-      </c>
-      <c r="O196" t="s">
-        <v>398</v>
-      </c>
-      <c r="P196" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q196" t="s">
-        <v>394</v>
-      </c>
-      <c r="R196" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>394</v>
-      </c>
-      <c r="B197" t="b">
-        <v>1</v>
-      </c>
-      <c r="C197" t="s">
-        <v>18</v>
-      </c>
-      <c r="D197" t="s">
-        <v>19</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" t="s">
-        <v>29</v>
-      </c>
-      <c r="I197" t="n">
-        <v>9</v>
-      </c>
-      <c r="J197" t="n">
-        <v>3</v>
-      </c>
-      <c r="K197" t="s">
-        <v>345</v>
-      </c>
-      <c r="L197" t="n">
-        <v>1</v>
-      </c>
-      <c r="M197" t="s">
-        <v>346</v>
-      </c>
-      <c r="N197"/>
-      <c r="O197" t="s">
-        <v>346</v>
-      </c>
-      <c r="P197"/>
-      <c r="Q197" t="s">
-        <v>346</v>
-      </c>
-      <c r="R197" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>395</v>
-      </c>
-      <c r="B198" t="b">
-        <v>1</v>
-      </c>
-      <c r="C198" t="s">
-        <v>18</v>
-      </c>
-      <c r="D198" t="s">
-        <v>19</v>
-      </c>
-      <c r="E198" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" t="n">
-        <v>2</v>
-      </c>
-      <c r="G198" t="n">
-        <v>1</v>
-      </c>
-      <c r="H198" t="s">
-        <v>29</v>
-      </c>
-      <c r="I198" t="n">
-        <v>9</v>
-      </c>
-      <c r="J198" t="n">
-        <v>3</v>
-      </c>
-      <c r="K198" t="s">
-        <v>345</v>
-      </c>
-      <c r="L198" t="n">
-        <v>2</v>
-      </c>
-      <c r="M198" t="s">
-        <v>346</v>
-      </c>
-      <c r="N198"/>
-      <c r="O198" t="s">
-        <v>346</v>
-      </c>
-      <c r="P198"/>
-      <c r="Q198" t="s">
-        <v>346</v>
-      </c>
-      <c r="R198" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>396</v>
-      </c>
-      <c r="B199" t="b">
-        <v>1</v>
-      </c>
-      <c r="C199" t="s">
-        <v>18</v>
-      </c>
-      <c r="D199" t="s">
-        <v>19</v>
-      </c>
-      <c r="E199" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" t="n">
-        <v>2</v>
-      </c>
-      <c r="G199" t="n">
-        <v>1</v>
-      </c>
-      <c r="H199" t="s">
-        <v>29</v>
-      </c>
-      <c r="I199" t="n">
-        <v>9</v>
-      </c>
-      <c r="J199" t="n">
-        <v>3</v>
-      </c>
-      <c r="K199" t="s">
-        <v>345</v>
-      </c>
-      <c r="L199" t="n">
-        <v>3</v>
-      </c>
-      <c r="M199" t="s">
-        <v>346</v>
-      </c>
-      <c r="N199"/>
-      <c r="O199" t="s">
-        <v>346</v>
-      </c>
-      <c r="P199"/>
-      <c r="Q199" t="s">
-        <v>346</v>
-      </c>
-      <c r="R199" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>400</v>
-      </c>
-      <c r="B200" t="b">
-        <v>1</v>
-      </c>
-      <c r="C200" t="s">
-        <v>18</v>
-      </c>
-      <c r="D200" t="s">
-        <v>19</v>
-      </c>
-      <c r="E200" t="n">
-        <v>2</v>
-      </c>
-      <c r="F200" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" t="n">
-        <v>1</v>
-      </c>
-      <c r="H200" t="s">
-        <v>38</v>
-      </c>
-      <c r="I200" t="n">
-        <v>9</v>
-      </c>
-      <c r="J200" t="n">
-        <v>3</v>
-      </c>
-      <c r="K200" t="s">
-        <v>391</v>
-      </c>
-      <c r="L200" t="n">
-        <v>1</v>
-      </c>
-      <c r="M200" t="s">
-        <v>346</v>
-      </c>
-      <c r="N200"/>
-      <c r="O200" t="s">
-        <v>346</v>
-      </c>
-      <c r="P200"/>
-      <c r="Q200" t="s">
-        <v>346</v>
-      </c>
-      <c r="R200" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>401</v>
-      </c>
-      <c r="B201" t="b">
-        <v>1</v>
-      </c>
-      <c r="C201" t="s">
-        <v>18</v>
-      </c>
-      <c r="D201" t="s">
-        <v>19</v>
-      </c>
-      <c r="E201" t="n">
-        <v>2</v>
-      </c>
-      <c r="F201" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" t="s">
-        <v>38</v>
-      </c>
-      <c r="I201" t="n">
-        <v>9</v>
-      </c>
-      <c r="J201" t="n">
-        <v>3</v>
-      </c>
-      <c r="K201" t="s">
-        <v>391</v>
-      </c>
-      <c r="L201" t="n">
-        <v>2</v>
-      </c>
-      <c r="M201" t="s">
-        <v>346</v>
-      </c>
-      <c r="N201"/>
-      <c r="O201" t="s">
-        <v>346</v>
-      </c>
-      <c r="P201"/>
-      <c r="Q201" t="s">
-        <v>346</v>
-      </c>
-      <c r="R201" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>402</v>
-      </c>
-      <c r="B202" t="b">
-        <v>1</v>
-      </c>
-      <c r="C202" t="s">
-        <v>18</v>
-      </c>
-      <c r="D202" t="s">
-        <v>19</v>
-      </c>
-      <c r="E202" t="n">
-        <v>2</v>
-      </c>
-      <c r="F202" t="n">
-        <v>1</v>
-      </c>
-      <c r="G202" t="n">
-        <v>1</v>
-      </c>
-      <c r="H202" t="s">
-        <v>38</v>
-      </c>
-      <c r="I202" t="n">
-        <v>9</v>
-      </c>
-      <c r="J202" t="n">
-        <v>3</v>
-      </c>
-      <c r="K202" t="s">
-        <v>391</v>
-      </c>
-      <c r="L202" t="n">
-        <v>3</v>
-      </c>
-      <c r="M202" t="s">
-        <v>346</v>
-      </c>
-      <c r="N202"/>
-      <c r="O202" t="s">
-        <v>346</v>
-      </c>
-      <c r="P202"/>
-      <c r="Q202" t="s">
-        <v>346</v>
-      </c>
-      <c r="R202" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>406</v>
-      </c>
-      <c r="B203" t="b">
-        <v>0</v>
-      </c>
-      <c r="C203" t="s">
-        <v>18</v>
-      </c>
-      <c r="D203" t="s">
-        <v>19</v>
-      </c>
-      <c r="E203" t="n">
-        <v>2</v>
-      </c>
-      <c r="F203" t="n">
-        <v>2</v>
-      </c>
-      <c r="G203" t="n">
-        <v>1</v>
-      </c>
-      <c r="H203" t="s">
-        <v>46</v>
-      </c>
-      <c r="I203" t="n">
-        <v>9</v>
-      </c>
-      <c r="J203" t="n">
-        <v>3</v>
-      </c>
-      <c r="K203" t="s">
-        <v>345</v>
-      </c>
-      <c r="L203" t="n">
-        <v>1</v>
-      </c>
-      <c r="M203" t="s">
-        <v>399</v>
-      </c>
-      <c r="N203" t="n">
-        <v>14</v>
-      </c>
-      <c r="O203" t="s">
-        <v>400</v>
-      </c>
-      <c r="P203" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q203" t="s">
-        <v>349</v>
-      </c>
-      <c r="R203" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>407</v>
-      </c>
-      <c r="B204" t="b">
-        <v>0</v>
-      </c>
-      <c r="C204" t="s">
-        <v>18</v>
-      </c>
-      <c r="D204" t="s">
-        <v>19</v>
-      </c>
-      <c r="E204" t="n">
-        <v>2</v>
-      </c>
-      <c r="F204" t="n">
-        <v>2</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" t="s">
-        <v>46</v>
-      </c>
-      <c r="I204" t="n">
-        <v>9</v>
-      </c>
-      <c r="J204" t="n">
-        <v>3</v>
-      </c>
-      <c r="K204" t="s">
-        <v>345</v>
-      </c>
-      <c r="L204" t="n">
-        <v>2</v>
-      </c>
-      <c r="M204" t="s">
-        <v>401</v>
-      </c>
-      <c r="N204" t="n">
-        <v>14</v>
-      </c>
-      <c r="O204" t="s">
-        <v>402</v>
-      </c>
-      <c r="P204" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q204" t="s">
-        <v>349</v>
-      </c>
-      <c r="R204" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>408</v>
-      </c>
-      <c r="B205" t="b">
-        <v>0</v>
-      </c>
-      <c r="C205" t="s">
-        <v>18</v>
-      </c>
-      <c r="D205" t="s">
-        <v>19</v>
-      </c>
-      <c r="E205" t="n">
-        <v>2</v>
-      </c>
-      <c r="F205" t="n">
-        <v>2</v>
-      </c>
-      <c r="G205" t="n">
-        <v>1</v>
-      </c>
-      <c r="H205" t="s">
-        <v>46</v>
-      </c>
-      <c r="I205" t="n">
-        <v>9</v>
-      </c>
-      <c r="J205" t="n">
-        <v>3</v>
-      </c>
-      <c r="K205" t="s">
-        <v>345</v>
-      </c>
-      <c r="L205" t="n">
-        <v>3</v>
-      </c>
-      <c r="M205" t="s">
-        <v>403</v>
-      </c>
-      <c r="N205" t="n">
-        <v>14</v>
-      </c>
-      <c r="O205" t="s">
-        <v>404</v>
-      </c>
-      <c r="P205" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q205" t="s">
-        <v>349</v>
-      </c>
-      <c r="R205" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>412</v>
-      </c>
-      <c r="B206" t="b">
-        <v>0</v>
-      </c>
-      <c r="C206" t="s">
-        <v>18</v>
-      </c>
-      <c r="D206" t="s">
-        <v>19</v>
-      </c>
-      <c r="E206" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" t="n">
-        <v>2</v>
-      </c>
-      <c r="H206" t="s">
-        <v>54</v>
-      </c>
-      <c r="I206" t="n">
-        <v>9</v>
-      </c>
-      <c r="J206" t="n">
-        <v>3</v>
-      </c>
-      <c r="K206" t="s">
-        <v>391</v>
-      </c>
-      <c r="L206" t="n">
-        <v>1</v>
-      </c>
-      <c r="M206" t="s">
-        <v>405</v>
-      </c>
-      <c r="N206" t="n">
-        <v>20</v>
-      </c>
-      <c r="O206" t="s">
-        <v>406</v>
-      </c>
-      <c r="P206" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q206" t="s">
-        <v>394</v>
-      </c>
-      <c r="R206" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>413</v>
-      </c>
-      <c r="B207" t="b">
-        <v>0</v>
-      </c>
-      <c r="C207" t="s">
-        <v>18</v>
-      </c>
-      <c r="D207" t="s">
-        <v>19</v>
-      </c>
-      <c r="E207" t="n">
-        <v>1</v>
-      </c>
-      <c r="F207" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" t="n">
-        <v>2</v>
-      </c>
-      <c r="H207" t="s">
-        <v>54</v>
-      </c>
-      <c r="I207" t="n">
-        <v>9</v>
-      </c>
-      <c r="J207" t="n">
-        <v>3</v>
-      </c>
-      <c r="K207" t="s">
-        <v>391</v>
-      </c>
-      <c r="L207" t="n">
-        <v>2</v>
-      </c>
-      <c r="M207" t="s">
-        <v>407</v>
-      </c>
-      <c r="N207" t="n">
-        <v>20</v>
-      </c>
-      <c r="O207" t="s">
-        <v>408</v>
-      </c>
-      <c r="P207" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q207" t="s">
-        <v>394</v>
-      </c>
-      <c r="R207" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>414</v>
-      </c>
-      <c r="B208" t="b">
-        <v>0</v>
-      </c>
-      <c r="C208" t="s">
-        <v>18</v>
-      </c>
-      <c r="D208" t="s">
-        <v>19</v>
-      </c>
-      <c r="E208" t="n">
-        <v>1</v>
-      </c>
-      <c r="F208" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" t="n">
-        <v>2</v>
-      </c>
-      <c r="H208" t="s">
-        <v>54</v>
-      </c>
-      <c r="I208" t="n">
-        <v>9</v>
-      </c>
-      <c r="J208" t="n">
-        <v>3</v>
-      </c>
-      <c r="K208" t="s">
-        <v>391</v>
-      </c>
-      <c r="L208" t="n">
-        <v>3</v>
-      </c>
-      <c r="M208" t="s">
-        <v>409</v>
-      </c>
-      <c r="N208" t="n">
-        <v>20</v>
-      </c>
-      <c r="O208" t="s">
-        <v>410</v>
-      </c>
-      <c r="P208" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q208" t="s">
-        <v>394</v>
-      </c>
-      <c r="R208" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>418</v>
-      </c>
-      <c r="B209" t="b">
-        <v>1</v>
-      </c>
-      <c r="C209" t="s">
-        <v>18</v>
-      </c>
-      <c r="D209" t="s">
-        <v>19</v>
-      </c>
-      <c r="E209" t="n">
-        <v>1</v>
-      </c>
-      <c r="F209" t="n">
-        <v>2</v>
-      </c>
-      <c r="G209" t="n">
-        <v>2</v>
-      </c>
-      <c r="H209" t="s">
-        <v>61</v>
-      </c>
-      <c r="I209" t="n">
-        <v>9</v>
-      </c>
-      <c r="J209" t="n">
-        <v>3</v>
-      </c>
-      <c r="K209" t="s">
-        <v>345</v>
-      </c>
-      <c r="L209" t="n">
-        <v>1</v>
-      </c>
-      <c r="M209" t="s">
-        <v>346</v>
-      </c>
-      <c r="N209"/>
-      <c r="O209" t="s">
-        <v>346</v>
-      </c>
-      <c r="P209"/>
-      <c r="Q209" t="s">
-        <v>346</v>
-      </c>
-      <c r="R209" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>419</v>
-      </c>
-      <c r="B210" t="b">
-        <v>1</v>
-      </c>
-      <c r="C210" t="s">
-        <v>18</v>
-      </c>
-      <c r="D210" t="s">
-        <v>19</v>
-      </c>
-      <c r="E210" t="n">
-        <v>1</v>
-      </c>
-      <c r="F210" t="n">
-        <v>2</v>
-      </c>
-      <c r="G210" t="n">
-        <v>2</v>
-      </c>
-      <c r="H210" t="s">
-        <v>61</v>
-      </c>
-      <c r="I210" t="n">
-        <v>9</v>
-      </c>
-      <c r="J210" t="n">
-        <v>3</v>
-      </c>
-      <c r="K210" t="s">
-        <v>345</v>
-      </c>
-      <c r="L210" t="n">
-        <v>2</v>
-      </c>
-      <c r="M210" t="s">
-        <v>346</v>
-      </c>
-      <c r="N210"/>
-      <c r="O210" t="s">
-        <v>346</v>
-      </c>
-      <c r="P210"/>
-      <c r="Q210" t="s">
-        <v>346</v>
-      </c>
-      <c r="R210" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>420</v>
-      </c>
-      <c r="B211" t="b">
-        <v>1</v>
-      </c>
-      <c r="C211" t="s">
-        <v>18</v>
-      </c>
-      <c r="D211" t="s">
-        <v>19</v>
-      </c>
-      <c r="E211" t="n">
-        <v>1</v>
-      </c>
-      <c r="F211" t="n">
-        <v>2</v>
-      </c>
-      <c r="G211" t="n">
-        <v>2</v>
-      </c>
-      <c r="H211" t="s">
-        <v>61</v>
-      </c>
-      <c r="I211" t="n">
-        <v>9</v>
-      </c>
-      <c r="J211" t="n">
-        <v>3</v>
-      </c>
-      <c r="K211" t="s">
-        <v>345</v>
-      </c>
-      <c r="L211" t="n">
-        <v>3</v>
-      </c>
-      <c r="M211" t="s">
-        <v>346</v>
-      </c>
-      <c r="N211"/>
-      <c r="O211" t="s">
-        <v>346</v>
-      </c>
-      <c r="P211"/>
-      <c r="Q211" t="s">
-        <v>346</v>
-      </c>
-      <c r="R211" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>424</v>
-      </c>
-      <c r="B212" t="b">
-        <v>1</v>
-      </c>
-      <c r="C212" t="s">
-        <v>18</v>
-      </c>
-      <c r="D212" t="s">
-        <v>19</v>
-      </c>
-      <c r="E212" t="n">
-        <v>2</v>
-      </c>
-      <c r="F212" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" t="n">
-        <v>2</v>
-      </c>
-      <c r="H212" t="s">
-        <v>68</v>
-      </c>
-      <c r="I212" t="n">
-        <v>9</v>
-      </c>
-      <c r="J212" t="n">
-        <v>3</v>
-      </c>
-      <c r="K212" t="s">
-        <v>391</v>
-      </c>
-      <c r="L212" t="n">
-        <v>1</v>
-      </c>
-      <c r="M212" t="s">
-        <v>346</v>
-      </c>
-      <c r="N212"/>
-      <c r="O212" t="s">
-        <v>346</v>
-      </c>
-      <c r="P212"/>
-      <c r="Q212" t="s">
-        <v>346</v>
-      </c>
-      <c r="R212" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>425</v>
-      </c>
-      <c r="B213" t="b">
-        <v>1</v>
-      </c>
-      <c r="C213" t="s">
-        <v>18</v>
-      </c>
-      <c r="D213" t="s">
-        <v>19</v>
-      </c>
-      <c r="E213" t="n">
-        <v>2</v>
-      </c>
-      <c r="F213" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" t="n">
-        <v>2</v>
-      </c>
-      <c r="H213" t="s">
-        <v>68</v>
-      </c>
-      <c r="I213" t="n">
-        <v>9</v>
-      </c>
-      <c r="J213" t="n">
-        <v>3</v>
-      </c>
-      <c r="K213" t="s">
-        <v>391</v>
-      </c>
-      <c r="L213" t="n">
-        <v>2</v>
-      </c>
-      <c r="M213" t="s">
-        <v>346</v>
-      </c>
-      <c r="N213"/>
-      <c r="O213" t="s">
-        <v>346</v>
-      </c>
-      <c r="P213"/>
-      <c r="Q213" t="s">
-        <v>346</v>
-      </c>
-      <c r="R213" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>426</v>
-      </c>
-      <c r="B214" t="b">
-        <v>1</v>
-      </c>
-      <c r="C214" t="s">
-        <v>18</v>
-      </c>
-      <c r="D214" t="s">
-        <v>19</v>
-      </c>
-      <c r="E214" t="n">
-        <v>2</v>
-      </c>
-      <c r="F214" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" t="n">
-        <v>2</v>
-      </c>
-      <c r="H214" t="s">
-        <v>68</v>
-      </c>
-      <c r="I214" t="n">
-        <v>9</v>
-      </c>
-      <c r="J214" t="n">
-        <v>3</v>
-      </c>
-      <c r="K214" t="s">
-        <v>391</v>
-      </c>
-      <c r="L214" t="n">
-        <v>3</v>
-      </c>
-      <c r="M214" t="s">
-        <v>346</v>
-      </c>
-      <c r="N214"/>
-      <c r="O214" t="s">
-        <v>346</v>
-      </c>
-      <c r="P214"/>
-      <c r="Q214" t="s">
-        <v>346</v>
-      </c>
-      <c r="R214" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>430</v>
-      </c>
-      <c r="B215" t="b">
-        <v>0</v>
-      </c>
-      <c r="C215" t="s">
-        <v>18</v>
-      </c>
-      <c r="D215" t="s">
-        <v>19</v>
-      </c>
-      <c r="E215" t="n">
-        <v>2</v>
-      </c>
-      <c r="F215" t="n">
-        <v>2</v>
-      </c>
-      <c r="G215" t="n">
-        <v>2</v>
-      </c>
-      <c r="H215" t="s">
-        <v>75</v>
-      </c>
-      <c r="I215" t="n">
-        <v>9</v>
-      </c>
-      <c r="J215" t="n">
-        <v>3</v>
-      </c>
-      <c r="K215" t="s">
-        <v>345</v>
-      </c>
-      <c r="L215" t="n">
-        <v>1</v>
-      </c>
-      <c r="M215" t="s">
-        <v>411</v>
-      </c>
-      <c r="N215" t="n">
-        <v>14</v>
-      </c>
-      <c r="O215" t="s">
-        <v>412</v>
-      </c>
-      <c r="P215" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q215" t="s">
-        <v>349</v>
-      </c>
-      <c r="R215" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>431</v>
-      </c>
-      <c r="B216" t="b">
-        <v>0</v>
-      </c>
-      <c r="C216" t="s">
-        <v>18</v>
-      </c>
-      <c r="D216" t="s">
-        <v>19</v>
-      </c>
-      <c r="E216" t="n">
-        <v>2</v>
-      </c>
-      <c r="F216" t="n">
-        <v>2</v>
-      </c>
-      <c r="G216" t="n">
-        <v>2</v>
-      </c>
-      <c r="H216" t="s">
-        <v>75</v>
-      </c>
-      <c r="I216" t="n">
-        <v>9</v>
-      </c>
-      <c r="J216" t="n">
-        <v>3</v>
-      </c>
-      <c r="K216" t="s">
-        <v>345</v>
-      </c>
-      <c r="L216" t="n">
-        <v>2</v>
-      </c>
-      <c r="M216" t="s">
-        <v>413</v>
-      </c>
-      <c r="N216" t="n">
-        <v>14</v>
-      </c>
-      <c r="O216" t="s">
-        <v>414</v>
-      </c>
-      <c r="P216" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q216" t="s">
-        <v>349</v>
-      </c>
-      <c r="R216" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>432</v>
-      </c>
-      <c r="B217" t="b">
-        <v>0</v>
-      </c>
-      <c r="C217" t="s">
-        <v>18</v>
-      </c>
-      <c r="D217" t="s">
-        <v>19</v>
-      </c>
-      <c r="E217" t="n">
-        <v>2</v>
-      </c>
-      <c r="F217" t="n">
-        <v>2</v>
-      </c>
-      <c r="G217" t="n">
-        <v>2</v>
-      </c>
-      <c r="H217" t="s">
-        <v>75</v>
-      </c>
-      <c r="I217" t="n">
-        <v>9</v>
-      </c>
-      <c r="J217" t="n">
-        <v>3</v>
-      </c>
-      <c r="K217" t="s">
-        <v>345</v>
-      </c>
-      <c r="L217" t="n">
-        <v>3</v>
-      </c>
-      <c r="M217" t="s">
-        <v>415</v>
-      </c>
-      <c r="N217" t="n">
-        <v>14</v>
-      </c>
-      <c r="O217" t="s">
-        <v>416</v>
-      </c>
-      <c r="P217" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q217" t="s">
-        <v>349</v>
-      </c>
-      <c r="R217" t="s">
-        <v>349</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
